--- a/data.xlsx
+++ b/data.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\simon\Desktop\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3BEBBC68-0669-43B8-AA05-8F01C0846E34}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{49644848-4F3C-4595-8067-1DD5996A6103}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-28898" yWindow="-4268" windowWidth="28996" windowHeight="15676" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -16,14 +16,14 @@
     <sheet name="Sheet0" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet0!$A$2:$FZ$7</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet0!$A$2:$FZ$8</definedName>
   </definedNames>
   <calcPr calcId="0"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1060" uniqueCount="453">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1234" uniqueCount="483">
   <si>
     <t>StartDate</t>
   </si>
@@ -938,6 +938,9 @@
     <t>No</t>
   </si>
   <si>
+    <t>Very familiar</t>
+  </si>
+  <si>
     <t>🗣️Version 2,🗣️🗣️ Version 3</t>
   </si>
   <si>
@@ -1032,6 +1035,9 @@
   </si>
   <si>
     <t>After I finish telling my current story / thought</t>
+  </si>
+  <si>
+    <t>Very difficult to detect</t>
   </si>
   <si>
     <t>Immediately</t>
@@ -1465,6 +1471,90 @@
   </si>
   <si>
     <t>1414</t>
+  </si>
+  <si>
+    <t>84.174.28.10</t>
+  </si>
+  <si>
+    <t>R_8Y4N7oD7EAbwXgl</t>
+  </si>
+  <si>
+    <t>Non-binary / third gender</t>
+  </si>
+  <si>
+    <t>North Korea</t>
+  </si>
+  <si>
+    <t>north korean</t>
+  </si>
+  <si>
+    <t>I regularly play an instrument (or sing) as a hobby / perform publicly.</t>
+  </si>
+  <si>
+    <t>No notification at all (Muted / Do Not Disturb)</t>
+  </si>
+  <si>
+    <t>Social Etiquette: To avoid disturbing or annoying people around me.,Personal Focus: To avoid distracting myself or breaking my concentration.</t>
+  </si>
+  <si>
+    <t>None of the above</t>
+  </si>
+  <si>
+    <t>It's disturbing</t>
+  </si>
+  <si>
+    <t>every situation in public places</t>
+  </si>
+  <si>
+    <t>Depends on context</t>
+  </si>
+  <si>
+    <t>first finishing work</t>
+  </si>
+  <si>
+    <t>Arbeitszeitbetrug</t>
+  </si>
+  <si>
+    <t>it would be very unpolite</t>
+  </si>
+  <si>
+    <t>less annoying</t>
+  </si>
+  <si>
+    <t>es nervt ungemein</t>
+  </si>
+  <si>
+    <t>Other (please specify):</t>
+  </si>
+  <si>
+    <t>Later, when I am done with music and relaxing</t>
+  </si>
+  <si>
+    <t>weil ich gerade Musik höre</t>
+  </si>
+  <si>
+    <t>Unhöflich der Gesprächspartnerin gegenüber</t>
+  </si>
+  <si>
+    <t>weil es unhöflich wäre, ein Gespräch dafür zu unterbrechen</t>
+  </si>
+  <si>
+    <t>Concentration on the traffic is much more important</t>
+  </si>
+  <si>
+    <t>keine Lust auf Verkehrsunfall</t>
+  </si>
+  <si>
+    <t>ich bin halt am Einkaufen</t>
+  </si>
+  <si>
+    <t>After I am done shopping</t>
+  </si>
+  <si>
+    <t>erstmal das Essen klären</t>
+  </si>
+  <si>
+    <t>1963</t>
   </si>
 </sst>
 </file>
@@ -1846,13 +1936,13 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:FZ6"/>
+  <dimension ref="A1:FZ9"/>
   <sheetFormatPr defaultRowHeight="14.6" x14ac:dyDescent="0.4"/>
   <cols>
-    <col min="1" max="1" width="19.3046875" customWidth="1"/>
+    <col min="1" max="1" width="19.4609375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:182" x14ac:dyDescent="0.4">
+    <row r="1" spans="1:182" ht="15" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A1" s="3" t="s">
         <v>0</v>
       </c>
@@ -2400,7 +2490,7 @@
         <v>181</v>
       </c>
     </row>
-    <row r="2" spans="1:182" x14ac:dyDescent="0.4">
+    <row r="2" spans="1:182" ht="15" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A2" s="3" t="s">
         <v>182</v>
       </c>
@@ -2948,7 +3038,7 @@
         <v>181</v>
       </c>
     </row>
-    <row r="3" spans="1:182" ht="41.6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="3" spans="1:182" ht="15" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A3" s="1">
         <v>46194.469131944446</v>
       </c>
@@ -2959,7 +3049,7 @@
         <v>185</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>341</v>
+        <v>343</v>
       </c>
       <c r="E3">
         <v>100</v>
@@ -2974,7 +3064,7 @@
         <v>46194.491778877316</v>
       </c>
       <c r="I3" s="2" t="s">
-        <v>342</v>
+        <v>344</v>
       </c>
       <c r="J3" s="2" t="s">
         <v>266</v>
@@ -3001,7 +3091,7 @@
         <v>268</v>
       </c>
       <c r="R3" s="2" t="s">
-        <v>328</v>
+        <v>330</v>
       </c>
       <c r="S3" s="2" t="s">
         <v>269</v>
@@ -3025,7 +3115,7 @@
         <v>274</v>
       </c>
       <c r="Z3" s="2" t="s">
-        <v>343</v>
+        <v>345</v>
       </c>
       <c r="AA3" s="2" t="s">
         <v>276</v>
@@ -3034,458 +3124,458 @@
         <v>266</v>
       </c>
       <c r="AC3" s="2" t="s">
-        <v>344</v>
+        <v>346</v>
       </c>
       <c r="AD3" s="2" t="s">
-        <v>345</v>
+        <v>347</v>
       </c>
       <c r="AE3" s="2" t="s">
-        <v>346</v>
+        <v>348</v>
       </c>
       <c r="AF3" s="2" t="s">
         <v>266</v>
       </c>
       <c r="AG3" s="2" t="s">
-        <v>329</v>
+        <v>331</v>
       </c>
       <c r="AH3" s="2" t="s">
-        <v>321</v>
+        <v>323</v>
       </c>
       <c r="AI3" s="2" t="s">
-        <v>322</v>
+        <v>324</v>
       </c>
       <c r="AJ3" s="2" t="s">
         <v>266</v>
       </c>
       <c r="AK3" s="2" t="s">
-        <v>323</v>
+        <v>325</v>
       </c>
       <c r="AL3" s="2" t="s">
-        <v>323</v>
+        <v>325</v>
       </c>
       <c r="AM3" s="2" t="s">
-        <v>347</v>
+        <v>349</v>
       </c>
       <c r="AN3" s="2" t="s">
-        <v>318</v>
+        <v>320</v>
       </c>
       <c r="AO3" s="2" t="s">
-        <v>318</v>
+        <v>320</v>
       </c>
       <c r="AP3" s="2" t="s">
-        <v>318</v>
+        <v>320</v>
       </c>
       <c r="AQ3" s="2" t="s">
-        <v>347</v>
+        <v>349</v>
       </c>
       <c r="AR3" s="2" t="s">
-        <v>348</v>
+        <v>350</v>
       </c>
       <c r="AS3" s="2" t="s">
-        <v>349</v>
+        <v>351</v>
       </c>
       <c r="AT3" s="2" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="AU3" s="2" t="s">
+        <v>280</v>
+      </c>
+      <c r="AV3" s="2" t="s">
+        <v>352</v>
+      </c>
+      <c r="AW3" s="2" t="s">
+        <v>266</v>
+      </c>
+      <c r="AX3" s="2" t="s">
+        <v>353</v>
+      </c>
+      <c r="AY3" s="2" t="s">
+        <v>266</v>
+      </c>
+      <c r="AZ3" s="2" t="s">
+        <v>282</v>
+      </c>
+      <c r="BA3" s="2" t="s">
+        <v>299</v>
+      </c>
+      <c r="BB3" s="2" t="s">
+        <v>299</v>
+      </c>
+      <c r="BC3" s="2" t="s">
+        <v>299</v>
+      </c>
+      <c r="BD3" s="2" t="s">
+        <v>284</v>
+      </c>
+      <c r="BE3" s="2" t="s">
+        <v>284</v>
+      </c>
+      <c r="BF3" s="2" t="s">
+        <v>284</v>
+      </c>
+      <c r="BG3" s="2" t="s">
+        <v>285</v>
+      </c>
+      <c r="BH3" s="2" t="s">
+        <v>327</v>
+      </c>
+      <c r="BI3" s="2" t="s">
+        <v>327</v>
+      </c>
+      <c r="BJ3" s="2" t="s">
+        <v>332</v>
+      </c>
+      <c r="BK3" s="2" t="s">
+        <v>335</v>
+      </c>
+      <c r="BL3" s="2" t="s">
+        <v>335</v>
+      </c>
+      <c r="BM3" s="2" t="s">
+        <v>298</v>
+      </c>
+      <c r="BN3" s="2" t="s">
+        <v>354</v>
+      </c>
+      <c r="BO3" s="2" t="s">
+        <v>355</v>
+      </c>
+      <c r="BP3" s="2" t="s">
+        <v>266</v>
+      </c>
+      <c r="BQ3" s="2" t="s">
+        <v>311</v>
+      </c>
+      <c r="BR3" s="2" t="s">
+        <v>298</v>
+      </c>
+      <c r="BS3" s="2" t="s">
+        <v>356</v>
+      </c>
+      <c r="BT3" s="2" t="s">
+        <v>290</v>
+      </c>
+      <c r="BU3" s="2" t="s">
+        <v>291</v>
+      </c>
+      <c r="BV3" s="2" t="s">
+        <v>291</v>
+      </c>
+      <c r="BW3" s="2" t="s">
+        <v>284</v>
+      </c>
+      <c r="BX3" s="2" t="s">
+        <v>284</v>
+      </c>
+      <c r="BY3" s="2" t="s">
+        <v>284</v>
+      </c>
+      <c r="BZ3" s="2" t="s">
+        <v>327</v>
+      </c>
+      <c r="CA3" s="2" t="s">
+        <v>308</v>
+      </c>
+      <c r="CB3" s="2" t="s">
+        <v>308</v>
+      </c>
+      <c r="CC3" s="2" t="s">
+        <v>341</v>
+      </c>
+      <c r="CD3" s="2" t="s">
+        <v>357</v>
+      </c>
+      <c r="CE3" s="2" t="s">
+        <v>357</v>
+      </c>
+      <c r="CF3" s="2" t="s">
+        <v>295</v>
+      </c>
+      <c r="CG3" s="2" t="s">
+        <v>358</v>
+      </c>
+      <c r="CH3" s="2" t="s">
+        <v>296</v>
+      </c>
+      <c r="CI3" s="2" t="s">
+        <v>266</v>
+      </c>
+      <c r="CJ3" s="2" t="s">
+        <v>297</v>
+      </c>
+      <c r="CK3" s="2" t="s">
+        <v>298</v>
+      </c>
+      <c r="CL3" s="2" t="s">
+        <v>359</v>
+      </c>
+      <c r="CM3" s="2" t="s">
+        <v>283</v>
+      </c>
+      <c r="CN3" s="2" t="s">
+        <v>283</v>
+      </c>
+      <c r="CO3" s="2" t="s">
+        <v>283</v>
+      </c>
+      <c r="CP3" s="2" t="s">
+        <v>284</v>
+      </c>
+      <c r="CQ3" s="2" t="s">
+        <v>284</v>
+      </c>
+      <c r="CR3" s="2" t="s">
+        <v>284</v>
+      </c>
+      <c r="CS3" s="2" t="s">
+        <v>285</v>
+      </c>
+      <c r="CT3" s="2" t="s">
+        <v>293</v>
+      </c>
+      <c r="CU3" s="2" t="s">
+        <v>327</v>
+      </c>
+      <c r="CV3" s="2" t="s">
+        <v>332</v>
+      </c>
+      <c r="CW3" s="2" t="s">
+        <v>332</v>
+      </c>
+      <c r="CX3" s="2" t="s">
+        <v>332</v>
+      </c>
+      <c r="CY3" s="2" t="s">
+        <v>298</v>
+      </c>
+      <c r="CZ3" s="2" t="s">
+        <v>360</v>
+      </c>
+      <c r="DA3" s="2" t="s">
+        <v>328</v>
+      </c>
+      <c r="DB3" s="2" t="s">
+        <v>266</v>
+      </c>
+      <c r="DC3" s="2" t="s">
+        <v>311</v>
+      </c>
+      <c r="DD3" s="2" t="s">
+        <v>298</v>
+      </c>
+      <c r="DE3" s="2" t="s">
+        <v>361</v>
+      </c>
+      <c r="DF3" s="2" t="s">
+        <v>304</v>
+      </c>
+      <c r="DG3" s="2" t="s">
+        <v>299</v>
+      </c>
+      <c r="DH3" s="2" t="s">
+        <v>283</v>
+      </c>
+      <c r="DI3" s="2" t="s">
+        <v>283</v>
+      </c>
+      <c r="DJ3" s="2" t="s">
+        <v>284</v>
+      </c>
+      <c r="DK3" s="2" t="s">
+        <v>307</v>
+      </c>
+      <c r="DL3" s="2" t="s">
+        <v>306</v>
+      </c>
+      <c r="DM3" s="2" t="s">
+        <v>327</v>
+      </c>
+      <c r="DN3" s="2" t="s">
+        <v>294</v>
+      </c>
+      <c r="DO3" s="2" t="s">
+        <v>308</v>
+      </c>
+      <c r="DP3" s="2" t="s">
+        <v>335</v>
+      </c>
+      <c r="DQ3" s="2" t="s">
+        <v>357</v>
+      </c>
+      <c r="DR3" s="2" t="s">
+        <v>357</v>
+      </c>
+      <c r="DS3" s="2" t="s">
+        <v>287</v>
+      </c>
+      <c r="DT3" s="2" t="s">
+        <v>362</v>
+      </c>
+      <c r="DU3" s="2" t="s">
+        <v>336</v>
+      </c>
+      <c r="DV3" s="2" t="s">
+        <v>266</v>
+      </c>
+      <c r="DW3" s="2" t="s">
+        <v>363</v>
+      </c>
+      <c r="DX3" s="2" t="s">
+        <v>298</v>
+      </c>
+      <c r="DY3" s="2" t="s">
+        <v>364</v>
+      </c>
+      <c r="DZ3" s="2" t="s">
+        <v>283</v>
+      </c>
+      <c r="EA3" s="2" t="s">
+        <v>300</v>
+      </c>
+      <c r="EB3" s="2" t="s">
+        <v>290</v>
+      </c>
+      <c r="EC3" s="2" t="s">
+        <v>284</v>
+      </c>
+      <c r="ED3" s="2" t="s">
+        <v>307</v>
+      </c>
+      <c r="EE3" s="2" t="s">
+        <v>307</v>
+      </c>
+      <c r="EF3" s="2" t="s">
+        <v>302</v>
+      </c>
+      <c r="EG3" s="2" t="s">
+        <v>293</v>
+      </c>
+      <c r="EH3" s="2" t="s">
+        <v>293</v>
+      </c>
+      <c r="EI3" s="2" t="s">
+        <v>332</v>
+      </c>
+      <c r="EJ3" s="2" t="s">
+        <v>342</v>
+      </c>
+      <c r="EK3" s="2" t="s">
+        <v>341</v>
+      </c>
+      <c r="EL3" s="2" t="s">
+        <v>287</v>
+      </c>
+      <c r="EM3" s="2" t="s">
+        <v>365</v>
+      </c>
+      <c r="EN3" s="2" t="s">
+        <v>366</v>
+      </c>
+      <c r="EO3" s="2" t="s">
+        <v>266</v>
+      </c>
+      <c r="EP3" s="2" t="s">
+        <v>311</v>
+      </c>
+      <c r="EQ3" s="2" t="s">
+        <v>298</v>
+      </c>
+      <c r="ER3" s="2" t="s">
+        <v>367</v>
+      </c>
+      <c r="ES3" s="2" t="s">
+        <v>283</v>
+      </c>
+      <c r="ET3" s="2" t="s">
+        <v>283</v>
+      </c>
+      <c r="EU3" s="2" t="s">
+        <v>300</v>
+      </c>
+      <c r="EV3" s="2" t="s">
+        <v>284</v>
+      </c>
+      <c r="EW3" s="2" t="s">
+        <v>284</v>
+      </c>
+      <c r="EX3" s="2" t="s">
+        <v>284</v>
+      </c>
+      <c r="EY3" s="2" t="s">
+        <v>302</v>
+      </c>
+      <c r="EZ3" s="2" t="s">
+        <v>285</v>
+      </c>
+      <c r="FA3" s="2" t="s">
+        <v>293</v>
+      </c>
+      <c r="FB3" s="2" t="s">
+        <v>332</v>
+      </c>
+      <c r="FC3" s="2" t="s">
+        <v>342</v>
+      </c>
+      <c r="FD3" s="2" t="s">
+        <v>341</v>
+      </c>
+      <c r="FE3" s="2" t="s">
+        <v>298</v>
+      </c>
+      <c r="FF3" s="2" t="s">
+        <v>368</v>
+      </c>
+      <c r="FG3" s="2" t="s">
+        <v>336</v>
+      </c>
+      <c r="FH3" s="2" t="s">
+        <v>266</v>
+      </c>
+      <c r="FI3" s="2" t="s">
+        <v>311</v>
+      </c>
+      <c r="FJ3" s="2" t="s">
+        <v>298</v>
+      </c>
+      <c r="FK3" s="2" t="s">
+        <v>369</v>
+      </c>
+      <c r="FL3" s="2" t="s">
+        <v>312</v>
+      </c>
+      <c r="FM3" s="2" t="s">
+        <v>313</v>
+      </c>
+      <c r="FN3" s="2" t="s">
+        <v>313</v>
+      </c>
+      <c r="FO3" s="2" t="s">
+        <v>313</v>
+      </c>
+      <c r="FP3" s="2" t="s">
+        <v>314</v>
+      </c>
+      <c r="FQ3" s="2" t="s">
+        <v>317</v>
+      </c>
+      <c r="FR3" s="2" t="s">
+        <v>317</v>
+      </c>
+      <c r="FS3" s="2" t="s">
+        <v>317</v>
+      </c>
+      <c r="FT3" s="2" t="s">
+        <v>319</v>
+      </c>
+      <c r="FU3" s="2" t="s">
+        <v>282</v>
+      </c>
+      <c r="FV3" s="2" t="s">
+        <v>325</v>
+      </c>
+      <c r="FW3" s="2" t="s">
         <v>279</v>
       </c>
-      <c r="AV3" s="2" t="s">
-        <v>350</v>
-      </c>
-      <c r="AW3" s="2" t="s">
-        <v>266</v>
-      </c>
-      <c r="AX3" s="2" t="s">
-        <v>351</v>
-      </c>
-      <c r="AY3" s="2" t="s">
-        <v>266</v>
-      </c>
-      <c r="AZ3" s="2" t="s">
-        <v>281</v>
-      </c>
-      <c r="BA3" s="2" t="s">
-        <v>298</v>
-      </c>
-      <c r="BB3" s="2" t="s">
-        <v>298</v>
-      </c>
-      <c r="BC3" s="2" t="s">
-        <v>298</v>
-      </c>
-      <c r="BD3" s="2" t="s">
-        <v>283</v>
-      </c>
-      <c r="BE3" s="2" t="s">
-        <v>283</v>
-      </c>
-      <c r="BF3" s="2" t="s">
-        <v>283</v>
-      </c>
-      <c r="BG3" s="2" t="s">
-        <v>284</v>
-      </c>
-      <c r="BH3" s="2" t="s">
-        <v>325</v>
-      </c>
-      <c r="BI3" s="2" t="s">
-        <v>325</v>
-      </c>
-      <c r="BJ3" s="2" t="s">
-        <v>330</v>
-      </c>
-      <c r="BK3" s="2" t="s">
-        <v>333</v>
-      </c>
-      <c r="BL3" s="2" t="s">
-        <v>333</v>
-      </c>
-      <c r="BM3" s="2" t="s">
-        <v>297</v>
-      </c>
-      <c r="BN3" s="2" t="s">
-        <v>352</v>
-      </c>
-      <c r="BO3" s="2" t="s">
-        <v>353</v>
-      </c>
-      <c r="BP3" s="2" t="s">
-        <v>266</v>
-      </c>
-      <c r="BQ3" s="2" t="s">
-        <v>309</v>
-      </c>
-      <c r="BR3" s="2" t="s">
-        <v>297</v>
-      </c>
-      <c r="BS3" s="2" t="s">
-        <v>354</v>
-      </c>
-      <c r="BT3" s="2" t="s">
-        <v>289</v>
-      </c>
-      <c r="BU3" s="2" t="s">
-        <v>290</v>
-      </c>
-      <c r="BV3" s="2" t="s">
-        <v>290</v>
-      </c>
-      <c r="BW3" s="2" t="s">
-        <v>283</v>
-      </c>
-      <c r="BX3" s="2" t="s">
-        <v>283</v>
-      </c>
-      <c r="BY3" s="2" t="s">
-        <v>283</v>
-      </c>
-      <c r="BZ3" s="2" t="s">
-        <v>325</v>
-      </c>
-      <c r="CA3" s="2" t="s">
-        <v>307</v>
-      </c>
-      <c r="CB3" s="2" t="s">
-        <v>307</v>
-      </c>
-      <c r="CC3" s="2" t="s">
-        <v>339</v>
-      </c>
-      <c r="CD3" s="2" t="s">
-        <v>355</v>
-      </c>
-      <c r="CE3" s="2" t="s">
-        <v>355</v>
-      </c>
-      <c r="CF3" s="2" t="s">
-        <v>294</v>
-      </c>
-      <c r="CG3" s="2" t="s">
-        <v>356</v>
-      </c>
-      <c r="CH3" s="2" t="s">
-        <v>295</v>
-      </c>
-      <c r="CI3" s="2" t="s">
-        <v>266</v>
-      </c>
-      <c r="CJ3" s="2" t="s">
-        <v>296</v>
-      </c>
-      <c r="CK3" s="2" t="s">
-        <v>297</v>
-      </c>
-      <c r="CL3" s="2" t="s">
-        <v>357</v>
-      </c>
-      <c r="CM3" s="2" t="s">
-        <v>282</v>
-      </c>
-      <c r="CN3" s="2" t="s">
-        <v>282</v>
-      </c>
-      <c r="CO3" s="2" t="s">
-        <v>282</v>
-      </c>
-      <c r="CP3" s="2" t="s">
-        <v>283</v>
-      </c>
-      <c r="CQ3" s="2" t="s">
-        <v>283</v>
-      </c>
-      <c r="CR3" s="2" t="s">
-        <v>283</v>
-      </c>
-      <c r="CS3" s="2" t="s">
-        <v>284</v>
-      </c>
-      <c r="CT3" s="2" t="s">
-        <v>292</v>
-      </c>
-      <c r="CU3" s="2" t="s">
-        <v>325</v>
-      </c>
-      <c r="CV3" s="2" t="s">
-        <v>330</v>
-      </c>
-      <c r="CW3" s="2" t="s">
-        <v>330</v>
-      </c>
-      <c r="CX3" s="2" t="s">
-        <v>330</v>
-      </c>
-      <c r="CY3" s="2" t="s">
-        <v>297</v>
-      </c>
-      <c r="CZ3" s="2" t="s">
-        <v>358</v>
-      </c>
-      <c r="DA3" s="2" t="s">
-        <v>326</v>
-      </c>
-      <c r="DB3" s="2" t="s">
-        <v>266</v>
-      </c>
-      <c r="DC3" s="2" t="s">
-        <v>309</v>
-      </c>
-      <c r="DD3" s="2" t="s">
-        <v>297</v>
-      </c>
-      <c r="DE3" s="2" t="s">
-        <v>359</v>
-      </c>
-      <c r="DF3" s="2" t="s">
-        <v>303</v>
-      </c>
-      <c r="DG3" s="2" t="s">
-        <v>298</v>
-      </c>
-      <c r="DH3" s="2" t="s">
-        <v>282</v>
-      </c>
-      <c r="DI3" s="2" t="s">
-        <v>282</v>
-      </c>
-      <c r="DJ3" s="2" t="s">
-        <v>283</v>
-      </c>
-      <c r="DK3" s="2" t="s">
-        <v>306</v>
-      </c>
-      <c r="DL3" s="2" t="s">
-        <v>305</v>
-      </c>
-      <c r="DM3" s="2" t="s">
-        <v>325</v>
-      </c>
-      <c r="DN3" s="2" t="s">
-        <v>293</v>
-      </c>
-      <c r="DO3" s="2" t="s">
-        <v>307</v>
-      </c>
-      <c r="DP3" s="2" t="s">
-        <v>333</v>
-      </c>
-      <c r="DQ3" s="2" t="s">
-        <v>355</v>
-      </c>
-      <c r="DR3" s="2" t="s">
-        <v>355</v>
-      </c>
-      <c r="DS3" s="2" t="s">
-        <v>286</v>
-      </c>
-      <c r="DT3" s="2" t="s">
-        <v>360</v>
-      </c>
-      <c r="DU3" s="2" t="s">
-        <v>334</v>
-      </c>
-      <c r="DV3" s="2" t="s">
-        <v>266</v>
-      </c>
-      <c r="DW3" s="2" t="s">
-        <v>361</v>
-      </c>
-      <c r="DX3" s="2" t="s">
-        <v>297</v>
-      </c>
-      <c r="DY3" s="2" t="s">
-        <v>362</v>
-      </c>
-      <c r="DZ3" s="2" t="s">
-        <v>282</v>
-      </c>
-      <c r="EA3" s="2" t="s">
-        <v>299</v>
-      </c>
-      <c r="EB3" s="2" t="s">
-        <v>289</v>
-      </c>
-      <c r="EC3" s="2" t="s">
-        <v>283</v>
-      </c>
-      <c r="ED3" s="2" t="s">
-        <v>306</v>
-      </c>
-      <c r="EE3" s="2" t="s">
-        <v>306</v>
-      </c>
-      <c r="EF3" s="2" t="s">
-        <v>301</v>
-      </c>
-      <c r="EG3" s="2" t="s">
-        <v>292</v>
-      </c>
-      <c r="EH3" s="2" t="s">
-        <v>292</v>
-      </c>
-      <c r="EI3" s="2" t="s">
-        <v>330</v>
-      </c>
-      <c r="EJ3" s="2" t="s">
-        <v>340</v>
-      </c>
-      <c r="EK3" s="2" t="s">
-        <v>339</v>
-      </c>
-      <c r="EL3" s="2" t="s">
-        <v>286</v>
-      </c>
-      <c r="EM3" s="2" t="s">
-        <v>363</v>
-      </c>
-      <c r="EN3" s="2" t="s">
-        <v>364</v>
-      </c>
-      <c r="EO3" s="2" t="s">
-        <v>266</v>
-      </c>
-      <c r="EP3" s="2" t="s">
-        <v>309</v>
-      </c>
-      <c r="EQ3" s="2" t="s">
-        <v>297</v>
-      </c>
-      <c r="ER3" s="2" t="s">
-        <v>365</v>
-      </c>
-      <c r="ES3" s="2" t="s">
-        <v>282</v>
-      </c>
-      <c r="ET3" s="2" t="s">
-        <v>282</v>
-      </c>
-      <c r="EU3" s="2" t="s">
-        <v>299</v>
-      </c>
-      <c r="EV3" s="2" t="s">
-        <v>283</v>
-      </c>
-      <c r="EW3" s="2" t="s">
-        <v>283</v>
-      </c>
-      <c r="EX3" s="2" t="s">
-        <v>283</v>
-      </c>
-      <c r="EY3" s="2" t="s">
-        <v>301</v>
-      </c>
-      <c r="EZ3" s="2" t="s">
-        <v>284</v>
-      </c>
-      <c r="FA3" s="2" t="s">
-        <v>292</v>
-      </c>
-      <c r="FB3" s="2" t="s">
-        <v>330</v>
-      </c>
-      <c r="FC3" s="2" t="s">
-        <v>340</v>
-      </c>
-      <c r="FD3" s="2" t="s">
-        <v>339</v>
-      </c>
-      <c r="FE3" s="2" t="s">
-        <v>297</v>
-      </c>
-      <c r="FF3" s="2" t="s">
-        <v>366</v>
-      </c>
-      <c r="FG3" s="2" t="s">
-        <v>334</v>
-      </c>
-      <c r="FH3" s="2" t="s">
-        <v>266</v>
-      </c>
-      <c r="FI3" s="2" t="s">
-        <v>309</v>
-      </c>
-      <c r="FJ3" s="2" t="s">
-        <v>297</v>
-      </c>
-      <c r="FK3" s="2" t="s">
-        <v>367</v>
-      </c>
-      <c r="FL3" s="2" t="s">
-        <v>310</v>
-      </c>
-      <c r="FM3" s="2" t="s">
-        <v>311</v>
-      </c>
-      <c r="FN3" s="2" t="s">
-        <v>311</v>
-      </c>
-      <c r="FO3" s="2" t="s">
-        <v>311</v>
-      </c>
-      <c r="FP3" s="2" t="s">
-        <v>312</v>
-      </c>
-      <c r="FQ3" s="2" t="s">
-        <v>315</v>
-      </c>
-      <c r="FR3" s="2" t="s">
-        <v>315</v>
-      </c>
-      <c r="FS3" s="2" t="s">
-        <v>315</v>
-      </c>
-      <c r="FT3" s="2" t="s">
-        <v>317</v>
-      </c>
-      <c r="FU3" s="2" t="s">
-        <v>281</v>
-      </c>
-      <c r="FV3" s="2" t="s">
-        <v>323</v>
-      </c>
-      <c r="FW3" s="2" t="s">
-        <v>278</v>
-      </c>
       <c r="FX3" s="2" t="s">
         <v>266</v>
       </c>
@@ -3493,10 +3583,10 @@
         <v>266</v>
       </c>
       <c r="FZ3" s="2" t="s">
-        <v>368</v>
+        <v>370</v>
       </c>
     </row>
-    <row r="4" spans="1:182" ht="22.3" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="4" spans="1:182" ht="15" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A4" s="1">
         <v>46194.56082175926</v>
       </c>
@@ -3507,7 +3597,7 @@
         <v>185</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>369</v>
+        <v>371</v>
       </c>
       <c r="E4">
         <v>100</v>
@@ -3522,7 +3612,7 @@
         <v>46194.580947881943</v>
       </c>
       <c r="I4" s="2" t="s">
-        <v>370</v>
+        <v>372</v>
       </c>
       <c r="J4" s="2" t="s">
         <v>266</v>
@@ -3549,7 +3639,7 @@
         <v>268</v>
       </c>
       <c r="R4" s="2" t="s">
-        <v>328</v>
+        <v>330</v>
       </c>
       <c r="S4" s="2" t="s">
         <v>269</v>
@@ -3582,458 +3672,458 @@
         <v>266</v>
       </c>
       <c r="AC4" s="2" t="s">
-        <v>344</v>
+        <v>346</v>
       </c>
       <c r="AD4" s="2" t="s">
-        <v>337</v>
+        <v>339</v>
       </c>
       <c r="AE4" s="2" t="s">
-        <v>371</v>
+        <v>373</v>
       </c>
       <c r="AF4" s="2" t="s">
         <v>266</v>
       </c>
       <c r="AG4" s="2" t="s">
-        <v>372</v>
+        <v>374</v>
       </c>
       <c r="AH4" s="2" t="s">
-        <v>373</v>
+        <v>375</v>
       </c>
       <c r="AI4" s="2" t="s">
-        <v>374</v>
+        <v>376</v>
       </c>
       <c r="AJ4" s="2" t="s">
         <v>266</v>
       </c>
       <c r="AK4" s="2" t="s">
-        <v>323</v>
+        <v>325</v>
       </c>
       <c r="AL4" s="2" t="s">
-        <v>323</v>
+        <v>325</v>
       </c>
       <c r="AM4" s="2" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="AN4" s="2" t="s">
-        <v>323</v>
+        <v>325</v>
       </c>
       <c r="AO4" s="2" t="s">
-        <v>338</v>
+        <v>340</v>
       </c>
       <c r="AP4" s="2" t="s">
-        <v>338</v>
+        <v>340</v>
       </c>
       <c r="AQ4" s="2" t="s">
+        <v>289</v>
+      </c>
+      <c r="AR4" s="2" t="s">
+        <v>377</v>
+      </c>
+      <c r="AS4" s="2" t="s">
+        <v>378</v>
+      </c>
+      <c r="AT4" s="2" t="s">
+        <v>282</v>
+      </c>
+      <c r="AU4" s="2" t="s">
+        <v>282</v>
+      </c>
+      <c r="AV4" s="2" t="s">
+        <v>379</v>
+      </c>
+      <c r="AW4" s="2" t="s">
+        <v>266</v>
+      </c>
+      <c r="AX4" s="2" t="s">
+        <v>380</v>
+      </c>
+      <c r="AY4" s="2" t="s">
+        <v>266</v>
+      </c>
+      <c r="AZ4" s="2" t="s">
+        <v>320</v>
+      </c>
+      <c r="BA4" s="2" t="s">
+        <v>299</v>
+      </c>
+      <c r="BB4" s="2" t="s">
+        <v>299</v>
+      </c>
+      <c r="BC4" s="2" t="s">
+        <v>299</v>
+      </c>
+      <c r="BD4" s="2" t="s">
+        <v>307</v>
+      </c>
+      <c r="BE4" s="2" t="s">
+        <v>307</v>
+      </c>
+      <c r="BF4" s="2" t="s">
+        <v>307</v>
+      </c>
+      <c r="BG4" s="2" t="s">
+        <v>285</v>
+      </c>
+      <c r="BH4" s="2" t="s">
+        <v>294</v>
+      </c>
+      <c r="BI4" s="2" t="s">
+        <v>308</v>
+      </c>
+      <c r="BJ4" s="2" t="s">
+        <v>335</v>
+      </c>
+      <c r="BK4" s="2" t="s">
+        <v>335</v>
+      </c>
+      <c r="BL4" s="2" t="s">
+        <v>335</v>
+      </c>
+      <c r="BM4" s="2" t="s">
+        <v>295</v>
+      </c>
+      <c r="BN4" s="2" t="s">
+        <v>381</v>
+      </c>
+      <c r="BO4" s="2" t="s">
         <v>288</v>
       </c>
-      <c r="AR4" s="2" t="s">
-        <v>375</v>
-      </c>
-      <c r="AS4" s="2" t="s">
-        <v>376</v>
-      </c>
-      <c r="AT4" s="2" t="s">
-        <v>281</v>
-      </c>
-      <c r="AU4" s="2" t="s">
-        <v>281</v>
-      </c>
-      <c r="AV4" s="2" t="s">
-        <v>377</v>
-      </c>
-      <c r="AW4" s="2" t="s">
-        <v>266</v>
-      </c>
-      <c r="AX4" s="2" t="s">
-        <v>378</v>
-      </c>
-      <c r="AY4" s="2" t="s">
-        <v>266</v>
-      </c>
-      <c r="AZ4" s="2" t="s">
-        <v>318</v>
-      </c>
-      <c r="BA4" s="2" t="s">
+      <c r="BP4" s="2" t="s">
+        <v>266</v>
+      </c>
+      <c r="BQ4" s="2" t="s">
+        <v>333</v>
+      </c>
+      <c r="BR4" s="2" t="s">
+        <v>289</v>
+      </c>
+      <c r="BS4" s="2" t="s">
+        <v>382</v>
+      </c>
+      <c r="BT4" s="2" t="s">
+        <v>299</v>
+      </c>
+      <c r="BU4" s="2" t="s">
+        <v>305</v>
+      </c>
+      <c r="BV4" s="2" t="s">
+        <v>291</v>
+      </c>
+      <c r="BW4" s="2" t="s">
+        <v>307</v>
+      </c>
+      <c r="BX4" s="2" t="s">
+        <v>307</v>
+      </c>
+      <c r="BY4" s="2" t="s">
+        <v>307</v>
+      </c>
+      <c r="BZ4" s="2" t="s">
+        <v>285</v>
+      </c>
+      <c r="CA4" s="2" t="s">
+        <v>294</v>
+      </c>
+      <c r="CB4" s="2" t="s">
+        <v>308</v>
+      </c>
+      <c r="CC4" s="2" t="s">
+        <v>332</v>
+      </c>
+      <c r="CD4" s="2" t="s">
+        <v>383</v>
+      </c>
+      <c r="CE4" s="2" t="s">
+        <v>357</v>
+      </c>
+      <c r="CF4" s="2" t="s">
+        <v>295</v>
+      </c>
+      <c r="CG4" s="2" t="s">
+        <v>384</v>
+      </c>
+      <c r="CH4" s="2" t="s">
+        <v>355</v>
+      </c>
+      <c r="CI4" s="2" t="s">
+        <v>266</v>
+      </c>
+      <c r="CJ4" s="2" t="s">
+        <v>297</v>
+      </c>
+      <c r="CK4" s="2" t="s">
+        <v>289</v>
+      </c>
+      <c r="CL4" s="2" t="s">
+        <v>385</v>
+      </c>
+      <c r="CM4" s="2" t="s">
+        <v>283</v>
+      </c>
+      <c r="CN4" s="2" t="s">
+        <v>283</v>
+      </c>
+      <c r="CO4" s="2" t="s">
+        <v>283</v>
+      </c>
+      <c r="CP4" s="2" t="s">
+        <v>306</v>
+      </c>
+      <c r="CQ4" s="2" t="s">
+        <v>301</v>
+      </c>
+      <c r="CR4" s="2" t="s">
+        <v>307</v>
+      </c>
+      <c r="CS4" s="2" t="s">
+        <v>302</v>
+      </c>
+      <c r="CT4" s="2" t="s">
+        <v>293</v>
+      </c>
+      <c r="CU4" s="2" t="s">
+        <v>286</v>
+      </c>
+      <c r="CV4" s="2" t="s">
+        <v>332</v>
+      </c>
+      <c r="CW4" s="2" t="s">
+        <v>332</v>
+      </c>
+      <c r="CX4" s="2" t="s">
+        <v>332</v>
+      </c>
+      <c r="CY4" s="2" t="s">
+        <v>289</v>
+      </c>
+      <c r="CZ4" s="2" t="s">
+        <v>386</v>
+      </c>
+      <c r="DA4" s="2" t="s">
+        <v>387</v>
+      </c>
+      <c r="DB4" s="2" t="s">
+        <v>266</v>
+      </c>
+      <c r="DC4" s="2" t="s">
+        <v>311</v>
+      </c>
+      <c r="DD4" s="2" t="s">
+        <v>334</v>
+      </c>
+      <c r="DE4" s="2" t="s">
+        <v>388</v>
+      </c>
+      <c r="DF4" s="2" t="s">
+        <v>304</v>
+      </c>
+      <c r="DG4" s="2" t="s">
+        <v>283</v>
+      </c>
+      <c r="DH4" s="2" t="s">
+        <v>283</v>
+      </c>
+      <c r="DI4" s="2" t="s">
+        <v>326</v>
+      </c>
+      <c r="DJ4" s="2" t="s">
+        <v>307</v>
+      </c>
+      <c r="DK4" s="2" t="s">
+        <v>284</v>
+      </c>
+      <c r="DL4" s="2" t="s">
+        <v>307</v>
+      </c>
+      <c r="DM4" s="2" t="s">
+        <v>285</v>
+      </c>
+      <c r="DN4" s="2" t="s">
+        <v>285</v>
+      </c>
+      <c r="DO4" s="2" t="s">
+        <v>294</v>
+      </c>
+      <c r="DP4" s="2" t="s">
+        <v>332</v>
+      </c>
+      <c r="DQ4" s="2" t="s">
+        <v>335</v>
+      </c>
+      <c r="DR4" s="2" t="s">
+        <v>341</v>
+      </c>
+      <c r="DS4" s="2" t="s">
         <v>298</v>
       </c>
-      <c r="BB4" s="2" t="s">
-        <v>298</v>
-      </c>
-      <c r="BC4" s="2" t="s">
-        <v>298</v>
-      </c>
-      <c r="BD4" s="2" t="s">
-        <v>306</v>
-      </c>
-      <c r="BE4" s="2" t="s">
-        <v>306</v>
-      </c>
-      <c r="BF4" s="2" t="s">
-        <v>306</v>
-      </c>
-      <c r="BG4" s="2" t="s">
+      <c r="DT4" s="2" t="s">
+        <v>389</v>
+      </c>
+      <c r="DU4" s="2" t="s">
+        <v>390</v>
+      </c>
+      <c r="DV4" s="2" t="s">
+        <v>266</v>
+      </c>
+      <c r="DW4" s="2" t="s">
+        <v>311</v>
+      </c>
+      <c r="DX4" s="2" t="s">
+        <v>334</v>
+      </c>
+      <c r="DY4" s="2" t="s">
+        <v>391</v>
+      </c>
+      <c r="DZ4" s="2" t="s">
+        <v>299</v>
+      </c>
+      <c r="EA4" s="2" t="s">
+        <v>299</v>
+      </c>
+      <c r="EB4" s="2" t="s">
+        <v>299</v>
+      </c>
+      <c r="EC4" s="2" t="s">
+        <v>292</v>
+      </c>
+      <c r="ED4" s="2" t="s">
+        <v>307</v>
+      </c>
+      <c r="EE4" s="2" t="s">
+        <v>307</v>
+      </c>
+      <c r="EF4" s="2" t="s">
+        <v>285</v>
+      </c>
+      <c r="EG4" s="2" t="s">
+        <v>294</v>
+      </c>
+      <c r="EH4" s="2" t="s">
+        <v>308</v>
+      </c>
+      <c r="EI4" s="2" t="s">
+        <v>332</v>
+      </c>
+      <c r="EJ4" s="2" t="s">
+        <v>332</v>
+      </c>
+      <c r="EK4" s="2" t="s">
+        <v>332</v>
+      </c>
+      <c r="EL4" s="2" t="s">
+        <v>287</v>
+      </c>
+      <c r="EM4" s="2" t="s">
+        <v>392</v>
+      </c>
+      <c r="EN4" s="2" t="s">
+        <v>393</v>
+      </c>
+      <c r="EO4" s="2" t="s">
+        <v>266</v>
+      </c>
+      <c r="EP4" s="2" t="s">
+        <v>311</v>
+      </c>
+      <c r="EQ4" s="2" t="s">
+        <v>334</v>
+      </c>
+      <c r="ER4" s="2" t="s">
+        <v>394</v>
+      </c>
+      <c r="ES4" s="2" t="s">
+        <v>283</v>
+      </c>
+      <c r="ET4" s="2" t="s">
+        <v>283</v>
+      </c>
+      <c r="EU4" s="2" t="s">
+        <v>283</v>
+      </c>
+      <c r="EV4" s="2" t="s">
+        <v>307</v>
+      </c>
+      <c r="EW4" s="2" t="s">
         <v>284</v>
       </c>
-      <c r="BH4" s="2" t="s">
+      <c r="EX4" s="2" t="s">
+        <v>284</v>
+      </c>
+      <c r="EY4" s="2" t="s">
+        <v>302</v>
+      </c>
+      <c r="EZ4" s="2" t="s">
         <v>293</v>
       </c>
-      <c r="BI4" s="2" t="s">
-        <v>307</v>
-      </c>
-      <c r="BJ4" s="2" t="s">
-        <v>333</v>
-      </c>
-      <c r="BK4" s="2" t="s">
-        <v>333</v>
-      </c>
-      <c r="BL4" s="2" t="s">
-        <v>333</v>
-      </c>
-      <c r="BM4" s="2" t="s">
-        <v>294</v>
-      </c>
-      <c r="BN4" s="2" t="s">
-        <v>379</v>
-      </c>
-      <c r="BO4" s="2" t="s">
-        <v>287</v>
-      </c>
-      <c r="BP4" s="2" t="s">
-        <v>266</v>
-      </c>
-      <c r="BQ4" s="2" t="s">
-        <v>331</v>
-      </c>
-      <c r="BR4" s="2" t="s">
-        <v>288</v>
-      </c>
-      <c r="BS4" s="2" t="s">
-        <v>380</v>
-      </c>
-      <c r="BT4" s="2" t="s">
-        <v>298</v>
-      </c>
-      <c r="BU4" s="2" t="s">
-        <v>304</v>
-      </c>
-      <c r="BV4" s="2" t="s">
-        <v>290</v>
-      </c>
-      <c r="BW4" s="2" t="s">
-        <v>306</v>
-      </c>
-      <c r="BX4" s="2" t="s">
-        <v>306</v>
-      </c>
-      <c r="BY4" s="2" t="s">
-        <v>306</v>
-      </c>
-      <c r="BZ4" s="2" t="s">
-        <v>284</v>
-      </c>
-      <c r="CA4" s="2" t="s">
+      <c r="FA4" s="2" t="s">
         <v>293</v>
       </c>
-      <c r="CB4" s="2" t="s">
-        <v>307</v>
-      </c>
-      <c r="CC4" s="2" t="s">
-        <v>330</v>
-      </c>
-      <c r="CD4" s="2" t="s">
-        <v>381</v>
-      </c>
-      <c r="CE4" s="2" t="s">
-        <v>355</v>
-      </c>
-      <c r="CF4" s="2" t="s">
-        <v>294</v>
-      </c>
-      <c r="CG4" s="2" t="s">
-        <v>382</v>
-      </c>
-      <c r="CH4" s="2" t="s">
-        <v>353</v>
-      </c>
-      <c r="CI4" s="2" t="s">
-        <v>266</v>
-      </c>
-      <c r="CJ4" s="2" t="s">
-        <v>296</v>
-      </c>
-      <c r="CK4" s="2" t="s">
-        <v>288</v>
-      </c>
-      <c r="CL4" s="2" t="s">
-        <v>383</v>
-      </c>
-      <c r="CM4" s="2" t="s">
+      <c r="FB4" s="2" t="s">
+        <v>332</v>
+      </c>
+      <c r="FC4" s="2" t="s">
+        <v>332</v>
+      </c>
+      <c r="FD4" s="2" t="s">
+        <v>332</v>
+      </c>
+      <c r="FE4" s="2" t="s">
+        <v>289</v>
+      </c>
+      <c r="FF4" s="2" t="s">
+        <v>395</v>
+      </c>
+      <c r="FG4" s="2" t="s">
+        <v>387</v>
+      </c>
+      <c r="FH4" s="2" t="s">
+        <v>266</v>
+      </c>
+      <c r="FI4" s="2" t="s">
+        <v>311</v>
+      </c>
+      <c r="FJ4" s="2" t="s">
+        <v>334</v>
+      </c>
+      <c r="FK4" s="2" t="s">
+        <v>396</v>
+      </c>
+      <c r="FL4" s="2" t="s">
+        <v>397</v>
+      </c>
+      <c r="FM4" s="2" t="s">
+        <v>313</v>
+      </c>
+      <c r="FN4" s="2" t="s">
+        <v>313</v>
+      </c>
+      <c r="FO4" s="2" t="s">
+        <v>314</v>
+      </c>
+      <c r="FP4" s="2" t="s">
+        <v>316</v>
+      </c>
+      <c r="FQ4" s="2" t="s">
+        <v>317</v>
+      </c>
+      <c r="FR4" s="2" t="s">
+        <v>317</v>
+      </c>
+      <c r="FS4" s="2" t="s">
+        <v>317</v>
+      </c>
+      <c r="FT4" s="2" t="s">
+        <v>398</v>
+      </c>
+      <c r="FU4" s="2" t="s">
+        <v>320</v>
+      </c>
+      <c r="FV4" s="2" t="s">
         <v>282</v>
       </c>
-      <c r="CN4" s="2" t="s">
+      <c r="FW4" s="2" t="s">
         <v>282</v>
       </c>
-      <c r="CO4" s="2" t="s">
-        <v>282</v>
-      </c>
-      <c r="CP4" s="2" t="s">
-        <v>305</v>
-      </c>
-      <c r="CQ4" s="2" t="s">
-        <v>300</v>
-      </c>
-      <c r="CR4" s="2" t="s">
-        <v>306</v>
-      </c>
-      <c r="CS4" s="2" t="s">
-        <v>301</v>
-      </c>
-      <c r="CT4" s="2" t="s">
-        <v>292</v>
-      </c>
-      <c r="CU4" s="2" t="s">
-        <v>285</v>
-      </c>
-      <c r="CV4" s="2" t="s">
-        <v>330</v>
-      </c>
-      <c r="CW4" s="2" t="s">
-        <v>330</v>
-      </c>
-      <c r="CX4" s="2" t="s">
-        <v>330</v>
-      </c>
-      <c r="CY4" s="2" t="s">
-        <v>288</v>
-      </c>
-      <c r="CZ4" s="2" t="s">
-        <v>384</v>
-      </c>
-      <c r="DA4" s="2" t="s">
-        <v>385</v>
-      </c>
-      <c r="DB4" s="2" t="s">
-        <v>266</v>
-      </c>
-      <c r="DC4" s="2" t="s">
-        <v>309</v>
-      </c>
-      <c r="DD4" s="2" t="s">
-        <v>332</v>
-      </c>
-      <c r="DE4" s="2" t="s">
-        <v>386</v>
-      </c>
-      <c r="DF4" s="2" t="s">
-        <v>303</v>
-      </c>
-      <c r="DG4" s="2" t="s">
-        <v>282</v>
-      </c>
-      <c r="DH4" s="2" t="s">
-        <v>282</v>
-      </c>
-      <c r="DI4" s="2" t="s">
-        <v>324</v>
-      </c>
-      <c r="DJ4" s="2" t="s">
-        <v>306</v>
-      </c>
-      <c r="DK4" s="2" t="s">
-        <v>283</v>
-      </c>
-      <c r="DL4" s="2" t="s">
-        <v>306</v>
-      </c>
-      <c r="DM4" s="2" t="s">
-        <v>284</v>
-      </c>
-      <c r="DN4" s="2" t="s">
-        <v>284</v>
-      </c>
-      <c r="DO4" s="2" t="s">
-        <v>293</v>
-      </c>
-      <c r="DP4" s="2" t="s">
-        <v>330</v>
-      </c>
-      <c r="DQ4" s="2" t="s">
-        <v>333</v>
-      </c>
-      <c r="DR4" s="2" t="s">
-        <v>339</v>
-      </c>
-      <c r="DS4" s="2" t="s">
-        <v>297</v>
-      </c>
-      <c r="DT4" s="2" t="s">
-        <v>387</v>
-      </c>
-      <c r="DU4" s="2" t="s">
-        <v>388</v>
-      </c>
-      <c r="DV4" s="2" t="s">
-        <v>266</v>
-      </c>
-      <c r="DW4" s="2" t="s">
-        <v>309</v>
-      </c>
-      <c r="DX4" s="2" t="s">
-        <v>332</v>
-      </c>
-      <c r="DY4" s="2" t="s">
-        <v>389</v>
-      </c>
-      <c r="DZ4" s="2" t="s">
-        <v>298</v>
-      </c>
-      <c r="EA4" s="2" t="s">
-        <v>298</v>
-      </c>
-      <c r="EB4" s="2" t="s">
-        <v>298</v>
-      </c>
-      <c r="EC4" s="2" t="s">
-        <v>291</v>
-      </c>
-      <c r="ED4" s="2" t="s">
-        <v>306</v>
-      </c>
-      <c r="EE4" s="2" t="s">
-        <v>306</v>
-      </c>
-      <c r="EF4" s="2" t="s">
-        <v>284</v>
-      </c>
-      <c r="EG4" s="2" t="s">
-        <v>293</v>
-      </c>
-      <c r="EH4" s="2" t="s">
-        <v>307</v>
-      </c>
-      <c r="EI4" s="2" t="s">
-        <v>330</v>
-      </c>
-      <c r="EJ4" s="2" t="s">
-        <v>330</v>
-      </c>
-      <c r="EK4" s="2" t="s">
-        <v>330</v>
-      </c>
-      <c r="EL4" s="2" t="s">
-        <v>286</v>
-      </c>
-      <c r="EM4" s="2" t="s">
-        <v>390</v>
-      </c>
-      <c r="EN4" s="2" t="s">
-        <v>391</v>
-      </c>
-      <c r="EO4" s="2" t="s">
-        <v>266</v>
-      </c>
-      <c r="EP4" s="2" t="s">
-        <v>309</v>
-      </c>
-      <c r="EQ4" s="2" t="s">
-        <v>332</v>
-      </c>
-      <c r="ER4" s="2" t="s">
-        <v>392</v>
-      </c>
-      <c r="ES4" s="2" t="s">
-        <v>282</v>
-      </c>
-      <c r="ET4" s="2" t="s">
-        <v>282</v>
-      </c>
-      <c r="EU4" s="2" t="s">
-        <v>282</v>
-      </c>
-      <c r="EV4" s="2" t="s">
-        <v>306</v>
-      </c>
-      <c r="EW4" s="2" t="s">
-        <v>283</v>
-      </c>
-      <c r="EX4" s="2" t="s">
-        <v>283</v>
-      </c>
-      <c r="EY4" s="2" t="s">
-        <v>301</v>
-      </c>
-      <c r="EZ4" s="2" t="s">
-        <v>292</v>
-      </c>
-      <c r="FA4" s="2" t="s">
-        <v>292</v>
-      </c>
-      <c r="FB4" s="2" t="s">
-        <v>330</v>
-      </c>
-      <c r="FC4" s="2" t="s">
-        <v>330</v>
-      </c>
-      <c r="FD4" s="2" t="s">
-        <v>330</v>
-      </c>
-      <c r="FE4" s="2" t="s">
-        <v>288</v>
-      </c>
-      <c r="FF4" s="2" t="s">
-        <v>393</v>
-      </c>
-      <c r="FG4" s="2" t="s">
-        <v>385</v>
-      </c>
-      <c r="FH4" s="2" t="s">
-        <v>266</v>
-      </c>
-      <c r="FI4" s="2" t="s">
-        <v>309</v>
-      </c>
-      <c r="FJ4" s="2" t="s">
-        <v>332</v>
-      </c>
-      <c r="FK4" s="2" t="s">
-        <v>394</v>
-      </c>
-      <c r="FL4" s="2" t="s">
-        <v>395</v>
-      </c>
-      <c r="FM4" s="2" t="s">
-        <v>311</v>
-      </c>
-      <c r="FN4" s="2" t="s">
-        <v>311</v>
-      </c>
-      <c r="FO4" s="2" t="s">
-        <v>312</v>
-      </c>
-      <c r="FP4" s="2" t="s">
-        <v>314</v>
-      </c>
-      <c r="FQ4" s="2" t="s">
-        <v>315</v>
-      </c>
-      <c r="FR4" s="2" t="s">
-        <v>315</v>
-      </c>
-      <c r="FS4" s="2" t="s">
-        <v>315</v>
-      </c>
-      <c r="FT4" s="2" t="s">
-        <v>396</v>
-      </c>
-      <c r="FU4" s="2" t="s">
-        <v>318</v>
-      </c>
-      <c r="FV4" s="2" t="s">
-        <v>281</v>
-      </c>
-      <c r="FW4" s="2" t="s">
-        <v>281</v>
-      </c>
       <c r="FX4" s="2" t="s">
         <v>266</v>
       </c>
@@ -4041,10 +4131,10 @@
         <v>266</v>
       </c>
       <c r="FZ4" s="2" t="s">
-        <v>397</v>
+        <v>399</v>
       </c>
     </row>
-    <row r="5" spans="1:182" ht="17.600000000000001" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="5" spans="1:182" ht="15" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A5" s="1">
         <v>46194.583449074074</v>
       </c>
@@ -4055,7 +4145,7 @@
         <v>185</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>398</v>
+        <v>400</v>
       </c>
       <c r="E5">
         <v>100</v>
@@ -4070,7 +4160,7 @@
         <v>46194.602760381946</v>
       </c>
       <c r="I5" s="2" t="s">
-        <v>399</v>
+        <v>401</v>
       </c>
       <c r="J5" s="2" t="s">
         <v>266</v>
@@ -4097,7 +4187,7 @@
         <v>268</v>
       </c>
       <c r="R5" s="2" t="s">
-        <v>328</v>
+        <v>330</v>
       </c>
       <c r="S5" s="2" t="s">
         <v>269</v>
@@ -4112,7 +4202,7 @@
         <v>25</v>
       </c>
       <c r="W5" s="2" t="s">
-        <v>319</v>
+        <v>321</v>
       </c>
       <c r="X5" s="2" t="s">
         <v>273</v>
@@ -4121,7 +4211,7 @@
         <v>274</v>
       </c>
       <c r="Z5" s="2" t="s">
-        <v>343</v>
+        <v>345</v>
       </c>
       <c r="AA5" s="2" t="s">
         <v>276</v>
@@ -4130,469 +4220,469 @@
         <v>266</v>
       </c>
       <c r="AC5" s="2" t="s">
-        <v>344</v>
+        <v>346</v>
       </c>
       <c r="AD5" s="2" t="s">
+        <v>339</v>
+      </c>
+      <c r="AE5" s="2" t="s">
+        <v>402</v>
+      </c>
+      <c r="AF5" s="2" t="s">
+        <v>266</v>
+      </c>
+      <c r="AG5" s="2" t="s">
+        <v>322</v>
+      </c>
+      <c r="AH5" s="2" t="s">
+        <v>323</v>
+      </c>
+      <c r="AI5" s="2" t="s">
+        <v>403</v>
+      </c>
+      <c r="AJ5" s="2" t="s">
+        <v>266</v>
+      </c>
+      <c r="AK5" s="2" t="s">
+        <v>279</v>
+      </c>
+      <c r="AL5" s="2" t="s">
+        <v>279</v>
+      </c>
+      <c r="AM5" s="2" t="s">
+        <v>278</v>
+      </c>
+      <c r="AN5" s="2" t="s">
+        <v>320</v>
+      </c>
+      <c r="AO5" s="2" t="s">
+        <v>325</v>
+      </c>
+      <c r="AP5" s="2" t="s">
+        <v>325</v>
+      </c>
+      <c r="AQ5" s="2" t="s">
+        <v>349</v>
+      </c>
+      <c r="AR5" s="2" t="s">
+        <v>404</v>
+      </c>
+      <c r="AS5" s="2" t="s">
+        <v>405</v>
+      </c>
+      <c r="AT5" s="2" t="s">
+        <v>282</v>
+      </c>
+      <c r="AU5" s="2" t="s">
+        <v>279</v>
+      </c>
+      <c r="AV5" s="2" t="s">
+        <v>406</v>
+      </c>
+      <c r="AW5" s="2" t="s">
+        <v>266</v>
+      </c>
+      <c r="AX5" s="2" t="s">
+        <v>353</v>
+      </c>
+      <c r="AY5" s="2" t="s">
+        <v>266</v>
+      </c>
+      <c r="AZ5" s="2" t="s">
+        <v>340</v>
+      </c>
+      <c r="BA5" s="2" t="s">
+        <v>283</v>
+      </c>
+      <c r="BB5" s="2" t="s">
+        <v>283</v>
+      </c>
+      <c r="BC5" s="2" t="s">
+        <v>299</v>
+      </c>
+      <c r="BD5" s="2" t="s">
+        <v>284</v>
+      </c>
+      <c r="BE5" s="2" t="s">
+        <v>284</v>
+      </c>
+      <c r="BF5" s="2" t="s">
+        <v>284</v>
+      </c>
+      <c r="BG5" s="2" t="s">
+        <v>285</v>
+      </c>
+      <c r="BH5" s="2" t="s">
+        <v>293</v>
+      </c>
+      <c r="BI5" s="2" t="s">
+        <v>286</v>
+      </c>
+      <c r="BJ5" s="2" t="s">
+        <v>332</v>
+      </c>
+      <c r="BK5" s="2" t="s">
+        <v>335</v>
+      </c>
+      <c r="BL5" s="2" t="s">
+        <v>335</v>
+      </c>
+      <c r="BM5" s="2" t="s">
+        <v>298</v>
+      </c>
+      <c r="BN5" s="2" t="s">
+        <v>407</v>
+      </c>
+      <c r="BO5" s="2" t="s">
+        <v>408</v>
+      </c>
+      <c r="BP5" s="2" t="s">
+        <v>266</v>
+      </c>
+      <c r="BQ5" s="2" t="s">
+        <v>311</v>
+      </c>
+      <c r="BR5" s="2" t="s">
+        <v>334</v>
+      </c>
+      <c r="BS5" s="2" t="s">
+        <v>409</v>
+      </c>
+      <c r="BT5" s="2" t="s">
+        <v>290</v>
+      </c>
+      <c r="BU5" s="2" t="s">
+        <v>305</v>
+      </c>
+      <c r="BV5" s="2" t="s">
+        <v>291</v>
+      </c>
+      <c r="BW5" s="2" t="s">
+        <v>307</v>
+      </c>
+      <c r="BX5" s="2" t="s">
+        <v>284</v>
+      </c>
+      <c r="BY5" s="2" t="s">
+        <v>284</v>
+      </c>
+      <c r="BZ5" s="2" t="s">
+        <v>327</v>
+      </c>
+      <c r="CA5" s="2" t="s">
+        <v>294</v>
+      </c>
+      <c r="CB5" s="2" t="s">
+        <v>308</v>
+      </c>
+      <c r="CC5" s="2" t="s">
+        <v>341</v>
+      </c>
+      <c r="CD5" s="2" t="s">
+        <v>341</v>
+      </c>
+      <c r="CE5" s="2" t="s">
+        <v>383</v>
+      </c>
+      <c r="CF5" s="2" t="s">
+        <v>295</v>
+      </c>
+      <c r="CG5" s="2" t="s">
+        <v>410</v>
+      </c>
+      <c r="CH5" s="2" t="s">
+        <v>296</v>
+      </c>
+      <c r="CI5" s="2" t="s">
+        <v>266</v>
+      </c>
+      <c r="CJ5" s="2" t="s">
+        <v>297</v>
+      </c>
+      <c r="CK5" s="2" t="s">
+        <v>298</v>
+      </c>
+      <c r="CL5" s="2" t="s">
+        <v>411</v>
+      </c>
+      <c r="CM5" s="2" t="s">
+        <v>283</v>
+      </c>
+      <c r="CN5" s="2" t="s">
+        <v>283</v>
+      </c>
+      <c r="CO5" s="2" t="s">
+        <v>283</v>
+      </c>
+      <c r="CP5" s="2" t="s">
+        <v>307</v>
+      </c>
+      <c r="CQ5" s="2" t="s">
+        <v>284</v>
+      </c>
+      <c r="CR5" s="2" t="s">
+        <v>284</v>
+      </c>
+      <c r="CS5" s="2" t="s">
+        <v>285</v>
+      </c>
+      <c r="CT5" s="2" t="s">
+        <v>286</v>
+      </c>
+      <c r="CU5" s="2" t="s">
+        <v>327</v>
+      </c>
+      <c r="CV5" s="2" t="s">
+        <v>332</v>
+      </c>
+      <c r="CW5" s="2" t="s">
+        <v>332</v>
+      </c>
+      <c r="CX5" s="2" t="s">
+        <v>335</v>
+      </c>
+      <c r="CY5" s="2" t="s">
+        <v>298</v>
+      </c>
+      <c r="CZ5" s="2" t="s">
+        <v>412</v>
+      </c>
+      <c r="DA5" s="2" t="s">
+        <v>413</v>
+      </c>
+      <c r="DB5" s="2" t="s">
+        <v>266</v>
+      </c>
+      <c r="DC5" s="2" t="s">
+        <v>311</v>
+      </c>
+      <c r="DD5" s="2" t="s">
+        <v>334</v>
+      </c>
+      <c r="DE5" s="2" t="s">
+        <v>414</v>
+      </c>
+      <c r="DF5" s="2" t="s">
+        <v>304</v>
+      </c>
+      <c r="DG5" s="2" t="s">
+        <v>299</v>
+      </c>
+      <c r="DH5" s="2" t="s">
+        <v>326</v>
+      </c>
+      <c r="DI5" s="2" t="s">
+        <v>290</v>
+      </c>
+      <c r="DJ5" s="2" t="s">
+        <v>307</v>
+      </c>
+      <c r="DK5" s="2" t="s">
+        <v>284</v>
+      </c>
+      <c r="DL5" s="2" t="s">
+        <v>284</v>
+      </c>
+      <c r="DM5" s="2" t="s">
+        <v>293</v>
+      </c>
+      <c r="DN5" s="2" t="s">
+        <v>327</v>
+      </c>
+      <c r="DO5" s="2" t="s">
+        <v>308</v>
+      </c>
+      <c r="DP5" s="2" t="s">
+        <v>332</v>
+      </c>
+      <c r="DQ5" s="2" t="s">
+        <v>335</v>
+      </c>
+      <c r="DR5" s="2" t="s">
+        <v>342</v>
+      </c>
+      <c r="DS5" s="2" t="s">
+        <v>287</v>
+      </c>
+      <c r="DT5" s="2" t="s">
+        <v>415</v>
+      </c>
+      <c r="DU5" s="2" t="s">
+        <v>393</v>
+      </c>
+      <c r="DV5" s="2" t="s">
+        <v>266</v>
+      </c>
+      <c r="DW5" s="2" t="s">
+        <v>309</v>
+      </c>
+      <c r="DX5" s="2" t="s">
+        <v>298</v>
+      </c>
+      <c r="DY5" s="2" t="s">
+        <v>416</v>
+      </c>
+      <c r="DZ5" s="2" t="s">
+        <v>299</v>
+      </c>
+      <c r="EA5" s="2" t="s">
+        <v>300</v>
+      </c>
+      <c r="EB5" s="2" t="s">
+        <v>326</v>
+      </c>
+      <c r="EC5" s="2" t="s">
+        <v>307</v>
+      </c>
+      <c r="ED5" s="2" t="s">
+        <v>284</v>
+      </c>
+      <c r="EE5" s="2" t="s">
+        <v>284</v>
+      </c>
+      <c r="EF5" s="2" t="s">
+        <v>293</v>
+      </c>
+      <c r="EG5" s="2" t="s">
+        <v>327</v>
+      </c>
+      <c r="EH5" s="2" t="s">
+        <v>294</v>
+      </c>
+      <c r="EI5" s="2" t="s">
+        <v>332</v>
+      </c>
+      <c r="EJ5" s="2" t="s">
+        <v>335</v>
+      </c>
+      <c r="EK5" s="2" t="s">
+        <v>342</v>
+      </c>
+      <c r="EL5" s="2" t="s">
+        <v>287</v>
+      </c>
+      <c r="EM5" s="2" t="s">
+        <v>417</v>
+      </c>
+      <c r="EN5" s="2" t="s">
+        <v>329</v>
+      </c>
+      <c r="EO5" s="2" t="s">
+        <v>266</v>
+      </c>
+      <c r="EP5" s="2" t="s">
         <v>337</v>
       </c>
-      <c r="AE5" s="2" t="s">
-        <v>400</v>
-      </c>
-      <c r="AF5" s="2" t="s">
-        <v>266</v>
-      </c>
-      <c r="AG5" s="2" t="s">
-        <v>320</v>
-      </c>
-      <c r="AH5" s="2" t="s">
-        <v>321</v>
-      </c>
-      <c r="AI5" s="2" t="s">
-        <v>401</v>
-      </c>
-      <c r="AJ5" s="2" t="s">
-        <v>266</v>
-      </c>
-      <c r="AK5" s="2" t="s">
-        <v>278</v>
-      </c>
-      <c r="AL5" s="2" t="s">
-        <v>278</v>
-      </c>
-      <c r="AM5" s="2" t="s">
-        <v>277</v>
-      </c>
-      <c r="AN5" s="2" t="s">
+      <c r="EQ5" s="2" t="s">
+        <v>289</v>
+      </c>
+      <c r="ER5" s="2" t="s">
+        <v>418</v>
+      </c>
+      <c r="ES5" s="2" t="s">
+        <v>283</v>
+      </c>
+      <c r="ET5" s="2" t="s">
+        <v>299</v>
+      </c>
+      <c r="EU5" s="2" t="s">
+        <v>299</v>
+      </c>
+      <c r="EV5" s="2" t="s">
+        <v>307</v>
+      </c>
+      <c r="EW5" s="2" t="s">
+        <v>284</v>
+      </c>
+      <c r="EX5" s="2" t="s">
+        <v>284</v>
+      </c>
+      <c r="EY5" s="2" t="s">
+        <v>285</v>
+      </c>
+      <c r="EZ5" s="2" t="s">
+        <v>293</v>
+      </c>
+      <c r="FA5" s="2" t="s">
+        <v>286</v>
+      </c>
+      <c r="FB5" s="2" t="s">
+        <v>332</v>
+      </c>
+      <c r="FC5" s="2" t="s">
+        <v>335</v>
+      </c>
+      <c r="FD5" s="2" t="s">
+        <v>335</v>
+      </c>
+      <c r="FE5" s="2" t="s">
+        <v>287</v>
+      </c>
+      <c r="FF5" s="2" t="s">
+        <v>419</v>
+      </c>
+      <c r="FG5" s="2" t="s">
+        <v>420</v>
+      </c>
+      <c r="FH5" s="2" t="s">
+        <v>266</v>
+      </c>
+      <c r="FI5" s="2" t="s">
+        <v>338</v>
+      </c>
+      <c r="FJ5" s="2" t="s">
+        <v>289</v>
+      </c>
+      <c r="FK5" s="2" t="s">
+        <v>421</v>
+      </c>
+      <c r="FL5" s="2" t="s">
+        <v>397</v>
+      </c>
+      <c r="FM5" s="2" t="s">
+        <v>314</v>
+      </c>
+      <c r="FN5" s="2" t="s">
+        <v>314</v>
+      </c>
+      <c r="FO5" s="2" t="s">
+        <v>313</v>
+      </c>
+      <c r="FP5" s="2" t="s">
+        <v>315</v>
+      </c>
+      <c r="FQ5" s="2" t="s">
         <v>318</v>
       </c>
-      <c r="AO5" s="2" t="s">
-        <v>323</v>
-      </c>
-      <c r="AP5" s="2" t="s">
-        <v>323</v>
-      </c>
-      <c r="AQ5" s="2" t="s">
-        <v>347</v>
-      </c>
-      <c r="AR5" s="2" t="s">
-        <v>402</v>
-      </c>
-      <c r="AS5" s="2" t="s">
-        <v>403</v>
-      </c>
-      <c r="AT5" s="2" t="s">
-        <v>281</v>
-      </c>
-      <c r="AU5" s="2" t="s">
-        <v>278</v>
-      </c>
-      <c r="AV5" s="2" t="s">
-        <v>404</v>
-      </c>
-      <c r="AW5" s="2" t="s">
-        <v>266</v>
-      </c>
-      <c r="AX5" s="2" t="s">
-        <v>351</v>
-      </c>
-      <c r="AY5" s="2" t="s">
-        <v>266</v>
-      </c>
-      <c r="AZ5" s="2" t="s">
-        <v>338</v>
-      </c>
-      <c r="BA5" s="2" t="s">
+      <c r="FR5" s="2" t="s">
+        <v>317</v>
+      </c>
+      <c r="FS5" s="2" t="s">
+        <v>317</v>
+      </c>
+      <c r="FT5" s="2" t="s">
+        <v>319</v>
+      </c>
+      <c r="FU5" s="2" t="s">
+        <v>325</v>
+      </c>
+      <c r="FV5" s="2" t="s">
+        <v>340</v>
+      </c>
+      <c r="FW5" s="2" t="s">
         <v>282</v>
       </c>
-      <c r="BB5" s="2" t="s">
-        <v>282</v>
-      </c>
-      <c r="BC5" s="2" t="s">
-        <v>298</v>
-      </c>
-      <c r="BD5" s="2" t="s">
-        <v>283</v>
-      </c>
-      <c r="BE5" s="2" t="s">
-        <v>283</v>
-      </c>
-      <c r="BF5" s="2" t="s">
-        <v>283</v>
-      </c>
-      <c r="BG5" s="2" t="s">
-        <v>284</v>
-      </c>
-      <c r="BH5" s="2" t="s">
-        <v>292</v>
-      </c>
-      <c r="BI5" s="2" t="s">
-        <v>285</v>
-      </c>
-      <c r="BJ5" s="2" t="s">
-        <v>330</v>
-      </c>
-      <c r="BK5" s="2" t="s">
-        <v>333</v>
-      </c>
-      <c r="BL5" s="2" t="s">
-        <v>333</v>
-      </c>
-      <c r="BM5" s="2" t="s">
-        <v>297</v>
-      </c>
-      <c r="BN5" s="2" t="s">
-        <v>405</v>
-      </c>
-      <c r="BO5" s="2" t="s">
-        <v>406</v>
-      </c>
-      <c r="BP5" s="2" t="s">
-        <v>266</v>
-      </c>
-      <c r="BQ5" s="2" t="s">
-        <v>309</v>
-      </c>
-      <c r="BR5" s="2" t="s">
-        <v>332</v>
-      </c>
-      <c r="BS5" s="2" t="s">
-        <v>407</v>
-      </c>
-      <c r="BT5" s="2" t="s">
-        <v>289</v>
-      </c>
-      <c r="BU5" s="2" t="s">
-        <v>304</v>
-      </c>
-      <c r="BV5" s="2" t="s">
-        <v>290</v>
-      </c>
-      <c r="BW5" s="2" t="s">
-        <v>306</v>
-      </c>
-      <c r="BX5" s="2" t="s">
-        <v>283</v>
-      </c>
-      <c r="BY5" s="2" t="s">
-        <v>283</v>
-      </c>
-      <c r="BZ5" s="2" t="s">
-        <v>325</v>
-      </c>
-      <c r="CA5" s="2" t="s">
-        <v>293</v>
-      </c>
-      <c r="CB5" s="2" t="s">
-        <v>307</v>
-      </c>
-      <c r="CC5" s="2" t="s">
-        <v>339</v>
-      </c>
-      <c r="CD5" s="2" t="s">
-        <v>339</v>
-      </c>
-      <c r="CE5" s="2" t="s">
-        <v>381</v>
-      </c>
-      <c r="CF5" s="2" t="s">
-        <v>294</v>
-      </c>
-      <c r="CG5" s="2" t="s">
-        <v>408</v>
-      </c>
-      <c r="CH5" s="2" t="s">
-        <v>295</v>
-      </c>
-      <c r="CI5" s="2" t="s">
-        <v>266</v>
-      </c>
-      <c r="CJ5" s="2" t="s">
-        <v>296</v>
-      </c>
-      <c r="CK5" s="2" t="s">
-        <v>297</v>
-      </c>
-      <c r="CL5" s="2" t="s">
-        <v>409</v>
-      </c>
-      <c r="CM5" s="2" t="s">
-        <v>282</v>
-      </c>
-      <c r="CN5" s="2" t="s">
-        <v>282</v>
-      </c>
-      <c r="CO5" s="2" t="s">
-        <v>282</v>
-      </c>
-      <c r="CP5" s="2" t="s">
-        <v>306</v>
-      </c>
-      <c r="CQ5" s="2" t="s">
-        <v>283</v>
-      </c>
-      <c r="CR5" s="2" t="s">
-        <v>283</v>
-      </c>
-      <c r="CS5" s="2" t="s">
-        <v>284</v>
-      </c>
-      <c r="CT5" s="2" t="s">
-        <v>285</v>
-      </c>
-      <c r="CU5" s="2" t="s">
-        <v>325</v>
-      </c>
-      <c r="CV5" s="2" t="s">
-        <v>330</v>
-      </c>
-      <c r="CW5" s="2" t="s">
-        <v>330</v>
-      </c>
-      <c r="CX5" s="2" t="s">
-        <v>333</v>
-      </c>
-      <c r="CY5" s="2" t="s">
-        <v>297</v>
-      </c>
-      <c r="CZ5" s="2" t="s">
-        <v>410</v>
-      </c>
-      <c r="DA5" s="2" t="s">
-        <v>411</v>
-      </c>
-      <c r="DB5" s="2" t="s">
-        <v>266</v>
-      </c>
-      <c r="DC5" s="2" t="s">
-        <v>309</v>
-      </c>
-      <c r="DD5" s="2" t="s">
-        <v>332</v>
-      </c>
-      <c r="DE5" s="2" t="s">
-        <v>412</v>
-      </c>
-      <c r="DF5" s="2" t="s">
-        <v>303</v>
-      </c>
-      <c r="DG5" s="2" t="s">
-        <v>298</v>
-      </c>
-      <c r="DH5" s="2" t="s">
-        <v>324</v>
-      </c>
-      <c r="DI5" s="2" t="s">
-        <v>289</v>
-      </c>
-      <c r="DJ5" s="2" t="s">
-        <v>306</v>
-      </c>
-      <c r="DK5" s="2" t="s">
-        <v>283</v>
-      </c>
-      <c r="DL5" s="2" t="s">
-        <v>283</v>
-      </c>
-      <c r="DM5" s="2" t="s">
-        <v>292</v>
-      </c>
-      <c r="DN5" s="2" t="s">
-        <v>325</v>
-      </c>
-      <c r="DO5" s="2" t="s">
-        <v>307</v>
-      </c>
-      <c r="DP5" s="2" t="s">
-        <v>330</v>
-      </c>
-      <c r="DQ5" s="2" t="s">
-        <v>333</v>
-      </c>
-      <c r="DR5" s="2" t="s">
-        <v>340</v>
-      </c>
-      <c r="DS5" s="2" t="s">
-        <v>286</v>
-      </c>
-      <c r="DT5" s="2" t="s">
-        <v>413</v>
-      </c>
-      <c r="DU5" s="2" t="s">
-        <v>391</v>
-      </c>
-      <c r="DV5" s="2" t="s">
-        <v>266</v>
-      </c>
-      <c r="DW5" s="2" t="s">
-        <v>308</v>
-      </c>
-      <c r="DX5" s="2" t="s">
-        <v>297</v>
-      </c>
-      <c r="DY5" s="2" t="s">
-        <v>414</v>
-      </c>
-      <c r="DZ5" s="2" t="s">
-        <v>298</v>
-      </c>
-      <c r="EA5" s="2" t="s">
-        <v>299</v>
-      </c>
-      <c r="EB5" s="2" t="s">
-        <v>324</v>
-      </c>
-      <c r="EC5" s="2" t="s">
-        <v>306</v>
-      </c>
-      <c r="ED5" s="2" t="s">
-        <v>283</v>
-      </c>
-      <c r="EE5" s="2" t="s">
-        <v>283</v>
-      </c>
-      <c r="EF5" s="2" t="s">
-        <v>292</v>
-      </c>
-      <c r="EG5" s="2" t="s">
-        <v>325</v>
-      </c>
-      <c r="EH5" s="2" t="s">
-        <v>293</v>
-      </c>
-      <c r="EI5" s="2" t="s">
-        <v>330</v>
-      </c>
-      <c r="EJ5" s="2" t="s">
-        <v>333</v>
-      </c>
-      <c r="EK5" s="2" t="s">
-        <v>340</v>
-      </c>
-      <c r="EL5" s="2" t="s">
-        <v>286</v>
-      </c>
-      <c r="EM5" s="2" t="s">
-        <v>415</v>
-      </c>
-      <c r="EN5" s="2" t="s">
-        <v>327</v>
-      </c>
-      <c r="EO5" s="2" t="s">
-        <v>266</v>
-      </c>
-      <c r="EP5" s="2" t="s">
-        <v>335</v>
-      </c>
-      <c r="EQ5" s="2" t="s">
-        <v>288</v>
-      </c>
-      <c r="ER5" s="2" t="s">
-        <v>416</v>
-      </c>
-      <c r="ES5" s="2" t="s">
-        <v>282</v>
-      </c>
-      <c r="ET5" s="2" t="s">
-        <v>298</v>
-      </c>
-      <c r="EU5" s="2" t="s">
-        <v>298</v>
-      </c>
-      <c r="EV5" s="2" t="s">
-        <v>306</v>
-      </c>
-      <c r="EW5" s="2" t="s">
-        <v>283</v>
-      </c>
-      <c r="EX5" s="2" t="s">
-        <v>283</v>
-      </c>
-      <c r="EY5" s="2" t="s">
-        <v>284</v>
-      </c>
-      <c r="EZ5" s="2" t="s">
-        <v>292</v>
-      </c>
-      <c r="FA5" s="2" t="s">
-        <v>285</v>
-      </c>
-      <c r="FB5" s="2" t="s">
-        <v>330</v>
-      </c>
-      <c r="FC5" s="2" t="s">
-        <v>333</v>
-      </c>
-      <c r="FD5" s="2" t="s">
-        <v>333</v>
-      </c>
-      <c r="FE5" s="2" t="s">
-        <v>286</v>
-      </c>
-      <c r="FF5" s="2" t="s">
-        <v>417</v>
-      </c>
-      <c r="FG5" s="2" t="s">
-        <v>418</v>
-      </c>
-      <c r="FH5" s="2" t="s">
-        <v>266</v>
-      </c>
-      <c r="FI5" s="2" t="s">
-        <v>336</v>
-      </c>
-      <c r="FJ5" s="2" t="s">
-        <v>288</v>
-      </c>
-      <c r="FK5" s="2" t="s">
-        <v>419</v>
-      </c>
-      <c r="FL5" s="2" t="s">
-        <v>395</v>
-      </c>
-      <c r="FM5" s="2" t="s">
-        <v>312</v>
-      </c>
-      <c r="FN5" s="2" t="s">
-        <v>312</v>
-      </c>
-      <c r="FO5" s="2" t="s">
-        <v>311</v>
-      </c>
-      <c r="FP5" s="2" t="s">
-        <v>313</v>
-      </c>
-      <c r="FQ5" s="2" t="s">
-        <v>316</v>
-      </c>
-      <c r="FR5" s="2" t="s">
-        <v>315</v>
-      </c>
-      <c r="FS5" s="2" t="s">
-        <v>315</v>
-      </c>
-      <c r="FT5" s="2" t="s">
-        <v>317</v>
-      </c>
-      <c r="FU5" s="2" t="s">
-        <v>323</v>
-      </c>
-      <c r="FV5" s="2" t="s">
-        <v>338</v>
-      </c>
-      <c r="FW5" s="2" t="s">
-        <v>281</v>
-      </c>
       <c r="FX5" s="2" t="s">
-        <v>420</v>
+        <v>422</v>
       </c>
       <c r="FY5" s="2" t="s">
         <v>266</v>
       </c>
       <c r="FZ5" s="2" t="s">
-        <v>421</v>
+        <v>423</v>
       </c>
     </row>
-    <row r="6" spans="1:182" ht="31.75" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="6" spans="1:182" ht="15" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A6" s="1">
         <v>46194.627511574072</v>
       </c>
@@ -4603,7 +4693,7 @@
         <v>185</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>422</v>
+        <v>424</v>
       </c>
       <c r="E6">
         <v>100</v>
@@ -4618,7 +4708,7 @@
         <v>46194.643903460645</v>
       </c>
       <c r="I6" s="2" t="s">
-        <v>423</v>
+        <v>425</v>
       </c>
       <c r="J6" s="2" t="s">
         <v>266</v>
@@ -4645,22 +4735,22 @@
         <v>268</v>
       </c>
       <c r="R6" s="2" t="s">
-        <v>328</v>
+        <v>330</v>
       </c>
       <c r="S6" s="2" t="s">
-        <v>424</v>
+        <v>426</v>
       </c>
       <c r="T6" s="2" t="s">
         <v>270</v>
       </c>
       <c r="U6" s="2" t="s">
-        <v>425</v>
+        <v>427</v>
       </c>
       <c r="V6">
         <v>25</v>
       </c>
       <c r="W6" s="2" t="s">
-        <v>319</v>
+        <v>321</v>
       </c>
       <c r="X6" s="2" t="s">
         <v>273</v>
@@ -4678,473 +4768,1023 @@
         <v>266</v>
       </c>
       <c r="AC6" s="2" t="s">
-        <v>426</v>
+        <v>428</v>
       </c>
       <c r="AD6" s="2" t="s">
-        <v>337</v>
+        <v>339</v>
       </c>
       <c r="AE6" s="2" t="s">
+        <v>429</v>
+      </c>
+      <c r="AF6" s="2" t="s">
+        <v>266</v>
+      </c>
+      <c r="AG6" s="2" t="s">
+        <v>374</v>
+      </c>
+      <c r="AH6" s="2" t="s">
+        <v>375</v>
+      </c>
+      <c r="AI6" s="2" t="s">
+        <v>430</v>
+      </c>
+      <c r="AJ6" s="2" t="s">
+        <v>431</v>
+      </c>
+      <c r="AK6" s="2" t="s">
+        <v>279</v>
+      </c>
+      <c r="AL6" s="2" t="s">
+        <v>279</v>
+      </c>
+      <c r="AM6" s="2" t="s">
+        <v>281</v>
+      </c>
+      <c r="AN6" s="2" t="s">
+        <v>320</v>
+      </c>
+      <c r="AO6" s="2" t="s">
+        <v>340</v>
+      </c>
+      <c r="AP6" s="2" t="s">
+        <v>325</v>
+      </c>
+      <c r="AQ6" s="2" t="s">
+        <v>432</v>
+      </c>
+      <c r="AR6" s="2" t="s">
+        <v>433</v>
+      </c>
+      <c r="AS6" s="2" t="s">
+        <v>434</v>
+      </c>
+      <c r="AT6" s="2" t="s">
+        <v>320</v>
+      </c>
+      <c r="AU6" s="2" t="s">
+        <v>304</v>
+      </c>
+      <c r="AV6" s="2" t="s">
+        <v>435</v>
+      </c>
+      <c r="AW6" s="2" t="s">
+        <v>266</v>
+      </c>
+      <c r="AX6" s="2" t="s">
+        <v>353</v>
+      </c>
+      <c r="AY6" s="2" t="s">
+        <v>266</v>
+      </c>
+      <c r="AZ6" s="2" t="s">
+        <v>280</v>
+      </c>
+      <c r="BA6" s="2" t="s">
+        <v>300</v>
+      </c>
+      <c r="BB6" s="2" t="s">
+        <v>291</v>
+      </c>
+      <c r="BC6" s="2" t="s">
+        <v>291</v>
+      </c>
+      <c r="BD6" s="2" t="s">
+        <v>284</v>
+      </c>
+      <c r="BE6" s="2" t="s">
+        <v>284</v>
+      </c>
+      <c r="BF6" s="2" t="s">
+        <v>284</v>
+      </c>
+      <c r="BG6" s="2" t="s">
+        <v>286</v>
+      </c>
+      <c r="BH6" s="2" t="s">
+        <v>308</v>
+      </c>
+      <c r="BI6" s="2" t="s">
+        <v>308</v>
+      </c>
+      <c r="BJ6" s="2" t="s">
+        <v>332</v>
+      </c>
+      <c r="BK6" s="2" t="s">
+        <v>332</v>
+      </c>
+      <c r="BL6" s="2" t="s">
+        <v>332</v>
+      </c>
+      <c r="BM6" s="2" t="s">
+        <v>295</v>
+      </c>
+      <c r="BN6" s="2" t="s">
+        <v>436</v>
+      </c>
+      <c r="BO6" s="2" t="s">
+        <v>288</v>
+      </c>
+      <c r="BP6" s="2" t="s">
+        <v>266</v>
+      </c>
+      <c r="BQ6" s="2" t="s">
+        <v>333</v>
+      </c>
+      <c r="BR6" s="2" t="s">
+        <v>287</v>
+      </c>
+      <c r="BS6" s="2" t="s">
+        <v>437</v>
+      </c>
+      <c r="BT6" s="2" t="s">
+        <v>291</v>
+      </c>
+      <c r="BU6" s="2" t="s">
+        <v>291</v>
+      </c>
+      <c r="BV6" s="2" t="s">
+        <v>291</v>
+      </c>
+      <c r="BW6" s="2" t="s">
+        <v>284</v>
+      </c>
+      <c r="BX6" s="2" t="s">
+        <v>284</v>
+      </c>
+      <c r="BY6" s="2" t="s">
+        <v>284</v>
+      </c>
+      <c r="BZ6" s="2" t="s">
+        <v>308</v>
+      </c>
+      <c r="CA6" s="2" t="s">
+        <v>308</v>
+      </c>
+      <c r="CB6" s="2" t="s">
+        <v>308</v>
+      </c>
+      <c r="CC6" s="2" t="s">
+        <v>357</v>
+      </c>
+      <c r="CD6" s="2" t="s">
+        <v>357</v>
+      </c>
+      <c r="CE6" s="2" t="s">
+        <v>357</v>
+      </c>
+      <c r="CF6" s="2" t="s">
+        <v>295</v>
+      </c>
+      <c r="CG6" s="2" t="s">
+        <v>438</v>
+      </c>
+      <c r="CH6" s="2" t="s">
+        <v>296</v>
+      </c>
+      <c r="CI6" s="2" t="s">
+        <v>266</v>
+      </c>
+      <c r="CJ6" s="2" t="s">
+        <v>297</v>
+      </c>
+      <c r="CK6" s="2" t="s">
+        <v>287</v>
+      </c>
+      <c r="CL6" s="2" t="s">
+        <v>439</v>
+      </c>
+      <c r="CM6" s="2" t="s">
+        <v>299</v>
+      </c>
+      <c r="CN6" s="2" t="s">
+        <v>326</v>
+      </c>
+      <c r="CO6" s="2" t="s">
+        <v>326</v>
+      </c>
+      <c r="CP6" s="2" t="s">
+        <v>284</v>
+      </c>
+      <c r="CQ6" s="2" t="s">
+        <v>284</v>
+      </c>
+      <c r="CR6" s="2" t="s">
+        <v>284</v>
+      </c>
+      <c r="CS6" s="2" t="s">
+        <v>286</v>
+      </c>
+      <c r="CT6" s="2" t="s">
+        <v>308</v>
+      </c>
+      <c r="CU6" s="2" t="s">
+        <v>308</v>
+      </c>
+      <c r="CV6" s="2" t="s">
+        <v>332</v>
+      </c>
+      <c r="CW6" s="2" t="s">
+        <v>332</v>
+      </c>
+      <c r="CX6" s="2" t="s">
+        <v>332</v>
+      </c>
+      <c r="CY6" s="2" t="s">
+        <v>287</v>
+      </c>
+      <c r="CZ6" s="2" t="s">
+        <v>440</v>
+      </c>
+      <c r="DA6" s="2" t="s">
+        <v>328</v>
+      </c>
+      <c r="DB6" s="2" t="s">
+        <v>266</v>
+      </c>
+      <c r="DC6" s="2" t="s">
+        <v>303</v>
+      </c>
+      <c r="DD6" s="2" t="s">
+        <v>287</v>
+      </c>
+      <c r="DE6" s="2" t="s">
+        <v>441</v>
+      </c>
+      <c r="DF6" s="2" t="s">
+        <v>304</v>
+      </c>
+      <c r="DG6" s="2" t="s">
+        <v>290</v>
+      </c>
+      <c r="DH6" s="2" t="s">
+        <v>291</v>
+      </c>
+      <c r="DI6" s="2" t="s">
+        <v>291</v>
+      </c>
+      <c r="DJ6" s="2" t="s">
+        <v>284</v>
+      </c>
+      <c r="DK6" s="2" t="s">
+        <v>284</v>
+      </c>
+      <c r="DL6" s="2" t="s">
+        <v>284</v>
+      </c>
+      <c r="DM6" s="2" t="s">
+        <v>293</v>
+      </c>
+      <c r="DN6" s="2" t="s">
+        <v>308</v>
+      </c>
+      <c r="DO6" s="2" t="s">
+        <v>308</v>
+      </c>
+      <c r="DP6" s="2" t="s">
+        <v>341</v>
+      </c>
+      <c r="DQ6" s="2" t="s">
+        <v>357</v>
+      </c>
+      <c r="DR6" s="2" t="s">
+        <v>357</v>
+      </c>
+      <c r="DS6" s="2" t="s">
+        <v>295</v>
+      </c>
+      <c r="DT6" s="2" t="s">
+        <v>442</v>
+      </c>
+      <c r="DU6" s="2" t="s">
+        <v>443</v>
+      </c>
+      <c r="DV6" s="2" t="s">
+        <v>266</v>
+      </c>
+      <c r="DW6" s="2" t="s">
+        <v>311</v>
+      </c>
+      <c r="DX6" s="2" t="s">
+        <v>334</v>
+      </c>
+      <c r="DY6" s="2" t="s">
+        <v>444</v>
+      </c>
+      <c r="DZ6" s="2" t="s">
+        <v>300</v>
+      </c>
+      <c r="EA6" s="2" t="s">
+        <v>291</v>
+      </c>
+      <c r="EB6" s="2" t="s">
+        <v>291</v>
+      </c>
+      <c r="EC6" s="2" t="s">
+        <v>292</v>
+      </c>
+      <c r="ED6" s="2" t="s">
+        <v>284</v>
+      </c>
+      <c r="EE6" s="2" t="s">
+        <v>284</v>
+      </c>
+      <c r="EF6" s="2" t="s">
+        <v>293</v>
+      </c>
+      <c r="EG6" s="2" t="s">
+        <v>308</v>
+      </c>
+      <c r="EH6" s="2" t="s">
+        <v>308</v>
+      </c>
+      <c r="EI6" s="2" t="s">
+        <v>332</v>
+      </c>
+      <c r="EJ6" s="2" t="s">
+        <v>357</v>
+      </c>
+      <c r="EK6" s="2" t="s">
+        <v>357</v>
+      </c>
+      <c r="EL6" s="2" t="s">
+        <v>287</v>
+      </c>
+      <c r="EM6" s="2" t="s">
+        <v>445</v>
+      </c>
+      <c r="EN6" s="2" t="s">
+        <v>446</v>
+      </c>
+      <c r="EO6" s="2" t="s">
+        <v>266</v>
+      </c>
+      <c r="EP6" s="2" t="s">
+        <v>447</v>
+      </c>
+      <c r="EQ6" s="2" t="s">
+        <v>287</v>
+      </c>
+      <c r="ER6" s="2" t="s">
+        <v>448</v>
+      </c>
+      <c r="ES6" s="2" t="s">
+        <v>283</v>
+      </c>
+      <c r="ET6" s="2" t="s">
+        <v>300</v>
+      </c>
+      <c r="EU6" s="2" t="s">
+        <v>300</v>
+      </c>
+      <c r="EV6" s="2" t="s">
+        <v>284</v>
+      </c>
+      <c r="EW6" s="2" t="s">
+        <v>284</v>
+      </c>
+      <c r="EX6" s="2" t="s">
+        <v>284</v>
+      </c>
+      <c r="EY6" s="2" t="s">
+        <v>285</v>
+      </c>
+      <c r="EZ6" s="2" t="s">
+        <v>308</v>
+      </c>
+      <c r="FA6" s="2" t="s">
+        <v>308</v>
+      </c>
+      <c r="FB6" s="2" t="s">
+        <v>332</v>
+      </c>
+      <c r="FC6" s="2" t="s">
+        <v>342</v>
+      </c>
+      <c r="FD6" s="2" t="s">
+        <v>342</v>
+      </c>
+      <c r="FE6" s="2" t="s">
+        <v>287</v>
+      </c>
+      <c r="FF6" s="2" t="s">
+        <v>449</v>
+      </c>
+      <c r="FG6" s="2" t="s">
+        <v>450</v>
+      </c>
+      <c r="FH6" s="2" t="s">
+        <v>266</v>
+      </c>
+      <c r="FI6" s="2" t="s">
+        <v>311</v>
+      </c>
+      <c r="FJ6" s="2" t="s">
+        <v>287</v>
+      </c>
+      <c r="FK6" s="2" t="s">
+        <v>451</v>
+      </c>
+      <c r="FL6" s="2" t="s">
+        <v>397</v>
+      </c>
+      <c r="FM6" s="2" t="s">
+        <v>314</v>
+      </c>
+      <c r="FN6" s="2" t="s">
+        <v>313</v>
+      </c>
+      <c r="FO6" s="2" t="s">
+        <v>313</v>
+      </c>
+      <c r="FP6" s="2" t="s">
+        <v>314</v>
+      </c>
+      <c r="FQ6" s="2" t="s">
+        <v>317</v>
+      </c>
+      <c r="FR6" s="2" t="s">
+        <v>318</v>
+      </c>
+      <c r="FS6" s="2" t="s">
+        <v>318</v>
+      </c>
+      <c r="FT6" s="2" t="s">
+        <v>319</v>
+      </c>
+      <c r="FU6" s="2" t="s">
+        <v>304</v>
+      </c>
+      <c r="FV6" s="2" t="s">
+        <v>282</v>
+      </c>
+      <c r="FW6" s="2" t="s">
+        <v>304</v>
+      </c>
+      <c r="FX6" s="2" t="s">
+        <v>452</v>
+      </c>
+      <c r="FY6" s="2" t="s">
+        <v>453</v>
+      </c>
+      <c r="FZ6" s="2" t="s">
+        <v>454</v>
+      </c>
+    </row>
+    <row r="7" spans="1:182" ht="15" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A7" s="1">
+        <v>46194.941365740742</v>
+      </c>
+      <c r="B7" s="1">
+        <v>46194.964085648149</v>
+      </c>
+      <c r="C7" s="2" t="s">
+        <v>185</v>
+      </c>
+      <c r="D7" s="2" t="s">
+        <v>455</v>
+      </c>
+      <c r="E7">
+        <v>100</v>
+      </c>
+      <c r="F7">
+        <v>1963</v>
+      </c>
+      <c r="G7" s="2" t="s">
+        <v>265</v>
+      </c>
+      <c r="H7" s="1">
+        <v>46194.964096006945</v>
+      </c>
+      <c r="I7" s="2" t="s">
+        <v>456</v>
+      </c>
+      <c r="J7" s="2" t="s">
+        <v>266</v>
+      </c>
+      <c r="K7" s="2" t="s">
+        <v>266</v>
+      </c>
+      <c r="L7" s="2" t="s">
+        <v>266</v>
+      </c>
+      <c r="M7" s="2" t="s">
+        <v>266</v>
+      </c>
+      <c r="N7">
+        <v>52.473199999999999</v>
+      </c>
+      <c r="O7">
+        <v>13.3147</v>
+      </c>
+      <c r="P7" s="2" t="s">
+        <v>267</v>
+      </c>
+      <c r="Q7" s="2" t="s">
+        <v>268</v>
+      </c>
+      <c r="R7" s="2" t="s">
+        <v>330</v>
+      </c>
+      <c r="S7" s="2" t="s">
+        <v>269</v>
+      </c>
+      <c r="T7" s="2" t="s">
+        <v>270</v>
+      </c>
+      <c r="U7" s="2" t="s">
         <v>427</v>
       </c>
-      <c r="AF6" s="2" t="s">
-        <v>266</v>
-      </c>
-      <c r="AG6" s="2" t="s">
-        <v>372</v>
-      </c>
-      <c r="AH6" s="2" t="s">
-        <v>373</v>
-      </c>
-      <c r="AI6" s="2" t="s">
-        <v>428</v>
-      </c>
-      <c r="AJ6" s="2" t="s">
-        <v>429</v>
-      </c>
-      <c r="AK6" s="2" t="s">
+      <c r="V7">
+        <v>93</v>
+      </c>
+      <c r="W7" s="2" t="s">
+        <v>457</v>
+      </c>
+      <c r="X7" s="2" t="s">
+        <v>458</v>
+      </c>
+      <c r="Y7" s="2" t="s">
+        <v>459</v>
+      </c>
+      <c r="Z7" s="2" t="s">
+        <v>275</v>
+      </c>
+      <c r="AA7" s="2" t="s">
+        <v>276</v>
+      </c>
+      <c r="AB7" s="2" t="s">
+        <v>266</v>
+      </c>
+      <c r="AC7" s="2" t="s">
+        <v>460</v>
+      </c>
+      <c r="AD7" s="2" t="s">
+        <v>461</v>
+      </c>
+      <c r="AE7" s="2" t="s">
+        <v>462</v>
+      </c>
+      <c r="AF7" s="2" t="s">
+        <v>266</v>
+      </c>
+      <c r="AG7" s="2" t="s">
+        <v>277</v>
+      </c>
+      <c r="AH7" s="2" t="s">
+        <v>323</v>
+      </c>
+      <c r="AI7" s="2" t="s">
+        <v>463</v>
+      </c>
+      <c r="AJ7" s="2" t="s">
+        <v>266</v>
+      </c>
+      <c r="AK7" s="2" t="s">
+        <v>280</v>
+      </c>
+      <c r="AL7" s="2" t="s">
+        <v>280</v>
+      </c>
+      <c r="AM7" s="2" t="s">
         <v>278</v>
       </c>
-      <c r="AL6" s="2" t="s">
-        <v>278</v>
-      </c>
-      <c r="AM6" s="2" t="s">
+      <c r="AN7" s="2" t="s">
         <v>280</v>
       </c>
-      <c r="AN6" s="2" t="s">
-        <v>318</v>
-      </c>
-      <c r="AO6" s="2" t="s">
-        <v>338</v>
-      </c>
-      <c r="AP6" s="2" t="s">
-        <v>323</v>
-      </c>
-      <c r="AQ6" s="2" t="s">
-        <v>430</v>
-      </c>
-      <c r="AR6" s="2" t="s">
-        <v>431</v>
-      </c>
-      <c r="AS6" s="2" t="s">
+      <c r="AO7" s="2" t="s">
+        <v>280</v>
+      </c>
+      <c r="AP7" s="2" t="s">
+        <v>280</v>
+      </c>
+      <c r="AQ7" s="2" t="s">
         <v>432</v>
       </c>
-      <c r="AT6" s="2" t="s">
-        <v>318</v>
-      </c>
-      <c r="AU6" s="2" t="s">
-        <v>303</v>
-      </c>
-      <c r="AV6" s="2" t="s">
-        <v>433</v>
-      </c>
-      <c r="AW6" s="2" t="s">
-        <v>266</v>
-      </c>
-      <c r="AX6" s="2" t="s">
-        <v>351</v>
-      </c>
-      <c r="AY6" s="2" t="s">
-        <v>266</v>
-      </c>
-      <c r="AZ6" s="2" t="s">
-        <v>279</v>
-      </c>
-      <c r="BA6" s="2" t="s">
-        <v>299</v>
-      </c>
-      <c r="BB6" s="2" t="s">
-        <v>290</v>
-      </c>
-      <c r="BC6" s="2" t="s">
-        <v>290</v>
-      </c>
-      <c r="BD6" s="2" t="s">
-        <v>283</v>
-      </c>
-      <c r="BE6" s="2" t="s">
-        <v>283</v>
-      </c>
-      <c r="BF6" s="2" t="s">
-        <v>283</v>
-      </c>
-      <c r="BG6" s="2" t="s">
-        <v>285</v>
-      </c>
-      <c r="BH6" s="2" t="s">
-        <v>307</v>
-      </c>
-      <c r="BI6" s="2" t="s">
-        <v>307</v>
-      </c>
-      <c r="BJ6" s="2" t="s">
-        <v>330</v>
-      </c>
-      <c r="BK6" s="2" t="s">
-        <v>330</v>
-      </c>
-      <c r="BL6" s="2" t="s">
-        <v>330</v>
-      </c>
-      <c r="BM6" s="2" t="s">
-        <v>294</v>
-      </c>
-      <c r="BN6" s="2" t="s">
-        <v>434</v>
-      </c>
-      <c r="BO6" s="2" t="s">
+      <c r="AR7" s="2" t="s">
+        <v>464</v>
+      </c>
+      <c r="AS7" s="2" t="s">
+        <v>465</v>
+      </c>
+      <c r="AT7" s="2" t="s">
+        <v>280</v>
+      </c>
+      <c r="AU7" s="2" t="s">
+        <v>280</v>
+      </c>
+      <c r="AV7" s="2" t="s">
+        <v>466</v>
+      </c>
+      <c r="AW7" s="2" t="s">
+        <v>266</v>
+      </c>
+      <c r="AX7" s="2" t="s">
+        <v>380</v>
+      </c>
+      <c r="AY7" s="2" t="s">
+        <v>266</v>
+      </c>
+      <c r="AZ7" s="2" t="s">
+        <v>280</v>
+      </c>
+      <c r="BA7" s="2" t="s">
+        <v>291</v>
+      </c>
+      <c r="BB7" s="2" t="s">
+        <v>291</v>
+      </c>
+      <c r="BC7" s="2" t="s">
+        <v>291</v>
+      </c>
+      <c r="BD7" s="2" t="s">
+        <v>284</v>
+      </c>
+      <c r="BE7" s="2" t="s">
+        <v>284</v>
+      </c>
+      <c r="BF7" s="2" t="s">
+        <v>284</v>
+      </c>
+      <c r="BG7" s="2" t="s">
+        <v>308</v>
+      </c>
+      <c r="BH7" s="2" t="s">
+        <v>308</v>
+      </c>
+      <c r="BI7" s="2" t="s">
+        <v>308</v>
+      </c>
+      <c r="BJ7" s="2" t="s">
+        <v>332</v>
+      </c>
+      <c r="BK7" s="2" t="s">
+        <v>332</v>
+      </c>
+      <c r="BL7" s="2" t="s">
+        <v>332</v>
+      </c>
+      <c r="BM7" s="2" t="s">
+        <v>295</v>
+      </c>
+      <c r="BN7" s="2" t="s">
+        <v>467</v>
+      </c>
+      <c r="BO7" s="2" t="s">
+        <v>288</v>
+      </c>
+      <c r="BP7" s="2" t="s">
+        <v>266</v>
+      </c>
+      <c r="BQ7" s="2" t="s">
+        <v>311</v>
+      </c>
+      <c r="BR7" s="2" t="s">
+        <v>334</v>
+      </c>
+      <c r="BS7" s="2" t="s">
+        <v>468</v>
+      </c>
+      <c r="BT7" s="2" t="s">
+        <v>291</v>
+      </c>
+      <c r="BU7" s="2" t="s">
+        <v>291</v>
+      </c>
+      <c r="BV7" s="2" t="s">
+        <v>291</v>
+      </c>
+      <c r="BW7" s="2" t="s">
+        <v>310</v>
+      </c>
+      <c r="BX7" s="2" t="s">
+        <v>310</v>
+      </c>
+      <c r="BY7" s="2" t="s">
+        <v>310</v>
+      </c>
+      <c r="BZ7" s="2" t="s">
+        <v>308</v>
+      </c>
+      <c r="CA7" s="2" t="s">
+        <v>308</v>
+      </c>
+      <c r="CB7" s="2" t="s">
+        <v>308</v>
+      </c>
+      <c r="CC7" s="2" t="s">
+        <v>357</v>
+      </c>
+      <c r="CD7" s="2" t="s">
+        <v>357</v>
+      </c>
+      <c r="CE7" s="2" t="s">
+        <v>357</v>
+      </c>
+      <c r="CF7" s="2" t="s">
+        <v>295</v>
+      </c>
+      <c r="CG7" s="2" t="s">
+        <v>469</v>
+      </c>
+      <c r="CH7" s="2" t="s">
+        <v>336</v>
+      </c>
+      <c r="CI7" s="2" t="s">
+        <v>266</v>
+      </c>
+      <c r="CJ7" s="2" t="s">
+        <v>297</v>
+      </c>
+      <c r="CK7" s="2" t="s">
+        <v>298</v>
+      </c>
+      <c r="CL7" s="2" t="s">
+        <v>470</v>
+      </c>
+      <c r="CM7" s="2" t="s">
+        <v>291</v>
+      </c>
+      <c r="CN7" s="2" t="s">
+        <v>291</v>
+      </c>
+      <c r="CO7" s="2" t="s">
+        <v>291</v>
+      </c>
+      <c r="CP7" s="2" t="s">
+        <v>310</v>
+      </c>
+      <c r="CQ7" s="2" t="s">
+        <v>310</v>
+      </c>
+      <c r="CR7" s="2" t="s">
+        <v>310</v>
+      </c>
+      <c r="CS7" s="2" t="s">
+        <v>308</v>
+      </c>
+      <c r="CT7" s="2" t="s">
+        <v>308</v>
+      </c>
+      <c r="CU7" s="2" t="s">
+        <v>308</v>
+      </c>
+      <c r="CV7" s="2" t="s">
+        <v>357</v>
+      </c>
+      <c r="CW7" s="2" t="s">
+        <v>357</v>
+      </c>
+      <c r="CX7" s="2" t="s">
+        <v>357</v>
+      </c>
+      <c r="CY7" s="2" t="s">
+        <v>295</v>
+      </c>
+      <c r="CZ7" s="2" t="s">
+        <v>471</v>
+      </c>
+      <c r="DA7" s="2" t="s">
+        <v>472</v>
+      </c>
+      <c r="DB7" s="2" t="s">
+        <v>266</v>
+      </c>
+      <c r="DC7" s="2" t="s">
+        <v>473</v>
+      </c>
+      <c r="DD7" s="2" t="s">
         <v>287</v>
       </c>
-      <c r="BP6" s="2" t="s">
-        <v>266</v>
-      </c>
-      <c r="BQ6" s="2" t="s">
-        <v>331</v>
-      </c>
-      <c r="BR6" s="2" t="s">
-        <v>286</v>
-      </c>
-      <c r="BS6" s="2" t="s">
-        <v>435</v>
-      </c>
-      <c r="BT6" s="2" t="s">
-        <v>290</v>
-      </c>
-      <c r="BU6" s="2" t="s">
-        <v>290</v>
-      </c>
-      <c r="BV6" s="2" t="s">
-        <v>290</v>
-      </c>
-      <c r="BW6" s="2" t="s">
-        <v>283</v>
-      </c>
-      <c r="BX6" s="2" t="s">
-        <v>283</v>
-      </c>
-      <c r="BY6" s="2" t="s">
-        <v>283</v>
-      </c>
-      <c r="BZ6" s="2" t="s">
-        <v>307</v>
-      </c>
-      <c r="CA6" s="2" t="s">
-        <v>307</v>
-      </c>
-      <c r="CB6" s="2" t="s">
-        <v>307</v>
-      </c>
-      <c r="CC6" s="2" t="s">
+      <c r="DE7" s="2" t="s">
+        <v>474</v>
+      </c>
+      <c r="DF7" s="2" t="s">
+        <v>304</v>
+      </c>
+      <c r="DG7" s="2" t="s">
+        <v>291</v>
+      </c>
+      <c r="DH7" s="2" t="s">
+        <v>291</v>
+      </c>
+      <c r="DI7" s="2" t="s">
+        <v>291</v>
+      </c>
+      <c r="DJ7" s="2" t="s">
+        <v>310</v>
+      </c>
+      <c r="DK7" s="2" t="s">
+        <v>310</v>
+      </c>
+      <c r="DL7" s="2" t="s">
+        <v>310</v>
+      </c>
+      <c r="DM7" s="2" t="s">
+        <v>308</v>
+      </c>
+      <c r="DN7" s="2" t="s">
+        <v>308</v>
+      </c>
+      <c r="DO7" s="2" t="s">
+        <v>308</v>
+      </c>
+      <c r="DP7" s="2" t="s">
+        <v>357</v>
+      </c>
+      <c r="DQ7" s="2" t="s">
+        <v>357</v>
+      </c>
+      <c r="DR7" s="2" t="s">
+        <v>357</v>
+      </c>
+      <c r="DS7" s="2" t="s">
+        <v>295</v>
+      </c>
+      <c r="DT7" s="2" t="s">
+        <v>475</v>
+      </c>
+      <c r="DU7" s="2" t="s">
         <v>355</v>
       </c>
-      <c r="CD6" s="2" t="s">
-        <v>355</v>
-      </c>
-      <c r="CE6" s="2" t="s">
-        <v>355</v>
-      </c>
-      <c r="CF6" s="2" t="s">
-        <v>294</v>
-      </c>
-      <c r="CG6" s="2" t="s">
-        <v>436</v>
-      </c>
-      <c r="CH6" s="2" t="s">
+      <c r="DV7" s="2" t="s">
+        <v>266</v>
+      </c>
+      <c r="DW7" s="2" t="s">
+        <v>363</v>
+      </c>
+      <c r="DX7" s="2" t="s">
+        <v>289</v>
+      </c>
+      <c r="DY7" s="2" t="s">
+        <v>476</v>
+      </c>
+      <c r="DZ7" s="2" t="s">
+        <v>291</v>
+      </c>
+      <c r="EA7" s="2" t="s">
+        <v>291</v>
+      </c>
+      <c r="EB7" s="2" t="s">
+        <v>291</v>
+      </c>
+      <c r="EC7" s="2" t="s">
+        <v>310</v>
+      </c>
+      <c r="ED7" s="2" t="s">
+        <v>310</v>
+      </c>
+      <c r="EE7" s="2" t="s">
+        <v>310</v>
+      </c>
+      <c r="EF7" s="2" t="s">
+        <v>308</v>
+      </c>
+      <c r="EG7" s="2" t="s">
+        <v>308</v>
+      </c>
+      <c r="EH7" s="2" t="s">
+        <v>308</v>
+      </c>
+      <c r="EI7" s="2" t="s">
+        <v>357</v>
+      </c>
+      <c r="EJ7" s="2" t="s">
+        <v>357</v>
+      </c>
+      <c r="EK7" s="2" t="s">
+        <v>357</v>
+      </c>
+      <c r="EL7" s="2" t="s">
         <v>295</v>
       </c>
-      <c r="CI6" s="2" t="s">
-        <v>266</v>
-      </c>
-      <c r="CJ6" s="2" t="s">
-        <v>296</v>
-      </c>
-      <c r="CK6" s="2" t="s">
-        <v>286</v>
-      </c>
-      <c r="CL6" s="2" t="s">
-        <v>437</v>
-      </c>
-      <c r="CM6" s="2" t="s">
+      <c r="EM7" s="2" t="s">
+        <v>477</v>
+      </c>
+      <c r="EN7" s="2" t="s">
+        <v>288</v>
+      </c>
+      <c r="EO7" s="2" t="s">
+        <v>266</v>
+      </c>
+      <c r="EP7" s="2" t="s">
+        <v>447</v>
+      </c>
+      <c r="EQ7" s="2" t="s">
         <v>298</v>
       </c>
-      <c r="CN6" s="2" t="s">
-        <v>324</v>
-      </c>
-      <c r="CO6" s="2" t="s">
-        <v>324</v>
-      </c>
-      <c r="CP6" s="2" t="s">
-        <v>283</v>
-      </c>
-      <c r="CQ6" s="2" t="s">
-        <v>283</v>
-      </c>
-      <c r="CR6" s="2" t="s">
-        <v>283</v>
-      </c>
-      <c r="CS6" s="2" t="s">
-        <v>285</v>
-      </c>
-      <c r="CT6" s="2" t="s">
-        <v>307</v>
-      </c>
-      <c r="CU6" s="2" t="s">
-        <v>307</v>
-      </c>
-      <c r="CV6" s="2" t="s">
-        <v>330</v>
-      </c>
-      <c r="CW6" s="2" t="s">
-        <v>330</v>
-      </c>
-      <c r="CX6" s="2" t="s">
-        <v>330</v>
-      </c>
-      <c r="CY6" s="2" t="s">
-        <v>286</v>
-      </c>
-      <c r="CZ6" s="2" t="s">
-        <v>438</v>
-      </c>
-      <c r="DA6" s="2" t="s">
-        <v>326</v>
-      </c>
-      <c r="DB6" s="2" t="s">
-        <v>266</v>
-      </c>
-      <c r="DC6" s="2" t="s">
-        <v>302</v>
-      </c>
-      <c r="DD6" s="2" t="s">
-        <v>286</v>
-      </c>
-      <c r="DE6" s="2" t="s">
-        <v>439</v>
-      </c>
-      <c r="DF6" s="2" t="s">
-        <v>303</v>
-      </c>
-      <c r="DG6" s="2" t="s">
-        <v>289</v>
-      </c>
-      <c r="DH6" s="2" t="s">
-        <v>290</v>
-      </c>
-      <c r="DI6" s="2" t="s">
-        <v>290</v>
-      </c>
-      <c r="DJ6" s="2" t="s">
-        <v>283</v>
-      </c>
-      <c r="DK6" s="2" t="s">
-        <v>283</v>
-      </c>
-      <c r="DL6" s="2" t="s">
-        <v>283</v>
-      </c>
-      <c r="DM6" s="2" t="s">
-        <v>292</v>
-      </c>
-      <c r="DN6" s="2" t="s">
-        <v>307</v>
-      </c>
-      <c r="DO6" s="2" t="s">
-        <v>307</v>
-      </c>
-      <c r="DP6" s="2" t="s">
-        <v>339</v>
-      </c>
-      <c r="DQ6" s="2" t="s">
-        <v>355</v>
-      </c>
-      <c r="DR6" s="2" t="s">
-        <v>355</v>
-      </c>
-      <c r="DS6" s="2" t="s">
-        <v>294</v>
-      </c>
-      <c r="DT6" s="2" t="s">
-        <v>440</v>
-      </c>
-      <c r="DU6" s="2" t="s">
-        <v>441</v>
-      </c>
-      <c r="DV6" s="2" t="s">
-        <v>266</v>
-      </c>
-      <c r="DW6" s="2" t="s">
-        <v>309</v>
-      </c>
-      <c r="DX6" s="2" t="s">
-        <v>332</v>
-      </c>
-      <c r="DY6" s="2" t="s">
-        <v>442</v>
-      </c>
-      <c r="DZ6" s="2" t="s">
-        <v>299</v>
-      </c>
-      <c r="EA6" s="2" t="s">
-        <v>290</v>
-      </c>
-      <c r="EB6" s="2" t="s">
-        <v>290</v>
-      </c>
-      <c r="EC6" s="2" t="s">
+      <c r="ER7" s="2" t="s">
+        <v>478</v>
+      </c>
+      <c r="ES7" s="2" t="s">
         <v>291</v>
       </c>
-      <c r="ED6" s="2" t="s">
-        <v>283</v>
-      </c>
-      <c r="EE6" s="2" t="s">
-        <v>283</v>
-      </c>
-      <c r="EF6" s="2" t="s">
-        <v>292</v>
-      </c>
-      <c r="EG6" s="2" t="s">
-        <v>307</v>
-      </c>
-      <c r="EH6" s="2" t="s">
-        <v>307</v>
-      </c>
-      <c r="EI6" s="2" t="s">
-        <v>330</v>
-      </c>
-      <c r="EJ6" s="2" t="s">
-        <v>355</v>
-      </c>
-      <c r="EK6" s="2" t="s">
-        <v>355</v>
-      </c>
-      <c r="EL6" s="2" t="s">
-        <v>286</v>
-      </c>
-      <c r="EM6" s="2" t="s">
+      <c r="ET7" s="2" t="s">
+        <v>291</v>
+      </c>
+      <c r="EU7" s="2" t="s">
+        <v>291</v>
+      </c>
+      <c r="EV7" s="2" t="s">
+        <v>310</v>
+      </c>
+      <c r="EW7" s="2" t="s">
+        <v>310</v>
+      </c>
+      <c r="EX7" s="2" t="s">
+        <v>310</v>
+      </c>
+      <c r="EY7" s="2" t="s">
+        <v>308</v>
+      </c>
+      <c r="EZ7" s="2" t="s">
+        <v>308</v>
+      </c>
+      <c r="FA7" s="2" t="s">
+        <v>308</v>
+      </c>
+      <c r="FB7" s="2" t="s">
+        <v>357</v>
+      </c>
+      <c r="FC7" s="2" t="s">
+        <v>357</v>
+      </c>
+      <c r="FD7" s="2" t="s">
+        <v>357</v>
+      </c>
+      <c r="FE7" s="2" t="s">
+        <v>295</v>
+      </c>
+      <c r="FF7" s="2" t="s">
+        <v>479</v>
+      </c>
+      <c r="FG7" s="2" t="s">
         <v>443</v>
       </c>
-      <c r="EN6" s="2" t="s">
-        <v>444</v>
-      </c>
-      <c r="EO6" s="2" t="s">
-        <v>266</v>
-      </c>
-      <c r="EP6" s="2" t="s">
-        <v>445</v>
-      </c>
-      <c r="EQ6" s="2" t="s">
-        <v>286</v>
-      </c>
-      <c r="ER6" s="2" t="s">
-        <v>446</v>
-      </c>
-      <c r="ES6" s="2" t="s">
-        <v>282</v>
-      </c>
-      <c r="ET6" s="2" t="s">
-        <v>299</v>
-      </c>
-      <c r="EU6" s="2" t="s">
-        <v>299</v>
-      </c>
-      <c r="EV6" s="2" t="s">
-        <v>283</v>
-      </c>
-      <c r="EW6" s="2" t="s">
-        <v>283</v>
-      </c>
-      <c r="EX6" s="2" t="s">
-        <v>283</v>
-      </c>
-      <c r="EY6" s="2" t="s">
-        <v>284</v>
-      </c>
-      <c r="EZ6" s="2" t="s">
-        <v>307</v>
-      </c>
-      <c r="FA6" s="2" t="s">
-        <v>307</v>
-      </c>
-      <c r="FB6" s="2" t="s">
-        <v>330</v>
-      </c>
-      <c r="FC6" s="2" t="s">
-        <v>340</v>
-      </c>
-      <c r="FD6" s="2" t="s">
-        <v>340</v>
-      </c>
-      <c r="FE6" s="2" t="s">
-        <v>286</v>
-      </c>
-      <c r="FF6" s="2" t="s">
-        <v>447</v>
-      </c>
-      <c r="FG6" s="2" t="s">
-        <v>448</v>
-      </c>
-      <c r="FH6" s="2" t="s">
-        <v>266</v>
-      </c>
-      <c r="FI6" s="2" t="s">
-        <v>309</v>
-      </c>
-      <c r="FJ6" s="2" t="s">
-        <v>286</v>
-      </c>
-      <c r="FK6" s="2" t="s">
-        <v>449</v>
-      </c>
-      <c r="FL6" s="2" t="s">
-        <v>395</v>
-      </c>
-      <c r="FM6" s="2" t="s">
+      <c r="FH7" s="2" t="s">
+        <v>266</v>
+      </c>
+      <c r="FI7" s="2" t="s">
+        <v>480</v>
+      </c>
+      <c r="FJ7" s="2" t="s">
+        <v>298</v>
+      </c>
+      <c r="FK7" s="2" t="s">
+        <v>481</v>
+      </c>
+      <c r="FL7" s="2" t="s">
         <v>312</v>
       </c>
-      <c r="FN6" s="2" t="s">
-        <v>311</v>
-      </c>
-      <c r="FO6" s="2" t="s">
-        <v>311</v>
-      </c>
-      <c r="FP6" s="2" t="s">
-        <v>312</v>
-      </c>
-      <c r="FQ6" s="2" t="s">
-        <v>315</v>
-      </c>
-      <c r="FR6" s="2" t="s">
-        <v>316</v>
-      </c>
-      <c r="FS6" s="2" t="s">
-        <v>316</v>
-      </c>
-      <c r="FT6" s="2" t="s">
+      <c r="FM7" s="2" t="s">
+        <v>313</v>
+      </c>
+      <c r="FN7" s="2" t="s">
+        <v>313</v>
+      </c>
+      <c r="FO7" s="2" t="s">
+        <v>313</v>
+      </c>
+      <c r="FP7" s="2" t="s">
+        <v>313</v>
+      </c>
+      <c r="FQ7" s="2" t="s">
         <v>317</v>
       </c>
-      <c r="FU6" s="2" t="s">
-        <v>303</v>
-      </c>
-      <c r="FV6" s="2" t="s">
-        <v>281</v>
-      </c>
-      <c r="FW6" s="2" t="s">
-        <v>303</v>
-      </c>
-      <c r="FX6" s="2" t="s">
-        <v>450</v>
-      </c>
-      <c r="FY6" s="2" t="s">
-        <v>451</v>
-      </c>
-      <c r="FZ6" s="2" t="s">
-        <v>452</v>
+      <c r="FR7" s="2" t="s">
+        <v>317</v>
+      </c>
+      <c r="FS7" s="2" t="s">
+        <v>317</v>
+      </c>
+      <c r="FT7" s="2" t="s">
+        <v>317</v>
+      </c>
+      <c r="FU7" s="2" t="s">
+        <v>280</v>
+      </c>
+      <c r="FV7" s="2" t="s">
+        <v>280</v>
+      </c>
+      <c r="FW7" s="2" t="s">
+        <v>280</v>
+      </c>
+      <c r="FX7" s="2" t="s">
+        <v>266</v>
+      </c>
+      <c r="FY7" s="2" t="s">
+        <v>266</v>
+      </c>
+      <c r="FZ7" s="2" t="s">
+        <v>482</v>
       </c>
     </row>
+    <row r="8" spans="1:182" ht="15" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="9" spans="1:182" ht="15" customHeight="1" x14ac:dyDescent="0.4"/>
   </sheetData>
-  <autoFilter ref="A2:FZ7" xr:uid="{00000000-0009-0000-0000-000000000000}"/>
+  <autoFilter ref="A2:FZ8" xr:uid="{00000000-0009-0000-0000-000000000000}"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <ignoredErrors>
-    <ignoredError sqref="C1:C2 D1:D2 G1:G2 I1:I2 J1:J2 K1:K2 L1:L2 M1:M2 P1:P2 Q1:Q2 R1:R2 S1:S2 T1:T2 U1:U2 W1:W2 X1:X2 Y1:Y2 Z1:Z2 AA1:AA2 AB1:AB2 AC1:AC2 AD1:AD2 AE1:AE2 AF1:AF2 AG1:AG2 AH1:AH2 AI1:AI2 AJ1:AJ2 AK1:AK2 AL1:AL2 AM1:AM2 AN1:AN2 AO1:AO2 AP1:AP2 AQ1:AQ2 AR1:AR2 AS1:AS2 AT1:AT2 AU1:AU2 AV1:AV2 AW1:AW2 AX1:AX2 AY1:AY2 AZ1:AZ2 BA1:BA2 BB1:BB2 BC1:BC2 BD1:BD2 BE1:BE2 BF1:BF2 BG1:BG2 BH1:BH2 BI1:BI2 BJ1:BJ2 BK1:BK2 BL1:BL2 BM1:BM2 BN1:BN2 BO1:BO2 BP1:BP2 BQ1:BQ2 BR1:BR2 BS1:BS2 BT1:BT2 BU1:BU2 BV1:BV2 BW1:BW2 BX1:BX2 BY1:BY2 BZ1:BZ2 CA1:CA2 CB1:CB2 CC1:CC2 CD1:CD2 CE1:CE2 CF1:CF2 CG1:CG2 CH1:CH2 CI1:CI2 CJ1:CJ2 CK1:CK2 CL1:CL2 CM1:CM2 CN1:CN2 CO1:CO2 CP1:CP2 CQ1:CQ2 CR1:CR2 CS1:CS2 CT1:CT2 CU1:CU2 CV1:CV2 CW1:CW2 CX1:CX2 CY1:CY2 CZ1:CZ2 DA1:DA2 DB1:DB2 DC1:DC2 DD1:DD2 DE1:DE2 DF1:DF2 DG1:DG2 DH1:DH2 DI1:DI2 DJ1:DJ2 DK1:DK2 DL1:DL2 DM1:DM2 DN1:DN2 DO1:DO2 DP1:DP2 DQ1:DQ2 DR1:DR2 DS1:DS2 DT1:DT2 DU1:DU2 DV1:DV2 DW1:DW2 DX1:DX2 DY1:DY2 DZ1:DZ2 EA1:EA2 EB1:EB2 EC1:EC2 ED1:ED2 EE1:EE2 EF1:EF2 EG1:EG2 EH1:EH2 EI1:EI2 EJ1:EJ2 EK1:EK2 EL1:EL2 EM1:EM2 EN1:EN2 EO1:EO2 EP1:EP2 EQ1:EQ2 ER1:ER2 ES1:ES2 ET1:ET2 EU1:EU2 EV1:EV2 EW1:EW2 EX1:EX2 EY1:EY2 EZ1:EZ2 FA1:FA2 FB1:FB2 FC1:FC2 FD1:FD2 FE1:FE2 FF1:FF2 FG1:FG2 FH1:FH2 FI1:FI2 FJ1:FJ2 FK1:FK2 FL1:FL2 FM1:FM2 FN1:FN2 FO1:FO2 FP1:FP2 FQ1:FQ2 FR1:FR2 FS1:FS2 FT1:FT2 FU1:FU2 FV1:FV2 FW1:FW2 FX1:FX2 FY1:FY2 FZ1:FZ2 C3:C6 D3:D6 G3:G6 I3:I6 J3:J6 K3:K6 L3:L6 M3:M6 P3:P6 Q3:Q6 R3:R6 S3:S6 T3:T6 U3:U6 W3:W6 X3:X6 Y3:Y6 Z3:Z6 AA3:AA6 AB3:AB6 AC3:AC6 AD3:AD6 AE3:AE6 AF3:AF6 AG3:AG6 AH3:AH6 AI3:AI6 AJ3:AJ6 AK3:AK6 AL3:AL6 AM3:AM6 AN3:AN6 AO3:AO6 AP3:AP6 AQ3:AQ6 AR3:AR6 AS3:AS6 AT3:AT6 AU3:AU6 AV3:AV6 AW3:AW6 AX3:AX6 AY3:AY6 AZ3:AZ6 BA3:BA6 BB3:BB6 BC3:BC6 BD3:BD6 BE3:BE6 BF3:BF6 BG3:BG6 BH3:BH6 BI3:BI6 BJ3:BJ6 BK3:BK6 BL3:BL6 BM3:BM6 BN3:BN6 BO3:BO6 BP3:BP6 BQ3:BQ6 BR3:BR6 BS3:BS6 BT3:BT6 BU3:BU6 BV3:BV6 BW3:BW6 BX3:BX6 BY3:BY6 BZ3:BZ6 CA3:CA6 CB3:CB6 CC3:CC6 CD3:CD6 CE3:CE6 CF3:CF6 CG3:CG6 CH3:CH6 CI3:CI6 CJ3:CJ6 CK3:CK6 CL3:CL6 CM3:CM6 CN3:CN6 CO3:CO6 CP3:CP6 CQ3:CQ6 CR3:CR6 CS3:CS6 CT3:CT6 CU3:CU6 CV3:CV6 CW3:CW6 CX3:CX6 CY3:CY6 CZ3:CZ6 DA3:DA6 DB3:DB6 DC3:DC6 DD3:DD6 DE3:DE6 DF3:DF6 DG3:DG6 DH3:DH6 DI3:DI6 DJ3:DJ6 DK3:DK6 DL3:DL6 DM3:DM6 DN3:DN6 DO3:DO6 DP3:DP6 DQ3:DQ6 DR3:DR6 DS3:DS6 DT3:DT6 DU3:DU6 DV3:DV6 DW3:DW6 DX3:DX6 DY3:DY6 DZ3:DZ6 EA3:EA6 EB3:EB6 EC3:EC6 ED3:ED6 EE3:EE6 EF3:EF6 EG3:EG6 EH3:EH6 EI3:EI6 EJ3:EJ6 EK3:EK6 EL3:EL6 EM3:EM6 EN3:EN6 EO3:EO6 EP3:EP6 EQ3:EQ6 ER3:ER6 ES3:ES6 ET3:ET6 EU3:EU6 EV3:EV6 EW3:EW6 EX3:EX6 EY3:EY6 EZ3:EZ6 FA3:FA6 FB3:FB6 FC3:FC6 FD3:FD6 FE3:FE6 FF3:FF6 FG3:FG6 FH3:FH6 FI3:FI6 FJ3:FJ6 FK3:FK6 FL3:FL6 FM3:FM6 FN3:FN6 FO3:FO6 FP3:FP6 FQ3:FQ6 FR3:FR6 FS3:FS6 FT3:FT6 FU3:FU6 FV3:FV6 FW3:FW6 FX3:FX6 FY3:FY6 FZ3:FZ6" numberStoredAsText="1"/>
+    <ignoredError sqref="C1:C2 D1:D2 G1:G2 I1:I2 J1:J2 K1:K2 L1:L2 M1:M2 P1:P2 Q1:Q2 R1:R2 S1:S2 T1:T2 U1:U2 W1:W2 X1:X2 Y1:Y2 Z1:Z2 AA1:AA2 AB1:AB2 AC1:AC2 AD1:AD2 AE1:AE2 AF1:AF2 AG1:AG2 AH1:AH2 AI1:AI2 AJ1:AJ2 AK1:AK2 AL1:AL2 AM1:AM2 AN1:AN2 AO1:AO2 AP1:AP2 AQ1:AQ2 AR1:AR2 AS1:AS2 AT1:AT2 AU1:AU2 AV1:AV2 AW1:AW2 AX1:AX2 AY1:AY2 AZ1:AZ2 BA1:BA2 BB1:BB2 BC1:BC2 BD1:BD2 BE1:BE2 BF1:BF2 BG1:BG2 BH1:BH2 BI1:BI2 BJ1:BJ2 BK1:BK2 BL1:BL2 BM1:BM2 BN1:BN2 BO1:BO2 BP1:BP2 BQ1:BQ2 BR1:BR2 BS1:BS2 BT1:BT2 BU1:BU2 BV1:BV2 BW1:BW2 BX1:BX2 BY1:BY2 BZ1:BZ2 CA1:CA2 CB1:CB2 CC1:CC2 CD1:CD2 CE1:CE2 CF1:CF2 CG1:CG2 CH1:CH2 CI1:CI2 CJ1:CJ2 CK1:CK2 CL1:CL2 CM1:CM2 CN1:CN2 CO1:CO2 CP1:CP2 CQ1:CQ2 CR1:CR2 CS1:CS2 CT1:CT2 CU1:CU2 CV1:CV2 CW1:CW2 CX1:CX2 CY1:CY2 CZ1:CZ2 DA1:DA2 DB1:DB2 DC1:DC2 DD1:DD2 DE1:DE2 DF1:DF2 DG1:DG2 DH1:DH2 DI1:DI2 DJ1:DJ2 DK1:DK2 DL1:DL2 DM1:DM2 DN1:DN2 DO1:DO2 DP1:DP2 DQ1:DQ2 DR1:DR2 DS1:DS2 DT1:DT2 DU1:DU2 DV1:DV2 DW1:DW2 DX1:DX2 DY1:DY2 DZ1:DZ2 EA1:EA2 EB1:EB2 EC1:EC2 ED1:ED2 EE1:EE2 EF1:EF2 EG1:EG2 EH1:EH2 EI1:EI2 EJ1:EJ2 EK1:EK2 EL1:EL2 EM1:EM2 EN1:EN2 EO1:EO2 EP1:EP2 EQ1:EQ2 ER1:ER2 ES1:ES2 ET1:ET2 EU1:EU2 EV1:EV2 EW1:EW2 EX1:EX2 EY1:EY2 EZ1:EZ2 FA1:FA2 FB1:FB2 FC1:FC2 FD1:FD2 FE1:FE2 FF1:FF2 FG1:FG2 FH1:FH2 FI1:FI2 FJ1:FJ2 FK1:FK2 FL1:FL2 FM1:FM2 FN1:FN2 FO1:FO2 FP1:FP2 FQ1:FQ2 FR1:FR2 FS1:FS2 FT1:FT2 FU1:FU2 FV1:FV2 FW1:FW2 FX1:FX2 FY1:FY2 FZ1:FZ2 C3:C7 D3:D7 G3:G7 I3:I7 J3:J7 K3:K7 L3:L7 M3:M7 P3:P7 Q3:Q7 R3:R7 S3:S7 T3:T7 U3:U7 W3:W7 X3:X7 Y3:Y7 Z3:Z7 AA3:AA7 AB3:AB7 AC3:AC7 AD3:AD7 AE3:AE7 AF3:AF7 AG3:AG7 AH3:AH7 AI3:AI7 AJ3:AJ7 AK3:AK7 AL3:AL7 AM3:AM7 AN3:AN7 AO3:AO7 AP3:AP7 AQ3:AQ7 AR3:AR7 AS3:AS7 AT3:AT7 AU3:AU7 AV3:AV7 AW3:AW7 AX3:AX7 AY3:AY7 AZ3:AZ7 BA3:BA7 BB3:BB7 BC3:BC7 BD3:BD7 BE3:BE7 BF3:BF7 BG3:BG7 BH3:BH7 BI3:BI7 BJ3:BJ7 BK3:BK7 BL3:BL7 BM3:BM7 BN3:BN7 BO3:BO7 BP3:BP7 BQ3:BQ7 BR3:BR7 BS3:BS7 BT3:BT7 BU3:BU7 BV3:BV7 BW3:BW7 BX3:BX7 BY3:BY7 BZ3:BZ7 CA3:CA7 CB3:CB7 CC3:CC7 CD3:CD7 CE3:CE7 CF3:CF7 CG3:CG7 CH3:CH7 CI3:CI7 CJ3:CJ7 CK3:CK7 CL3:CL7 CM3:CM7 CN3:CN7 CO3:CO7 CP3:CP7 CQ3:CQ7 CR3:CR7 CS3:CS7 CT3:CT7 CU3:CU7 CV3:CV7 CW3:CW7 CX3:CX7 CY3:CY7 CZ3:CZ7 DA3:DA7 DB3:DB7 DC3:DC7 DD3:DD7 DE3:DE7 DF3:DF7 DG3:DG7 DH3:DH7 DI3:DI7 DJ3:DJ7 DK3:DK7 DL3:DL7 DM3:DM7 DN3:DN7 DO3:DO7 DP3:DP7 DQ3:DQ7 DR3:DR7 DS3:DS7 DT3:DT7 DU3:DU7 DV3:DV7 DW3:DW7 DX3:DX7 DY3:DY7 DZ3:DZ7 EA3:EA7 EB3:EB7 EC3:EC7 ED3:ED7 EE3:EE7 EF3:EF7 EG3:EG7 EH3:EH7 EI3:EI7 EJ3:EJ7 EK3:EK7 EL3:EL7 EM3:EM7 EN3:EN7 EO3:EO7 EP3:EP7 EQ3:EQ7 ER3:ER7 ES3:ES7 ET3:ET7 EU3:EU7 EV3:EV7 EW3:EW7 EX3:EX7 EY3:EY7 EZ3:EZ7 FA3:FA7 FB3:FB7 FC3:FC7 FD3:FD7 FE3:FE7 FF3:FF7 FG3:FG7 FH3:FH7 FI3:FI7 FJ3:FJ7 FK3:FK7 FL3:FL7 FM3:FM7 FN3:FN7 FO3:FO7 FP3:FP7 FQ3:FQ7 FR3:FR7 FS3:FS7 FT3:FT7 FU3:FU7 FV3:FV7 FW3:FW7 FX3:FX7 FY3:FY7 FZ3:FZ7" numberStoredAsText="1"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/data.xlsx
+++ b/data.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\simon\Desktop\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{49644848-4F3C-4595-8067-1DD5996A6103}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6F9C9904-DD22-415E-BD8E-FA7B96F1FCBA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-28898" yWindow="-4268" windowWidth="28996" windowHeight="15676" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -16,14 +16,14 @@
     <sheet name="Sheet0" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet0!$A$2:$FZ$8</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet0!$A$2:$FZ$7</definedName>
   </definedNames>
   <calcPr calcId="0"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1234" uniqueCount="483">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1060" uniqueCount="442">
   <si>
     <t>StartDate</t>
   </si>
@@ -938,9 +938,6 @@
     <t>No</t>
   </si>
   <si>
-    <t>Very familiar</t>
-  </si>
-  <si>
     <t>🗣️Version 2,🗣️🗣️ Version 3</t>
   </si>
   <si>
@@ -950,12 +947,12 @@
     <t>Strongly disagree</t>
   </si>
   <si>
-    <t>🔔Version 1</t>
-  </si>
-  <si>
     <t>Somewhat agree</t>
   </si>
   <si>
+    <t>Very short (1 sentence / headline only),Short (2–3 sentences)</t>
+  </si>
+  <si>
     <t>Completely appropriate</t>
   </si>
   <si>
@@ -1037,9 +1034,6 @@
     <t>After I finish telling my current story / thought</t>
   </si>
   <si>
-    <t>Very difficult to detect</t>
-  </si>
-  <si>
     <t>Immediately</t>
   </si>
   <si>
@@ -1128,6 +1122,9 @@
   </si>
   <si>
     <t>Neither agree nor disagree</t>
+  </si>
+  <si>
+    <t>Neither acceptable nor unacceptable</t>
   </si>
   <si>
     <t>Somewhat unacceptable</t>
@@ -1380,181 +1377,61 @@
     <t>1667</t>
   </si>
   <si>
-    <t>79.206.240.242</t>
-  </si>
-  <si>
-    <t>R_8pMrwscyOUCApou</t>
-  </si>
-  <si>
-    <t>No, I am using a mobile device.</t>
-  </si>
-  <si>
-    <t>Both Channels</t>
-  </si>
-  <si>
-    <t>I know how to play an instrument (or sing), but rarely do.</t>
-  </si>
-  <si>
-    <t>Social Etiquette: To avoid disturbing or annoying people around me.,Personal Focus: To avoid distracting myself or breaking my concentration.,Privacy: So people around me don't know when I receive a message.,Awareness: To ensure I don't miss any messages (e.g., needing sound/vibration to notice them).</t>
-  </si>
-  <si>
-    <t>Phone Calls,Calendar / Reminder Alerts,Navigation / Directions,Others:</t>
-  </si>
-  <si>
-    <t>Timers</t>
-  </si>
-  <si>
-    <t>I don't want to be notified auditorily about this notification</t>
-  </si>
-  <si>
-    <t>I prefer this version because I deem messages as less important. If something is urgent, give me a call. My friends, family, coworkers and my social circle is aware of this</t>
-  </si>
-  <si>
-    <t xml:space="preserve">No, since I don't wish to be notified </t>
-  </si>
-  <si>
-    <t>Too intrusive,I prefer control over when notifications speak,Depends on context,Depends on the notification/message</t>
-  </si>
-  <si>
-    <t xml:space="preserve">I'd prefer to not recieve notifications while working with focus. I'd turn my phone silent or switch to airplane mode. </t>
-  </si>
-  <si>
-    <t xml:space="preserve">In this scenario, id prefer to be notified when I'm done working, but how are the glasses supposed to know? </t>
-  </si>
-  <si>
-    <t xml:space="preserve">When talking to colleagues, it is etiquette to have your phone silent in meetings, unless you expect an urgent call. This is not appropriate </t>
-  </si>
-  <si>
-    <t xml:space="preserve">If I had to choose to be notified, id pick the simple alert. Everything else is just plan annoying </t>
-  </si>
-  <si>
-    <t xml:space="preserve">Because having it read out interrups my listening session </t>
-  </si>
-  <si>
-    <t xml:space="preserve">It's alright between songs, it isn't annoying </t>
-  </si>
-  <si>
-    <t xml:space="preserve">I prefer to not recieve any notifications on these specific issues. Additionally, it is not polite to have your phone out when talking, and the npise interrupted the flow of the conversation </t>
-  </si>
-  <si>
-    <t>Focus &amp; Mental Effort (e.g., needing to concentrate on my current task without being interrupted),Social Appropriateness (e.g., the presence of others, social etiquette, or not wanting to appear distracted),Desire for Information (e.g., wanting to know the exact sender or content immediately without having to use my hands/phone)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">If I had to choose a timing, id prefer an immediate notification over anything else. It'd imply the glasses are actively monitoring the conversation and I'd feel observed and uneasy about talking. Additionally, I think delaying the ping destroys the purpose. If I decide I want important messages delivered via audible ques, why would I then artificially delay it? </t>
-  </si>
-  <si>
-    <t xml:space="preserve">I have to pay attention to the road and my surroundings. </t>
-  </si>
-  <si>
-    <t>Acoustic Environment (e.g., the level of background noise, music, or other people talking),Physical Safety &amp; Awareness (e.g., needing to pay visual or mental attention to my physical surroundings, like traffic)</t>
-  </si>
-  <si>
-    <t>After I have finished cycling / reached my destination</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Receiving notes like this in a busy intersection, with the glasses reading out the content is extremely disruptive and dangerous in my opinion. And you could easily loose focus, which makes it even more dangerous. Additionally - how am I even answering on a bike anyway? </t>
-  </si>
-  <si>
-    <t>The other messages just take way longer than the simple beep</t>
-  </si>
-  <si>
-    <t>Acoustic Environment (e.g., the level of background noise, music, or other people talking),Social Appropriateness (e.g., the presence of others, social etiquette, or not wanting to appear distracted)</t>
-  </si>
-  <si>
-    <t>No need to delay</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Privacy, safety, reliability </t>
-  </si>
-  <si>
-    <t xml:space="preserve">Very interesting. Good luck! </t>
-  </si>
-  <si>
-    <t>1414</t>
-  </si>
-  <si>
-    <t>84.174.28.10</t>
-  </si>
-  <si>
-    <t>R_8Y4N7oD7EAbwXgl</t>
-  </si>
-  <si>
-    <t>Non-binary / third gender</t>
-  </si>
-  <si>
-    <t>North Korea</t>
-  </si>
-  <si>
-    <t>north korean</t>
-  </si>
-  <si>
-    <t>I regularly play an instrument (or sing) as a hobby / perform publicly.</t>
-  </si>
-  <si>
-    <t>No notification at all (Muted / Do Not Disturb)</t>
-  </si>
-  <si>
-    <t>Social Etiquette: To avoid disturbing or annoying people around me.,Personal Focus: To avoid distracting myself or breaking my concentration.</t>
-  </si>
-  <si>
-    <t>None of the above</t>
-  </si>
-  <si>
-    <t>It's disturbing</t>
-  </si>
-  <si>
-    <t>every situation in public places</t>
-  </si>
-  <si>
-    <t>Depends on context</t>
-  </si>
-  <si>
-    <t>first finishing work</t>
-  </si>
-  <si>
-    <t>Arbeitszeitbetrug</t>
-  </si>
-  <si>
-    <t>it would be very unpolite</t>
-  </si>
-  <si>
-    <t>less annoying</t>
-  </si>
-  <si>
-    <t>es nervt ungemein</t>
-  </si>
-  <si>
-    <t>Other (please specify):</t>
-  </si>
-  <si>
-    <t>Later, when I am done with music and relaxing</t>
-  </si>
-  <si>
-    <t>weil ich gerade Musik höre</t>
-  </si>
-  <si>
-    <t>Unhöflich der Gesprächspartnerin gegenüber</t>
-  </si>
-  <si>
-    <t>weil es unhöflich wäre, ein Gespräch dafür zu unterbrechen</t>
-  </si>
-  <si>
-    <t>Concentration on the traffic is much more important</t>
-  </si>
-  <si>
-    <t>keine Lust auf Verkehrsunfall</t>
-  </si>
-  <si>
-    <t>ich bin halt am Einkaufen</t>
-  </si>
-  <si>
-    <t>After I am done shopping</t>
-  </si>
-  <si>
-    <t>erstmal das Essen klären</t>
-  </si>
-  <si>
-    <t>1963</t>
+    <t>194.39.218.19</t>
+  </si>
+  <si>
+    <t>R_8DMpkifD7ykuMXT</t>
+  </si>
+  <si>
+    <t>Phone Calls,Calendar / Reminder Alerts,Navigation / Directions</t>
+  </si>
+  <si>
+    <t>If i already hear something AND the message is short like the example, i would like to hear it right away and do not want to search my phone</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Probably some quite private stuff e.g. sexual, financial </t>
+  </si>
+  <si>
+    <t>Reduces need to look at a device,Depends on the notification/message</t>
+  </si>
+  <si>
+    <t>It could kill my flow which i want to avoid</t>
+  </si>
+  <si>
+    <t>When i am done i can hear the full message and avoid taking a look at the phone</t>
+  </si>
+  <si>
+    <t>I am highly focused, speaking so i want to avoid any disturbance. It could crash my talking and would be completly weird. In addition it will cause distraction</t>
+  </si>
+  <si>
+    <t>Once the meeting is over, give me all information as long as the message is short 1-2 sentences</t>
+  </si>
+  <si>
+    <t>When i am listening to music, the disturbance with the voice is to strong</t>
+  </si>
+  <si>
+    <t>i am still into the music and want to avoid the disturbance as good as possible, but i would also like to have the information if the notification is important or not (which  is given by the name)</t>
+  </si>
+  <si>
+    <t>I am talking to a person, so i do not want to get interrupted</t>
+  </si>
+  <si>
+    <t>The sender is the most important information for me to decide if need to take care sooner or later. Or if the notification is even not important at all for me</t>
+  </si>
+  <si>
+    <t>exactly the info i need as i am cycling through the city and can not access my phone directly</t>
+  </si>
+  <si>
+    <t>it is not changing my focus away from the traffic so give me the info immediately</t>
+  </si>
+  <si>
+    <t>It is a anonymous environment and also none which takes a lot of mental effort</t>
+  </si>
+  <si>
+    <t>anonymous situation, i can receive it right away</t>
+  </si>
+  <si>
+    <t>1628</t>
   </si>
 </sst>
 </file>
@@ -1936,13 +1813,15 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:FZ9"/>
+  <dimension ref="A1:FZ6"/>
   <sheetFormatPr defaultRowHeight="14.6" x14ac:dyDescent="0.4"/>
   <cols>
-    <col min="1" max="1" width="19.4609375" customWidth="1"/>
+    <col min="1" max="1" width="16.53515625" customWidth="1"/>
+    <col min="8" max="8" width="18.15234375" customWidth="1"/>
+    <col min="9" max="9" width="28.765625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:182" ht="15" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="1" spans="1:182" x14ac:dyDescent="0.4">
       <c r="A1" s="3" t="s">
         <v>0</v>
       </c>
@@ -2490,7 +2369,7 @@
         <v>181</v>
       </c>
     </row>
-    <row r="2" spans="1:182" ht="15" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="2" spans="1:182" ht="20.05" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A2" s="3" t="s">
         <v>182</v>
       </c>
@@ -3038,7 +2917,7 @@
         <v>181</v>
       </c>
     </row>
-    <row r="3" spans="1:182" ht="15" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="3" spans="1:182" ht="20.05" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A3" s="1">
         <v>46194.469131944446</v>
       </c>
@@ -3049,7 +2928,7 @@
         <v>185</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
       <c r="E3">
         <v>100</v>
@@ -3064,7 +2943,7 @@
         <v>46194.491778877316</v>
       </c>
       <c r="I3" s="2" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
       <c r="J3" s="2" t="s">
         <v>266</v>
@@ -3091,7 +2970,7 @@
         <v>268</v>
       </c>
       <c r="R3" s="2" t="s">
-        <v>330</v>
+        <v>328</v>
       </c>
       <c r="S3" s="2" t="s">
         <v>269</v>
@@ -3115,7 +2994,7 @@
         <v>274</v>
       </c>
       <c r="Z3" s="2" t="s">
-        <v>345</v>
+        <v>344</v>
       </c>
       <c r="AA3" s="2" t="s">
         <v>276</v>
@@ -3124,469 +3003,469 @@
         <v>266</v>
       </c>
       <c r="AC3" s="2" t="s">
+        <v>345</v>
+      </c>
+      <c r="AD3" s="2" t="s">
         <v>346</v>
       </c>
-      <c r="AD3" s="2" t="s">
+      <c r="AE3" s="2" t="s">
         <v>347</v>
       </c>
-      <c r="AE3" s="2" t="s">
+      <c r="AF3" s="2" t="s">
+        <v>266</v>
+      </c>
+      <c r="AG3" s="2" t="s">
+        <v>329</v>
+      </c>
+      <c r="AH3" s="2" t="s">
+        <v>321</v>
+      </c>
+      <c r="AI3" s="2" t="s">
+        <v>322</v>
+      </c>
+      <c r="AJ3" s="2" t="s">
+        <v>266</v>
+      </c>
+      <c r="AK3" s="2" t="s">
+        <v>323</v>
+      </c>
+      <c r="AL3" s="2" t="s">
+        <v>323</v>
+      </c>
+      <c r="AM3" s="2" t="s">
         <v>348</v>
       </c>
-      <c r="AF3" s="2" t="s">
-        <v>266</v>
-      </c>
-      <c r="AG3" s="2" t="s">
-        <v>331</v>
-      </c>
-      <c r="AH3" s="2" t="s">
+      <c r="AN3" s="2" t="s">
+        <v>318</v>
+      </c>
+      <c r="AO3" s="2" t="s">
+        <v>318</v>
+      </c>
+      <c r="AP3" s="2" t="s">
+        <v>318</v>
+      </c>
+      <c r="AQ3" s="2" t="s">
+        <v>348</v>
+      </c>
+      <c r="AR3" s="2" t="s">
+        <v>349</v>
+      </c>
+      <c r="AS3" s="2" t="s">
+        <v>350</v>
+      </c>
+      <c r="AT3" s="2" t="s">
+        <v>280</v>
+      </c>
+      <c r="AU3" s="2" t="s">
+        <v>279</v>
+      </c>
+      <c r="AV3" s="2" t="s">
+        <v>351</v>
+      </c>
+      <c r="AW3" s="2" t="s">
+        <v>266</v>
+      </c>
+      <c r="AX3" s="2" t="s">
+        <v>352</v>
+      </c>
+      <c r="AY3" s="2" t="s">
+        <v>266</v>
+      </c>
+      <c r="AZ3" s="2" t="s">
+        <v>280</v>
+      </c>
+      <c r="BA3" s="2" t="s">
+        <v>298</v>
+      </c>
+      <c r="BB3" s="2" t="s">
+        <v>298</v>
+      </c>
+      <c r="BC3" s="2" t="s">
+        <v>298</v>
+      </c>
+      <c r="BD3" s="2" t="s">
+        <v>283</v>
+      </c>
+      <c r="BE3" s="2" t="s">
+        <v>283</v>
+      </c>
+      <c r="BF3" s="2" t="s">
+        <v>283</v>
+      </c>
+      <c r="BG3" s="2" t="s">
+        <v>284</v>
+      </c>
+      <c r="BH3" s="2" t="s">
+        <v>325</v>
+      </c>
+      <c r="BI3" s="2" t="s">
+        <v>325</v>
+      </c>
+      <c r="BJ3" s="2" t="s">
+        <v>330</v>
+      </c>
+      <c r="BK3" s="2" t="s">
+        <v>333</v>
+      </c>
+      <c r="BL3" s="2" t="s">
+        <v>333</v>
+      </c>
+      <c r="BM3" s="2" t="s">
+        <v>297</v>
+      </c>
+      <c r="BN3" s="2" t="s">
+        <v>353</v>
+      </c>
+      <c r="BO3" s="2" t="s">
+        <v>354</v>
+      </c>
+      <c r="BP3" s="2" t="s">
+        <v>266</v>
+      </c>
+      <c r="BQ3" s="2" t="s">
+        <v>309</v>
+      </c>
+      <c r="BR3" s="2" t="s">
+        <v>297</v>
+      </c>
+      <c r="BS3" s="2" t="s">
+        <v>355</v>
+      </c>
+      <c r="BT3" s="2" t="s">
+        <v>289</v>
+      </c>
+      <c r="BU3" s="2" t="s">
+        <v>290</v>
+      </c>
+      <c r="BV3" s="2" t="s">
+        <v>290</v>
+      </c>
+      <c r="BW3" s="2" t="s">
+        <v>283</v>
+      </c>
+      <c r="BX3" s="2" t="s">
+        <v>283</v>
+      </c>
+      <c r="BY3" s="2" t="s">
+        <v>283</v>
+      </c>
+      <c r="BZ3" s="2" t="s">
+        <v>325</v>
+      </c>
+      <c r="CA3" s="2" t="s">
+        <v>307</v>
+      </c>
+      <c r="CB3" s="2" t="s">
+        <v>307</v>
+      </c>
+      <c r="CC3" s="2" t="s">
+        <v>340</v>
+      </c>
+      <c r="CD3" s="2" t="s">
+        <v>356</v>
+      </c>
+      <c r="CE3" s="2" t="s">
+        <v>356</v>
+      </c>
+      <c r="CF3" s="2" t="s">
+        <v>294</v>
+      </c>
+      <c r="CG3" s="2" t="s">
+        <v>357</v>
+      </c>
+      <c r="CH3" s="2" t="s">
+        <v>295</v>
+      </c>
+      <c r="CI3" s="2" t="s">
+        <v>266</v>
+      </c>
+      <c r="CJ3" s="2" t="s">
+        <v>296</v>
+      </c>
+      <c r="CK3" s="2" t="s">
+        <v>297</v>
+      </c>
+      <c r="CL3" s="2" t="s">
+        <v>358</v>
+      </c>
+      <c r="CM3" s="2" t="s">
+        <v>282</v>
+      </c>
+      <c r="CN3" s="2" t="s">
+        <v>282</v>
+      </c>
+      <c r="CO3" s="2" t="s">
+        <v>282</v>
+      </c>
+      <c r="CP3" s="2" t="s">
+        <v>283</v>
+      </c>
+      <c r="CQ3" s="2" t="s">
+        <v>283</v>
+      </c>
+      <c r="CR3" s="2" t="s">
+        <v>283</v>
+      </c>
+      <c r="CS3" s="2" t="s">
+        <v>284</v>
+      </c>
+      <c r="CT3" s="2" t="s">
+        <v>292</v>
+      </c>
+      <c r="CU3" s="2" t="s">
+        <v>325</v>
+      </c>
+      <c r="CV3" s="2" t="s">
+        <v>330</v>
+      </c>
+      <c r="CW3" s="2" t="s">
+        <v>330</v>
+      </c>
+      <c r="CX3" s="2" t="s">
+        <v>330</v>
+      </c>
+      <c r="CY3" s="2" t="s">
+        <v>297</v>
+      </c>
+      <c r="CZ3" s="2" t="s">
+        <v>359</v>
+      </c>
+      <c r="DA3" s="2" t="s">
+        <v>326</v>
+      </c>
+      <c r="DB3" s="2" t="s">
+        <v>266</v>
+      </c>
+      <c r="DC3" s="2" t="s">
+        <v>309</v>
+      </c>
+      <c r="DD3" s="2" t="s">
+        <v>297</v>
+      </c>
+      <c r="DE3" s="2" t="s">
+        <v>360</v>
+      </c>
+      <c r="DF3" s="2" t="s">
+        <v>303</v>
+      </c>
+      <c r="DG3" s="2" t="s">
+        <v>298</v>
+      </c>
+      <c r="DH3" s="2" t="s">
+        <v>282</v>
+      </c>
+      <c r="DI3" s="2" t="s">
+        <v>282</v>
+      </c>
+      <c r="DJ3" s="2" t="s">
+        <v>283</v>
+      </c>
+      <c r="DK3" s="2" t="s">
+        <v>306</v>
+      </c>
+      <c r="DL3" s="2" t="s">
+        <v>305</v>
+      </c>
+      <c r="DM3" s="2" t="s">
+        <v>325</v>
+      </c>
+      <c r="DN3" s="2" t="s">
+        <v>293</v>
+      </c>
+      <c r="DO3" s="2" t="s">
+        <v>307</v>
+      </c>
+      <c r="DP3" s="2" t="s">
+        <v>333</v>
+      </c>
+      <c r="DQ3" s="2" t="s">
+        <v>356</v>
+      </c>
+      <c r="DR3" s="2" t="s">
+        <v>356</v>
+      </c>
+      <c r="DS3" s="2" t="s">
+        <v>286</v>
+      </c>
+      <c r="DT3" s="2" t="s">
+        <v>361</v>
+      </c>
+      <c r="DU3" s="2" t="s">
+        <v>334</v>
+      </c>
+      <c r="DV3" s="2" t="s">
+        <v>266</v>
+      </c>
+      <c r="DW3" s="2" t="s">
+        <v>362</v>
+      </c>
+      <c r="DX3" s="2" t="s">
+        <v>297</v>
+      </c>
+      <c r="DY3" s="2" t="s">
+        <v>363</v>
+      </c>
+      <c r="DZ3" s="2" t="s">
+        <v>282</v>
+      </c>
+      <c r="EA3" s="2" t="s">
+        <v>299</v>
+      </c>
+      <c r="EB3" s="2" t="s">
+        <v>289</v>
+      </c>
+      <c r="EC3" s="2" t="s">
+        <v>283</v>
+      </c>
+      <c r="ED3" s="2" t="s">
+        <v>306</v>
+      </c>
+      <c r="EE3" s="2" t="s">
+        <v>306</v>
+      </c>
+      <c r="EF3" s="2" t="s">
+        <v>301</v>
+      </c>
+      <c r="EG3" s="2" t="s">
+        <v>292</v>
+      </c>
+      <c r="EH3" s="2" t="s">
+        <v>292</v>
+      </c>
+      <c r="EI3" s="2" t="s">
+        <v>330</v>
+      </c>
+      <c r="EJ3" s="2" t="s">
+        <v>341</v>
+      </c>
+      <c r="EK3" s="2" t="s">
+        <v>340</v>
+      </c>
+      <c r="EL3" s="2" t="s">
+        <v>286</v>
+      </c>
+      <c r="EM3" s="2" t="s">
+        <v>364</v>
+      </c>
+      <c r="EN3" s="2" t="s">
+        <v>365</v>
+      </c>
+      <c r="EO3" s="2" t="s">
+        <v>266</v>
+      </c>
+      <c r="EP3" s="2" t="s">
+        <v>309</v>
+      </c>
+      <c r="EQ3" s="2" t="s">
+        <v>297</v>
+      </c>
+      <c r="ER3" s="2" t="s">
+        <v>366</v>
+      </c>
+      <c r="ES3" s="2" t="s">
+        <v>282</v>
+      </c>
+      <c r="ET3" s="2" t="s">
+        <v>282</v>
+      </c>
+      <c r="EU3" s="2" t="s">
+        <v>299</v>
+      </c>
+      <c r="EV3" s="2" t="s">
+        <v>283</v>
+      </c>
+      <c r="EW3" s="2" t="s">
+        <v>283</v>
+      </c>
+      <c r="EX3" s="2" t="s">
+        <v>283</v>
+      </c>
+      <c r="EY3" s="2" t="s">
+        <v>301</v>
+      </c>
+      <c r="EZ3" s="2" t="s">
+        <v>284</v>
+      </c>
+      <c r="FA3" s="2" t="s">
+        <v>292</v>
+      </c>
+      <c r="FB3" s="2" t="s">
+        <v>330</v>
+      </c>
+      <c r="FC3" s="2" t="s">
+        <v>341</v>
+      </c>
+      <c r="FD3" s="2" t="s">
+        <v>340</v>
+      </c>
+      <c r="FE3" s="2" t="s">
+        <v>297</v>
+      </c>
+      <c r="FF3" s="2" t="s">
+        <v>367</v>
+      </c>
+      <c r="FG3" s="2" t="s">
+        <v>334</v>
+      </c>
+      <c r="FH3" s="2" t="s">
+        <v>266</v>
+      </c>
+      <c r="FI3" s="2" t="s">
+        <v>309</v>
+      </c>
+      <c r="FJ3" s="2" t="s">
+        <v>297</v>
+      </c>
+      <c r="FK3" s="2" t="s">
+        <v>368</v>
+      </c>
+      <c r="FL3" s="2" t="s">
+        <v>310</v>
+      </c>
+      <c r="FM3" s="2" t="s">
+        <v>311</v>
+      </c>
+      <c r="FN3" s="2" t="s">
+        <v>311</v>
+      </c>
+      <c r="FO3" s="2" t="s">
+        <v>311</v>
+      </c>
+      <c r="FP3" s="2" t="s">
+        <v>312</v>
+      </c>
+      <c r="FQ3" s="2" t="s">
+        <v>315</v>
+      </c>
+      <c r="FR3" s="2" t="s">
+        <v>315</v>
+      </c>
+      <c r="FS3" s="2" t="s">
+        <v>315</v>
+      </c>
+      <c r="FT3" s="2" t="s">
+        <v>317</v>
+      </c>
+      <c r="FU3" s="2" t="s">
+        <v>280</v>
+      </c>
+      <c r="FV3" s="2" t="s">
         <v>323</v>
       </c>
-      <c r="AI3" s="2" t="s">
-        <v>324</v>
-      </c>
-      <c r="AJ3" s="2" t="s">
-        <v>266</v>
-      </c>
-      <c r="AK3" s="2" t="s">
-        <v>325</v>
-      </c>
-      <c r="AL3" s="2" t="s">
-        <v>325</v>
-      </c>
-      <c r="AM3" s="2" t="s">
-        <v>349</v>
-      </c>
-      <c r="AN3" s="2" t="s">
-        <v>320</v>
-      </c>
-      <c r="AO3" s="2" t="s">
-        <v>320</v>
-      </c>
-      <c r="AP3" s="2" t="s">
-        <v>320</v>
-      </c>
-      <c r="AQ3" s="2" t="s">
-        <v>349</v>
-      </c>
-      <c r="AR3" s="2" t="s">
-        <v>350</v>
-      </c>
-      <c r="AS3" s="2" t="s">
-        <v>351</v>
-      </c>
-      <c r="AT3" s="2" t="s">
-        <v>282</v>
-      </c>
-      <c r="AU3" s="2" t="s">
-        <v>280</v>
-      </c>
-      <c r="AV3" s="2" t="s">
-        <v>352</v>
-      </c>
-      <c r="AW3" s="2" t="s">
-        <v>266</v>
-      </c>
-      <c r="AX3" s="2" t="s">
-        <v>353</v>
-      </c>
-      <c r="AY3" s="2" t="s">
-        <v>266</v>
-      </c>
-      <c r="AZ3" s="2" t="s">
-        <v>282</v>
-      </c>
-      <c r="BA3" s="2" t="s">
-        <v>299</v>
-      </c>
-      <c r="BB3" s="2" t="s">
-        <v>299</v>
-      </c>
-      <c r="BC3" s="2" t="s">
-        <v>299</v>
-      </c>
-      <c r="BD3" s="2" t="s">
-        <v>284</v>
-      </c>
-      <c r="BE3" s="2" t="s">
-        <v>284</v>
-      </c>
-      <c r="BF3" s="2" t="s">
-        <v>284</v>
-      </c>
-      <c r="BG3" s="2" t="s">
-        <v>285</v>
-      </c>
-      <c r="BH3" s="2" t="s">
-        <v>327</v>
-      </c>
-      <c r="BI3" s="2" t="s">
-        <v>327</v>
-      </c>
-      <c r="BJ3" s="2" t="s">
-        <v>332</v>
-      </c>
-      <c r="BK3" s="2" t="s">
-        <v>335</v>
-      </c>
-      <c r="BL3" s="2" t="s">
-        <v>335</v>
-      </c>
-      <c r="BM3" s="2" t="s">
-        <v>298</v>
-      </c>
-      <c r="BN3" s="2" t="s">
-        <v>354</v>
-      </c>
-      <c r="BO3" s="2" t="s">
-        <v>355</v>
-      </c>
-      <c r="BP3" s="2" t="s">
-        <v>266</v>
-      </c>
-      <c r="BQ3" s="2" t="s">
-        <v>311</v>
-      </c>
-      <c r="BR3" s="2" t="s">
-        <v>298</v>
-      </c>
-      <c r="BS3" s="2" t="s">
-        <v>356</v>
-      </c>
-      <c r="BT3" s="2" t="s">
-        <v>290</v>
-      </c>
-      <c r="BU3" s="2" t="s">
-        <v>291</v>
-      </c>
-      <c r="BV3" s="2" t="s">
-        <v>291</v>
-      </c>
-      <c r="BW3" s="2" t="s">
-        <v>284</v>
-      </c>
-      <c r="BX3" s="2" t="s">
-        <v>284</v>
-      </c>
-      <c r="BY3" s="2" t="s">
-        <v>284</v>
-      </c>
-      <c r="BZ3" s="2" t="s">
-        <v>327</v>
-      </c>
-      <c r="CA3" s="2" t="s">
-        <v>308</v>
-      </c>
-      <c r="CB3" s="2" t="s">
-        <v>308</v>
-      </c>
-      <c r="CC3" s="2" t="s">
-        <v>341</v>
-      </c>
-      <c r="CD3" s="2" t="s">
-        <v>357</v>
-      </c>
-      <c r="CE3" s="2" t="s">
-        <v>357</v>
-      </c>
-      <c r="CF3" s="2" t="s">
-        <v>295</v>
-      </c>
-      <c r="CG3" s="2" t="s">
-        <v>358</v>
-      </c>
-      <c r="CH3" s="2" t="s">
-        <v>296</v>
-      </c>
-      <c r="CI3" s="2" t="s">
-        <v>266</v>
-      </c>
-      <c r="CJ3" s="2" t="s">
-        <v>297</v>
-      </c>
-      <c r="CK3" s="2" t="s">
-        <v>298</v>
-      </c>
-      <c r="CL3" s="2" t="s">
-        <v>359</v>
-      </c>
-      <c r="CM3" s="2" t="s">
-        <v>283</v>
-      </c>
-      <c r="CN3" s="2" t="s">
-        <v>283</v>
-      </c>
-      <c r="CO3" s="2" t="s">
-        <v>283</v>
-      </c>
-      <c r="CP3" s="2" t="s">
-        <v>284</v>
-      </c>
-      <c r="CQ3" s="2" t="s">
-        <v>284</v>
-      </c>
-      <c r="CR3" s="2" t="s">
-        <v>284</v>
-      </c>
-      <c r="CS3" s="2" t="s">
-        <v>285</v>
-      </c>
-      <c r="CT3" s="2" t="s">
-        <v>293</v>
-      </c>
-      <c r="CU3" s="2" t="s">
-        <v>327</v>
-      </c>
-      <c r="CV3" s="2" t="s">
-        <v>332</v>
-      </c>
-      <c r="CW3" s="2" t="s">
-        <v>332</v>
-      </c>
-      <c r="CX3" s="2" t="s">
-        <v>332</v>
-      </c>
-      <c r="CY3" s="2" t="s">
-        <v>298</v>
-      </c>
-      <c r="CZ3" s="2" t="s">
-        <v>360</v>
-      </c>
-      <c r="DA3" s="2" t="s">
-        <v>328</v>
-      </c>
-      <c r="DB3" s="2" t="s">
-        <v>266</v>
-      </c>
-      <c r="DC3" s="2" t="s">
-        <v>311</v>
-      </c>
-      <c r="DD3" s="2" t="s">
-        <v>298</v>
-      </c>
-      <c r="DE3" s="2" t="s">
-        <v>361</v>
-      </c>
-      <c r="DF3" s="2" t="s">
-        <v>304</v>
-      </c>
-      <c r="DG3" s="2" t="s">
-        <v>299</v>
-      </c>
-      <c r="DH3" s="2" t="s">
-        <v>283</v>
-      </c>
-      <c r="DI3" s="2" t="s">
-        <v>283</v>
-      </c>
-      <c r="DJ3" s="2" t="s">
-        <v>284</v>
-      </c>
-      <c r="DK3" s="2" t="s">
-        <v>307</v>
-      </c>
-      <c r="DL3" s="2" t="s">
-        <v>306</v>
-      </c>
-      <c r="DM3" s="2" t="s">
-        <v>327</v>
-      </c>
-      <c r="DN3" s="2" t="s">
-        <v>294</v>
-      </c>
-      <c r="DO3" s="2" t="s">
-        <v>308</v>
-      </c>
-      <c r="DP3" s="2" t="s">
-        <v>335</v>
-      </c>
-      <c r="DQ3" s="2" t="s">
-        <v>357</v>
-      </c>
-      <c r="DR3" s="2" t="s">
-        <v>357</v>
-      </c>
-      <c r="DS3" s="2" t="s">
-        <v>287</v>
-      </c>
-      <c r="DT3" s="2" t="s">
-        <v>362</v>
-      </c>
-      <c r="DU3" s="2" t="s">
-        <v>336</v>
-      </c>
-      <c r="DV3" s="2" t="s">
-        <v>266</v>
-      </c>
-      <c r="DW3" s="2" t="s">
-        <v>363</v>
-      </c>
-      <c r="DX3" s="2" t="s">
-        <v>298</v>
-      </c>
-      <c r="DY3" s="2" t="s">
-        <v>364</v>
-      </c>
-      <c r="DZ3" s="2" t="s">
-        <v>283</v>
-      </c>
-      <c r="EA3" s="2" t="s">
-        <v>300</v>
-      </c>
-      <c r="EB3" s="2" t="s">
-        <v>290</v>
-      </c>
-      <c r="EC3" s="2" t="s">
-        <v>284</v>
-      </c>
-      <c r="ED3" s="2" t="s">
-        <v>307</v>
-      </c>
-      <c r="EE3" s="2" t="s">
-        <v>307</v>
-      </c>
-      <c r="EF3" s="2" t="s">
-        <v>302</v>
-      </c>
-      <c r="EG3" s="2" t="s">
-        <v>293</v>
-      </c>
-      <c r="EH3" s="2" t="s">
-        <v>293</v>
-      </c>
-      <c r="EI3" s="2" t="s">
-        <v>332</v>
-      </c>
-      <c r="EJ3" s="2" t="s">
-        <v>342</v>
-      </c>
-      <c r="EK3" s="2" t="s">
-        <v>341</v>
-      </c>
-      <c r="EL3" s="2" t="s">
-        <v>287</v>
-      </c>
-      <c r="EM3" s="2" t="s">
-        <v>365</v>
-      </c>
-      <c r="EN3" s="2" t="s">
-        <v>366</v>
-      </c>
-      <c r="EO3" s="2" t="s">
-        <v>266</v>
-      </c>
-      <c r="EP3" s="2" t="s">
-        <v>311</v>
-      </c>
-      <c r="EQ3" s="2" t="s">
-        <v>298</v>
-      </c>
-      <c r="ER3" s="2" t="s">
-        <v>367</v>
-      </c>
-      <c r="ES3" s="2" t="s">
-        <v>283</v>
-      </c>
-      <c r="ET3" s="2" t="s">
-        <v>283</v>
-      </c>
-      <c r="EU3" s="2" t="s">
-        <v>300</v>
-      </c>
-      <c r="EV3" s="2" t="s">
-        <v>284</v>
-      </c>
-      <c r="EW3" s="2" t="s">
-        <v>284</v>
-      </c>
-      <c r="EX3" s="2" t="s">
-        <v>284</v>
-      </c>
-      <c r="EY3" s="2" t="s">
-        <v>302</v>
-      </c>
-      <c r="EZ3" s="2" t="s">
-        <v>285</v>
-      </c>
-      <c r="FA3" s="2" t="s">
-        <v>293</v>
-      </c>
-      <c r="FB3" s="2" t="s">
-        <v>332</v>
-      </c>
-      <c r="FC3" s="2" t="s">
-        <v>342</v>
-      </c>
-      <c r="FD3" s="2" t="s">
-        <v>341</v>
-      </c>
-      <c r="FE3" s="2" t="s">
-        <v>298</v>
-      </c>
-      <c r="FF3" s="2" t="s">
-        <v>368</v>
-      </c>
-      <c r="FG3" s="2" t="s">
-        <v>336</v>
-      </c>
-      <c r="FH3" s="2" t="s">
-        <v>266</v>
-      </c>
-      <c r="FI3" s="2" t="s">
-        <v>311</v>
-      </c>
-      <c r="FJ3" s="2" t="s">
-        <v>298</v>
-      </c>
-      <c r="FK3" s="2" t="s">
+      <c r="FW3" s="2" t="s">
+        <v>278</v>
+      </c>
+      <c r="FX3" s="2" t="s">
+        <v>266</v>
+      </c>
+      <c r="FY3" s="2" t="s">
+        <v>266</v>
+      </c>
+      <c r="FZ3" s="2" t="s">
         <v>369</v>
       </c>
-      <c r="FL3" s="2" t="s">
-        <v>312</v>
-      </c>
-      <c r="FM3" s="2" t="s">
-        <v>313</v>
-      </c>
-      <c r="FN3" s="2" t="s">
-        <v>313</v>
-      </c>
-      <c r="FO3" s="2" t="s">
-        <v>313</v>
-      </c>
-      <c r="FP3" s="2" t="s">
-        <v>314</v>
-      </c>
-      <c r="FQ3" s="2" t="s">
-        <v>317</v>
-      </c>
-      <c r="FR3" s="2" t="s">
-        <v>317</v>
-      </c>
-      <c r="FS3" s="2" t="s">
-        <v>317</v>
-      </c>
-      <c r="FT3" s="2" t="s">
-        <v>319</v>
-      </c>
-      <c r="FU3" s="2" t="s">
-        <v>282</v>
-      </c>
-      <c r="FV3" s="2" t="s">
-        <v>325</v>
-      </c>
-      <c r="FW3" s="2" t="s">
-        <v>279</v>
-      </c>
-      <c r="FX3" s="2" t="s">
-        <v>266</v>
-      </c>
-      <c r="FY3" s="2" t="s">
-        <v>266</v>
-      </c>
-      <c r="FZ3" s="2" t="s">
-        <v>370</v>
-      </c>
     </row>
-    <row r="4" spans="1:182" ht="15" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="4" spans="1:182" ht="20.05" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A4" s="1">
         <v>46194.56082175926</v>
       </c>
@@ -3597,7 +3476,7 @@
         <v>185</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>371</v>
+        <v>370</v>
       </c>
       <c r="E4">
         <v>100</v>
@@ -3612,7 +3491,7 @@
         <v>46194.580947881943</v>
       </c>
       <c r="I4" s="2" t="s">
-        <v>372</v>
+        <v>371</v>
       </c>
       <c r="J4" s="2" t="s">
         <v>266</v>
@@ -3639,7 +3518,7 @@
         <v>268</v>
       </c>
       <c r="R4" s="2" t="s">
-        <v>330</v>
+        <v>328</v>
       </c>
       <c r="S4" s="2" t="s">
         <v>269</v>
@@ -3672,469 +3551,469 @@
         <v>266</v>
       </c>
       <c r="AC4" s="2" t="s">
-        <v>346</v>
+        <v>345</v>
       </c>
       <c r="AD4" s="2" t="s">
-        <v>339</v>
+        <v>337</v>
       </c>
       <c r="AE4" s="2" t="s">
+        <v>372</v>
+      </c>
+      <c r="AF4" s="2" t="s">
+        <v>266</v>
+      </c>
+      <c r="AG4" s="2" t="s">
         <v>373</v>
       </c>
-      <c r="AF4" s="2" t="s">
-        <v>266</v>
-      </c>
-      <c r="AG4" s="2" t="s">
+      <c r="AH4" s="2" t="s">
         <v>374</v>
       </c>
-      <c r="AH4" s="2" t="s">
+      <c r="AI4" s="2" t="s">
         <v>375</v>
       </c>
-      <c r="AI4" s="2" t="s">
+      <c r="AJ4" s="2" t="s">
+        <v>266</v>
+      </c>
+      <c r="AK4" s="2" t="s">
+        <v>323</v>
+      </c>
+      <c r="AL4" s="2" t="s">
+        <v>323</v>
+      </c>
+      <c r="AM4" s="2" t="s">
+        <v>277</v>
+      </c>
+      <c r="AN4" s="2" t="s">
+        <v>323</v>
+      </c>
+      <c r="AO4" s="2" t="s">
+        <v>338</v>
+      </c>
+      <c r="AP4" s="2" t="s">
+        <v>338</v>
+      </c>
+      <c r="AQ4" s="2" t="s">
+        <v>288</v>
+      </c>
+      <c r="AR4" s="2" t="s">
         <v>376</v>
       </c>
-      <c r="AJ4" s="2" t="s">
-        <v>266</v>
-      </c>
-      <c r="AK4" s="2" t="s">
-        <v>325</v>
-      </c>
-      <c r="AL4" s="2" t="s">
-        <v>325</v>
-      </c>
-      <c r="AM4" s="2" t="s">
-        <v>278</v>
-      </c>
-      <c r="AN4" s="2" t="s">
-        <v>325</v>
-      </c>
-      <c r="AO4" s="2" t="s">
+      <c r="AS4" s="2" t="s">
+        <v>377</v>
+      </c>
+      <c r="AT4" s="2" t="s">
+        <v>280</v>
+      </c>
+      <c r="AU4" s="2" t="s">
+        <v>280</v>
+      </c>
+      <c r="AV4" s="2" t="s">
+        <v>378</v>
+      </c>
+      <c r="AW4" s="2" t="s">
+        <v>266</v>
+      </c>
+      <c r="AX4" s="2" t="s">
+        <v>379</v>
+      </c>
+      <c r="AY4" s="2" t="s">
+        <v>266</v>
+      </c>
+      <c r="AZ4" s="2" t="s">
+        <v>318</v>
+      </c>
+      <c r="BA4" s="2" t="s">
+        <v>298</v>
+      </c>
+      <c r="BB4" s="2" t="s">
+        <v>298</v>
+      </c>
+      <c r="BC4" s="2" t="s">
+        <v>298</v>
+      </c>
+      <c r="BD4" s="2" t="s">
+        <v>306</v>
+      </c>
+      <c r="BE4" s="2" t="s">
+        <v>306</v>
+      </c>
+      <c r="BF4" s="2" t="s">
+        <v>306</v>
+      </c>
+      <c r="BG4" s="2" t="s">
+        <v>284</v>
+      </c>
+      <c r="BH4" s="2" t="s">
+        <v>293</v>
+      </c>
+      <c r="BI4" s="2" t="s">
+        <v>307</v>
+      </c>
+      <c r="BJ4" s="2" t="s">
+        <v>333</v>
+      </c>
+      <c r="BK4" s="2" t="s">
+        <v>333</v>
+      </c>
+      <c r="BL4" s="2" t="s">
+        <v>333</v>
+      </c>
+      <c r="BM4" s="2" t="s">
+        <v>294</v>
+      </c>
+      <c r="BN4" s="2" t="s">
+        <v>380</v>
+      </c>
+      <c r="BO4" s="2" t="s">
+        <v>287</v>
+      </c>
+      <c r="BP4" s="2" t="s">
+        <v>266</v>
+      </c>
+      <c r="BQ4" s="2" t="s">
+        <v>331</v>
+      </c>
+      <c r="BR4" s="2" t="s">
+        <v>288</v>
+      </c>
+      <c r="BS4" s="2" t="s">
+        <v>381</v>
+      </c>
+      <c r="BT4" s="2" t="s">
+        <v>298</v>
+      </c>
+      <c r="BU4" s="2" t="s">
+        <v>304</v>
+      </c>
+      <c r="BV4" s="2" t="s">
+        <v>290</v>
+      </c>
+      <c r="BW4" s="2" t="s">
+        <v>306</v>
+      </c>
+      <c r="BX4" s="2" t="s">
+        <v>306</v>
+      </c>
+      <c r="BY4" s="2" t="s">
+        <v>306</v>
+      </c>
+      <c r="BZ4" s="2" t="s">
+        <v>284</v>
+      </c>
+      <c r="CA4" s="2" t="s">
+        <v>293</v>
+      </c>
+      <c r="CB4" s="2" t="s">
+        <v>307</v>
+      </c>
+      <c r="CC4" s="2" t="s">
+        <v>330</v>
+      </c>
+      <c r="CD4" s="2" t="s">
+        <v>382</v>
+      </c>
+      <c r="CE4" s="2" t="s">
+        <v>356</v>
+      </c>
+      <c r="CF4" s="2" t="s">
+        <v>294</v>
+      </c>
+      <c r="CG4" s="2" t="s">
+        <v>383</v>
+      </c>
+      <c r="CH4" s="2" t="s">
+        <v>354</v>
+      </c>
+      <c r="CI4" s="2" t="s">
+        <v>266</v>
+      </c>
+      <c r="CJ4" s="2" t="s">
+        <v>296</v>
+      </c>
+      <c r="CK4" s="2" t="s">
+        <v>288</v>
+      </c>
+      <c r="CL4" s="2" t="s">
+        <v>384</v>
+      </c>
+      <c r="CM4" s="2" t="s">
+        <v>282</v>
+      </c>
+      <c r="CN4" s="2" t="s">
+        <v>282</v>
+      </c>
+      <c r="CO4" s="2" t="s">
+        <v>282</v>
+      </c>
+      <c r="CP4" s="2" t="s">
+        <v>305</v>
+      </c>
+      <c r="CQ4" s="2" t="s">
+        <v>300</v>
+      </c>
+      <c r="CR4" s="2" t="s">
+        <v>306</v>
+      </c>
+      <c r="CS4" s="2" t="s">
+        <v>301</v>
+      </c>
+      <c r="CT4" s="2" t="s">
+        <v>292</v>
+      </c>
+      <c r="CU4" s="2" t="s">
+        <v>285</v>
+      </c>
+      <c r="CV4" s="2" t="s">
+        <v>330</v>
+      </c>
+      <c r="CW4" s="2" t="s">
+        <v>330</v>
+      </c>
+      <c r="CX4" s="2" t="s">
+        <v>330</v>
+      </c>
+      <c r="CY4" s="2" t="s">
+        <v>288</v>
+      </c>
+      <c r="CZ4" s="2" t="s">
+        <v>385</v>
+      </c>
+      <c r="DA4" s="2" t="s">
+        <v>386</v>
+      </c>
+      <c r="DB4" s="2" t="s">
+        <v>266</v>
+      </c>
+      <c r="DC4" s="2" t="s">
+        <v>309</v>
+      </c>
+      <c r="DD4" s="2" t="s">
+        <v>332</v>
+      </c>
+      <c r="DE4" s="2" t="s">
+        <v>387</v>
+      </c>
+      <c r="DF4" s="2" t="s">
+        <v>303</v>
+      </c>
+      <c r="DG4" s="2" t="s">
+        <v>282</v>
+      </c>
+      <c r="DH4" s="2" t="s">
+        <v>282</v>
+      </c>
+      <c r="DI4" s="2" t="s">
+        <v>324</v>
+      </c>
+      <c r="DJ4" s="2" t="s">
+        <v>306</v>
+      </c>
+      <c r="DK4" s="2" t="s">
+        <v>283</v>
+      </c>
+      <c r="DL4" s="2" t="s">
+        <v>306</v>
+      </c>
+      <c r="DM4" s="2" t="s">
+        <v>284</v>
+      </c>
+      <c r="DN4" s="2" t="s">
+        <v>284</v>
+      </c>
+      <c r="DO4" s="2" t="s">
+        <v>293</v>
+      </c>
+      <c r="DP4" s="2" t="s">
+        <v>330</v>
+      </c>
+      <c r="DQ4" s="2" t="s">
+        <v>333</v>
+      </c>
+      <c r="DR4" s="2" t="s">
         <v>340</v>
       </c>
-      <c r="AP4" s="2" t="s">
-        <v>340</v>
-      </c>
-      <c r="AQ4" s="2" t="s">
-        <v>289</v>
-      </c>
-      <c r="AR4" s="2" t="s">
-        <v>377</v>
-      </c>
-      <c r="AS4" s="2" t="s">
-        <v>378</v>
-      </c>
-      <c r="AT4" s="2" t="s">
+      <c r="DS4" s="2" t="s">
+        <v>297</v>
+      </c>
+      <c r="DT4" s="2" t="s">
+        <v>388</v>
+      </c>
+      <c r="DU4" s="2" t="s">
+        <v>389</v>
+      </c>
+      <c r="DV4" s="2" t="s">
+        <v>266</v>
+      </c>
+      <c r="DW4" s="2" t="s">
+        <v>309</v>
+      </c>
+      <c r="DX4" s="2" t="s">
+        <v>332</v>
+      </c>
+      <c r="DY4" s="2" t="s">
+        <v>390</v>
+      </c>
+      <c r="DZ4" s="2" t="s">
+        <v>298</v>
+      </c>
+      <c r="EA4" s="2" t="s">
+        <v>298</v>
+      </c>
+      <c r="EB4" s="2" t="s">
+        <v>298</v>
+      </c>
+      <c r="EC4" s="2" t="s">
+        <v>291</v>
+      </c>
+      <c r="ED4" s="2" t="s">
+        <v>306</v>
+      </c>
+      <c r="EE4" s="2" t="s">
+        <v>306</v>
+      </c>
+      <c r="EF4" s="2" t="s">
+        <v>284</v>
+      </c>
+      <c r="EG4" s="2" t="s">
+        <v>293</v>
+      </c>
+      <c r="EH4" s="2" t="s">
+        <v>307</v>
+      </c>
+      <c r="EI4" s="2" t="s">
+        <v>330</v>
+      </c>
+      <c r="EJ4" s="2" t="s">
+        <v>330</v>
+      </c>
+      <c r="EK4" s="2" t="s">
+        <v>330</v>
+      </c>
+      <c r="EL4" s="2" t="s">
+        <v>286</v>
+      </c>
+      <c r="EM4" s="2" t="s">
+        <v>391</v>
+      </c>
+      <c r="EN4" s="2" t="s">
+        <v>392</v>
+      </c>
+      <c r="EO4" s="2" t="s">
+        <v>266</v>
+      </c>
+      <c r="EP4" s="2" t="s">
+        <v>309</v>
+      </c>
+      <c r="EQ4" s="2" t="s">
+        <v>332</v>
+      </c>
+      <c r="ER4" s="2" t="s">
+        <v>393</v>
+      </c>
+      <c r="ES4" s="2" t="s">
         <v>282</v>
       </c>
-      <c r="AU4" s="2" t="s">
+      <c r="ET4" s="2" t="s">
         <v>282</v>
       </c>
-      <c r="AV4" s="2" t="s">
-        <v>379</v>
-      </c>
-      <c r="AW4" s="2" t="s">
-        <v>266</v>
-      </c>
-      <c r="AX4" s="2" t="s">
-        <v>380</v>
-      </c>
-      <c r="AY4" s="2" t="s">
-        <v>266</v>
-      </c>
-      <c r="AZ4" s="2" t="s">
-        <v>320</v>
-      </c>
-      <c r="BA4" s="2" t="s">
-        <v>299</v>
-      </c>
-      <c r="BB4" s="2" t="s">
-        <v>299</v>
-      </c>
-      <c r="BC4" s="2" t="s">
-        <v>299</v>
-      </c>
-      <c r="BD4" s="2" t="s">
-        <v>307</v>
-      </c>
-      <c r="BE4" s="2" t="s">
-        <v>307</v>
-      </c>
-      <c r="BF4" s="2" t="s">
-        <v>307</v>
-      </c>
-      <c r="BG4" s="2" t="s">
-        <v>285</v>
-      </c>
-      <c r="BH4" s="2" t="s">
-        <v>294</v>
-      </c>
-      <c r="BI4" s="2" t="s">
-        <v>308</v>
-      </c>
-      <c r="BJ4" s="2" t="s">
-        <v>335</v>
-      </c>
-      <c r="BK4" s="2" t="s">
-        <v>335</v>
-      </c>
-      <c r="BL4" s="2" t="s">
-        <v>335</v>
-      </c>
-      <c r="BM4" s="2" t="s">
-        <v>295</v>
-      </c>
-      <c r="BN4" s="2" t="s">
-        <v>381</v>
-      </c>
-      <c r="BO4" s="2" t="s">
+      <c r="EU4" s="2" t="s">
+        <v>282</v>
+      </c>
+      <c r="EV4" s="2" t="s">
+        <v>306</v>
+      </c>
+      <c r="EW4" s="2" t="s">
+        <v>283</v>
+      </c>
+      <c r="EX4" s="2" t="s">
+        <v>283</v>
+      </c>
+      <c r="EY4" s="2" t="s">
+        <v>301</v>
+      </c>
+      <c r="EZ4" s="2" t="s">
+        <v>292</v>
+      </c>
+      <c r="FA4" s="2" t="s">
+        <v>292</v>
+      </c>
+      <c r="FB4" s="2" t="s">
+        <v>330</v>
+      </c>
+      <c r="FC4" s="2" t="s">
+        <v>330</v>
+      </c>
+      <c r="FD4" s="2" t="s">
+        <v>330</v>
+      </c>
+      <c r="FE4" s="2" t="s">
         <v>288</v>
       </c>
-      <c r="BP4" s="2" t="s">
-        <v>266</v>
-      </c>
-      <c r="BQ4" s="2" t="s">
-        <v>333</v>
-      </c>
-      <c r="BR4" s="2" t="s">
-        <v>289</v>
-      </c>
-      <c r="BS4" s="2" t="s">
-        <v>382</v>
-      </c>
-      <c r="BT4" s="2" t="s">
-        <v>299</v>
-      </c>
-      <c r="BU4" s="2" t="s">
-        <v>305</v>
-      </c>
-      <c r="BV4" s="2" t="s">
-        <v>291</v>
-      </c>
-      <c r="BW4" s="2" t="s">
-        <v>307</v>
-      </c>
-      <c r="BX4" s="2" t="s">
-        <v>307</v>
-      </c>
-      <c r="BY4" s="2" t="s">
-        <v>307</v>
-      </c>
-      <c r="BZ4" s="2" t="s">
-        <v>285</v>
-      </c>
-      <c r="CA4" s="2" t="s">
-        <v>294</v>
-      </c>
-      <c r="CB4" s="2" t="s">
-        <v>308</v>
-      </c>
-      <c r="CC4" s="2" t="s">
+      <c r="FF4" s="2" t="s">
+        <v>394</v>
+      </c>
+      <c r="FG4" s="2" t="s">
+        <v>386</v>
+      </c>
+      <c r="FH4" s="2" t="s">
+        <v>266</v>
+      </c>
+      <c r="FI4" s="2" t="s">
+        <v>309</v>
+      </c>
+      <c r="FJ4" s="2" t="s">
         <v>332</v>
       </c>
-      <c r="CD4" s="2" t="s">
-        <v>383</v>
-      </c>
-      <c r="CE4" s="2" t="s">
-        <v>357</v>
-      </c>
-      <c r="CF4" s="2" t="s">
-        <v>295</v>
-      </c>
-      <c r="CG4" s="2" t="s">
-        <v>384</v>
-      </c>
-      <c r="CH4" s="2" t="s">
-        <v>355</v>
-      </c>
-      <c r="CI4" s="2" t="s">
-        <v>266</v>
-      </c>
-      <c r="CJ4" s="2" t="s">
-        <v>297</v>
-      </c>
-      <c r="CK4" s="2" t="s">
-        <v>289</v>
-      </c>
-      <c r="CL4" s="2" t="s">
-        <v>385</v>
-      </c>
-      <c r="CM4" s="2" t="s">
-        <v>283</v>
-      </c>
-      <c r="CN4" s="2" t="s">
-        <v>283</v>
-      </c>
-      <c r="CO4" s="2" t="s">
-        <v>283</v>
-      </c>
-      <c r="CP4" s="2" t="s">
-        <v>306</v>
-      </c>
-      <c r="CQ4" s="2" t="s">
-        <v>301</v>
-      </c>
-      <c r="CR4" s="2" t="s">
-        <v>307</v>
-      </c>
-      <c r="CS4" s="2" t="s">
-        <v>302</v>
-      </c>
-      <c r="CT4" s="2" t="s">
-        <v>293</v>
-      </c>
-      <c r="CU4" s="2" t="s">
-        <v>286</v>
-      </c>
-      <c r="CV4" s="2" t="s">
-        <v>332</v>
-      </c>
-      <c r="CW4" s="2" t="s">
-        <v>332</v>
-      </c>
-      <c r="CX4" s="2" t="s">
-        <v>332</v>
-      </c>
-      <c r="CY4" s="2" t="s">
-        <v>289</v>
-      </c>
-      <c r="CZ4" s="2" t="s">
-        <v>386</v>
-      </c>
-      <c r="DA4" s="2" t="s">
-        <v>387</v>
-      </c>
-      <c r="DB4" s="2" t="s">
-        <v>266</v>
-      </c>
-      <c r="DC4" s="2" t="s">
+      <c r="FK4" s="2" t="s">
+        <v>395</v>
+      </c>
+      <c r="FL4" s="2" t="s">
+        <v>396</v>
+      </c>
+      <c r="FM4" s="2" t="s">
         <v>311</v>
       </c>
-      <c r="DD4" s="2" t="s">
-        <v>334</v>
-      </c>
-      <c r="DE4" s="2" t="s">
-        <v>388</v>
-      </c>
-      <c r="DF4" s="2" t="s">
-        <v>304</v>
-      </c>
-      <c r="DG4" s="2" t="s">
-        <v>283</v>
-      </c>
-      <c r="DH4" s="2" t="s">
-        <v>283</v>
-      </c>
-      <c r="DI4" s="2" t="s">
-        <v>326</v>
-      </c>
-      <c r="DJ4" s="2" t="s">
-        <v>307</v>
-      </c>
-      <c r="DK4" s="2" t="s">
-        <v>284</v>
-      </c>
-      <c r="DL4" s="2" t="s">
-        <v>307</v>
-      </c>
-      <c r="DM4" s="2" t="s">
-        <v>285</v>
-      </c>
-      <c r="DN4" s="2" t="s">
-        <v>285</v>
-      </c>
-      <c r="DO4" s="2" t="s">
-        <v>294</v>
-      </c>
-      <c r="DP4" s="2" t="s">
-        <v>332</v>
-      </c>
-      <c r="DQ4" s="2" t="s">
-        <v>335</v>
-      </c>
-      <c r="DR4" s="2" t="s">
-        <v>341</v>
-      </c>
-      <c r="DS4" s="2" t="s">
-        <v>298</v>
-      </c>
-      <c r="DT4" s="2" t="s">
-        <v>389</v>
-      </c>
-      <c r="DU4" s="2" t="s">
-        <v>390</v>
-      </c>
-      <c r="DV4" s="2" t="s">
-        <v>266</v>
-      </c>
-      <c r="DW4" s="2" t="s">
+      <c r="FN4" s="2" t="s">
         <v>311</v>
       </c>
-      <c r="DX4" s="2" t="s">
-        <v>334</v>
-      </c>
-      <c r="DY4" s="2" t="s">
-        <v>391</v>
-      </c>
-      <c r="DZ4" s="2" t="s">
-        <v>299</v>
-      </c>
-      <c r="EA4" s="2" t="s">
-        <v>299</v>
-      </c>
-      <c r="EB4" s="2" t="s">
-        <v>299</v>
-      </c>
-      <c r="EC4" s="2" t="s">
-        <v>292</v>
-      </c>
-      <c r="ED4" s="2" t="s">
-        <v>307</v>
-      </c>
-      <c r="EE4" s="2" t="s">
-        <v>307</v>
-      </c>
-      <c r="EF4" s="2" t="s">
-        <v>285</v>
-      </c>
-      <c r="EG4" s="2" t="s">
-        <v>294</v>
-      </c>
-      <c r="EH4" s="2" t="s">
-        <v>308</v>
-      </c>
-      <c r="EI4" s="2" t="s">
-        <v>332</v>
-      </c>
-      <c r="EJ4" s="2" t="s">
-        <v>332</v>
-      </c>
-      <c r="EK4" s="2" t="s">
-        <v>332</v>
-      </c>
-      <c r="EL4" s="2" t="s">
-        <v>287</v>
-      </c>
-      <c r="EM4" s="2" t="s">
-        <v>392</v>
-      </c>
-      <c r="EN4" s="2" t="s">
-        <v>393</v>
-      </c>
-      <c r="EO4" s="2" t="s">
-        <v>266</v>
-      </c>
-      <c r="EP4" s="2" t="s">
-        <v>311</v>
-      </c>
-      <c r="EQ4" s="2" t="s">
-        <v>334</v>
-      </c>
-      <c r="ER4" s="2" t="s">
-        <v>394</v>
-      </c>
-      <c r="ES4" s="2" t="s">
-        <v>283</v>
-      </c>
-      <c r="ET4" s="2" t="s">
-        <v>283</v>
-      </c>
-      <c r="EU4" s="2" t="s">
-        <v>283</v>
-      </c>
-      <c r="EV4" s="2" t="s">
-        <v>307</v>
-      </c>
-      <c r="EW4" s="2" t="s">
-        <v>284</v>
-      </c>
-      <c r="EX4" s="2" t="s">
-        <v>284</v>
-      </c>
-      <c r="EY4" s="2" t="s">
-        <v>302</v>
-      </c>
-      <c r="EZ4" s="2" t="s">
-        <v>293</v>
-      </c>
-      <c r="FA4" s="2" t="s">
-        <v>293</v>
-      </c>
-      <c r="FB4" s="2" t="s">
-        <v>332</v>
-      </c>
-      <c r="FC4" s="2" t="s">
-        <v>332</v>
-      </c>
-      <c r="FD4" s="2" t="s">
-        <v>332</v>
-      </c>
-      <c r="FE4" s="2" t="s">
-        <v>289</v>
-      </c>
-      <c r="FF4" s="2" t="s">
-        <v>395</v>
-      </c>
-      <c r="FG4" s="2" t="s">
-        <v>387</v>
-      </c>
-      <c r="FH4" s="2" t="s">
-        <v>266</v>
-      </c>
-      <c r="FI4" s="2" t="s">
-        <v>311</v>
-      </c>
-      <c r="FJ4" s="2" t="s">
-        <v>334</v>
-      </c>
-      <c r="FK4" s="2" t="s">
-        <v>396</v>
-      </c>
-      <c r="FL4" s="2" t="s">
+      <c r="FO4" s="2" t="s">
+        <v>312</v>
+      </c>
+      <c r="FP4" s="2" t="s">
+        <v>314</v>
+      </c>
+      <c r="FQ4" s="2" t="s">
+        <v>315</v>
+      </c>
+      <c r="FR4" s="2" t="s">
+        <v>315</v>
+      </c>
+      <c r="FS4" s="2" t="s">
+        <v>315</v>
+      </c>
+      <c r="FT4" s="2" t="s">
         <v>397</v>
       </c>
-      <c r="FM4" s="2" t="s">
-        <v>313</v>
-      </c>
-      <c r="FN4" s="2" t="s">
-        <v>313</v>
-      </c>
-      <c r="FO4" s="2" t="s">
-        <v>314</v>
-      </c>
-      <c r="FP4" s="2" t="s">
-        <v>316</v>
-      </c>
-      <c r="FQ4" s="2" t="s">
-        <v>317</v>
-      </c>
-      <c r="FR4" s="2" t="s">
-        <v>317</v>
-      </c>
-      <c r="FS4" s="2" t="s">
-        <v>317</v>
-      </c>
-      <c r="FT4" s="2" t="s">
+      <c r="FU4" s="2" t="s">
+        <v>318</v>
+      </c>
+      <c r="FV4" s="2" t="s">
+        <v>280</v>
+      </c>
+      <c r="FW4" s="2" t="s">
+        <v>280</v>
+      </c>
+      <c r="FX4" s="2" t="s">
+        <v>266</v>
+      </c>
+      <c r="FY4" s="2" t="s">
+        <v>266</v>
+      </c>
+      <c r="FZ4" s="2" t="s">
         <v>398</v>
       </c>
-      <c r="FU4" s="2" t="s">
-        <v>320</v>
-      </c>
-      <c r="FV4" s="2" t="s">
-        <v>282</v>
-      </c>
-      <c r="FW4" s="2" t="s">
-        <v>282</v>
-      </c>
-      <c r="FX4" s="2" t="s">
-        <v>266</v>
-      </c>
-      <c r="FY4" s="2" t="s">
-        <v>266</v>
-      </c>
-      <c r="FZ4" s="2" t="s">
-        <v>399</v>
-      </c>
     </row>
-    <row r="5" spans="1:182" ht="15" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="5" spans="1:182" ht="20.05" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A5" s="1">
         <v>46194.583449074074</v>
       </c>
@@ -4145,7 +4024,7 @@
         <v>185</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>400</v>
+        <v>399</v>
       </c>
       <c r="E5">
         <v>100</v>
@@ -4160,7 +4039,7 @@
         <v>46194.602760381946</v>
       </c>
       <c r="I5" s="2" t="s">
-        <v>401</v>
+        <v>400</v>
       </c>
       <c r="J5" s="2" t="s">
         <v>266</v>
@@ -4187,7 +4066,7 @@
         <v>268</v>
       </c>
       <c r="R5" s="2" t="s">
-        <v>330</v>
+        <v>328</v>
       </c>
       <c r="S5" s="2" t="s">
         <v>269</v>
@@ -4202,7 +4081,7 @@
         <v>25</v>
       </c>
       <c r="W5" s="2" t="s">
-        <v>321</v>
+        <v>319</v>
       </c>
       <c r="X5" s="2" t="s">
         <v>273</v>
@@ -4211,7 +4090,7 @@
         <v>274</v>
       </c>
       <c r="Z5" s="2" t="s">
-        <v>345</v>
+        <v>344</v>
       </c>
       <c r="AA5" s="2" t="s">
         <v>276</v>
@@ -4220,495 +4099,495 @@
         <v>266</v>
       </c>
       <c r="AC5" s="2" t="s">
-        <v>346</v>
+        <v>345</v>
       </c>
       <c r="AD5" s="2" t="s">
-        <v>339</v>
+        <v>337</v>
       </c>
       <c r="AE5" s="2" t="s">
+        <v>401</v>
+      </c>
+      <c r="AF5" s="2" t="s">
+        <v>266</v>
+      </c>
+      <c r="AG5" s="2" t="s">
+        <v>320</v>
+      </c>
+      <c r="AH5" s="2" t="s">
+        <v>321</v>
+      </c>
+      <c r="AI5" s="2" t="s">
         <v>402</v>
       </c>
-      <c r="AF5" s="2" t="s">
-        <v>266</v>
-      </c>
-      <c r="AG5" s="2" t="s">
-        <v>322</v>
-      </c>
-      <c r="AH5" s="2" t="s">
+      <c r="AJ5" s="2" t="s">
+        <v>266</v>
+      </c>
+      <c r="AK5" s="2" t="s">
+        <v>278</v>
+      </c>
+      <c r="AL5" s="2" t="s">
+        <v>278</v>
+      </c>
+      <c r="AM5" s="2" t="s">
+        <v>277</v>
+      </c>
+      <c r="AN5" s="2" t="s">
+        <v>318</v>
+      </c>
+      <c r="AO5" s="2" t="s">
         <v>323</v>
       </c>
-      <c r="AI5" s="2" t="s">
+      <c r="AP5" s="2" t="s">
+        <v>323</v>
+      </c>
+      <c r="AQ5" s="2" t="s">
+        <v>348</v>
+      </c>
+      <c r="AR5" s="2" t="s">
         <v>403</v>
       </c>
-      <c r="AJ5" s="2" t="s">
-        <v>266</v>
-      </c>
-      <c r="AK5" s="2" t="s">
-        <v>279</v>
-      </c>
-      <c r="AL5" s="2" t="s">
-        <v>279</v>
-      </c>
-      <c r="AM5" s="2" t="s">
+      <c r="AS5" s="2" t="s">
+        <v>404</v>
+      </c>
+      <c r="AT5" s="2" t="s">
+        <v>280</v>
+      </c>
+      <c r="AU5" s="2" t="s">
         <v>278</v>
       </c>
-      <c r="AN5" s="2" t="s">
-        <v>320</v>
-      </c>
-      <c r="AO5" s="2" t="s">
+      <c r="AV5" s="2" t="s">
+        <v>405</v>
+      </c>
+      <c r="AW5" s="2" t="s">
+        <v>266</v>
+      </c>
+      <c r="AX5" s="2" t="s">
+        <v>352</v>
+      </c>
+      <c r="AY5" s="2" t="s">
+        <v>266</v>
+      </c>
+      <c r="AZ5" s="2" t="s">
+        <v>338</v>
+      </c>
+      <c r="BA5" s="2" t="s">
+        <v>282</v>
+      </c>
+      <c r="BB5" s="2" t="s">
+        <v>282</v>
+      </c>
+      <c r="BC5" s="2" t="s">
+        <v>298</v>
+      </c>
+      <c r="BD5" s="2" t="s">
+        <v>283</v>
+      </c>
+      <c r="BE5" s="2" t="s">
+        <v>283</v>
+      </c>
+      <c r="BF5" s="2" t="s">
+        <v>283</v>
+      </c>
+      <c r="BG5" s="2" t="s">
+        <v>284</v>
+      </c>
+      <c r="BH5" s="2" t="s">
+        <v>292</v>
+      </c>
+      <c r="BI5" s="2" t="s">
+        <v>285</v>
+      </c>
+      <c r="BJ5" s="2" t="s">
+        <v>330</v>
+      </c>
+      <c r="BK5" s="2" t="s">
+        <v>333</v>
+      </c>
+      <c r="BL5" s="2" t="s">
+        <v>333</v>
+      </c>
+      <c r="BM5" s="2" t="s">
+        <v>297</v>
+      </c>
+      <c r="BN5" s="2" t="s">
+        <v>406</v>
+      </c>
+      <c r="BO5" s="2" t="s">
+        <v>407</v>
+      </c>
+      <c r="BP5" s="2" t="s">
+        <v>266</v>
+      </c>
+      <c r="BQ5" s="2" t="s">
+        <v>309</v>
+      </c>
+      <c r="BR5" s="2" t="s">
+        <v>332</v>
+      </c>
+      <c r="BS5" s="2" t="s">
+        <v>408</v>
+      </c>
+      <c r="BT5" s="2" t="s">
+        <v>289</v>
+      </c>
+      <c r="BU5" s="2" t="s">
+        <v>304</v>
+      </c>
+      <c r="BV5" s="2" t="s">
+        <v>290</v>
+      </c>
+      <c r="BW5" s="2" t="s">
+        <v>306</v>
+      </c>
+      <c r="BX5" s="2" t="s">
+        <v>283</v>
+      </c>
+      <c r="BY5" s="2" t="s">
+        <v>283</v>
+      </c>
+      <c r="BZ5" s="2" t="s">
         <v>325</v>
       </c>
-      <c r="AP5" s="2" t="s">
+      <c r="CA5" s="2" t="s">
+        <v>293</v>
+      </c>
+      <c r="CB5" s="2" t="s">
+        <v>307</v>
+      </c>
+      <c r="CC5" s="2" t="s">
+        <v>340</v>
+      </c>
+      <c r="CD5" s="2" t="s">
+        <v>340</v>
+      </c>
+      <c r="CE5" s="2" t="s">
+        <v>382</v>
+      </c>
+      <c r="CF5" s="2" t="s">
+        <v>294</v>
+      </c>
+      <c r="CG5" s="2" t="s">
+        <v>409</v>
+      </c>
+      <c r="CH5" s="2" t="s">
+        <v>295</v>
+      </c>
+      <c r="CI5" s="2" t="s">
+        <v>266</v>
+      </c>
+      <c r="CJ5" s="2" t="s">
+        <v>296</v>
+      </c>
+      <c r="CK5" s="2" t="s">
+        <v>297</v>
+      </c>
+      <c r="CL5" s="2" t="s">
+        <v>410</v>
+      </c>
+      <c r="CM5" s="2" t="s">
+        <v>282</v>
+      </c>
+      <c r="CN5" s="2" t="s">
+        <v>282</v>
+      </c>
+      <c r="CO5" s="2" t="s">
+        <v>282</v>
+      </c>
+      <c r="CP5" s="2" t="s">
+        <v>306</v>
+      </c>
+      <c r="CQ5" s="2" t="s">
+        <v>283</v>
+      </c>
+      <c r="CR5" s="2" t="s">
+        <v>283</v>
+      </c>
+      <c r="CS5" s="2" t="s">
+        <v>284</v>
+      </c>
+      <c r="CT5" s="2" t="s">
+        <v>285</v>
+      </c>
+      <c r="CU5" s="2" t="s">
         <v>325</v>
       </c>
-      <c r="AQ5" s="2" t="s">
-        <v>349</v>
-      </c>
-      <c r="AR5" s="2" t="s">
-        <v>404</v>
-      </c>
-      <c r="AS5" s="2" t="s">
-        <v>405</v>
-      </c>
-      <c r="AT5" s="2" t="s">
+      <c r="CV5" s="2" t="s">
+        <v>330</v>
+      </c>
+      <c r="CW5" s="2" t="s">
+        <v>330</v>
+      </c>
+      <c r="CX5" s="2" t="s">
+        <v>333</v>
+      </c>
+      <c r="CY5" s="2" t="s">
+        <v>297</v>
+      </c>
+      <c r="CZ5" s="2" t="s">
+        <v>411</v>
+      </c>
+      <c r="DA5" s="2" t="s">
+        <v>412</v>
+      </c>
+      <c r="DB5" s="2" t="s">
+        <v>266</v>
+      </c>
+      <c r="DC5" s="2" t="s">
+        <v>309</v>
+      </c>
+      <c r="DD5" s="2" t="s">
+        <v>332</v>
+      </c>
+      <c r="DE5" s="2" t="s">
+        <v>413</v>
+      </c>
+      <c r="DF5" s="2" t="s">
+        <v>303</v>
+      </c>
+      <c r="DG5" s="2" t="s">
+        <v>298</v>
+      </c>
+      <c r="DH5" s="2" t="s">
+        <v>324</v>
+      </c>
+      <c r="DI5" s="2" t="s">
+        <v>289</v>
+      </c>
+      <c r="DJ5" s="2" t="s">
+        <v>306</v>
+      </c>
+      <c r="DK5" s="2" t="s">
+        <v>283</v>
+      </c>
+      <c r="DL5" s="2" t="s">
+        <v>283</v>
+      </c>
+      <c r="DM5" s="2" t="s">
+        <v>292</v>
+      </c>
+      <c r="DN5" s="2" t="s">
+        <v>325</v>
+      </c>
+      <c r="DO5" s="2" t="s">
+        <v>307</v>
+      </c>
+      <c r="DP5" s="2" t="s">
+        <v>330</v>
+      </c>
+      <c r="DQ5" s="2" t="s">
+        <v>333</v>
+      </c>
+      <c r="DR5" s="2" t="s">
+        <v>341</v>
+      </c>
+      <c r="DS5" s="2" t="s">
+        <v>286</v>
+      </c>
+      <c r="DT5" s="2" t="s">
+        <v>414</v>
+      </c>
+      <c r="DU5" s="2" t="s">
+        <v>392</v>
+      </c>
+      <c r="DV5" s="2" t="s">
+        <v>266</v>
+      </c>
+      <c r="DW5" s="2" t="s">
+        <v>308</v>
+      </c>
+      <c r="DX5" s="2" t="s">
+        <v>297</v>
+      </c>
+      <c r="DY5" s="2" t="s">
+        <v>415</v>
+      </c>
+      <c r="DZ5" s="2" t="s">
+        <v>298</v>
+      </c>
+      <c r="EA5" s="2" t="s">
+        <v>299</v>
+      </c>
+      <c r="EB5" s="2" t="s">
+        <v>324</v>
+      </c>
+      <c r="EC5" s="2" t="s">
+        <v>306</v>
+      </c>
+      <c r="ED5" s="2" t="s">
+        <v>283</v>
+      </c>
+      <c r="EE5" s="2" t="s">
+        <v>283</v>
+      </c>
+      <c r="EF5" s="2" t="s">
+        <v>292</v>
+      </c>
+      <c r="EG5" s="2" t="s">
+        <v>325</v>
+      </c>
+      <c r="EH5" s="2" t="s">
+        <v>293</v>
+      </c>
+      <c r="EI5" s="2" t="s">
+        <v>330</v>
+      </c>
+      <c r="EJ5" s="2" t="s">
+        <v>333</v>
+      </c>
+      <c r="EK5" s="2" t="s">
+        <v>341</v>
+      </c>
+      <c r="EL5" s="2" t="s">
+        <v>286</v>
+      </c>
+      <c r="EM5" s="2" t="s">
+        <v>416</v>
+      </c>
+      <c r="EN5" s="2" t="s">
+        <v>327</v>
+      </c>
+      <c r="EO5" s="2" t="s">
+        <v>266</v>
+      </c>
+      <c r="EP5" s="2" t="s">
+        <v>335</v>
+      </c>
+      <c r="EQ5" s="2" t="s">
+        <v>288</v>
+      </c>
+      <c r="ER5" s="2" t="s">
+        <v>417</v>
+      </c>
+      <c r="ES5" s="2" t="s">
         <v>282</v>
       </c>
-      <c r="AU5" s="2" t="s">
-        <v>279</v>
-      </c>
-      <c r="AV5" s="2" t="s">
-        <v>406</v>
-      </c>
-      <c r="AW5" s="2" t="s">
-        <v>266</v>
-      </c>
-      <c r="AX5" s="2" t="s">
-        <v>353</v>
-      </c>
-      <c r="AY5" s="2" t="s">
-        <v>266</v>
-      </c>
-      <c r="AZ5" s="2" t="s">
-        <v>340</v>
-      </c>
-      <c r="BA5" s="2" t="s">
+      <c r="ET5" s="2" t="s">
+        <v>298</v>
+      </c>
+      <c r="EU5" s="2" t="s">
+        <v>298</v>
+      </c>
+      <c r="EV5" s="2" t="s">
+        <v>306</v>
+      </c>
+      <c r="EW5" s="2" t="s">
         <v>283</v>
       </c>
-      <c r="BB5" s="2" t="s">
+      <c r="EX5" s="2" t="s">
         <v>283</v>
       </c>
-      <c r="BC5" s="2" t="s">
-        <v>299</v>
-      </c>
-      <c r="BD5" s="2" t="s">
+      <c r="EY5" s="2" t="s">
         <v>284</v>
       </c>
-      <c r="BE5" s="2" t="s">
-        <v>284</v>
-      </c>
-      <c r="BF5" s="2" t="s">
-        <v>284</v>
-      </c>
-      <c r="BG5" s="2" t="s">
+      <c r="EZ5" s="2" t="s">
+        <v>292</v>
+      </c>
+      <c r="FA5" s="2" t="s">
         <v>285</v>
       </c>
-      <c r="BH5" s="2" t="s">
-        <v>293</v>
-      </c>
-      <c r="BI5" s="2" t="s">
+      <c r="FB5" s="2" t="s">
+        <v>330</v>
+      </c>
+      <c r="FC5" s="2" t="s">
+        <v>333</v>
+      </c>
+      <c r="FD5" s="2" t="s">
+        <v>333</v>
+      </c>
+      <c r="FE5" s="2" t="s">
         <v>286</v>
       </c>
-      <c r="BJ5" s="2" t="s">
-        <v>332</v>
-      </c>
-      <c r="BK5" s="2" t="s">
-        <v>335</v>
-      </c>
-      <c r="BL5" s="2" t="s">
-        <v>335</v>
-      </c>
-      <c r="BM5" s="2" t="s">
-        <v>298</v>
-      </c>
-      <c r="BN5" s="2" t="s">
-        <v>407</v>
-      </c>
-      <c r="BO5" s="2" t="s">
-        <v>408</v>
-      </c>
-      <c r="BP5" s="2" t="s">
-        <v>266</v>
-      </c>
-      <c r="BQ5" s="2" t="s">
+      <c r="FF5" s="2" t="s">
+        <v>418</v>
+      </c>
+      <c r="FG5" s="2" t="s">
+        <v>419</v>
+      </c>
+      <c r="FH5" s="2" t="s">
+        <v>266</v>
+      </c>
+      <c r="FI5" s="2" t="s">
+        <v>336</v>
+      </c>
+      <c r="FJ5" s="2" t="s">
+        <v>288</v>
+      </c>
+      <c r="FK5" s="2" t="s">
+        <v>420</v>
+      </c>
+      <c r="FL5" s="2" t="s">
+        <v>396</v>
+      </c>
+      <c r="FM5" s="2" t="s">
+        <v>312</v>
+      </c>
+      <c r="FN5" s="2" t="s">
+        <v>312</v>
+      </c>
+      <c r="FO5" s="2" t="s">
         <v>311</v>
       </c>
-      <c r="BR5" s="2" t="s">
-        <v>334</v>
-      </c>
-      <c r="BS5" s="2" t="s">
-        <v>409</v>
-      </c>
-      <c r="BT5" s="2" t="s">
-        <v>290</v>
-      </c>
-      <c r="BU5" s="2" t="s">
-        <v>305</v>
-      </c>
-      <c r="BV5" s="2" t="s">
-        <v>291</v>
-      </c>
-      <c r="BW5" s="2" t="s">
-        <v>307</v>
-      </c>
-      <c r="BX5" s="2" t="s">
-        <v>284</v>
-      </c>
-      <c r="BY5" s="2" t="s">
-        <v>284</v>
-      </c>
-      <c r="BZ5" s="2" t="s">
-        <v>327</v>
-      </c>
-      <c r="CA5" s="2" t="s">
-        <v>294</v>
-      </c>
-      <c r="CB5" s="2" t="s">
-        <v>308</v>
-      </c>
-      <c r="CC5" s="2" t="s">
-        <v>341</v>
-      </c>
-      <c r="CD5" s="2" t="s">
-        <v>341</v>
-      </c>
-      <c r="CE5" s="2" t="s">
-        <v>383</v>
-      </c>
-      <c r="CF5" s="2" t="s">
-        <v>295</v>
-      </c>
-      <c r="CG5" s="2" t="s">
-        <v>410</v>
-      </c>
-      <c r="CH5" s="2" t="s">
-        <v>296</v>
-      </c>
-      <c r="CI5" s="2" t="s">
-        <v>266</v>
-      </c>
-      <c r="CJ5" s="2" t="s">
-        <v>297</v>
-      </c>
-      <c r="CK5" s="2" t="s">
-        <v>298</v>
-      </c>
-      <c r="CL5" s="2" t="s">
-        <v>411</v>
-      </c>
-      <c r="CM5" s="2" t="s">
-        <v>283</v>
-      </c>
-      <c r="CN5" s="2" t="s">
-        <v>283</v>
-      </c>
-      <c r="CO5" s="2" t="s">
-        <v>283</v>
-      </c>
-      <c r="CP5" s="2" t="s">
-        <v>307</v>
-      </c>
-      <c r="CQ5" s="2" t="s">
-        <v>284</v>
-      </c>
-      <c r="CR5" s="2" t="s">
-        <v>284</v>
-      </c>
-      <c r="CS5" s="2" t="s">
-        <v>285</v>
-      </c>
-      <c r="CT5" s="2" t="s">
-        <v>286</v>
-      </c>
-      <c r="CU5" s="2" t="s">
-        <v>327</v>
-      </c>
-      <c r="CV5" s="2" t="s">
-        <v>332</v>
-      </c>
-      <c r="CW5" s="2" t="s">
-        <v>332</v>
-      </c>
-      <c r="CX5" s="2" t="s">
-        <v>335</v>
-      </c>
-      <c r="CY5" s="2" t="s">
-        <v>298</v>
-      </c>
-      <c r="CZ5" s="2" t="s">
-        <v>412</v>
-      </c>
-      <c r="DA5" s="2" t="s">
-        <v>413</v>
-      </c>
-      <c r="DB5" s="2" t="s">
-        <v>266</v>
-      </c>
-      <c r="DC5" s="2" t="s">
-        <v>311</v>
-      </c>
-      <c r="DD5" s="2" t="s">
-        <v>334</v>
-      </c>
-      <c r="DE5" s="2" t="s">
-        <v>414</v>
-      </c>
-      <c r="DF5" s="2" t="s">
-        <v>304</v>
-      </c>
-      <c r="DG5" s="2" t="s">
-        <v>299</v>
-      </c>
-      <c r="DH5" s="2" t="s">
-        <v>326</v>
-      </c>
-      <c r="DI5" s="2" t="s">
-        <v>290</v>
-      </c>
-      <c r="DJ5" s="2" t="s">
-        <v>307</v>
-      </c>
-      <c r="DK5" s="2" t="s">
-        <v>284</v>
-      </c>
-      <c r="DL5" s="2" t="s">
-        <v>284</v>
-      </c>
-      <c r="DM5" s="2" t="s">
-        <v>293</v>
-      </c>
-      <c r="DN5" s="2" t="s">
-        <v>327</v>
-      </c>
-      <c r="DO5" s="2" t="s">
-        <v>308</v>
-      </c>
-      <c r="DP5" s="2" t="s">
-        <v>332</v>
-      </c>
-      <c r="DQ5" s="2" t="s">
-        <v>335</v>
-      </c>
-      <c r="DR5" s="2" t="s">
-        <v>342</v>
-      </c>
-      <c r="DS5" s="2" t="s">
-        <v>287</v>
-      </c>
-      <c r="DT5" s="2" t="s">
-        <v>415</v>
-      </c>
-      <c r="DU5" s="2" t="s">
-        <v>393</v>
-      </c>
-      <c r="DV5" s="2" t="s">
-        <v>266</v>
-      </c>
-      <c r="DW5" s="2" t="s">
-        <v>309</v>
-      </c>
-      <c r="DX5" s="2" t="s">
-        <v>298</v>
-      </c>
-      <c r="DY5" s="2" t="s">
-        <v>416</v>
-      </c>
-      <c r="DZ5" s="2" t="s">
-        <v>299</v>
-      </c>
-      <c r="EA5" s="2" t="s">
-        <v>300</v>
-      </c>
-      <c r="EB5" s="2" t="s">
-        <v>326</v>
-      </c>
-      <c r="EC5" s="2" t="s">
-        <v>307</v>
-      </c>
-      <c r="ED5" s="2" t="s">
-        <v>284</v>
-      </c>
-      <c r="EE5" s="2" t="s">
-        <v>284</v>
-      </c>
-      <c r="EF5" s="2" t="s">
-        <v>293</v>
-      </c>
-      <c r="EG5" s="2" t="s">
-        <v>327</v>
-      </c>
-      <c r="EH5" s="2" t="s">
-        <v>294</v>
-      </c>
-      <c r="EI5" s="2" t="s">
-        <v>332</v>
-      </c>
-      <c r="EJ5" s="2" t="s">
-        <v>335</v>
-      </c>
-      <c r="EK5" s="2" t="s">
-        <v>342</v>
-      </c>
-      <c r="EL5" s="2" t="s">
-        <v>287</v>
-      </c>
-      <c r="EM5" s="2" t="s">
-        <v>417</v>
-      </c>
-      <c r="EN5" s="2" t="s">
-        <v>329</v>
-      </c>
-      <c r="EO5" s="2" t="s">
-        <v>266</v>
-      </c>
-      <c r="EP5" s="2" t="s">
-        <v>337</v>
-      </c>
-      <c r="EQ5" s="2" t="s">
-        <v>289</v>
-      </c>
-      <c r="ER5" s="2" t="s">
-        <v>418</v>
-      </c>
-      <c r="ES5" s="2" t="s">
-        <v>283</v>
-      </c>
-      <c r="ET5" s="2" t="s">
-        <v>299</v>
-      </c>
-      <c r="EU5" s="2" t="s">
-        <v>299</v>
-      </c>
-      <c r="EV5" s="2" t="s">
-        <v>307</v>
-      </c>
-      <c r="EW5" s="2" t="s">
-        <v>284</v>
-      </c>
-      <c r="EX5" s="2" t="s">
-        <v>284</v>
-      </c>
-      <c r="EY5" s="2" t="s">
-        <v>285</v>
-      </c>
-      <c r="EZ5" s="2" t="s">
-        <v>293</v>
-      </c>
-      <c r="FA5" s="2" t="s">
-        <v>286</v>
-      </c>
-      <c r="FB5" s="2" t="s">
-        <v>332</v>
-      </c>
-      <c r="FC5" s="2" t="s">
-        <v>335</v>
-      </c>
-      <c r="FD5" s="2" t="s">
-        <v>335</v>
-      </c>
-      <c r="FE5" s="2" t="s">
-        <v>287</v>
-      </c>
-      <c r="FF5" s="2" t="s">
-        <v>419</v>
-      </c>
-      <c r="FG5" s="2" t="s">
-        <v>420</v>
-      </c>
-      <c r="FH5" s="2" t="s">
-        <v>266</v>
-      </c>
-      <c r="FI5" s="2" t="s">
+      <c r="FP5" s="2" t="s">
+        <v>313</v>
+      </c>
+      <c r="FQ5" s="2" t="s">
+        <v>316</v>
+      </c>
+      <c r="FR5" s="2" t="s">
+        <v>315</v>
+      </c>
+      <c r="FS5" s="2" t="s">
+        <v>315</v>
+      </c>
+      <c r="FT5" s="2" t="s">
+        <v>317</v>
+      </c>
+      <c r="FU5" s="2" t="s">
+        <v>323</v>
+      </c>
+      <c r="FV5" s="2" t="s">
         <v>338</v>
       </c>
-      <c r="FJ5" s="2" t="s">
-        <v>289</v>
-      </c>
-      <c r="FK5" s="2" t="s">
+      <c r="FW5" s="2" t="s">
+        <v>280</v>
+      </c>
+      <c r="FX5" s="2" t="s">
         <v>421</v>
       </c>
-      <c r="FL5" s="2" t="s">
-        <v>397</v>
-      </c>
-      <c r="FM5" s="2" t="s">
-        <v>314</v>
-      </c>
-      <c r="FN5" s="2" t="s">
-        <v>314</v>
-      </c>
-      <c r="FO5" s="2" t="s">
-        <v>313</v>
-      </c>
-      <c r="FP5" s="2" t="s">
-        <v>315</v>
-      </c>
-      <c r="FQ5" s="2" t="s">
-        <v>318</v>
-      </c>
-      <c r="FR5" s="2" t="s">
-        <v>317</v>
-      </c>
-      <c r="FS5" s="2" t="s">
-        <v>317</v>
-      </c>
-      <c r="FT5" s="2" t="s">
-        <v>319</v>
-      </c>
-      <c r="FU5" s="2" t="s">
-        <v>325</v>
-      </c>
-      <c r="FV5" s="2" t="s">
-        <v>340</v>
-      </c>
-      <c r="FW5" s="2" t="s">
-        <v>282</v>
-      </c>
-      <c r="FX5" s="2" t="s">
+      <c r="FY5" s="2" t="s">
+        <v>266</v>
+      </c>
+      <c r="FZ5" s="2" t="s">
         <v>422</v>
       </c>
-      <c r="FY5" s="2" t="s">
-        <v>266</v>
-      </c>
-      <c r="FZ5" s="2" t="s">
-        <v>423</v>
-      </c>
     </row>
-    <row r="6" spans="1:182" ht="15" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="6" spans="1:182" ht="20.05" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A6" s="1">
-        <v>46194.627511574072</v>
+        <v>46196.361087962963</v>
       </c>
       <c r="B6" s="1">
-        <v>46194.643888888888</v>
+        <v>46196.379930555559</v>
       </c>
       <c r="C6" s="2" t="s">
         <v>185</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>424</v>
+        <v>423</v>
       </c>
       <c r="E6">
         <v>100</v>
       </c>
       <c r="F6">
-        <v>1414</v>
+        <v>1628</v>
       </c>
       <c r="G6" s="2" t="s">
         <v>265</v>
       </c>
       <c r="H6" s="1">
-        <v>46194.643903460645</v>
+        <v>46196.379947731482</v>
       </c>
       <c r="I6" s="2" t="s">
-        <v>425</v>
+        <v>424</v>
       </c>
       <c r="J6" s="2" t="s">
         <v>266</v>
@@ -4723,10 +4602,10 @@
         <v>266</v>
       </c>
       <c r="N6">
-        <v>51.4724</v>
+        <v>48.767000000000003</v>
       </c>
       <c r="O6">
-        <v>11.9572</v>
+        <v>9.1827000000000005</v>
       </c>
       <c r="P6" s="2" t="s">
         <v>267</v>
@@ -4735,22 +4614,22 @@
         <v>268</v>
       </c>
       <c r="R6" s="2" t="s">
-        <v>330</v>
+        <v>328</v>
       </c>
       <c r="S6" s="2" t="s">
-        <v>426</v>
+        <v>269</v>
       </c>
       <c r="T6" s="2" t="s">
         <v>270</v>
       </c>
       <c r="U6" s="2" t="s">
-        <v>427</v>
+        <v>271</v>
       </c>
       <c r="V6">
-        <v>25</v>
+        <v>33</v>
       </c>
       <c r="W6" s="2" t="s">
-        <v>321</v>
+        <v>319</v>
       </c>
       <c r="X6" s="2" t="s">
         <v>273</v>
@@ -4759,7 +4638,7 @@
         <v>274</v>
       </c>
       <c r="Z6" s="2" t="s">
-        <v>275</v>
+        <v>344</v>
       </c>
       <c r="AA6" s="2" t="s">
         <v>276</v>
@@ -4768,424 +4647,424 @@
         <v>266</v>
       </c>
       <c r="AC6" s="2" t="s">
+        <v>345</v>
+      </c>
+      <c r="AD6" s="2" t="s">
+        <v>346</v>
+      </c>
+      <c r="AE6" s="2" t="s">
+        <v>347</v>
+      </c>
+      <c r="AF6" s="2" t="s">
+        <v>266</v>
+      </c>
+      <c r="AG6" s="2" t="s">
+        <v>373</v>
+      </c>
+      <c r="AH6" s="2" t="s">
+        <v>321</v>
+      </c>
+      <c r="AI6" s="2" t="s">
+        <v>425</v>
+      </c>
+      <c r="AJ6" s="2" t="s">
+        <v>266</v>
+      </c>
+      <c r="AK6" s="2" t="s">
+        <v>323</v>
+      </c>
+      <c r="AL6" s="2" t="s">
+        <v>318</v>
+      </c>
+      <c r="AM6" s="2" t="s">
+        <v>277</v>
+      </c>
+      <c r="AN6" s="2" t="s">
+        <v>278</v>
+      </c>
+      <c r="AO6" s="2" t="s">
+        <v>278</v>
+      </c>
+      <c r="AP6" s="2" t="s">
+        <v>279</v>
+      </c>
+      <c r="AQ6" s="2" t="s">
+        <v>288</v>
+      </c>
+      <c r="AR6" s="2" t="s">
+        <v>426</v>
+      </c>
+      <c r="AS6" s="2" t="s">
+        <v>427</v>
+      </c>
+      <c r="AT6" s="2" t="s">
+        <v>280</v>
+      </c>
+      <c r="AU6" s="2" t="s">
+        <v>318</v>
+      </c>
+      <c r="AV6" s="2" t="s">
         <v>428</v>
       </c>
-      <c r="AD6" s="2" t="s">
+      <c r="AW6" s="2" t="s">
+        <v>266</v>
+      </c>
+      <c r="AX6" s="2" t="s">
+        <v>281</v>
+      </c>
+      <c r="AY6" s="2" t="s">
+        <v>266</v>
+      </c>
+      <c r="AZ6" s="2" t="s">
+        <v>279</v>
+      </c>
+      <c r="BA6" s="2" t="s">
+        <v>324</v>
+      </c>
+      <c r="BB6" s="2" t="s">
+        <v>324</v>
+      </c>
+      <c r="BC6" s="2" t="s">
+        <v>324</v>
+      </c>
+      <c r="BD6" s="2" t="s">
+        <v>283</v>
+      </c>
+      <c r="BE6" s="2" t="s">
+        <v>283</v>
+      </c>
+      <c r="BF6" s="2" t="s">
+        <v>283</v>
+      </c>
+      <c r="BG6" s="2" t="s">
+        <v>292</v>
+      </c>
+      <c r="BH6" s="2" t="s">
+        <v>293</v>
+      </c>
+      <c r="BI6" s="2" t="s">
+        <v>307</v>
+      </c>
+      <c r="BJ6" s="2" t="s">
+        <v>330</v>
+      </c>
+      <c r="BK6" s="2" t="s">
+        <v>330</v>
+      </c>
+      <c r="BL6" s="2" t="s">
+        <v>330</v>
+      </c>
+      <c r="BM6" s="2" t="s">
+        <v>294</v>
+      </c>
+      <c r="BN6" s="2" t="s">
+        <v>429</v>
+      </c>
+      <c r="BO6" s="2" t="s">
+        <v>287</v>
+      </c>
+      <c r="BP6" s="2" t="s">
+        <v>266</v>
+      </c>
+      <c r="BQ6" s="2" t="s">
+        <v>331</v>
+      </c>
+      <c r="BR6" s="2" t="s">
+        <v>288</v>
+      </c>
+      <c r="BS6" s="2" t="s">
+        <v>430</v>
+      </c>
+      <c r="BT6" s="2" t="s">
+        <v>304</v>
+      </c>
+      <c r="BU6" s="2" t="s">
+        <v>290</v>
+      </c>
+      <c r="BV6" s="2" t="s">
+        <v>290</v>
+      </c>
+      <c r="BW6" s="2" t="s">
+        <v>283</v>
+      </c>
+      <c r="BX6" s="2" t="s">
+        <v>283</v>
+      </c>
+      <c r="BY6" s="2" t="s">
+        <v>283</v>
+      </c>
+      <c r="BZ6" s="2" t="s">
+        <v>293</v>
+      </c>
+      <c r="CA6" s="2" t="s">
+        <v>307</v>
+      </c>
+      <c r="CB6" s="2" t="s">
+        <v>307</v>
+      </c>
+      <c r="CC6" s="2" t="s">
+        <v>341</v>
+      </c>
+      <c r="CD6" s="2" t="s">
+        <v>356</v>
+      </c>
+      <c r="CE6" s="2" t="s">
+        <v>356</v>
+      </c>
+      <c r="CF6" s="2" t="s">
+        <v>294</v>
+      </c>
+      <c r="CG6" s="2" t="s">
+        <v>431</v>
+      </c>
+      <c r="CH6" s="2" t="s">
+        <v>354</v>
+      </c>
+      <c r="CI6" s="2" t="s">
+        <v>266</v>
+      </c>
+      <c r="CJ6" s="2" t="s">
+        <v>296</v>
+      </c>
+      <c r="CK6" s="2" t="s">
+        <v>288</v>
+      </c>
+      <c r="CL6" s="2" t="s">
+        <v>432</v>
+      </c>
+      <c r="CM6" s="2" t="s">
+        <v>282</v>
+      </c>
+      <c r="CN6" s="2" t="s">
+        <v>299</v>
+      </c>
+      <c r="CO6" s="2" t="s">
+        <v>289</v>
+      </c>
+      <c r="CP6" s="2" t="s">
+        <v>306</v>
+      </c>
+      <c r="CQ6" s="2" t="s">
+        <v>283</v>
+      </c>
+      <c r="CR6" s="2" t="s">
+        <v>283</v>
+      </c>
+      <c r="CS6" s="2" t="s">
+        <v>284</v>
+      </c>
+      <c r="CT6" s="2" t="s">
+        <v>325</v>
+      </c>
+      <c r="CU6" s="2" t="s">
+        <v>307</v>
+      </c>
+      <c r="CV6" s="2" t="s">
+        <v>333</v>
+      </c>
+      <c r="CW6" s="2" t="s">
         <v>339</v>
       </c>
-      <c r="AE6" s="2" t="s">
-        <v>429</v>
-      </c>
-      <c r="AF6" s="2" t="s">
-        <v>266</v>
-      </c>
-      <c r="AG6" s="2" t="s">
-        <v>374</v>
-      </c>
-      <c r="AH6" s="2" t="s">
-        <v>375</v>
-      </c>
-      <c r="AI6" s="2" t="s">
-        <v>430</v>
-      </c>
-      <c r="AJ6" s="2" t="s">
-        <v>431</v>
-      </c>
-      <c r="AK6" s="2" t="s">
-        <v>279</v>
-      </c>
-      <c r="AL6" s="2" t="s">
-        <v>279</v>
-      </c>
-      <c r="AM6" s="2" t="s">
-        <v>281</v>
-      </c>
-      <c r="AN6" s="2" t="s">
-        <v>320</v>
-      </c>
-      <c r="AO6" s="2" t="s">
+      <c r="CX6" s="2" t="s">
         <v>340</v>
       </c>
-      <c r="AP6" s="2" t="s">
+      <c r="CY6" s="2" t="s">
+        <v>286</v>
+      </c>
+      <c r="CZ6" s="2" t="s">
+        <v>433</v>
+      </c>
+      <c r="DA6" s="2" t="s">
+        <v>326</v>
+      </c>
+      <c r="DB6" s="2" t="s">
+        <v>266</v>
+      </c>
+      <c r="DC6" s="2" t="s">
+        <v>302</v>
+      </c>
+      <c r="DD6" s="2" t="s">
+        <v>297</v>
+      </c>
+      <c r="DE6" s="2" t="s">
+        <v>434</v>
+      </c>
+      <c r="DF6" s="2" t="s">
+        <v>303</v>
+      </c>
+      <c r="DG6" s="2" t="s">
+        <v>289</v>
+      </c>
+      <c r="DH6" s="2" t="s">
+        <v>304</v>
+      </c>
+      <c r="DI6" s="2" t="s">
+        <v>290</v>
+      </c>
+      <c r="DJ6" s="2" t="s">
+        <v>283</v>
+      </c>
+      <c r="DK6" s="2" t="s">
+        <v>283</v>
+      </c>
+      <c r="DL6" s="2" t="s">
+        <v>283</v>
+      </c>
+      <c r="DM6" s="2" t="s">
         <v>325</v>
       </c>
-      <c r="AQ6" s="2" t="s">
-        <v>432</v>
-      </c>
-      <c r="AR6" s="2" t="s">
-        <v>433</v>
-      </c>
-      <c r="AS6" s="2" t="s">
-        <v>434</v>
-      </c>
-      <c r="AT6" s="2" t="s">
-        <v>320</v>
-      </c>
-      <c r="AU6" s="2" t="s">
-        <v>304</v>
-      </c>
-      <c r="AV6" s="2" t="s">
+      <c r="DN6" s="2" t="s">
+        <v>307</v>
+      </c>
+      <c r="DO6" s="2" t="s">
+        <v>307</v>
+      </c>
+      <c r="DP6" s="2" t="s">
+        <v>339</v>
+      </c>
+      <c r="DQ6" s="2" t="s">
+        <v>382</v>
+      </c>
+      <c r="DR6" s="2" t="s">
+        <v>356</v>
+      </c>
+      <c r="DS6" s="2" t="s">
+        <v>294</v>
+      </c>
+      <c r="DT6" s="2" t="s">
         <v>435</v>
       </c>
-      <c r="AW6" s="2" t="s">
-        <v>266</v>
-      </c>
-      <c r="AX6" s="2" t="s">
-        <v>353</v>
-      </c>
-      <c r="AY6" s="2" t="s">
-        <v>266</v>
-      </c>
-      <c r="AZ6" s="2" t="s">
-        <v>280</v>
-      </c>
-      <c r="BA6" s="2" t="s">
-        <v>300</v>
-      </c>
-      <c r="BB6" s="2" t="s">
+      <c r="DU6" s="2" t="s">
+        <v>354</v>
+      </c>
+      <c r="DV6" s="2" t="s">
+        <v>266</v>
+      </c>
+      <c r="DW6" s="2" t="s">
+        <v>362</v>
+      </c>
+      <c r="DX6" s="2" t="s">
+        <v>297</v>
+      </c>
+      <c r="DY6" s="2" t="s">
+        <v>436</v>
+      </c>
+      <c r="DZ6" s="2" t="s">
+        <v>282</v>
+      </c>
+      <c r="EA6" s="2" t="s">
+        <v>282</v>
+      </c>
+      <c r="EB6" s="2" t="s">
+        <v>282</v>
+      </c>
+      <c r="EC6" s="2" t="s">
         <v>291</v>
       </c>
-      <c r="BC6" s="2" t="s">
-        <v>291</v>
-      </c>
-      <c r="BD6" s="2" t="s">
+      <c r="ED6" s="2" t="s">
+        <v>306</v>
+      </c>
+      <c r="EE6" s="2" t="s">
+        <v>306</v>
+      </c>
+      <c r="EF6" s="2" t="s">
+        <v>301</v>
+      </c>
+      <c r="EG6" s="2" t="s">
+        <v>301</v>
+      </c>
+      <c r="EH6" s="2" t="s">
+        <v>301</v>
+      </c>
+      <c r="EI6" s="2" t="s">
+        <v>330</v>
+      </c>
+      <c r="EJ6" s="2" t="s">
+        <v>330</v>
+      </c>
+      <c r="EK6" s="2" t="s">
+        <v>330</v>
+      </c>
+      <c r="EL6" s="2" t="s">
+        <v>288</v>
+      </c>
+      <c r="EM6" s="2" t="s">
+        <v>437</v>
+      </c>
+      <c r="EN6" s="2" t="s">
+        <v>326</v>
+      </c>
+      <c r="EO6" s="2" t="s">
+        <v>266</v>
+      </c>
+      <c r="EP6" s="2" t="s">
+        <v>309</v>
+      </c>
+      <c r="EQ6" s="2" t="s">
+        <v>332</v>
+      </c>
+      <c r="ER6" s="2" t="s">
+        <v>438</v>
+      </c>
+      <c r="ES6" s="2" t="s">
+        <v>282</v>
+      </c>
+      <c r="ET6" s="2" t="s">
+        <v>282</v>
+      </c>
+      <c r="EU6" s="2" t="s">
+        <v>282</v>
+      </c>
+      <c r="EV6" s="2" t="s">
+        <v>283</v>
+      </c>
+      <c r="EW6" s="2" t="s">
+        <v>283</v>
+      </c>
+      <c r="EX6" s="2" t="s">
+        <v>283</v>
+      </c>
+      <c r="EY6" s="2" t="s">
+        <v>301</v>
+      </c>
+      <c r="EZ6" s="2" t="s">
         <v>284</v>
       </c>
-      <c r="BE6" s="2" t="s">
+      <c r="FA6" s="2" t="s">
         <v>284</v>
       </c>
-      <c r="BF6" s="2" t="s">
-        <v>284</v>
-      </c>
-      <c r="BG6" s="2" t="s">
-        <v>286</v>
-      </c>
-      <c r="BH6" s="2" t="s">
-        <v>308</v>
-      </c>
-      <c r="BI6" s="2" t="s">
-        <v>308</v>
-      </c>
-      <c r="BJ6" s="2" t="s">
+      <c r="FB6" s="2" t="s">
+        <v>330</v>
+      </c>
+      <c r="FC6" s="2" t="s">
+        <v>330</v>
+      </c>
+      <c r="FD6" s="2" t="s">
+        <v>330</v>
+      </c>
+      <c r="FE6" s="2" t="s">
+        <v>288</v>
+      </c>
+      <c r="FF6" s="2" t="s">
+        <v>439</v>
+      </c>
+      <c r="FG6" s="2" t="s">
+        <v>386</v>
+      </c>
+      <c r="FH6" s="2" t="s">
+        <v>266</v>
+      </c>
+      <c r="FI6" s="2" t="s">
+        <v>309</v>
+      </c>
+      <c r="FJ6" s="2" t="s">
         <v>332</v>
       </c>
-      <c r="BK6" s="2" t="s">
-        <v>332</v>
-      </c>
-      <c r="BL6" s="2" t="s">
-        <v>332</v>
-      </c>
-      <c r="BM6" s="2" t="s">
-        <v>295</v>
-      </c>
-      <c r="BN6" s="2" t="s">
-        <v>436</v>
-      </c>
-      <c r="BO6" s="2" t="s">
-        <v>288</v>
-      </c>
-      <c r="BP6" s="2" t="s">
-        <v>266</v>
-      </c>
-      <c r="BQ6" s="2" t="s">
-        <v>333</v>
-      </c>
-      <c r="BR6" s="2" t="s">
-        <v>287</v>
-      </c>
-      <c r="BS6" s="2" t="s">
-        <v>437</v>
-      </c>
-      <c r="BT6" s="2" t="s">
-        <v>291</v>
-      </c>
-      <c r="BU6" s="2" t="s">
-        <v>291</v>
-      </c>
-      <c r="BV6" s="2" t="s">
-        <v>291</v>
-      </c>
-      <c r="BW6" s="2" t="s">
-        <v>284</v>
-      </c>
-      <c r="BX6" s="2" t="s">
-        <v>284</v>
-      </c>
-      <c r="BY6" s="2" t="s">
-        <v>284</v>
-      </c>
-      <c r="BZ6" s="2" t="s">
-        <v>308</v>
-      </c>
-      <c r="CA6" s="2" t="s">
-        <v>308</v>
-      </c>
-      <c r="CB6" s="2" t="s">
-        <v>308</v>
-      </c>
-      <c r="CC6" s="2" t="s">
-        <v>357</v>
-      </c>
-      <c r="CD6" s="2" t="s">
-        <v>357</v>
-      </c>
-      <c r="CE6" s="2" t="s">
-        <v>357</v>
-      </c>
-      <c r="CF6" s="2" t="s">
-        <v>295</v>
-      </c>
-      <c r="CG6" s="2" t="s">
-        <v>438</v>
-      </c>
-      <c r="CH6" s="2" t="s">
-        <v>296</v>
-      </c>
-      <c r="CI6" s="2" t="s">
-        <v>266</v>
-      </c>
-      <c r="CJ6" s="2" t="s">
-        <v>297</v>
-      </c>
-      <c r="CK6" s="2" t="s">
-        <v>287</v>
-      </c>
-      <c r="CL6" s="2" t="s">
-        <v>439</v>
-      </c>
-      <c r="CM6" s="2" t="s">
-        <v>299</v>
-      </c>
-      <c r="CN6" s="2" t="s">
-        <v>326</v>
-      </c>
-      <c r="CO6" s="2" t="s">
-        <v>326</v>
-      </c>
-      <c r="CP6" s="2" t="s">
-        <v>284</v>
-      </c>
-      <c r="CQ6" s="2" t="s">
-        <v>284</v>
-      </c>
-      <c r="CR6" s="2" t="s">
-        <v>284</v>
-      </c>
-      <c r="CS6" s="2" t="s">
-        <v>286</v>
-      </c>
-      <c r="CT6" s="2" t="s">
-        <v>308</v>
-      </c>
-      <c r="CU6" s="2" t="s">
-        <v>308</v>
-      </c>
-      <c r="CV6" s="2" t="s">
-        <v>332</v>
-      </c>
-      <c r="CW6" s="2" t="s">
-        <v>332</v>
-      </c>
-      <c r="CX6" s="2" t="s">
-        <v>332</v>
-      </c>
-      <c r="CY6" s="2" t="s">
-        <v>287</v>
-      </c>
-      <c r="CZ6" s="2" t="s">
+      <c r="FK6" s="2" t="s">
         <v>440</v>
       </c>
-      <c r="DA6" s="2" t="s">
-        <v>328</v>
-      </c>
-      <c r="DB6" s="2" t="s">
-        <v>266</v>
-      </c>
-      <c r="DC6" s="2" t="s">
-        <v>303</v>
-      </c>
-      <c r="DD6" s="2" t="s">
-        <v>287</v>
-      </c>
-      <c r="DE6" s="2" t="s">
-        <v>441</v>
-      </c>
-      <c r="DF6" s="2" t="s">
-        <v>304</v>
-      </c>
-      <c r="DG6" s="2" t="s">
-        <v>290</v>
-      </c>
-      <c r="DH6" s="2" t="s">
-        <v>291</v>
-      </c>
-      <c r="DI6" s="2" t="s">
-        <v>291</v>
-      </c>
-      <c r="DJ6" s="2" t="s">
-        <v>284</v>
-      </c>
-      <c r="DK6" s="2" t="s">
-        <v>284</v>
-      </c>
-      <c r="DL6" s="2" t="s">
-        <v>284</v>
-      </c>
-      <c r="DM6" s="2" t="s">
-        <v>293</v>
-      </c>
-      <c r="DN6" s="2" t="s">
-        <v>308</v>
-      </c>
-      <c r="DO6" s="2" t="s">
-        <v>308</v>
-      </c>
-      <c r="DP6" s="2" t="s">
-        <v>341</v>
-      </c>
-      <c r="DQ6" s="2" t="s">
-        <v>357</v>
-      </c>
-      <c r="DR6" s="2" t="s">
-        <v>357</v>
-      </c>
-      <c r="DS6" s="2" t="s">
-        <v>295</v>
-      </c>
-      <c r="DT6" s="2" t="s">
-        <v>442</v>
-      </c>
-      <c r="DU6" s="2" t="s">
-        <v>443</v>
-      </c>
-      <c r="DV6" s="2" t="s">
-        <v>266</v>
-      </c>
-      <c r="DW6" s="2" t="s">
-        <v>311</v>
-      </c>
-      <c r="DX6" s="2" t="s">
-        <v>334</v>
-      </c>
-      <c r="DY6" s="2" t="s">
-        <v>444</v>
-      </c>
-      <c r="DZ6" s="2" t="s">
-        <v>300</v>
-      </c>
-      <c r="EA6" s="2" t="s">
-        <v>291</v>
-      </c>
-      <c r="EB6" s="2" t="s">
-        <v>291</v>
-      </c>
-      <c r="EC6" s="2" t="s">
-        <v>292</v>
-      </c>
-      <c r="ED6" s="2" t="s">
-        <v>284</v>
-      </c>
-      <c r="EE6" s="2" t="s">
-        <v>284</v>
-      </c>
-      <c r="EF6" s="2" t="s">
-        <v>293</v>
-      </c>
-      <c r="EG6" s="2" t="s">
-        <v>308</v>
-      </c>
-      <c r="EH6" s="2" t="s">
-        <v>308</v>
-      </c>
-      <c r="EI6" s="2" t="s">
-        <v>332</v>
-      </c>
-      <c r="EJ6" s="2" t="s">
-        <v>357</v>
-      </c>
-      <c r="EK6" s="2" t="s">
-        <v>357</v>
-      </c>
-      <c r="EL6" s="2" t="s">
-        <v>287</v>
-      </c>
-      <c r="EM6" s="2" t="s">
-        <v>445</v>
-      </c>
-      <c r="EN6" s="2" t="s">
-        <v>446</v>
-      </c>
-      <c r="EO6" s="2" t="s">
-        <v>266</v>
-      </c>
-      <c r="EP6" s="2" t="s">
-        <v>447</v>
-      </c>
-      <c r="EQ6" s="2" t="s">
-        <v>287</v>
-      </c>
-      <c r="ER6" s="2" t="s">
-        <v>448</v>
-      </c>
-      <c r="ES6" s="2" t="s">
-        <v>283</v>
-      </c>
-      <c r="ET6" s="2" t="s">
-        <v>300</v>
-      </c>
-      <c r="EU6" s="2" t="s">
-        <v>300</v>
-      </c>
-      <c r="EV6" s="2" t="s">
-        <v>284</v>
-      </c>
-      <c r="EW6" s="2" t="s">
-        <v>284</v>
-      </c>
-      <c r="EX6" s="2" t="s">
-        <v>284</v>
-      </c>
-      <c r="EY6" s="2" t="s">
-        <v>285</v>
-      </c>
-      <c r="EZ6" s="2" t="s">
-        <v>308</v>
-      </c>
-      <c r="FA6" s="2" t="s">
-        <v>308</v>
-      </c>
-      <c r="FB6" s="2" t="s">
-        <v>332</v>
-      </c>
-      <c r="FC6" s="2" t="s">
-        <v>342</v>
-      </c>
-      <c r="FD6" s="2" t="s">
-        <v>342</v>
-      </c>
-      <c r="FE6" s="2" t="s">
-        <v>287</v>
-      </c>
-      <c r="FF6" s="2" t="s">
-        <v>449</v>
-      </c>
-      <c r="FG6" s="2" t="s">
-        <v>450</v>
-      </c>
-      <c r="FH6" s="2" t="s">
-        <v>266</v>
-      </c>
-      <c r="FI6" s="2" t="s">
-        <v>311</v>
-      </c>
-      <c r="FJ6" s="2" t="s">
-        <v>287</v>
-      </c>
-      <c r="FK6" s="2" t="s">
-        <v>451</v>
-      </c>
       <c r="FL6" s="2" t="s">
-        <v>397</v>
+        <v>310</v>
       </c>
       <c r="FM6" s="2" t="s">
         <v>314</v>
@@ -5194,597 +5073,47 @@
         <v>313</v>
       </c>
       <c r="FO6" s="2" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="FP6" s="2" t="s">
         <v>314</v>
       </c>
       <c r="FQ6" s="2" t="s">
+        <v>315</v>
+      </c>
+      <c r="FR6" s="2" t="s">
+        <v>315</v>
+      </c>
+      <c r="FS6" s="2" t="s">
+        <v>315</v>
+      </c>
+      <c r="FT6" s="2" t="s">
         <v>317</v>
       </c>
-      <c r="FR6" s="2" t="s">
-        <v>318</v>
-      </c>
-      <c r="FS6" s="2" t="s">
-        <v>318</v>
-      </c>
-      <c r="FT6" s="2" t="s">
-        <v>319</v>
-      </c>
       <c r="FU6" s="2" t="s">
-        <v>304</v>
+        <v>280</v>
       </c>
       <c r="FV6" s="2" t="s">
-        <v>282</v>
+        <v>323</v>
       </c>
       <c r="FW6" s="2" t="s">
-        <v>304</v>
+        <v>278</v>
       </c>
       <c r="FX6" s="2" t="s">
-        <v>452</v>
+        <v>266</v>
       </c>
       <c r="FY6" s="2" t="s">
-        <v>453</v>
+        <v>266</v>
       </c>
       <c r="FZ6" s="2" t="s">
-        <v>454</v>
+        <v>441</v>
       </c>
     </row>
-    <row r="7" spans="1:182" ht="15" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A7" s="1">
-        <v>46194.941365740742</v>
-      </c>
-      <c r="B7" s="1">
-        <v>46194.964085648149</v>
-      </c>
-      <c r="C7" s="2" t="s">
-        <v>185</v>
-      </c>
-      <c r="D7" s="2" t="s">
-        <v>455</v>
-      </c>
-      <c r="E7">
-        <v>100</v>
-      </c>
-      <c r="F7">
-        <v>1963</v>
-      </c>
-      <c r="G7" s="2" t="s">
-        <v>265</v>
-      </c>
-      <c r="H7" s="1">
-        <v>46194.964096006945</v>
-      </c>
-      <c r="I7" s="2" t="s">
-        <v>456</v>
-      </c>
-      <c r="J7" s="2" t="s">
-        <v>266</v>
-      </c>
-      <c r="K7" s="2" t="s">
-        <v>266</v>
-      </c>
-      <c r="L7" s="2" t="s">
-        <v>266</v>
-      </c>
-      <c r="M7" s="2" t="s">
-        <v>266</v>
-      </c>
-      <c r="N7">
-        <v>52.473199999999999</v>
-      </c>
-      <c r="O7">
-        <v>13.3147</v>
-      </c>
-      <c r="P7" s="2" t="s">
-        <v>267</v>
-      </c>
-      <c r="Q7" s="2" t="s">
-        <v>268</v>
-      </c>
-      <c r="R7" s="2" t="s">
-        <v>330</v>
-      </c>
-      <c r="S7" s="2" t="s">
-        <v>269</v>
-      </c>
-      <c r="T7" s="2" t="s">
-        <v>270</v>
-      </c>
-      <c r="U7" s="2" t="s">
-        <v>427</v>
-      </c>
-      <c r="V7">
-        <v>93</v>
-      </c>
-      <c r="W7" s="2" t="s">
-        <v>457</v>
-      </c>
-      <c r="X7" s="2" t="s">
-        <v>458</v>
-      </c>
-      <c r="Y7" s="2" t="s">
-        <v>459</v>
-      </c>
-      <c r="Z7" s="2" t="s">
-        <v>275</v>
-      </c>
-      <c r="AA7" s="2" t="s">
-        <v>276</v>
-      </c>
-      <c r="AB7" s="2" t="s">
-        <v>266</v>
-      </c>
-      <c r="AC7" s="2" t="s">
-        <v>460</v>
-      </c>
-      <c r="AD7" s="2" t="s">
-        <v>461</v>
-      </c>
-      <c r="AE7" s="2" t="s">
-        <v>462</v>
-      </c>
-      <c r="AF7" s="2" t="s">
-        <v>266</v>
-      </c>
-      <c r="AG7" s="2" t="s">
-        <v>277</v>
-      </c>
-      <c r="AH7" s="2" t="s">
-        <v>323</v>
-      </c>
-      <c r="AI7" s="2" t="s">
-        <v>463</v>
-      </c>
-      <c r="AJ7" s="2" t="s">
-        <v>266</v>
-      </c>
-      <c r="AK7" s="2" t="s">
-        <v>280</v>
-      </c>
-      <c r="AL7" s="2" t="s">
-        <v>280</v>
-      </c>
-      <c r="AM7" s="2" t="s">
-        <v>278</v>
-      </c>
-      <c r="AN7" s="2" t="s">
-        <v>280</v>
-      </c>
-      <c r="AO7" s="2" t="s">
-        <v>280</v>
-      </c>
-      <c r="AP7" s="2" t="s">
-        <v>280</v>
-      </c>
-      <c r="AQ7" s="2" t="s">
-        <v>432</v>
-      </c>
-      <c r="AR7" s="2" t="s">
-        <v>464</v>
-      </c>
-      <c r="AS7" s="2" t="s">
-        <v>465</v>
-      </c>
-      <c r="AT7" s="2" t="s">
-        <v>280</v>
-      </c>
-      <c r="AU7" s="2" t="s">
-        <v>280</v>
-      </c>
-      <c r="AV7" s="2" t="s">
-        <v>466</v>
-      </c>
-      <c r="AW7" s="2" t="s">
-        <v>266</v>
-      </c>
-      <c r="AX7" s="2" t="s">
-        <v>380</v>
-      </c>
-      <c r="AY7" s="2" t="s">
-        <v>266</v>
-      </c>
-      <c r="AZ7" s="2" t="s">
-        <v>280</v>
-      </c>
-      <c r="BA7" s="2" t="s">
-        <v>291</v>
-      </c>
-      <c r="BB7" s="2" t="s">
-        <v>291</v>
-      </c>
-      <c r="BC7" s="2" t="s">
-        <v>291</v>
-      </c>
-      <c r="BD7" s="2" t="s">
-        <v>284</v>
-      </c>
-      <c r="BE7" s="2" t="s">
-        <v>284</v>
-      </c>
-      <c r="BF7" s="2" t="s">
-        <v>284</v>
-      </c>
-      <c r="BG7" s="2" t="s">
-        <v>308</v>
-      </c>
-      <c r="BH7" s="2" t="s">
-        <v>308</v>
-      </c>
-      <c r="BI7" s="2" t="s">
-        <v>308</v>
-      </c>
-      <c r="BJ7" s="2" t="s">
-        <v>332</v>
-      </c>
-      <c r="BK7" s="2" t="s">
-        <v>332</v>
-      </c>
-      <c r="BL7" s="2" t="s">
-        <v>332</v>
-      </c>
-      <c r="BM7" s="2" t="s">
-        <v>295</v>
-      </c>
-      <c r="BN7" s="2" t="s">
-        <v>467</v>
-      </c>
-      <c r="BO7" s="2" t="s">
-        <v>288</v>
-      </c>
-      <c r="BP7" s="2" t="s">
-        <v>266</v>
-      </c>
-      <c r="BQ7" s="2" t="s">
-        <v>311</v>
-      </c>
-      <c r="BR7" s="2" t="s">
-        <v>334</v>
-      </c>
-      <c r="BS7" s="2" t="s">
-        <v>468</v>
-      </c>
-      <c r="BT7" s="2" t="s">
-        <v>291</v>
-      </c>
-      <c r="BU7" s="2" t="s">
-        <v>291</v>
-      </c>
-      <c r="BV7" s="2" t="s">
-        <v>291</v>
-      </c>
-      <c r="BW7" s="2" t="s">
-        <v>310</v>
-      </c>
-      <c r="BX7" s="2" t="s">
-        <v>310</v>
-      </c>
-      <c r="BY7" s="2" t="s">
-        <v>310</v>
-      </c>
-      <c r="BZ7" s="2" t="s">
-        <v>308</v>
-      </c>
-      <c r="CA7" s="2" t="s">
-        <v>308</v>
-      </c>
-      <c r="CB7" s="2" t="s">
-        <v>308</v>
-      </c>
-      <c r="CC7" s="2" t="s">
-        <v>357</v>
-      </c>
-      <c r="CD7" s="2" t="s">
-        <v>357</v>
-      </c>
-      <c r="CE7" s="2" t="s">
-        <v>357</v>
-      </c>
-      <c r="CF7" s="2" t="s">
-        <v>295</v>
-      </c>
-      <c r="CG7" s="2" t="s">
-        <v>469</v>
-      </c>
-      <c r="CH7" s="2" t="s">
-        <v>336</v>
-      </c>
-      <c r="CI7" s="2" t="s">
-        <v>266</v>
-      </c>
-      <c r="CJ7" s="2" t="s">
-        <v>297</v>
-      </c>
-      <c r="CK7" s="2" t="s">
-        <v>298</v>
-      </c>
-      <c r="CL7" s="2" t="s">
-        <v>470</v>
-      </c>
-      <c r="CM7" s="2" t="s">
-        <v>291</v>
-      </c>
-      <c r="CN7" s="2" t="s">
-        <v>291</v>
-      </c>
-      <c r="CO7" s="2" t="s">
-        <v>291</v>
-      </c>
-      <c r="CP7" s="2" t="s">
-        <v>310</v>
-      </c>
-      <c r="CQ7" s="2" t="s">
-        <v>310</v>
-      </c>
-      <c r="CR7" s="2" t="s">
-        <v>310</v>
-      </c>
-      <c r="CS7" s="2" t="s">
-        <v>308</v>
-      </c>
-      <c r="CT7" s="2" t="s">
-        <v>308</v>
-      </c>
-      <c r="CU7" s="2" t="s">
-        <v>308</v>
-      </c>
-      <c r="CV7" s="2" t="s">
-        <v>357</v>
-      </c>
-      <c r="CW7" s="2" t="s">
-        <v>357</v>
-      </c>
-      <c r="CX7" s="2" t="s">
-        <v>357</v>
-      </c>
-      <c r="CY7" s="2" t="s">
-        <v>295</v>
-      </c>
-      <c r="CZ7" s="2" t="s">
-        <v>471</v>
-      </c>
-      <c r="DA7" s="2" t="s">
-        <v>472</v>
-      </c>
-      <c r="DB7" s="2" t="s">
-        <v>266</v>
-      </c>
-      <c r="DC7" s="2" t="s">
-        <v>473</v>
-      </c>
-      <c r="DD7" s="2" t="s">
-        <v>287</v>
-      </c>
-      <c r="DE7" s="2" t="s">
-        <v>474</v>
-      </c>
-      <c r="DF7" s="2" t="s">
-        <v>304</v>
-      </c>
-      <c r="DG7" s="2" t="s">
-        <v>291</v>
-      </c>
-      <c r="DH7" s="2" t="s">
-        <v>291</v>
-      </c>
-      <c r="DI7" s="2" t="s">
-        <v>291</v>
-      </c>
-      <c r="DJ7" s="2" t="s">
-        <v>310</v>
-      </c>
-      <c r="DK7" s="2" t="s">
-        <v>310</v>
-      </c>
-      <c r="DL7" s="2" t="s">
-        <v>310</v>
-      </c>
-      <c r="DM7" s="2" t="s">
-        <v>308</v>
-      </c>
-      <c r="DN7" s="2" t="s">
-        <v>308</v>
-      </c>
-      <c r="DO7" s="2" t="s">
-        <v>308</v>
-      </c>
-      <c r="DP7" s="2" t="s">
-        <v>357</v>
-      </c>
-      <c r="DQ7" s="2" t="s">
-        <v>357</v>
-      </c>
-      <c r="DR7" s="2" t="s">
-        <v>357</v>
-      </c>
-      <c r="DS7" s="2" t="s">
-        <v>295</v>
-      </c>
-      <c r="DT7" s="2" t="s">
-        <v>475</v>
-      </c>
-      <c r="DU7" s="2" t="s">
-        <v>355</v>
-      </c>
-      <c r="DV7" s="2" t="s">
-        <v>266</v>
-      </c>
-      <c r="DW7" s="2" t="s">
-        <v>363</v>
-      </c>
-      <c r="DX7" s="2" t="s">
-        <v>289</v>
-      </c>
-      <c r="DY7" s="2" t="s">
-        <v>476</v>
-      </c>
-      <c r="DZ7" s="2" t="s">
-        <v>291</v>
-      </c>
-      <c r="EA7" s="2" t="s">
-        <v>291</v>
-      </c>
-      <c r="EB7" s="2" t="s">
-        <v>291</v>
-      </c>
-      <c r="EC7" s="2" t="s">
-        <v>310</v>
-      </c>
-      <c r="ED7" s="2" t="s">
-        <v>310</v>
-      </c>
-      <c r="EE7" s="2" t="s">
-        <v>310</v>
-      </c>
-      <c r="EF7" s="2" t="s">
-        <v>308</v>
-      </c>
-      <c r="EG7" s="2" t="s">
-        <v>308</v>
-      </c>
-      <c r="EH7" s="2" t="s">
-        <v>308</v>
-      </c>
-      <c r="EI7" s="2" t="s">
-        <v>357</v>
-      </c>
-      <c r="EJ7" s="2" t="s">
-        <v>357</v>
-      </c>
-      <c r="EK7" s="2" t="s">
-        <v>357</v>
-      </c>
-      <c r="EL7" s="2" t="s">
-        <v>295</v>
-      </c>
-      <c r="EM7" s="2" t="s">
-        <v>477</v>
-      </c>
-      <c r="EN7" s="2" t="s">
-        <v>288</v>
-      </c>
-      <c r="EO7" s="2" t="s">
-        <v>266</v>
-      </c>
-      <c r="EP7" s="2" t="s">
-        <v>447</v>
-      </c>
-      <c r="EQ7" s="2" t="s">
-        <v>298</v>
-      </c>
-      <c r="ER7" s="2" t="s">
-        <v>478</v>
-      </c>
-      <c r="ES7" s="2" t="s">
-        <v>291</v>
-      </c>
-      <c r="ET7" s="2" t="s">
-        <v>291</v>
-      </c>
-      <c r="EU7" s="2" t="s">
-        <v>291</v>
-      </c>
-      <c r="EV7" s="2" t="s">
-        <v>310</v>
-      </c>
-      <c r="EW7" s="2" t="s">
-        <v>310</v>
-      </c>
-      <c r="EX7" s="2" t="s">
-        <v>310</v>
-      </c>
-      <c r="EY7" s="2" t="s">
-        <v>308</v>
-      </c>
-      <c r="EZ7" s="2" t="s">
-        <v>308</v>
-      </c>
-      <c r="FA7" s="2" t="s">
-        <v>308</v>
-      </c>
-      <c r="FB7" s="2" t="s">
-        <v>357</v>
-      </c>
-      <c r="FC7" s="2" t="s">
-        <v>357</v>
-      </c>
-      <c r="FD7" s="2" t="s">
-        <v>357</v>
-      </c>
-      <c r="FE7" s="2" t="s">
-        <v>295</v>
-      </c>
-      <c r="FF7" s="2" t="s">
-        <v>479</v>
-      </c>
-      <c r="FG7" s="2" t="s">
-        <v>443</v>
-      </c>
-      <c r="FH7" s="2" t="s">
-        <v>266</v>
-      </c>
-      <c r="FI7" s="2" t="s">
-        <v>480</v>
-      </c>
-      <c r="FJ7" s="2" t="s">
-        <v>298</v>
-      </c>
-      <c r="FK7" s="2" t="s">
-        <v>481</v>
-      </c>
-      <c r="FL7" s="2" t="s">
-        <v>312</v>
-      </c>
-      <c r="FM7" s="2" t="s">
-        <v>313</v>
-      </c>
-      <c r="FN7" s="2" t="s">
-        <v>313</v>
-      </c>
-      <c r="FO7" s="2" t="s">
-        <v>313</v>
-      </c>
-      <c r="FP7" s="2" t="s">
-        <v>313</v>
-      </c>
-      <c r="FQ7" s="2" t="s">
-        <v>317</v>
-      </c>
-      <c r="FR7" s="2" t="s">
-        <v>317</v>
-      </c>
-      <c r="FS7" s="2" t="s">
-        <v>317</v>
-      </c>
-      <c r="FT7" s="2" t="s">
-        <v>317</v>
-      </c>
-      <c r="FU7" s="2" t="s">
-        <v>280</v>
-      </c>
-      <c r="FV7" s="2" t="s">
-        <v>280</v>
-      </c>
-      <c r="FW7" s="2" t="s">
-        <v>280</v>
-      </c>
-      <c r="FX7" s="2" t="s">
-        <v>266</v>
-      </c>
-      <c r="FY7" s="2" t="s">
-        <v>266</v>
-      </c>
-      <c r="FZ7" s="2" t="s">
-        <v>482</v>
-      </c>
-    </row>
-    <row r="8" spans="1:182" ht="15" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="9" spans="1:182" ht="15" customHeight="1" x14ac:dyDescent="0.4"/>
   </sheetData>
-  <autoFilter ref="A2:FZ8" xr:uid="{00000000-0009-0000-0000-000000000000}"/>
+  <autoFilter ref="A2:FZ7" xr:uid="{00000000-0009-0000-0000-000000000000}"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <ignoredErrors>
-    <ignoredError sqref="C1:C2 D1:D2 G1:G2 I1:I2 J1:J2 K1:K2 L1:L2 M1:M2 P1:P2 Q1:Q2 R1:R2 S1:S2 T1:T2 U1:U2 W1:W2 X1:X2 Y1:Y2 Z1:Z2 AA1:AA2 AB1:AB2 AC1:AC2 AD1:AD2 AE1:AE2 AF1:AF2 AG1:AG2 AH1:AH2 AI1:AI2 AJ1:AJ2 AK1:AK2 AL1:AL2 AM1:AM2 AN1:AN2 AO1:AO2 AP1:AP2 AQ1:AQ2 AR1:AR2 AS1:AS2 AT1:AT2 AU1:AU2 AV1:AV2 AW1:AW2 AX1:AX2 AY1:AY2 AZ1:AZ2 BA1:BA2 BB1:BB2 BC1:BC2 BD1:BD2 BE1:BE2 BF1:BF2 BG1:BG2 BH1:BH2 BI1:BI2 BJ1:BJ2 BK1:BK2 BL1:BL2 BM1:BM2 BN1:BN2 BO1:BO2 BP1:BP2 BQ1:BQ2 BR1:BR2 BS1:BS2 BT1:BT2 BU1:BU2 BV1:BV2 BW1:BW2 BX1:BX2 BY1:BY2 BZ1:BZ2 CA1:CA2 CB1:CB2 CC1:CC2 CD1:CD2 CE1:CE2 CF1:CF2 CG1:CG2 CH1:CH2 CI1:CI2 CJ1:CJ2 CK1:CK2 CL1:CL2 CM1:CM2 CN1:CN2 CO1:CO2 CP1:CP2 CQ1:CQ2 CR1:CR2 CS1:CS2 CT1:CT2 CU1:CU2 CV1:CV2 CW1:CW2 CX1:CX2 CY1:CY2 CZ1:CZ2 DA1:DA2 DB1:DB2 DC1:DC2 DD1:DD2 DE1:DE2 DF1:DF2 DG1:DG2 DH1:DH2 DI1:DI2 DJ1:DJ2 DK1:DK2 DL1:DL2 DM1:DM2 DN1:DN2 DO1:DO2 DP1:DP2 DQ1:DQ2 DR1:DR2 DS1:DS2 DT1:DT2 DU1:DU2 DV1:DV2 DW1:DW2 DX1:DX2 DY1:DY2 DZ1:DZ2 EA1:EA2 EB1:EB2 EC1:EC2 ED1:ED2 EE1:EE2 EF1:EF2 EG1:EG2 EH1:EH2 EI1:EI2 EJ1:EJ2 EK1:EK2 EL1:EL2 EM1:EM2 EN1:EN2 EO1:EO2 EP1:EP2 EQ1:EQ2 ER1:ER2 ES1:ES2 ET1:ET2 EU1:EU2 EV1:EV2 EW1:EW2 EX1:EX2 EY1:EY2 EZ1:EZ2 FA1:FA2 FB1:FB2 FC1:FC2 FD1:FD2 FE1:FE2 FF1:FF2 FG1:FG2 FH1:FH2 FI1:FI2 FJ1:FJ2 FK1:FK2 FL1:FL2 FM1:FM2 FN1:FN2 FO1:FO2 FP1:FP2 FQ1:FQ2 FR1:FR2 FS1:FS2 FT1:FT2 FU1:FU2 FV1:FV2 FW1:FW2 FX1:FX2 FY1:FY2 FZ1:FZ2 C3:C7 D3:D7 G3:G7 I3:I7 J3:J7 K3:K7 L3:L7 M3:M7 P3:P7 Q3:Q7 R3:R7 S3:S7 T3:T7 U3:U7 W3:W7 X3:X7 Y3:Y7 Z3:Z7 AA3:AA7 AB3:AB7 AC3:AC7 AD3:AD7 AE3:AE7 AF3:AF7 AG3:AG7 AH3:AH7 AI3:AI7 AJ3:AJ7 AK3:AK7 AL3:AL7 AM3:AM7 AN3:AN7 AO3:AO7 AP3:AP7 AQ3:AQ7 AR3:AR7 AS3:AS7 AT3:AT7 AU3:AU7 AV3:AV7 AW3:AW7 AX3:AX7 AY3:AY7 AZ3:AZ7 BA3:BA7 BB3:BB7 BC3:BC7 BD3:BD7 BE3:BE7 BF3:BF7 BG3:BG7 BH3:BH7 BI3:BI7 BJ3:BJ7 BK3:BK7 BL3:BL7 BM3:BM7 BN3:BN7 BO3:BO7 BP3:BP7 BQ3:BQ7 BR3:BR7 BS3:BS7 BT3:BT7 BU3:BU7 BV3:BV7 BW3:BW7 BX3:BX7 BY3:BY7 BZ3:BZ7 CA3:CA7 CB3:CB7 CC3:CC7 CD3:CD7 CE3:CE7 CF3:CF7 CG3:CG7 CH3:CH7 CI3:CI7 CJ3:CJ7 CK3:CK7 CL3:CL7 CM3:CM7 CN3:CN7 CO3:CO7 CP3:CP7 CQ3:CQ7 CR3:CR7 CS3:CS7 CT3:CT7 CU3:CU7 CV3:CV7 CW3:CW7 CX3:CX7 CY3:CY7 CZ3:CZ7 DA3:DA7 DB3:DB7 DC3:DC7 DD3:DD7 DE3:DE7 DF3:DF7 DG3:DG7 DH3:DH7 DI3:DI7 DJ3:DJ7 DK3:DK7 DL3:DL7 DM3:DM7 DN3:DN7 DO3:DO7 DP3:DP7 DQ3:DQ7 DR3:DR7 DS3:DS7 DT3:DT7 DU3:DU7 DV3:DV7 DW3:DW7 DX3:DX7 DY3:DY7 DZ3:DZ7 EA3:EA7 EB3:EB7 EC3:EC7 ED3:ED7 EE3:EE7 EF3:EF7 EG3:EG7 EH3:EH7 EI3:EI7 EJ3:EJ7 EK3:EK7 EL3:EL7 EM3:EM7 EN3:EN7 EO3:EO7 EP3:EP7 EQ3:EQ7 ER3:ER7 ES3:ES7 ET3:ET7 EU3:EU7 EV3:EV7 EW3:EW7 EX3:EX7 EY3:EY7 EZ3:EZ7 FA3:FA7 FB3:FB7 FC3:FC7 FD3:FD7 FE3:FE7 FF3:FF7 FG3:FG7 FH3:FH7 FI3:FI7 FJ3:FJ7 FK3:FK7 FL3:FL7 FM3:FM7 FN3:FN7 FO3:FO7 FP3:FP7 FQ3:FQ7 FR3:FR7 FS3:FS7 FT3:FT7 FU3:FU7 FV3:FV7 FW3:FW7 FX3:FX7 FY3:FY7 FZ3:FZ7" numberStoredAsText="1"/>
+    <ignoredError sqref="C1:C2 D1:D2 G1:G2 I1:I2 J1:J2 K1:K2 L1:L2 M1:M2 P1:P2 Q1:Q2 R1:R2 S1:S2 T1:T2 U1:U2 W1:W2 X1:X2 Y1:Y2 Z1:Z2 AA1:AA2 AB1:AB2 AC1:AC2 AD1:AD2 AE1:AE2 AF1:AF2 AG1:AG2 AH1:AH2 AI1:AI2 AJ1:AJ2 AK1:AK2 AL1:AL2 AM1:AM2 AN1:AN2 AO1:AO2 AP1:AP2 AQ1:AQ2 AR1:AR2 AS1:AS2 AT1:AT2 AU1:AU2 AV1:AV2 AW1:AW2 AX1:AX2 AY1:AY2 AZ1:AZ2 BA1:BA2 BB1:BB2 BC1:BC2 BD1:BD2 BE1:BE2 BF1:BF2 BG1:BG2 BH1:BH2 BI1:BI2 BJ1:BJ2 BK1:BK2 BL1:BL2 BM1:BM2 BN1:BN2 BO1:BO2 BP1:BP2 BQ1:BQ2 BR1:BR2 BS1:BS2 BT1:BT2 BU1:BU2 BV1:BV2 BW1:BW2 BX1:BX2 BY1:BY2 BZ1:BZ2 CA1:CA2 CB1:CB2 CC1:CC2 CD1:CD2 CE1:CE2 CF1:CF2 CG1:CG2 CH1:CH2 CI1:CI2 CJ1:CJ2 CK1:CK2 CL1:CL2 CM1:CM2 CN1:CN2 CO1:CO2 CP1:CP2 CQ1:CQ2 CR1:CR2 CS1:CS2 CT1:CT2 CU1:CU2 CV1:CV2 CW1:CW2 CX1:CX2 CY1:CY2 CZ1:CZ2 DA1:DA2 DB1:DB2 DC1:DC2 DD1:DD2 DE1:DE2 DF1:DF2 DG1:DG2 DH1:DH2 DI1:DI2 DJ1:DJ2 DK1:DK2 DL1:DL2 DM1:DM2 DN1:DN2 DO1:DO2 DP1:DP2 DQ1:DQ2 DR1:DR2 DS1:DS2 DT1:DT2 DU1:DU2 DV1:DV2 DW1:DW2 DX1:DX2 DY1:DY2 DZ1:DZ2 EA1:EA2 EB1:EB2 EC1:EC2 ED1:ED2 EE1:EE2 EF1:EF2 EG1:EG2 EH1:EH2 EI1:EI2 EJ1:EJ2 EK1:EK2 EL1:EL2 EM1:EM2 EN1:EN2 EO1:EO2 EP1:EP2 EQ1:EQ2 ER1:ER2 ES1:ES2 ET1:ET2 EU1:EU2 EV1:EV2 EW1:EW2 EX1:EX2 EY1:EY2 EZ1:EZ2 FA1:FA2 FB1:FB2 FC1:FC2 FD1:FD2 FE1:FE2 FF1:FF2 FG1:FG2 FH1:FH2 FI1:FI2 FJ1:FJ2 FK1:FK2 FL1:FL2 FM1:FM2 FN1:FN2 FO1:FO2 FP1:FP2 FQ1:FQ2 FR1:FR2 FS1:FS2 FT1:FT2 FU1:FU2 FV1:FV2 FW1:FW2 FX1:FX2 FY1:FY2 FZ1:FZ2 C3:C5 D3:D5 G3:G5 I3:I5 J3:J5 K3:K5 L3:L5 M3:M5 P3:P5 Q3:Q5 R3:R5 S3:S5 T3:T5 U3:U5 W3:W5 X3:X5 Y3:Y5 Z3:Z5 AA3:AA5 AB3:AB5 AC3:AC5 AD3:AD5 AE3:AE5 AF3:AF5 AG3:AG5 AH3:AH5 AI3:AI5 AJ3:AJ5 AK3:AK5 AL3:AL5 AM3:AM5 AN3:AN5 AO3:AO5 AP3:AP5 AQ3:AQ5 AR3:AR5 AS3:AS5 AT3:AT5 AU3:AU5 AV3:AV5 AW3:AW5 AX3:AX5 AY3:AY5 AZ3:AZ5 BA3:BA5 BB3:BB5 BC3:BC5 BD3:BD5 BE3:BE5 BF3:BF5 BG3:BG5 BH3:BH5 BI3:BI5 BJ3:BJ5 BK3:BK5 BL3:BL5 BM3:BM5 BN3:BN5 BO3:BO5 BP3:BP5 BQ3:BQ5 BR3:BR5 BS3:BS5 BT3:BT5 BU3:BU5 BV3:BV5 BW3:BW5 BX3:BX5 BY3:BY5 BZ3:BZ5 CA3:CA5 CB3:CB5 CC3:CC5 CD3:CD5 CE3:CE5 CF3:CF5 CG3:CG5 CH3:CH5 CI3:CI5 CJ3:CJ5 CK3:CK5 CL3:CL5 CM3:CM5 CN3:CN5 CO3:CO5 CP3:CP5 CQ3:CQ5 CR3:CR5 CS3:CS5 CT3:CT5 CU3:CU5 CV3:CV5 CW3:CW5 CX3:CX5 CY3:CY5 CZ3:CZ5 DA3:DA5 DB3:DB5 DC3:DC5 DD3:DD5 DE3:DE5 DF3:DF5 DG3:DG5 DH3:DH5 DI3:DI5 DJ3:DJ5 DK3:DK5 DL3:DL5 DM3:DM5 DN3:DN5 DO3:DO5 DP3:DP5 DQ3:DQ5 DR3:DR5 DS3:DS5 DT3:DT5 DU3:DU5 DV3:DV5 DW3:DW5 DX3:DX5 DY3:DY5 DZ3:DZ5 EA3:EA5 EB3:EB5 EC3:EC5 ED3:ED5 EE3:EE5 EF3:EF5 EG3:EG5 EH3:EH5 EI3:EI5 EJ3:EJ5 EK3:EK5 EL3:EL5 EM3:EM5 EN3:EN5 EO3:EO5 EP3:EP5 EQ3:EQ5 ER3:ER5 ES3:ES5 ET3:ET5 EU3:EU5 EV3:EV5 EW3:EW5 EX3:EX5 EY3:EY5 EZ3:EZ5 FA3:FA5 FB3:FB5 FC3:FC5 FD3:FD5 FE3:FE5 FF3:FF5 FG3:FG5 FH3:FH5 FI3:FI5 FJ3:FJ5 FK3:FK5 FL3:FL5 FM3:FM5 FN3:FN5 FO3:FO5 FP3:FP5 FQ3:FQ5 FR3:FR5 FS3:FS5 FT3:FT5 FU3:FU5 FV3:FV5 FW3:FW5 FX3:FX5 FY3:FY5 FZ3:FZ5 C6 D6 G6 I6 J6 K6 L6 M6 P6 Q6 R6 S6 T6 U6 W6 X6 Y6 Z6 AA6 AB6 AC6 AD6 AE6 AF6 AG6 AH6 AI6 AJ6 AK6 AL6 AM6 AN6 AO6 AP6 AQ6 AR6 AS6 AT6 AU6 AV6 AW6 AX6 AY6 AZ6 BA6 BB6 BC6 BD6 BE6 BF6 BG6 BH6 BI6 BJ6 BK6 BL6 BM6 BN6 BO6 BP6 BQ6 BR6 BS6 BT6 BU6 BV6 BW6 BX6 BY6 BZ6 CA6 CB6 CC6 CD6 CE6 CF6 CG6 CH6 CI6 CJ6 CK6 CL6 CM6 CN6 CO6 CP6 CQ6 CR6 CS6 CT6 CU6 CV6 CW6 CX6 CY6 CZ6 DA6 DB6 DC6 DD6 DE6 DF6 DG6 DH6 DI6 DJ6 DK6 DL6 DM6 DN6 DO6 DP6 DQ6 DR6 DS6 DT6 DU6 DV6 DW6 DX6 DY6 DZ6 EA6 EB6 EC6 ED6 EE6 EF6 EG6 EH6 EI6 EJ6 EK6 EL6 EM6 EN6 EO6 EP6 EQ6 ER6 ES6 ET6 EU6 EV6 EW6 EX6 EY6 EZ6 FA6 FB6 FC6 FD6 FE6 FF6 FG6 FH6 FI6 FJ6 FK6 FL6 FM6 FN6 FO6 FP6 FQ6 FR6 FS6 FT6 FU6 FV6 FW6 FX6 FY6 FZ6" numberStoredAsText="1"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/data.xlsx
+++ b/data.xlsx
@@ -9,7 +9,7 @@
     <sheet name="Sheet0" r:id="rId3" sheetId="1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="true">Sheet0!$A$2:$KS$35</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="true">Sheet0!$A$2:$KS$37</definedName>
   </definedNames>
 </workbook>
 </file>
@@ -49926,307 +49926,3057 @@
         </is>
       </c>
     </row>
+    <row r="35">
+      <c r="A35" s="1" t="n">
+        <v>46204.59408564815</v>
+      </c>
+      <c r="B35" s="1" t="n">
+        <v>46204.62136574074</v>
+      </c>
+      <c r="C35" s="2" t="inlineStr">
+        <is>
+          <t>IP Address</t>
+        </is>
+      </c>
+      <c r="D35" s="2" t="inlineStr">
+        <is>
+          <t>138.246.3.45</t>
+        </is>
+      </c>
+      <c r="E35" t="n">
+        <v>100.0</v>
+      </c>
+      <c r="F35" t="n">
+        <v>2356.0</v>
+      </c>
+      <c r="G35" s="2" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="H35" s="1" t="n">
+        <v>46204.62138388889</v>
+      </c>
+      <c r="I35" s="2" t="inlineStr">
+        <is>
+          <t>R_2d6lMi9DzUFJ8XY</t>
+        </is>
+      </c>
+      <c r="J35" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="K35" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="L35" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="M35" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="N35" t="n">
+        <v>48.1477</v>
+      </c>
+      <c r="O35" t="n">
+        <v>11.5695</v>
+      </c>
+      <c r="P35" s="2" t="inlineStr">
+        <is>
+          <t>anonymous</t>
+        </is>
+      </c>
+      <c r="Q35" s="2" t="inlineStr">
+        <is>
+          <t>EN</t>
+        </is>
+      </c>
+      <c r="R35" s="2" t="inlineStr">
+        <is>
+          <t>I understand the explanation provided to me. I was able to save a copy of this form. I reached out to the listed researchers and have had all my questions answered to my satisfaction. Therefore, I voluntarily agree to participate in this online study.,I voluntarily consent to my data being recorded and subsequently processed in line with the GDPR. I have been informed about the consequences of withdrawing my consent.</t>
+        </is>
+      </c>
+      <c r="S35" t="n">
+        <v>27.955</v>
+      </c>
+      <c r="T35" t="n">
+        <v>28.667</v>
+      </c>
+      <c r="U35" t="n">
+        <v>31.071</v>
+      </c>
+      <c r="V35" t="n">
+        <v>2.0</v>
+      </c>
+      <c r="W35" s="2" t="inlineStr">
+        <is>
+          <t>Yes, I am using a desktop or laptop computer.</t>
+        </is>
+      </c>
+      <c r="X35" s="2" t="inlineStr">
+        <is>
+          <t>Yes, I am wearing headphones.</t>
+        </is>
+      </c>
+      <c r="Y35" s="2" t="inlineStr">
+        <is>
+          <t>Left Channel</t>
+        </is>
+      </c>
+      <c r="Z35" t="n">
+        <v>3.724</v>
+      </c>
+      <c r="AA35" t="n">
+        <v>28.491</v>
+      </c>
+      <c r="AB35" t="n">
+        <v>31.695</v>
+      </c>
+      <c r="AC35" t="n">
+        <v>5.0</v>
+      </c>
+      <c r="AD35" t="n">
+        <v>27.0</v>
+      </c>
+      <c r="AE35" s="2" t="inlineStr">
+        <is>
+          <t>Male</t>
+        </is>
+      </c>
+      <c r="AF35" s="2" t="inlineStr">
+        <is>
+          <t>Turkish</t>
+        </is>
+      </c>
+      <c r="AG35" s="2" t="inlineStr">
+        <is>
+          <t>Understand perfectly</t>
+        </is>
+      </c>
+      <c r="AH35" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="AI35" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AJ35" s="2" t="inlineStr">
+        <is>
+          <t>Visual only (Screen lights up or shows banner, no sound/vibration)</t>
+        </is>
+      </c>
+      <c r="AK35" s="2" t="inlineStr">
+        <is>
+          <t>Social Etiquette: To avoid disturbing or annoying people around me.,Personal Focus: To avoid distracting myself or breaking my concentration.</t>
+        </is>
+      </c>
+      <c r="AL35" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AM35" s="2" t="inlineStr">
+        <is>
+          <t>Never</t>
+        </is>
+      </c>
+      <c r="AN35" s="2" t="inlineStr">
+        <is>
+          <t>Phone Calls,Calendar / Reminder Alerts</t>
+        </is>
+      </c>
+      <c r="AO35" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AP35" s="2" t="inlineStr">
+        <is>
+          <t>Somewhat agree</t>
+        </is>
+      </c>
+      <c r="AQ35" s="2" t="inlineStr">
+        <is>
+          <t>Agree</t>
+        </is>
+      </c>
+      <c r="AR35" t="n">
+        <v>0.977</v>
+      </c>
+      <c r="AS35" t="n">
+        <v>67.825</v>
+      </c>
+      <c r="AT35" t="n">
+        <v>69.077</v>
+      </c>
+      <c r="AU35" t="n">
+        <v>13.0</v>
+      </c>
+      <c r="AV35" s="2" t="inlineStr">
+        <is>
+          <t>🗣️Version 2,🗣️🗣️ Version 3</t>
+        </is>
+      </c>
+      <c r="AW35" s="2" t="inlineStr">
+        <is>
+          <t>🗣️🗣️ Version 3</t>
+        </is>
+      </c>
+      <c r="AX35" s="2" t="inlineStr">
+        <is>
+          <t>Because if it is urgent I would like to hear the content and evaluate the urgency as well</t>
+        </is>
+      </c>
+      <c r="AY35" s="2" t="inlineStr">
+        <is>
+          <t>Agree</t>
+        </is>
+      </c>
+      <c r="AZ35" s="2" t="inlineStr">
+        <is>
+          <t>Disagree</t>
+        </is>
+      </c>
+      <c r="BA35" s="2" t="inlineStr">
+        <is>
+          <t>Too intrusive,I don’t trust automatic speech output</t>
+        </is>
+      </c>
+      <c r="BB35" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="BC35" s="2" t="inlineStr">
+        <is>
+          <t>Short (2–3 sentences),It depends on the situation,It depends on the message/notification</t>
+        </is>
+      </c>
+      <c r="BD35" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="BE35" s="2" t="inlineStr">
+        <is>
+          <t>Somewhat agree</t>
+        </is>
+      </c>
+      <c r="BF35" t="n">
+        <v>4.355</v>
+      </c>
+      <c r="BG35" t="n">
+        <v>44.355</v>
+      </c>
+      <c r="BH35" t="n">
+        <v>45.125</v>
+      </c>
+      <c r="BI35" t="n">
+        <v>10.0</v>
+      </c>
+      <c r="BJ35" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="BK35" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="BL35" t="n">
+        <v>24.221</v>
+      </c>
+      <c r="BM35" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="BN35" s="2" t="inlineStr">
+        <is>
+          <t>Somewhat appropriate</t>
+        </is>
+      </c>
+      <c r="BO35" s="2" t="inlineStr">
+        <is>
+          <t>Somewhat inappropriate</t>
+        </is>
+      </c>
+      <c r="BP35" s="2" t="inlineStr">
+        <is>
+          <t>Completely inappropriate</t>
+        </is>
+      </c>
+      <c r="BQ35" s="2" t="inlineStr">
+        <is>
+          <t>Very easy to detect</t>
+        </is>
+      </c>
+      <c r="BR35" s="2" t="inlineStr">
+        <is>
+          <t>Very easy to detect</t>
+        </is>
+      </c>
+      <c r="BS35" s="2" t="inlineStr">
+        <is>
+          <t>Very easy to detect</t>
+        </is>
+      </c>
+      <c r="BT35" s="2" t="inlineStr">
+        <is>
+          <t>Slightly disruptive</t>
+        </is>
+      </c>
+      <c r="BU35" s="2" t="inlineStr">
+        <is>
+          <t>Disruptive</t>
+        </is>
+      </c>
+      <c r="BV35" s="2" t="inlineStr">
+        <is>
+          <t>Extremely disruptive</t>
+        </is>
+      </c>
+      <c r="BW35" s="2" t="inlineStr">
+        <is>
+          <t>Acceptable</t>
+        </is>
+      </c>
+      <c r="BX35" s="2" t="inlineStr">
+        <is>
+          <t>Somewhat acceptable</t>
+        </is>
+      </c>
+      <c r="BY35" s="2" t="inlineStr">
+        <is>
+          <t>Somewhat acceptable</t>
+        </is>
+      </c>
+      <c r="BZ35" s="2" t="inlineStr">
+        <is>
+          <t>🗣️ Version 2</t>
+        </is>
+      </c>
+      <c r="CA35" s="2" t="inlineStr">
+        <is>
+          <t>I am immersed in a mentally cognitive task, I understand the urgency and importance of the message so there should be something for me to interrupt my focus. If the sender information is included, I can do that.</t>
+        </is>
+      </c>
+      <c r="CB35" s="2" t="inlineStr">
+        <is>
+          <t>Focus &amp; Mental Effort (e.g., needing to concentrate on my current task without being interrupted)</t>
+        </is>
+      </c>
+      <c r="CC35" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="CD35" s="2" t="inlineStr">
+        <is>
+          <t>When I briefly pause while writing / thinking</t>
+        </is>
+      </c>
+      <c r="CE35" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="CF35" s="2" t="inlineStr">
+        <is>
+          <t>🗣️🗣️ Version 3</t>
+        </is>
+      </c>
+      <c r="CG35" s="2" t="inlineStr">
+        <is>
+          <t>When I briefly pause, I can hear the content of the message as well since I am already pausing my focus briefly.</t>
+        </is>
+      </c>
+      <c r="CH35" t="n">
+        <v>28.765</v>
+      </c>
+      <c r="CI35" t="n">
+        <v>126.533</v>
+      </c>
+      <c r="CJ35" t="n">
+        <v>149.849</v>
+      </c>
+      <c r="CK35" t="n">
+        <v>20.0</v>
+      </c>
+      <c r="CL35" s="2" t="inlineStr">
+        <is>
+          <t>Appropriate</t>
+        </is>
+      </c>
+      <c r="CM35" s="2" t="inlineStr">
+        <is>
+          <t>Somewhat inappropriate</t>
+        </is>
+      </c>
+      <c r="CN35" s="2" t="inlineStr">
+        <is>
+          <t>Inappropriate</t>
+        </is>
+      </c>
+      <c r="CO35" s="2" t="inlineStr">
+        <is>
+          <t>Easy to detect</t>
+        </is>
+      </c>
+      <c r="CP35" s="2" t="inlineStr">
+        <is>
+          <t>Very easy to detect</t>
+        </is>
+      </c>
+      <c r="CQ35" s="2" t="inlineStr">
+        <is>
+          <t>Very easy to detect</t>
+        </is>
+      </c>
+      <c r="CR35" s="2" t="inlineStr">
+        <is>
+          <t>Not disruptive at all</t>
+        </is>
+      </c>
+      <c r="CS35" s="2" t="inlineStr">
+        <is>
+          <t>Somewhat disruptive</t>
+        </is>
+      </c>
+      <c r="CT35" s="2" t="inlineStr">
+        <is>
+          <t>Disruptive</t>
+        </is>
+      </c>
+      <c r="CU35" s="2" t="inlineStr">
+        <is>
+          <t>Somewhat acceptable</t>
+        </is>
+      </c>
+      <c r="CV35" s="2" t="inlineStr">
+        <is>
+          <t>Somewhat unacceptable</t>
+        </is>
+      </c>
+      <c r="CW35" s="2" t="inlineStr">
+        <is>
+          <t>Completely unacceptable</t>
+        </is>
+      </c>
+      <c r="CX35" s="2" t="inlineStr">
+        <is>
+          <t>🗣️ Version 2</t>
+        </is>
+      </c>
+      <c r="CY35" s="2" t="inlineStr">
+        <is>
+          <t>Considering that the text is urgent and important, and I am in a meeting, I would prefer to know the sender's name briefly so that I can evaluate the urgency of the message.</t>
+        </is>
+      </c>
+      <c r="CZ35" s="2" t="inlineStr">
+        <is>
+          <t>Acoustic Environment (e.g., the level of background noise, music, or other people talking),Focus &amp; Mental Effort (e.g., needing to concentrate on my current task without being interrupted),Social Appropriateness (e.g., the presence of others, social etiquette, or not wanting to appear distracted)</t>
+        </is>
+      </c>
+      <c r="DA35" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="DB35" s="2" t="inlineStr">
+        <is>
+          <t>Immediately</t>
+        </is>
+      </c>
+      <c r="DC35" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="DD35" s="2" t="inlineStr">
+        <is>
+          <t>Not applicable (I chose "Immediately" in the previous question).</t>
+        </is>
+      </c>
+      <c r="DE35" s="2" t="inlineStr">
+        <is>
+          <t>Although I am involved in a mental task of contributing to the meeting, if I just briefly hear that the message is from Lily, that will not distract me so much and still give me information to decide whether I should check it or not.</t>
+        </is>
+      </c>
+      <c r="DF35" t="n">
+        <v>32.136</v>
+      </c>
+      <c r="DG35" t="n">
+        <v>165.6</v>
+      </c>
+      <c r="DH35" t="n">
+        <v>168.076</v>
+      </c>
+      <c r="DI35" t="n">
+        <v>28.0</v>
+      </c>
+      <c r="DJ35" s="2" t="inlineStr">
+        <is>
+          <t>Completely appropriate</t>
+        </is>
+      </c>
+      <c r="DK35" s="2" t="inlineStr">
+        <is>
+          <t>Somewhat inappropriate</t>
+        </is>
+      </c>
+      <c r="DL35" s="2" t="inlineStr">
+        <is>
+          <t>Inappropriate</t>
+        </is>
+      </c>
+      <c r="DM35" s="2" t="inlineStr">
+        <is>
+          <t>Somewhat easy to detect</t>
+        </is>
+      </c>
+      <c r="DN35" s="2" t="inlineStr">
+        <is>
+          <t>Easy to detect</t>
+        </is>
+      </c>
+      <c r="DO35" s="2" t="inlineStr">
+        <is>
+          <t>Very easy to detect</t>
+        </is>
+      </c>
+      <c r="DP35" s="2" t="inlineStr">
+        <is>
+          <t>Not disruptive at all</t>
+        </is>
+      </c>
+      <c r="DQ35" s="2" t="inlineStr">
+        <is>
+          <t>Somewhat disruptive</t>
+        </is>
+      </c>
+      <c r="DR35" s="2" t="inlineStr">
+        <is>
+          <t>Disruptive</t>
+        </is>
+      </c>
+      <c r="DS35" s="2" t="inlineStr">
+        <is>
+          <t>Completely Acceptable</t>
+        </is>
+      </c>
+      <c r="DT35" s="2" t="inlineStr">
+        <is>
+          <t>Somewhat acceptable</t>
+        </is>
+      </c>
+      <c r="DU35" s="2" t="inlineStr">
+        <is>
+          <t>Somewhat unacceptable</t>
+        </is>
+      </c>
+      <c r="DV35" s="2" t="inlineStr">
+        <is>
+          <t>🔔 Version 1</t>
+        </is>
+      </c>
+      <c r="DW35" s="2" t="inlineStr">
+        <is>
+          <t>Because I am relaxing and my mind is already clear. The notification can be delivered through the speakers of my glasses. There are no mental distractions, thus if I only hear the notification sound I can easily pick up my phone and respond.</t>
+        </is>
+      </c>
+      <c r="DX35" s="2" t="inlineStr">
+        <is>
+          <t>Acoustic Environment (e.g., the level of background noise, music, or other people talking)</t>
+        </is>
+      </c>
+      <c r="DY35" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="DZ35" s="2" t="inlineStr">
+        <is>
+          <t>When I am between songs / during a natural pause in music</t>
+        </is>
+      </c>
+      <c r="EA35" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="EB35" s="2" t="inlineStr">
+        <is>
+          <t>🗣️ Version 2</t>
+        </is>
+      </c>
+      <c r="EC35" s="2" t="inlineStr">
+        <is>
+          <t>During a pause in the music, it is fine to be notified about the sender's name. So I can know that it's Lily and anticipate that it might be urgent.</t>
+        </is>
+      </c>
+      <c r="ED35" t="n">
+        <v>39.455</v>
+      </c>
+      <c r="EE35" t="n">
+        <v>151.454</v>
+      </c>
+      <c r="EF35" t="n">
+        <v>181.378</v>
+      </c>
+      <c r="EG35" t="n">
+        <v>21.0</v>
+      </c>
+      <c r="EH35" s="2" t="inlineStr">
+        <is>
+          <t>Somewhat disagree</t>
+        </is>
+      </c>
+      <c r="EI35" t="n">
+        <v>2.264</v>
+      </c>
+      <c r="EJ35" t="n">
+        <v>2.264</v>
+      </c>
+      <c r="EK35" t="n">
+        <v>2.955</v>
+      </c>
+      <c r="EL35" t="n">
+        <v>1.0</v>
+      </c>
+      <c r="EM35" s="2" t="inlineStr">
+        <is>
+          <t>Appropriate</t>
+        </is>
+      </c>
+      <c r="EN35" s="2" t="inlineStr">
+        <is>
+          <t>Appropriate</t>
+        </is>
+      </c>
+      <c r="EO35" s="2" t="inlineStr">
+        <is>
+          <t>Completely appropriate</t>
+        </is>
+      </c>
+      <c r="EP35" s="2" t="inlineStr">
+        <is>
+          <t>Somewhat difficult to detect</t>
+        </is>
+      </c>
+      <c r="EQ35" s="2" t="inlineStr">
+        <is>
+          <t>Neither easy nor difficult to detect</t>
+        </is>
+      </c>
+      <c r="ER35" s="2" t="inlineStr">
+        <is>
+          <t>Easy to detect</t>
+        </is>
+      </c>
+      <c r="ES35" s="2" t="inlineStr">
+        <is>
+          <t>Not disruptive at all</t>
+        </is>
+      </c>
+      <c r="ET35" s="2" t="inlineStr">
+        <is>
+          <t>Somewhat disruptive</t>
+        </is>
+      </c>
+      <c r="EU35" s="2" t="inlineStr">
+        <is>
+          <t>Disruptive</t>
+        </is>
+      </c>
+      <c r="EV35" s="2" t="inlineStr">
+        <is>
+          <t>Acceptable</t>
+        </is>
+      </c>
+      <c r="EW35" s="2" t="inlineStr">
+        <is>
+          <t>Acceptable</t>
+        </is>
+      </c>
+      <c r="EX35" s="2" t="inlineStr">
+        <is>
+          <t>Acceptable</t>
+        </is>
+      </c>
+      <c r="EY35" s="2" t="inlineStr">
+        <is>
+          <t>🗣️🗣️ Version 3</t>
+        </is>
+      </c>
+      <c r="EZ35" s="2" t="inlineStr">
+        <is>
+          <t>It is a loud environment with physical activity going on, so if it is an urgent message I would like to hear the sender and the content so I can stop what I am doing and respond.</t>
+        </is>
+      </c>
+      <c r="FA35" s="2" t="inlineStr">
+        <is>
+          <t>Acoustic Environment (e.g., the level of background noise, music, or other people talking),Focus &amp; Mental Effort (e.g., needing to concentrate on my current task without being interrupted),Desire for Information (e.g., wanting to know the exact sender or content immediately without having to use my hands/phone)</t>
+        </is>
+      </c>
+      <c r="FB35" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="FC35" s="2" t="inlineStr">
+        <is>
+          <t>Immediately</t>
+        </is>
+      </c>
+      <c r="FD35" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="FE35" s="2" t="inlineStr">
+        <is>
+          <t>Not applicable (I chose "Immediately" in the previous question).</t>
+        </is>
+      </c>
+      <c r="FF35" s="2" t="inlineStr">
+        <is>
+          <t>Urgency of the message</t>
+        </is>
+      </c>
+      <c r="FG35" t="n">
+        <v>65.219</v>
+      </c>
+      <c r="FH35" t="n">
+        <v>166.874</v>
+      </c>
+      <c r="FI35" t="n">
+        <v>169.222</v>
+      </c>
+      <c r="FJ35" t="n">
+        <v>22.0</v>
+      </c>
+      <c r="FK35" s="2" t="inlineStr">
+        <is>
+          <t>Appropriate</t>
+        </is>
+      </c>
+      <c r="FL35" s="2" t="inlineStr">
+        <is>
+          <t>Appropriate</t>
+        </is>
+      </c>
+      <c r="FM35" s="2" t="inlineStr">
+        <is>
+          <t>Somewhat appropriate</t>
+        </is>
+      </c>
+      <c r="FN35" s="2" t="inlineStr">
+        <is>
+          <t>Very easy to detect</t>
+        </is>
+      </c>
+      <c r="FO35" s="2" t="inlineStr">
+        <is>
+          <t>Very easy to detect</t>
+        </is>
+      </c>
+      <c r="FP35" s="2" t="inlineStr">
+        <is>
+          <t>Very easy to detect</t>
+        </is>
+      </c>
+      <c r="FQ35" s="2" t="inlineStr">
+        <is>
+          <t>Not disruptive at all</t>
+        </is>
+      </c>
+      <c r="FR35" s="2" t="inlineStr">
+        <is>
+          <t>Slightly disruptive</t>
+        </is>
+      </c>
+      <c r="FS35" s="2" t="inlineStr">
+        <is>
+          <t>Somewhat disruptive</t>
+        </is>
+      </c>
+      <c r="FT35" s="2" t="inlineStr">
+        <is>
+          <t>Completely Acceptable</t>
+        </is>
+      </c>
+      <c r="FU35" s="2" t="inlineStr">
+        <is>
+          <t>Acceptable</t>
+        </is>
+      </c>
+      <c r="FV35" s="2" t="inlineStr">
+        <is>
+          <t>Somewhat acceptable</t>
+        </is>
+      </c>
+      <c r="FW35" s="2" t="inlineStr">
+        <is>
+          <t>🔔 Version 1</t>
+        </is>
+      </c>
+      <c r="FX35" s="2" t="inlineStr">
+        <is>
+          <t>I want to focus on my surroundings during cycling, so only being notified with a ping is sufficient.</t>
+        </is>
+      </c>
+      <c r="FY35" s="2" t="inlineStr">
+        <is>
+          <t>Physical Safety &amp; Awareness (e.g., needing to pay visual or mental attention to my physical surroundings, like traffic)</t>
+        </is>
+      </c>
+      <c r="FZ35" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="GA35" s="2" t="inlineStr">
+        <is>
+          <t>After I reach a safe stopping point (e.g., at a traffic light)</t>
+        </is>
+      </c>
+      <c r="GB35" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="GC35" s="2" t="inlineStr">
+        <is>
+          <t>🗣️ Version 2</t>
+        </is>
+      </c>
+      <c r="GD35" s="2" t="inlineStr">
+        <is>
+          <t>While waiting for a traffic light or when I am in a safe spot, notification can inform me on the message being from Lily so I can decide that it might be urgent and important thus respond to her while I am waiting.</t>
+        </is>
+      </c>
+      <c r="GE35" t="n">
+        <v>28.069</v>
+      </c>
+      <c r="GF35" t="n">
+        <v>82.005</v>
+      </c>
+      <c r="GG35" t="n">
+        <v>132.456</v>
+      </c>
+      <c r="GH35" t="n">
+        <v>21.0</v>
+      </c>
+      <c r="GI35" s="2" t="inlineStr">
+        <is>
+          <t>Completely appropriate</t>
+        </is>
+      </c>
+      <c r="GJ35" s="2" t="inlineStr">
+        <is>
+          <t>Completely appropriate</t>
+        </is>
+      </c>
+      <c r="GK35" s="2" t="inlineStr">
+        <is>
+          <t>Completely appropriate</t>
+        </is>
+      </c>
+      <c r="GL35" s="2" t="inlineStr">
+        <is>
+          <t>Somewhat difficult to detect</t>
+        </is>
+      </c>
+      <c r="GM35" s="2" t="inlineStr">
+        <is>
+          <t>Somewhat easy to detect</t>
+        </is>
+      </c>
+      <c r="GN35" s="2" t="inlineStr">
+        <is>
+          <t>Very easy to detect</t>
+        </is>
+      </c>
+      <c r="GO35" s="2" t="inlineStr">
+        <is>
+          <t>Not disruptive at all</t>
+        </is>
+      </c>
+      <c r="GP35" s="2" t="inlineStr">
+        <is>
+          <t>Slightly disruptive</t>
+        </is>
+      </c>
+      <c r="GQ35" s="2" t="inlineStr">
+        <is>
+          <t>Moderately disruptive</t>
+        </is>
+      </c>
+      <c r="GR35" s="2" t="inlineStr">
+        <is>
+          <t>Completely Acceptable</t>
+        </is>
+      </c>
+      <c r="GS35" s="2" t="inlineStr">
+        <is>
+          <t>Somewhat acceptable</t>
+        </is>
+      </c>
+      <c r="GT35" s="2" t="inlineStr">
+        <is>
+          <t>Somewhat acceptable</t>
+        </is>
+      </c>
+      <c r="GU35" s="2" t="inlineStr">
+        <is>
+          <t>🗣️🗣️ Version 3</t>
+        </is>
+      </c>
+      <c r="GV35" s="2" t="inlineStr">
+        <is>
+          <t>Since my hands are occupied, and there is an active announcement going on it is better to hear the full content of the message without needing to reach my phone.</t>
+        </is>
+      </c>
+      <c r="GW35" s="2" t="inlineStr">
+        <is>
+          <t>Acoustic Environment (e.g., the level of background noise, music, or other people talking),Desire for Information (e.g., wanting to know the exact sender or content immediately without having to use my hands/phone)</t>
+        </is>
+      </c>
+      <c r="GX35" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="GY35" s="2" t="inlineStr">
+        <is>
+          <t>Immediately</t>
+        </is>
+      </c>
+      <c r="GZ35" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="HA35" s="2" t="inlineStr">
+        <is>
+          <t>Not applicable (I chose "Immediately" in the previous question).</t>
+        </is>
+      </c>
+      <c r="HB35" s="2" t="inlineStr">
+        <is>
+          <t>If it was only the notification ping, I would be curious about the message and interrupt what I am doing to check my phone. However, with the content included I can know the content without interrupting my shopping.</t>
+        </is>
+      </c>
+      <c r="HC35" t="n">
+        <v>41.955</v>
+      </c>
+      <c r="HD35" t="n">
+        <v>163.211</v>
+      </c>
+      <c r="HE35" t="n">
+        <v>163.719</v>
+      </c>
+      <c r="HF35" t="n">
+        <v>20.0</v>
+      </c>
+      <c r="HG35" s="2" t="inlineStr">
+        <is>
+          <t>Agree</t>
+        </is>
+      </c>
+      <c r="HH35" t="n">
+        <v>2.257</v>
+      </c>
+      <c r="HI35" t="n">
+        <v>2.257</v>
+      </c>
+      <c r="HJ35" t="n">
+        <v>3.035</v>
+      </c>
+      <c r="HK35" t="n">
+        <v>1.0</v>
+      </c>
+      <c r="HL35" s="2" t="inlineStr">
+        <is>
+          <t>Appropriate</t>
+        </is>
+      </c>
+      <c r="HM35" s="2" t="inlineStr">
+        <is>
+          <t>Appropriate</t>
+        </is>
+      </c>
+      <c r="HN35" s="2" t="inlineStr">
+        <is>
+          <t>Appropriate</t>
+        </is>
+      </c>
+      <c r="HO35" s="2" t="inlineStr">
+        <is>
+          <t>Somewhat easy to detect</t>
+        </is>
+      </c>
+      <c r="HP35" s="2" t="inlineStr">
+        <is>
+          <t>Easy to detect</t>
+        </is>
+      </c>
+      <c r="HQ35" s="2" t="inlineStr">
+        <is>
+          <t>Very easy to detect</t>
+        </is>
+      </c>
+      <c r="HR35" s="2" t="inlineStr">
+        <is>
+          <t>Not disruptive at all</t>
+        </is>
+      </c>
+      <c r="HS35" s="2" t="inlineStr">
+        <is>
+          <t>Slightly disruptive</t>
+        </is>
+      </c>
+      <c r="HT35" s="2" t="inlineStr">
+        <is>
+          <t>Moderately disruptive</t>
+        </is>
+      </c>
+      <c r="HU35" s="2" t="inlineStr">
+        <is>
+          <t>Acceptable</t>
+        </is>
+      </c>
+      <c r="HV35" s="2" t="inlineStr">
+        <is>
+          <t>Acceptable</t>
+        </is>
+      </c>
+      <c r="HW35" s="2" t="inlineStr">
+        <is>
+          <t>Acceptable</t>
+        </is>
+      </c>
+      <c r="HX35" s="2" t="inlineStr">
+        <is>
+          <t>🔔 Version 1</t>
+        </is>
+      </c>
+      <c r="HY35" s="2" t="inlineStr">
+        <is>
+          <t>The need to focus on cooking and not to be distracted is my main reason. Because, when I am cooking I can be somewhat clumsy and a detailed notification would probably overstimulate me in that situation.</t>
+        </is>
+      </c>
+      <c r="HZ35" s="2" t="inlineStr">
+        <is>
+          <t>Focus &amp; Mental Effort (e.g., needing to concentrate on my current task without being interrupted),Physical Safety &amp; Awareness (e.g., needing to pay visual or mental attention to my physical surroundings, like traffic)</t>
+        </is>
+      </c>
+      <c r="IA35" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="IB35" s="2" t="inlineStr">
+        <is>
+          <t>After I finish an active cooking step (e.g., finishing chopping the vegetables)</t>
+        </is>
+      </c>
+      <c r="IC35" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="ID35" s="2" t="inlineStr">
+        <is>
+          <t>🗣️🗣️ Version 3</t>
+        </is>
+      </c>
+      <c r="IE35" s="2" t="inlineStr">
+        <is>
+          <t>After I finish an active step, it is okay to notify me about the content of the message as well. Then I can wash my hands if necessary and respond to Lily.</t>
+        </is>
+      </c>
+      <c r="IF35" t="n">
+        <v>46.831</v>
+      </c>
+      <c r="IG35" t="n">
+        <v>135.351</v>
+      </c>
+      <c r="IH35" t="n">
+        <v>170.738</v>
+      </c>
+      <c r="II35" t="n">
+        <v>20.0</v>
+      </c>
+      <c r="IJ35" s="2" t="inlineStr">
+        <is>
+          <t>Appropriate</t>
+        </is>
+      </c>
+      <c r="IK35" s="2" t="inlineStr">
+        <is>
+          <t>Somewhat inappropriate</t>
+        </is>
+      </c>
+      <c r="IL35" s="2" t="inlineStr">
+        <is>
+          <t>Inappropriate</t>
+        </is>
+      </c>
+      <c r="IM35" s="2" t="inlineStr">
+        <is>
+          <t>Easy to detect</t>
+        </is>
+      </c>
+      <c r="IN35" s="2" t="inlineStr">
+        <is>
+          <t>Easy to detect</t>
+        </is>
+      </c>
+      <c r="IO35" s="2" t="inlineStr">
+        <is>
+          <t>Very easy to detect</t>
+        </is>
+      </c>
+      <c r="IP35" s="2" t="inlineStr">
+        <is>
+          <t>Slightly disruptive</t>
+        </is>
+      </c>
+      <c r="IQ35" s="2" t="inlineStr">
+        <is>
+          <t>Somewhat disruptive</t>
+        </is>
+      </c>
+      <c r="IR35" s="2" t="inlineStr">
+        <is>
+          <t>Moderately disruptive</t>
+        </is>
+      </c>
+      <c r="IS35" s="2" t="inlineStr">
+        <is>
+          <t>Acceptable</t>
+        </is>
+      </c>
+      <c r="IT35" s="2" t="inlineStr">
+        <is>
+          <t>Somewhat acceptable</t>
+        </is>
+      </c>
+      <c r="IU35" s="2" t="inlineStr">
+        <is>
+          <t>Neither acceptable nor unacceptable</t>
+        </is>
+      </c>
+      <c r="IV35" s="2" t="inlineStr">
+        <is>
+          <t>🔔 Version 1</t>
+        </is>
+      </c>
+      <c r="IW35" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">I don't want to strongly disrupt my focus, so my preference is definitely a ping in that situation. </t>
+        </is>
+      </c>
+      <c r="IX35" s="2" t="inlineStr">
+        <is>
+          <t>Focus &amp; Mental Effort (e.g., needing to concentrate on my current task without being interrupted)</t>
+        </is>
+      </c>
+      <c r="IY35" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="IZ35" s="2" t="inlineStr">
+        <is>
+          <t>When I briefly pause my studying/reading to take a sip of coffee or look up</t>
+        </is>
+      </c>
+      <c r="JA35" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="JB35" s="2" t="inlineStr">
+        <is>
+          <t>🗣️ Version 2</t>
+        </is>
+      </c>
+      <c r="JC35" s="2" t="inlineStr">
+        <is>
+          <t>When I briefly pause for a sip or turning the page, I would prefer hearing that the message is from Lily so I can use that opportunity to respond to her.</t>
+        </is>
+      </c>
+      <c r="JD35" t="n">
+        <v>26.588</v>
+      </c>
+      <c r="JE35" t="n">
+        <v>94.956</v>
+      </c>
+      <c r="JF35" t="n">
+        <v>129.509</v>
+      </c>
+      <c r="JG35" t="n">
+        <v>22.0</v>
+      </c>
+      <c r="JH35" s="2" t="inlineStr">
+        <is>
+          <t>Appropriate</t>
+        </is>
+      </c>
+      <c r="JI35" s="2" t="inlineStr">
+        <is>
+          <t>Somewhat appropriate</t>
+        </is>
+      </c>
+      <c r="JJ35" s="2" t="inlineStr">
+        <is>
+          <t>Somewhat inappropriate</t>
+        </is>
+      </c>
+      <c r="JK35" s="2" t="inlineStr">
+        <is>
+          <t>Very easy to detect</t>
+        </is>
+      </c>
+      <c r="JL35" s="2" t="inlineStr">
+        <is>
+          <t>Very easy to detect</t>
+        </is>
+      </c>
+      <c r="JM35" s="2" t="inlineStr">
+        <is>
+          <t>Very easy to detect</t>
+        </is>
+      </c>
+      <c r="JN35" s="2" t="inlineStr">
+        <is>
+          <t>Not disruptive at all</t>
+        </is>
+      </c>
+      <c r="JO35" s="2" t="inlineStr">
+        <is>
+          <t>Not disruptive at all</t>
+        </is>
+      </c>
+      <c r="JP35" s="2" t="inlineStr">
+        <is>
+          <t>Slightly disruptive</t>
+        </is>
+      </c>
+      <c r="JQ35" s="2" t="inlineStr">
+        <is>
+          <t>Somewhat acceptable</t>
+        </is>
+      </c>
+      <c r="JR35" s="2" t="inlineStr">
+        <is>
+          <t>Neither acceptable nor unacceptable</t>
+        </is>
+      </c>
+      <c r="JS35" s="2" t="inlineStr">
+        <is>
+          <t>Neither acceptable nor unacceptable</t>
+        </is>
+      </c>
+      <c r="JT35" s="2" t="inlineStr">
+        <is>
+          <t>🔔 Version 1</t>
+        </is>
+      </c>
+      <c r="JU35" s="2" t="inlineStr">
+        <is>
+          <t>Since Jessica already stopped to check something on her phone, just hearing the notification ping is enough. Because there is already a pause in the social interaction, so I can also check my phone to see what's going on.</t>
+        </is>
+      </c>
+      <c r="JV35" s="2" t="inlineStr">
+        <is>
+          <t>Acoustic Environment (e.g., the level of background noise, music, or other people talking)</t>
+        </is>
+      </c>
+      <c r="JW35" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="JX35" s="2" t="inlineStr">
+        <is>
+          <t>Immediately</t>
+        </is>
+      </c>
+      <c r="JY35" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="JZ35" s="2" t="inlineStr">
+        <is>
+          <t>Not applicable (I chose "Immediately" in the previous question).</t>
+        </is>
+      </c>
+      <c r="KA35" s="2" t="inlineStr">
+        <is>
+          <t>Considering the brief pause in the interaction, I think it is a good moment for just a ping and me reaching my phone to shortly check it.</t>
+        </is>
+      </c>
+      <c r="KB35" t="n">
+        <v>29.709</v>
+      </c>
+      <c r="KC35" t="n">
+        <v>111.404</v>
+      </c>
+      <c r="KD35" t="n">
+        <v>139.28</v>
+      </c>
+      <c r="KE35" t="n">
+        <v>19.0</v>
+      </c>
+      <c r="KF35" s="2" t="inlineStr">
+        <is>
+          <t>Mute (Do not notify me auditorily at all) 🔕</t>
+        </is>
+      </c>
+      <c r="KG35" s="2" t="inlineStr">
+        <is>
+          <t>Mute (Do not notify me auditorily at all) 🔕</t>
+        </is>
+      </c>
+      <c r="KH35" s="2" t="inlineStr">
+        <is>
+          <t>Sound Only 'Version 1' 🔔</t>
+        </is>
+      </c>
+      <c r="KI35" s="2" t="inlineStr">
+        <is>
+          <t>Speech 'Version 3' (Sender + Full/Summarized Content) 🗣️🗣️</t>
+        </is>
+      </c>
+      <c r="KJ35" s="2" t="inlineStr">
+        <is>
+          <t>Indefinite delay (Hours): Can be withheld entirely until I manually check my phone or ask the device.</t>
+        </is>
+      </c>
+      <c r="KK35" s="2" t="inlineStr">
+        <is>
+          <t>Indefinite delay (Hours): Can be withheld entirely until I manually check my phone or ask the device.</t>
+        </is>
+      </c>
+      <c r="KL35" s="2" t="inlineStr">
+        <is>
+          <t>Moderate delay (Minutes): Can wait until I finish my current task (e.g., finishing an email or a conversation).</t>
+        </is>
+      </c>
+      <c r="KM35" s="2" t="inlineStr">
+        <is>
+          <t>Brief delay (Seconds): Can wait for a quick safe moment (e.g., until I finish crossing the street, silence).</t>
+        </is>
+      </c>
+      <c r="KN35" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="KO35" t="n">
+        <v>21.385</v>
+      </c>
+      <c r="KP35" t="n">
+        <v>90.584</v>
+      </c>
+      <c r="KQ35" t="n">
+        <v>95.075</v>
+      </c>
+      <c r="KR35" t="n">
+        <v>11.0</v>
+      </c>
+      <c r="KS35" s="2" t="inlineStr">
+        <is>
+          <t>2356</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="1" t="n">
+        <v>46204.6125</v>
+      </c>
+      <c r="B36" s="1" t="n">
+        <v>46204.62747685185</v>
+      </c>
+      <c r="C36" s="2" t="inlineStr">
+        <is>
+          <t>IP Address</t>
+        </is>
+      </c>
+      <c r="D36" s="2" t="inlineStr">
+        <is>
+          <t>138.246.3.119</t>
+        </is>
+      </c>
+      <c r="E36" t="n">
+        <v>100.0</v>
+      </c>
+      <c r="F36" t="n">
+        <v>1293.0</v>
+      </c>
+      <c r="G36" s="2" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="H36" s="1" t="n">
+        <v>46204.627489467595</v>
+      </c>
+      <c r="I36" s="2" t="inlineStr">
+        <is>
+          <t>R_8eXdWDp0BXIS3ih</t>
+        </is>
+      </c>
+      <c r="J36" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="K36" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="L36" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="M36" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="N36" t="n">
+        <v>48.1477</v>
+      </c>
+      <c r="O36" t="n">
+        <v>11.5695</v>
+      </c>
+      <c r="P36" s="2" t="inlineStr">
+        <is>
+          <t>anonymous</t>
+        </is>
+      </c>
+      <c r="Q36" s="2" t="inlineStr">
+        <is>
+          <t>EN</t>
+        </is>
+      </c>
+      <c r="R36" s="2" t="inlineStr">
+        <is>
+          <t>I understand the explanation provided to me. I was able to save a copy of this form. I reached out to the listed researchers and have had all my questions answered to my satisfaction. Therefore, I voluntarily agree to participate in this online study.,I voluntarily consent to my data being recorded and subsequently processed in line with the GDPR. I have been informed about the consequences of withdrawing my consent.</t>
+        </is>
+      </c>
+      <c r="S36" t="n">
+        <v>22.472</v>
+      </c>
+      <c r="T36" t="n">
+        <v>23.68</v>
+      </c>
+      <c r="U36" t="n">
+        <v>26.946</v>
+      </c>
+      <c r="V36" t="n">
+        <v>2.0</v>
+      </c>
+      <c r="W36" s="2" t="inlineStr">
+        <is>
+          <t>Yes, I am using a desktop or laptop computer.</t>
+        </is>
+      </c>
+      <c r="X36" s="2" t="inlineStr">
+        <is>
+          <t>Yes, I am wearing headphones.</t>
+        </is>
+      </c>
+      <c r="Y36" s="2" t="inlineStr">
+        <is>
+          <t>Right Channel</t>
+        </is>
+      </c>
+      <c r="Z36" t="n">
+        <v>7.503</v>
+      </c>
+      <c r="AA36" t="n">
+        <v>33.807</v>
+      </c>
+      <c r="AB36" t="n">
+        <v>35.315</v>
+      </c>
+      <c r="AC36" t="n">
+        <v>6.0</v>
+      </c>
+      <c r="AD36" t="n">
+        <v>25.0</v>
+      </c>
+      <c r="AE36" s="2" t="inlineStr">
+        <is>
+          <t>Female</t>
+        </is>
+      </c>
+      <c r="AF36" s="2" t="inlineStr">
+        <is>
+          <t>German</t>
+        </is>
+      </c>
+      <c r="AG36" s="2" t="inlineStr">
+        <is>
+          <t>Understand very well</t>
+        </is>
+      </c>
+      <c r="AH36" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="AI36" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AJ36" s="2" t="inlineStr">
+        <is>
+          <t>No notification at all (Muted / Do Not Disturb)</t>
+        </is>
+      </c>
+      <c r="AK36" s="2" t="inlineStr">
+        <is>
+          <t>Personal Focus: To avoid distracting myself or breaking my concentration.</t>
+        </is>
+      </c>
+      <c r="AL36" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AM36" s="2" t="inlineStr">
+        <is>
+          <t>Never</t>
+        </is>
+      </c>
+      <c r="AN36" s="2" t="inlineStr">
+        <is>
+          <t>Phone Calls,Navigation / Directions</t>
+        </is>
+      </c>
+      <c r="AO36" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AP36" s="2" t="inlineStr">
+        <is>
+          <t>Somewhat disagree</t>
+        </is>
+      </c>
+      <c r="AQ36" s="2" t="inlineStr">
+        <is>
+          <t>Somewhat disagree</t>
+        </is>
+      </c>
+      <c r="AR36" t="n">
+        <v>1.222</v>
+      </c>
+      <c r="AS36" t="n">
+        <v>94.1</v>
+      </c>
+      <c r="AT36" t="n">
+        <v>94.443</v>
+      </c>
+      <c r="AU36" t="n">
+        <v>16.0</v>
+      </c>
+      <c r="AV36" s="2" t="inlineStr">
+        <is>
+          <t>🗣️Version 2,🗣️🗣️ Version 3</t>
+        </is>
+      </c>
+      <c r="AW36" s="2" t="inlineStr">
+        <is>
+          <t>I don't want to be notified auditorily about this notification</t>
+        </is>
+      </c>
+      <c r="AX36" s="2" t="inlineStr">
+        <is>
+          <t>möchte die Info asynchron erhalten (also möchte diese Nachricht eher lesen)</t>
+        </is>
+      </c>
+      <c r="AY36" s="2" t="inlineStr">
+        <is>
+          <t>Agree</t>
+        </is>
+      </c>
+      <c r="AZ36" s="2" t="inlineStr">
+        <is>
+          <t>Disagree</t>
+        </is>
+      </c>
+      <c r="BA36" s="2" t="inlineStr">
+        <is>
+          <t>Too intrusive</t>
+        </is>
+      </c>
+      <c r="BB36" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="BC36" s="2" t="inlineStr">
+        <is>
+          <t>Long (no strong limit)</t>
+        </is>
+      </c>
+      <c r="BD36" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="BE36" s="2" t="inlineStr">
+        <is>
+          <t>Disagree</t>
+        </is>
+      </c>
+      <c r="BF36" t="n">
+        <v>14.762</v>
+      </c>
+      <c r="BG36" t="n">
+        <v>51.537</v>
+      </c>
+      <c r="BH36" t="n">
+        <v>52.702</v>
+      </c>
+      <c r="BI36" t="n">
+        <v>13.0</v>
+      </c>
+      <c r="BJ36" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="BK36" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="BL36" t="n">
+        <v>12.234</v>
+      </c>
+      <c r="BM36" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="BN36" s="2" t="inlineStr">
+        <is>
+          <t>Somewhat inappropriate</t>
+        </is>
+      </c>
+      <c r="BO36" s="2" t="inlineStr">
+        <is>
+          <t>Somewhat inappropriate</t>
+        </is>
+      </c>
+      <c r="BP36" s="2" t="inlineStr">
+        <is>
+          <t>Somewhat inappropriate</t>
+        </is>
+      </c>
+      <c r="BQ36" s="2" t="inlineStr">
+        <is>
+          <t>Easy to detect</t>
+        </is>
+      </c>
+      <c r="BR36" s="2" t="inlineStr">
+        <is>
+          <t>Easy to detect</t>
+        </is>
+      </c>
+      <c r="BS36" s="2" t="inlineStr">
+        <is>
+          <t>Easy to detect</t>
+        </is>
+      </c>
+      <c r="BT36" s="2" t="inlineStr">
+        <is>
+          <t>Very disruptive</t>
+        </is>
+      </c>
+      <c r="BU36" s="2" t="inlineStr">
+        <is>
+          <t>Very disruptive</t>
+        </is>
+      </c>
+      <c r="BV36" s="2" t="inlineStr">
+        <is>
+          <t>Very disruptive</t>
+        </is>
+      </c>
+      <c r="BW36" s="2" t="inlineStr">
+        <is>
+          <t>Acceptable</t>
+        </is>
+      </c>
+      <c r="BX36" s="2" t="inlineStr">
+        <is>
+          <t>Acceptable</t>
+        </is>
+      </c>
+      <c r="BY36" s="2" t="inlineStr">
+        <is>
+          <t>Acceptable</t>
+        </is>
+      </c>
+      <c r="BZ36" s="2" t="inlineStr">
+        <is>
+          <t>No audio notification at all</t>
+        </is>
+      </c>
+      <c r="CA36" s="2" t="inlineStr">
+        <is>
+          <t>need to concentrate</t>
+        </is>
+      </c>
+      <c r="CB36" s="2" t="inlineStr">
+        <is>
+          <t>Focus &amp; Mental Effort (e.g., needing to concentrate on my current task without being interrupted)</t>
+        </is>
+      </c>
+      <c r="CC36" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="CD36" s="2" t="inlineStr">
+        <is>
+          <t>Later, when I am done working</t>
+        </is>
+      </c>
+      <c r="CE36" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="CF36" s="2" t="inlineStr">
+        <is>
+          <t>🗣️🗣️ Version 3</t>
+        </is>
+      </c>
+      <c r="CG36" s="2" t="inlineStr">
+        <is>
+          <t>immediate information</t>
+        </is>
+      </c>
+      <c r="CH36" t="n">
+        <v>9.131</v>
+      </c>
+      <c r="CI36" t="n">
+        <v>65.544</v>
+      </c>
+      <c r="CJ36" t="n">
+        <v>73.246</v>
+      </c>
+      <c r="CK36" t="n">
+        <v>25.0</v>
+      </c>
+      <c r="CL36" s="2" t="inlineStr">
+        <is>
+          <t>Completely inappropriate</t>
+        </is>
+      </c>
+      <c r="CM36" s="2" t="inlineStr">
+        <is>
+          <t>Completely inappropriate</t>
+        </is>
+      </c>
+      <c r="CN36" s="2" t="inlineStr">
+        <is>
+          <t>Completely inappropriate</t>
+        </is>
+      </c>
+      <c r="CO36" s="2" t="inlineStr">
+        <is>
+          <t>Somewhat easy to detect</t>
+        </is>
+      </c>
+      <c r="CP36" s="2" t="inlineStr">
+        <is>
+          <t>Somewhat easy to detect</t>
+        </is>
+      </c>
+      <c r="CQ36" s="2" t="inlineStr">
+        <is>
+          <t>Somewhat easy to detect</t>
+        </is>
+      </c>
+      <c r="CR36" s="2" t="inlineStr">
+        <is>
+          <t>Very disruptive</t>
+        </is>
+      </c>
+      <c r="CS36" s="2" t="inlineStr">
+        <is>
+          <t>Extremely disruptive</t>
+        </is>
+      </c>
+      <c r="CT36" s="2" t="inlineStr">
+        <is>
+          <t>Extremely disruptive</t>
+        </is>
+      </c>
+      <c r="CU36" s="2" t="inlineStr">
+        <is>
+          <t>Unacceptable</t>
+        </is>
+      </c>
+      <c r="CV36" s="2" t="inlineStr">
+        <is>
+          <t>Unacceptable</t>
+        </is>
+      </c>
+      <c r="CW36" s="2" t="inlineStr">
+        <is>
+          <t>Unacceptable</t>
+        </is>
+      </c>
+      <c r="CX36" s="2" t="inlineStr">
+        <is>
+          <t>No audio notification at all</t>
+        </is>
+      </c>
+      <c r="CY36" s="2" t="inlineStr">
+        <is>
+          <t>have to concentrate</t>
+        </is>
+      </c>
+      <c r="CZ36" s="2" t="inlineStr">
+        <is>
+          <t>Focus &amp; Mental Effort (e.g., needing to concentrate on my current task without being interrupted),Social Appropriateness (e.g., the presence of others, social etiquette, or not wanting to appear distracted)</t>
+        </is>
+      </c>
+      <c r="DA36" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="DB36" s="2" t="inlineStr">
+        <is>
+          <t>Later, when the meeting is over</t>
+        </is>
+      </c>
+      <c r="DC36" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="DD36" s="2" t="inlineStr">
+        <is>
+          <t>🗣️🗣️ Version 3</t>
+        </is>
+      </c>
+      <c r="DE36" s="2" t="inlineStr">
+        <is>
+          <t>no disruption</t>
+        </is>
+      </c>
+      <c r="DF36" t="n">
+        <v>2.601</v>
+      </c>
+      <c r="DG36" t="n">
+        <v>66.934</v>
+      </c>
+      <c r="DH36" t="n">
+        <v>73.916</v>
+      </c>
+      <c r="DI36" t="n">
+        <v>27.0</v>
+      </c>
+      <c r="DJ36" s="2" t="inlineStr">
+        <is>
+          <t>Appropriate</t>
+        </is>
+      </c>
+      <c r="DK36" s="2" t="inlineStr">
+        <is>
+          <t>Appropriate</t>
+        </is>
+      </c>
+      <c r="DL36" s="2" t="inlineStr">
+        <is>
+          <t>Appropriate</t>
+        </is>
+      </c>
+      <c r="DM36" s="2" t="inlineStr">
+        <is>
+          <t>Easy to detect</t>
+        </is>
+      </c>
+      <c r="DN36" s="2" t="inlineStr">
+        <is>
+          <t>Easy to detect</t>
+        </is>
+      </c>
+      <c r="DO36" s="2" t="inlineStr">
+        <is>
+          <t>Easy to detect</t>
+        </is>
+      </c>
+      <c r="DP36" s="2" t="inlineStr">
+        <is>
+          <t>Slightly disruptive</t>
+        </is>
+      </c>
+      <c r="DQ36" s="2" t="inlineStr">
+        <is>
+          <t>Somewhat disruptive</t>
+        </is>
+      </c>
+      <c r="DR36" s="2" t="inlineStr">
+        <is>
+          <t>Somewhat disruptive</t>
+        </is>
+      </c>
+      <c r="DS36" s="2" t="inlineStr">
+        <is>
+          <t>Acceptable</t>
+        </is>
+      </c>
+      <c r="DT36" s="2" t="inlineStr">
+        <is>
+          <t>Acceptable</t>
+        </is>
+      </c>
+      <c r="DU36" s="2" t="inlineStr">
+        <is>
+          <t>Acceptable</t>
+        </is>
+      </c>
+      <c r="DV36" s="2" t="inlineStr">
+        <is>
+          <t>🗣️🗣️ Version 3</t>
+        </is>
+      </c>
+      <c r="DW36" s="2" t="inlineStr">
+        <is>
+          <t>immediate information</t>
+        </is>
+      </c>
+      <c r="DX36" s="2" t="inlineStr">
+        <is>
+          <t>Other (please specify):</t>
+        </is>
+      </c>
+      <c r="DY36" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="DZ36" s="2" t="inlineStr">
+        <is>
+          <t>Immediately</t>
+        </is>
+      </c>
+      <c r="EA36" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="EB36" s="2" t="inlineStr">
+        <is>
+          <t>Not applicable (I chose "Immediately" in the previous question).</t>
+        </is>
+      </c>
+      <c r="EC36" s="2" t="inlineStr">
+        <is>
+          <t>immediate information</t>
+        </is>
+      </c>
+      <c r="ED36" t="n">
+        <v>0.427</v>
+      </c>
+      <c r="EE36" t="n">
+        <v>57.268</v>
+      </c>
+      <c r="EF36" t="n">
+        <v>58.727</v>
+      </c>
+      <c r="EG36" t="n">
+        <v>30.0</v>
+      </c>
+      <c r="EH36" s="2" t="inlineStr">
+        <is>
+          <t>Somewhat disagree</t>
+        </is>
+      </c>
+      <c r="EI36" t="n">
+        <v>2.558</v>
+      </c>
+      <c r="EJ36" t="n">
+        <v>2.558</v>
+      </c>
+      <c r="EK36" t="n">
+        <v>3.497</v>
+      </c>
+      <c r="EL36" t="n">
+        <v>1.0</v>
+      </c>
+      <c r="EM36" s="2" t="inlineStr">
+        <is>
+          <t>Somewhat appropriate</t>
+        </is>
+      </c>
+      <c r="EN36" s="2" t="inlineStr">
+        <is>
+          <t>Neither appropriate nor inappropriate</t>
+        </is>
+      </c>
+      <c r="EO36" s="2" t="inlineStr">
+        <is>
+          <t>Neither appropriate nor inappropriate</t>
+        </is>
+      </c>
+      <c r="EP36" s="2" t="inlineStr">
+        <is>
+          <t>Easy to detect</t>
+        </is>
+      </c>
+      <c r="EQ36" s="2" t="inlineStr">
+        <is>
+          <t>Somewhat easy to detect</t>
+        </is>
+      </c>
+      <c r="ER36" s="2" t="inlineStr">
+        <is>
+          <t>Somewhat easy to detect</t>
+        </is>
+      </c>
+      <c r="ES36" s="2" t="inlineStr">
+        <is>
+          <t>Slightly disruptive</t>
+        </is>
+      </c>
+      <c r="ET36" s="2" t="inlineStr">
+        <is>
+          <t>Somewhat disruptive</t>
+        </is>
+      </c>
+      <c r="EU36" s="2" t="inlineStr">
+        <is>
+          <t>Somewhat disruptive</t>
+        </is>
+      </c>
+      <c r="EV36" s="2" t="inlineStr">
+        <is>
+          <t>Somewhat acceptable</t>
+        </is>
+      </c>
+      <c r="EW36" s="2" t="inlineStr">
+        <is>
+          <t>Somewhat acceptable</t>
+        </is>
+      </c>
+      <c r="EX36" s="2" t="inlineStr">
+        <is>
+          <t>Somewhat acceptable</t>
+        </is>
+      </c>
+      <c r="EY36" s="2" t="inlineStr">
+        <is>
+          <t>🗣️🗣️ Version 3</t>
+        </is>
+      </c>
+      <c r="EZ36" s="2" t="inlineStr">
+        <is>
+          <t>immediate information</t>
+        </is>
+      </c>
+      <c r="FA36" s="2" t="inlineStr">
+        <is>
+          <t>Social Appropriateness (e.g., the presence of others, social etiquette, or not wanting to appear distracted),Desire for Information (e.g., wanting to know the exact sender or content immediately without having to use my hands/phone)</t>
+        </is>
+      </c>
+      <c r="FB36" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="FC36" s="2" t="inlineStr">
+        <is>
+          <t>Immediately</t>
+        </is>
+      </c>
+      <c r="FD36" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="FE36" s="2" t="inlineStr">
+        <is>
+          <t>Not applicable (I chose "Immediately" in the previous question).</t>
+        </is>
+      </c>
+      <c r="FF36" s="2" t="inlineStr">
+        <is>
+          <t>immediate information</t>
+        </is>
+      </c>
+      <c r="FG36" t="n">
+        <v>5.413</v>
+      </c>
+      <c r="FH36" t="n">
+        <v>87.344</v>
+      </c>
+      <c r="FI36" t="n">
+        <v>88.294</v>
+      </c>
+      <c r="FJ36" t="n">
+        <v>29.0</v>
+      </c>
+      <c r="FK36" s="2" t="inlineStr">
+        <is>
+          <t>Somewhat inappropriate</t>
+        </is>
+      </c>
+      <c r="FL36" s="2" t="inlineStr">
+        <is>
+          <t>Inappropriate</t>
+        </is>
+      </c>
+      <c r="FM36" s="2" t="inlineStr">
+        <is>
+          <t>Inappropriate</t>
+        </is>
+      </c>
+      <c r="FN36" s="2" t="inlineStr">
+        <is>
+          <t>Somewhat easy to detect</t>
+        </is>
+      </c>
+      <c r="FO36" s="2" t="inlineStr">
+        <is>
+          <t>Somewhat easy to detect</t>
+        </is>
+      </c>
+      <c r="FP36" s="2" t="inlineStr">
+        <is>
+          <t>Somewhat easy to detect</t>
+        </is>
+      </c>
+      <c r="FQ36" s="2" t="inlineStr">
+        <is>
+          <t>Moderately disruptive</t>
+        </is>
+      </c>
+      <c r="FR36" s="2" t="inlineStr">
+        <is>
+          <t>Disruptive</t>
+        </is>
+      </c>
+      <c r="FS36" s="2" t="inlineStr">
+        <is>
+          <t>Disruptive</t>
+        </is>
+      </c>
+      <c r="FT36" s="2" t="inlineStr">
+        <is>
+          <t>Somewhat acceptable</t>
+        </is>
+      </c>
+      <c r="FU36" s="2" t="inlineStr">
+        <is>
+          <t>Somewhat acceptable</t>
+        </is>
+      </c>
+      <c r="FV36" s="2" t="inlineStr">
+        <is>
+          <t>Somewhat acceptable</t>
+        </is>
+      </c>
+      <c r="FW36" s="2" t="inlineStr">
+        <is>
+          <t>🔔 Version 1</t>
+        </is>
+      </c>
+      <c r="FX36" s="2" t="inlineStr">
+        <is>
+          <t>safety</t>
+        </is>
+      </c>
+      <c r="FY36" s="2" t="inlineStr">
+        <is>
+          <t>Focus &amp; Mental Effort (e.g., needing to concentrate on my current task without being interrupted)</t>
+        </is>
+      </c>
+      <c r="FZ36" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="GA36" s="2" t="inlineStr">
+        <is>
+          <t>After I have finished cycling / reached my destination</t>
+        </is>
+      </c>
+      <c r="GB36" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="GC36" s="2" t="inlineStr">
+        <is>
+          <t>🗣️🗣️ Version 3</t>
+        </is>
+      </c>
+      <c r="GD36" s="2" t="inlineStr">
+        <is>
+          <t>safety</t>
+        </is>
+      </c>
+      <c r="GE36" t="n">
+        <v>7.162</v>
+      </c>
+      <c r="GF36" t="n">
+        <v>103.923</v>
+      </c>
+      <c r="GG36" t="n">
+        <v>104.881</v>
+      </c>
+      <c r="GH36" t="n">
+        <v>34.0</v>
+      </c>
+      <c r="GI36" s="2" t="inlineStr">
+        <is>
+          <t>Appropriate</t>
+        </is>
+      </c>
+      <c r="GJ36" s="2" t="inlineStr">
+        <is>
+          <t>Appropriate</t>
+        </is>
+      </c>
+      <c r="GK36" s="2" t="inlineStr">
+        <is>
+          <t>Appropriate</t>
+        </is>
+      </c>
+      <c r="GL36" s="2" t="inlineStr">
+        <is>
+          <t>Somewhat easy to detect</t>
+        </is>
+      </c>
+      <c r="GM36" s="2" t="inlineStr">
+        <is>
+          <t>Somewhat easy to detect</t>
+        </is>
+      </c>
+      <c r="GN36" s="2" t="inlineStr">
+        <is>
+          <t>Somewhat easy to detect</t>
+        </is>
+      </c>
+      <c r="GO36" s="2" t="inlineStr">
+        <is>
+          <t>Slightly disruptive</t>
+        </is>
+      </c>
+      <c r="GP36" s="2" t="inlineStr">
+        <is>
+          <t>Slightly disruptive</t>
+        </is>
+      </c>
+      <c r="GQ36" s="2" t="inlineStr">
+        <is>
+          <t>Slightly disruptive</t>
+        </is>
+      </c>
+      <c r="GR36" s="2" t="inlineStr">
+        <is>
+          <t>Acceptable</t>
+        </is>
+      </c>
+      <c r="GS36" s="2" t="inlineStr">
+        <is>
+          <t>Acceptable</t>
+        </is>
+      </c>
+      <c r="GT36" s="2" t="inlineStr">
+        <is>
+          <t>Acceptable</t>
+        </is>
+      </c>
+      <c r="GU36" s="2" t="inlineStr">
+        <is>
+          <t>🗣️🗣️ Version 3</t>
+        </is>
+      </c>
+      <c r="GV36" s="2" t="inlineStr">
+        <is>
+          <t>all information at once</t>
+        </is>
+      </c>
+      <c r="GW36" s="2" t="inlineStr">
+        <is>
+          <t>Desire for Information (e.g., wanting to know the exact sender or content immediately without having to use my hands/phone)</t>
+        </is>
+      </c>
+      <c r="GX36" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="GY36" s="2" t="inlineStr">
+        <is>
+          <t>Immediately</t>
+        </is>
+      </c>
+      <c r="GZ36" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="HA36" s="2" t="inlineStr">
+        <is>
+          <t>Not applicable (I chose "Immediately" in the previous question).</t>
+        </is>
+      </c>
+      <c r="HB36" s="2" t="inlineStr">
+        <is>
+          <t>all information at once</t>
+        </is>
+      </c>
+      <c r="HC36" t="n">
+        <v>1.036</v>
+      </c>
+      <c r="HD36" t="n">
+        <v>85.741</v>
+      </c>
+      <c r="HE36" t="n">
+        <v>96.605</v>
+      </c>
+      <c r="HF36" t="n">
+        <v>27.0</v>
+      </c>
+      <c r="HG36" s="2" t="inlineStr">
+        <is>
+          <t>Agree</t>
+        </is>
+      </c>
+      <c r="HH36" t="n">
+        <v>2.923</v>
+      </c>
+      <c r="HI36" t="n">
+        <v>2.923</v>
+      </c>
+      <c r="HJ36" t="n">
+        <v>3.848</v>
+      </c>
+      <c r="HK36" t="n">
+        <v>1.0</v>
+      </c>
+      <c r="HL36" s="2" t="inlineStr">
+        <is>
+          <t>Inappropriate</t>
+        </is>
+      </c>
+      <c r="HM36" s="2" t="inlineStr">
+        <is>
+          <t>Inappropriate</t>
+        </is>
+      </c>
+      <c r="HN36" s="2" t="inlineStr">
+        <is>
+          <t>Inappropriate</t>
+        </is>
+      </c>
+      <c r="HO36" s="2" t="inlineStr">
+        <is>
+          <t>Somewhat easy to detect</t>
+        </is>
+      </c>
+      <c r="HP36" s="2" t="inlineStr">
+        <is>
+          <t>Somewhat difficult to detect</t>
+        </is>
+      </c>
+      <c r="HQ36" s="2" t="inlineStr">
+        <is>
+          <t>Somewhat difficult to detect</t>
+        </is>
+      </c>
+      <c r="HR36" s="2" t="inlineStr">
+        <is>
+          <t>Moderately disruptive</t>
+        </is>
+      </c>
+      <c r="HS36" s="2" t="inlineStr">
+        <is>
+          <t>Very disruptive</t>
+        </is>
+      </c>
+      <c r="HT36" s="2" t="inlineStr">
+        <is>
+          <t>Very disruptive</t>
+        </is>
+      </c>
+      <c r="HU36" s="2" t="inlineStr">
+        <is>
+          <t>Somewhat acceptable</t>
+        </is>
+      </c>
+      <c r="HV36" s="2" t="inlineStr">
+        <is>
+          <t>Somewhat unacceptable</t>
+        </is>
+      </c>
+      <c r="HW36" s="2" t="inlineStr">
+        <is>
+          <t>Somewhat unacceptable</t>
+        </is>
+      </c>
+      <c r="HX36" s="2" t="inlineStr">
+        <is>
+          <t>🔔 Version 1</t>
+        </is>
+      </c>
+      <c r="HY36" s="2" t="inlineStr">
+        <is>
+          <t>less disruptive</t>
+        </is>
+      </c>
+      <c r="HZ36" s="2" t="inlineStr">
+        <is>
+          <t>Acoustic Environment (e.g., the level of background noise, music, or other people talking),Focus &amp; Mental Effort (e.g., needing to concentrate on my current task without being interrupted),Social Appropriateness (e.g., the presence of others, social etiquette, or not wanting to appear distracted)</t>
+        </is>
+      </c>
+      <c r="IA36" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="IB36" s="2" t="inlineStr">
+        <is>
+          <t>Later, when dinner is completely cooked and I am done in the kitchen</t>
+        </is>
+      </c>
+      <c r="IC36" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="ID36" s="2" t="inlineStr">
+        <is>
+          <t>🗣️🗣️ Version 3</t>
+        </is>
+      </c>
+      <c r="IE36" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">don't want to be disrupted </t>
+        </is>
+      </c>
+      <c r="IF36" t="n">
+        <v>0.762</v>
+      </c>
+      <c r="IG36" t="n">
+        <v>89.59</v>
+      </c>
+      <c r="IH36" t="n">
+        <v>99.734</v>
+      </c>
+      <c r="II36" t="n">
+        <v>28.0</v>
+      </c>
+      <c r="IJ36" s="2" t="inlineStr">
+        <is>
+          <t>Appropriate</t>
+        </is>
+      </c>
+      <c r="IK36" s="2" t="inlineStr">
+        <is>
+          <t>Somewhat appropriate</t>
+        </is>
+      </c>
+      <c r="IL36" s="2" t="inlineStr">
+        <is>
+          <t>Somewhat appropriate</t>
+        </is>
+      </c>
+      <c r="IM36" s="2" t="inlineStr">
+        <is>
+          <t>Easy to detect</t>
+        </is>
+      </c>
+      <c r="IN36" s="2" t="inlineStr">
+        <is>
+          <t>Somewhat easy to detect</t>
+        </is>
+      </c>
+      <c r="IO36" s="2" t="inlineStr">
+        <is>
+          <t>Somewhat easy to detect</t>
+        </is>
+      </c>
+      <c r="IP36" s="2" t="inlineStr">
+        <is>
+          <t>Disruptive</t>
+        </is>
+      </c>
+      <c r="IQ36" s="2" t="inlineStr">
+        <is>
+          <t>Very disruptive</t>
+        </is>
+      </c>
+      <c r="IR36" s="2" t="inlineStr">
+        <is>
+          <t>Very disruptive</t>
+        </is>
+      </c>
+      <c r="IS36" s="2" t="inlineStr">
+        <is>
+          <t>Acceptable</t>
+        </is>
+      </c>
+      <c r="IT36" s="2" t="inlineStr">
+        <is>
+          <t>Somewhat acceptable</t>
+        </is>
+      </c>
+      <c r="IU36" s="2" t="inlineStr">
+        <is>
+          <t>Somewhat acceptable</t>
+        </is>
+      </c>
+      <c r="IV36" s="2" t="inlineStr">
+        <is>
+          <t>🔔 Version 1</t>
+        </is>
+      </c>
+      <c r="IW36" s="2" t="inlineStr">
+        <is>
+          <t>I am studying</t>
+        </is>
+      </c>
+      <c r="IX36" s="2" t="inlineStr">
+        <is>
+          <t>Focus &amp; Mental Effort (e.g., needing to concentrate on my current task without being interrupted)</t>
+        </is>
+      </c>
+      <c r="IY36" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="IZ36" s="2" t="inlineStr">
+        <is>
+          <t>When I briefly pause my studying/reading to take a sip of coffee or look up</t>
+        </is>
+      </c>
+      <c r="JA36" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="JB36" s="2" t="inlineStr">
+        <is>
+          <t>🗣️🗣️ Version 3</t>
+        </is>
+      </c>
+      <c r="JC36" s="2" t="inlineStr">
+        <is>
+          <t>no disruption</t>
+        </is>
+      </c>
+      <c r="JD36" t="n">
+        <v>1.551</v>
+      </c>
+      <c r="JE36" t="n">
+        <v>78.537</v>
+      </c>
+      <c r="JF36" t="n">
+        <v>79.271</v>
+      </c>
+      <c r="JG36" t="n">
+        <v>31.0</v>
+      </c>
+      <c r="JH36" s="2" t="inlineStr">
+        <is>
+          <t>Neither appropriate nor inappropriate</t>
+        </is>
+      </c>
+      <c r="JI36" s="2" t="inlineStr">
+        <is>
+          <t>Neither appropriate nor inappropriate</t>
+        </is>
+      </c>
+      <c r="JJ36" s="2" t="inlineStr">
+        <is>
+          <t>Neither appropriate nor inappropriate</t>
+        </is>
+      </c>
+      <c r="JK36" s="2" t="inlineStr">
+        <is>
+          <t>Somewhat easy to detect</t>
+        </is>
+      </c>
+      <c r="JL36" s="2" t="inlineStr">
+        <is>
+          <t>Somewhat easy to detect</t>
+        </is>
+      </c>
+      <c r="JM36" s="2" t="inlineStr">
+        <is>
+          <t>Somewhat easy to detect</t>
+        </is>
+      </c>
+      <c r="JN36" s="2" t="inlineStr">
+        <is>
+          <t>Disruptive</t>
+        </is>
+      </c>
+      <c r="JO36" s="2" t="inlineStr">
+        <is>
+          <t>Disruptive</t>
+        </is>
+      </c>
+      <c r="JP36" s="2" t="inlineStr">
+        <is>
+          <t>Disruptive</t>
+        </is>
+      </c>
+      <c r="JQ36" s="2" t="inlineStr">
+        <is>
+          <t>Somewhat acceptable</t>
+        </is>
+      </c>
+      <c r="JR36" s="2" t="inlineStr">
+        <is>
+          <t>Somewhat acceptable</t>
+        </is>
+      </c>
+      <c r="JS36" s="2" t="inlineStr">
+        <is>
+          <t>Somewhat acceptable</t>
+        </is>
+      </c>
+      <c r="JT36" s="2" t="inlineStr">
+        <is>
+          <t>🗣️🗣️ Version 3</t>
+        </is>
+      </c>
+      <c r="JU36" s="2" t="inlineStr">
+        <is>
+          <t>don't have to look up message (its content) anymore</t>
+        </is>
+      </c>
+      <c r="JV36" s="2" t="inlineStr">
+        <is>
+          <t>Focus &amp; Mental Effort (e.g., needing to concentrate on my current task without being interrupted),Social Appropriateness (e.g., the presence of others, social etiquette, or not wanting to appear distracted)</t>
+        </is>
+      </c>
+      <c r="JW36" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="JX36" s="2" t="inlineStr">
+        <is>
+          <t>At the next natural pause in the conversation after we resume talking</t>
+        </is>
+      </c>
+      <c r="JY36" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="JZ36" s="2" t="inlineStr">
+        <is>
+          <t>🗣️🗣️ Version 3</t>
+        </is>
+      </c>
+      <c r="KA36" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">want to end up conversation </t>
+        </is>
+      </c>
+      <c r="KB36" t="n">
+        <v>1.234</v>
+      </c>
+      <c r="KC36" t="n">
+        <v>155.335</v>
+      </c>
+      <c r="KD36" t="n">
+        <v>156.531</v>
+      </c>
+      <c r="KE36" t="n">
+        <v>30.0</v>
+      </c>
+      <c r="KF36" s="2" t="inlineStr">
+        <is>
+          <t>Mute (Do not notify me auditorily at all) 🔕</t>
+        </is>
+      </c>
+      <c r="KG36" s="2" t="inlineStr">
+        <is>
+          <t>Mute (Do not notify me auditorily at all) 🔕</t>
+        </is>
+      </c>
+      <c r="KH36" s="2" t="inlineStr">
+        <is>
+          <t>Mute (Do not notify me auditorily at all) 🔕</t>
+        </is>
+      </c>
+      <c r="KI36" s="2" t="inlineStr">
+        <is>
+          <t>Speech 'Version 3' (Sender + Full/Summarized Content) 🗣️🗣️</t>
+        </is>
+      </c>
+      <c r="KJ36" s="2" t="inlineStr">
+        <is>
+          <t>Indefinite delay (Hours): Can be withheld entirely until I manually check my phone or ask the device.</t>
+        </is>
+      </c>
+      <c r="KK36" s="2" t="inlineStr">
+        <is>
+          <t>Indefinite delay (Hours): Can be withheld entirely until I manually check my phone or ask the device.</t>
+        </is>
+      </c>
+      <c r="KL36" s="2" t="inlineStr">
+        <is>
+          <t>Indefinite delay (Hours): Can be withheld entirely until I manually check my phone or ask the device.</t>
+        </is>
+      </c>
+      <c r="KM36" s="2" t="inlineStr">
+        <is>
+          <t>Moderate delay (Minutes): Can wait until I finish my current task (e.g., finishing an email or a conversation).</t>
+        </is>
+      </c>
+      <c r="KN36" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="KO36" t="n">
+        <v>25.49</v>
+      </c>
+      <c r="KP36" t="n">
+        <v>70.047</v>
+      </c>
+      <c r="KQ36" t="n">
+        <v>73.203</v>
+      </c>
+      <c r="KR36" t="n">
+        <v>11.0</v>
+      </c>
+      <c r="KS36" s="2" t="inlineStr">
+        <is>
+          <t>1293</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A2:KS35"/>
+  <autoFilter ref="A2:KS37"/>
   <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
   <ignoredErrors>
-    <ignoredError sqref="C1:C34" numberStoredAsText="true"/>
-    <ignoredError sqref="D1:D34" numberStoredAsText="true"/>
-    <ignoredError sqref="G1:G34" numberStoredAsText="true"/>
-    <ignoredError sqref="I1:I34" numberStoredAsText="true"/>
-    <ignoredError sqref="J1:J34" numberStoredAsText="true"/>
-    <ignoredError sqref="K1:K34" numberStoredAsText="true"/>
-    <ignoredError sqref="L1:L34" numberStoredAsText="true"/>
-    <ignoredError sqref="M1:M34" numberStoredAsText="true"/>
-    <ignoredError sqref="P1:P34" numberStoredAsText="true"/>
-    <ignoredError sqref="Q1:Q34" numberStoredAsText="true"/>
-    <ignoredError sqref="R1:R34" numberStoredAsText="true"/>
-    <ignoredError sqref="S1:S34" numberStoredAsText="true"/>
-    <ignoredError sqref="T1:T34" numberStoredAsText="true"/>
-    <ignoredError sqref="U1:U34" numberStoredAsText="true"/>
-    <ignoredError sqref="V1:V34" numberStoredAsText="true"/>
-    <ignoredError sqref="W1:W34" numberStoredAsText="true"/>
-    <ignoredError sqref="X1:X34" numberStoredAsText="true"/>
-    <ignoredError sqref="Y1:Y34" numberStoredAsText="true"/>
-    <ignoredError sqref="Z1:Z34" numberStoredAsText="true"/>
-    <ignoredError sqref="AA1:AA34" numberStoredAsText="true"/>
-    <ignoredError sqref="AB1:AB34" numberStoredAsText="true"/>
-    <ignoredError sqref="AC1:AC34" numberStoredAsText="true"/>
-    <ignoredError sqref="AE1:AE34" numberStoredAsText="true"/>
-    <ignoredError sqref="AF1:AF34" numberStoredAsText="true"/>
-    <ignoredError sqref="AG1:AG34" numberStoredAsText="true"/>
-    <ignoredError sqref="AH1:AH34" numberStoredAsText="true"/>
-    <ignoredError sqref="AI1:AI34" numberStoredAsText="true"/>
-    <ignoredError sqref="AJ1:AJ34" numberStoredAsText="true"/>
-    <ignoredError sqref="AK1:AK34" numberStoredAsText="true"/>
-    <ignoredError sqref="AL1:AL34" numberStoredAsText="true"/>
-    <ignoredError sqref="AM1:AM34" numberStoredAsText="true"/>
-    <ignoredError sqref="AN1:AN34" numberStoredAsText="true"/>
-    <ignoredError sqref="AO1:AO34" numberStoredAsText="true"/>
-    <ignoredError sqref="AP1:AP34" numberStoredAsText="true"/>
-    <ignoredError sqref="AQ1:AQ34" numberStoredAsText="true"/>
-    <ignoredError sqref="AR1:AR34" numberStoredAsText="true"/>
-    <ignoredError sqref="AS1:AS34" numberStoredAsText="true"/>
-    <ignoredError sqref="AT1:AT34" numberStoredAsText="true"/>
-    <ignoredError sqref="AU1:AU34" numberStoredAsText="true"/>
-    <ignoredError sqref="AV1:AV34" numberStoredAsText="true"/>
-    <ignoredError sqref="AW1:AW34" numberStoredAsText="true"/>
-    <ignoredError sqref="AX1:AX34" numberStoredAsText="true"/>
-    <ignoredError sqref="AY1:AY34" numberStoredAsText="true"/>
-    <ignoredError sqref="AZ1:AZ34" numberStoredAsText="true"/>
-    <ignoredError sqref="BA1:BA34" numberStoredAsText="true"/>
-    <ignoredError sqref="BB1:BB34" numberStoredAsText="true"/>
-    <ignoredError sqref="BC1:BC34" numberStoredAsText="true"/>
-    <ignoredError sqref="BD1:BD34" numberStoredAsText="true"/>
-    <ignoredError sqref="BE1:BE34" numberStoredAsText="true"/>
-    <ignoredError sqref="BF1:BF34" numberStoredAsText="true"/>
-    <ignoredError sqref="BG1:BG34" numberStoredAsText="true"/>
-    <ignoredError sqref="BH1:BH34" numberStoredAsText="true"/>
-    <ignoredError sqref="BI1:BI34" numberStoredAsText="true"/>
-    <ignoredError sqref="BJ1:BJ34" numberStoredAsText="true"/>
-    <ignoredError sqref="BK1:BK34" numberStoredAsText="true"/>
-    <ignoredError sqref="BL1:BL34" numberStoredAsText="true"/>
-    <ignoredError sqref="BM1:BM34" numberStoredAsText="true"/>
-    <ignoredError sqref="BN1:BN34" numberStoredAsText="true"/>
-    <ignoredError sqref="BO1:BO34" numberStoredAsText="true"/>
-    <ignoredError sqref="BP1:BP34" numberStoredAsText="true"/>
-    <ignoredError sqref="BQ1:BQ34" numberStoredAsText="true"/>
-    <ignoredError sqref="BR1:BR34" numberStoredAsText="true"/>
-    <ignoredError sqref="BS1:BS34" numberStoredAsText="true"/>
-    <ignoredError sqref="BT1:BT34" numberStoredAsText="true"/>
-    <ignoredError sqref="BU1:BU34" numberStoredAsText="true"/>
-    <ignoredError sqref="BV1:BV34" numberStoredAsText="true"/>
-    <ignoredError sqref="BW1:BW34" numberStoredAsText="true"/>
-    <ignoredError sqref="BX1:BX34" numberStoredAsText="true"/>
-    <ignoredError sqref="BY1:BY34" numberStoredAsText="true"/>
-    <ignoredError sqref="BZ1:BZ34" numberStoredAsText="true"/>
-    <ignoredError sqref="CA1:CA34" numberStoredAsText="true"/>
-    <ignoredError sqref="CB1:CB34" numberStoredAsText="true"/>
-    <ignoredError sqref="CC1:CC34" numberStoredAsText="true"/>
-    <ignoredError sqref="CD1:CD34" numberStoredAsText="true"/>
-    <ignoredError sqref="CE1:CE34" numberStoredAsText="true"/>
-    <ignoredError sqref="CF1:CF34" numberStoredAsText="true"/>
-    <ignoredError sqref="CG1:CG34" numberStoredAsText="true"/>
-    <ignoredError sqref="CH1:CH34" numberStoredAsText="true"/>
-    <ignoredError sqref="CI1:CI34" numberStoredAsText="true"/>
-    <ignoredError sqref="CJ1:CJ34" numberStoredAsText="true"/>
-    <ignoredError sqref="CK1:CK34" numberStoredAsText="true"/>
-    <ignoredError sqref="CL1:CL34" numberStoredAsText="true"/>
-    <ignoredError sqref="CM1:CM34" numberStoredAsText="true"/>
-    <ignoredError sqref="CN1:CN34" numberStoredAsText="true"/>
-    <ignoredError sqref="CO1:CO34" numberStoredAsText="true"/>
-    <ignoredError sqref="CP1:CP34" numberStoredAsText="true"/>
-    <ignoredError sqref="CQ1:CQ34" numberStoredAsText="true"/>
-    <ignoredError sqref="CR1:CR34" numberStoredAsText="true"/>
-    <ignoredError sqref="CS1:CS34" numberStoredAsText="true"/>
-    <ignoredError sqref="CT1:CT34" numberStoredAsText="true"/>
-    <ignoredError sqref="CU1:CU34" numberStoredAsText="true"/>
-    <ignoredError sqref="CV1:CV34" numberStoredAsText="true"/>
-    <ignoredError sqref="CW1:CW34" numberStoredAsText="true"/>
-    <ignoredError sqref="CX1:CX34" numberStoredAsText="true"/>
-    <ignoredError sqref="CY1:CY34" numberStoredAsText="true"/>
-    <ignoredError sqref="CZ1:CZ34" numberStoredAsText="true"/>
-    <ignoredError sqref="DA1:DA34" numberStoredAsText="true"/>
-    <ignoredError sqref="DB1:DB34" numberStoredAsText="true"/>
-    <ignoredError sqref="DC1:DC34" numberStoredAsText="true"/>
-    <ignoredError sqref="DD1:DD34" numberStoredAsText="true"/>
-    <ignoredError sqref="DE1:DE34" numberStoredAsText="true"/>
-    <ignoredError sqref="DF1:DF34" numberStoredAsText="true"/>
-    <ignoredError sqref="DG1:DG34" numberStoredAsText="true"/>
-    <ignoredError sqref="DH1:DH34" numberStoredAsText="true"/>
-    <ignoredError sqref="DI1:DI34" numberStoredAsText="true"/>
-    <ignoredError sqref="DJ1:DJ34" numberStoredAsText="true"/>
-    <ignoredError sqref="DK1:DK34" numberStoredAsText="true"/>
-    <ignoredError sqref="DL1:DL34" numberStoredAsText="true"/>
-    <ignoredError sqref="DM1:DM34" numberStoredAsText="true"/>
-    <ignoredError sqref="DN1:DN34" numberStoredAsText="true"/>
-    <ignoredError sqref="DO1:DO34" numberStoredAsText="true"/>
-    <ignoredError sqref="DP1:DP34" numberStoredAsText="true"/>
-    <ignoredError sqref="DQ1:DQ34" numberStoredAsText="true"/>
-    <ignoredError sqref="DR1:DR34" numberStoredAsText="true"/>
-    <ignoredError sqref="DS1:DS34" numberStoredAsText="true"/>
-    <ignoredError sqref="DT1:DT34" numberStoredAsText="true"/>
-    <ignoredError sqref="DU1:DU34" numberStoredAsText="true"/>
-    <ignoredError sqref="DV1:DV34" numberStoredAsText="true"/>
-    <ignoredError sqref="DW1:DW34" numberStoredAsText="true"/>
-    <ignoredError sqref="DX1:DX34" numberStoredAsText="true"/>
-    <ignoredError sqref="DY1:DY34" numberStoredAsText="true"/>
-    <ignoredError sqref="DZ1:DZ34" numberStoredAsText="true"/>
-    <ignoredError sqref="EA1:EA34" numberStoredAsText="true"/>
-    <ignoredError sqref="EB1:EB34" numberStoredAsText="true"/>
-    <ignoredError sqref="EC1:EC34" numberStoredAsText="true"/>
-    <ignoredError sqref="ED1:ED34" numberStoredAsText="true"/>
-    <ignoredError sqref="EE1:EE34" numberStoredAsText="true"/>
-    <ignoredError sqref="EF1:EF34" numberStoredAsText="true"/>
-    <ignoredError sqref="EG1:EG34" numberStoredAsText="true"/>
-    <ignoredError sqref="EH1:EH34" numberStoredAsText="true"/>
-    <ignoredError sqref="EI1:EI34" numberStoredAsText="true"/>
-    <ignoredError sqref="EJ1:EJ34" numberStoredAsText="true"/>
-    <ignoredError sqref="EK1:EK34" numberStoredAsText="true"/>
-    <ignoredError sqref="EL1:EL34" numberStoredAsText="true"/>
-    <ignoredError sqref="EM1:EM34" numberStoredAsText="true"/>
-    <ignoredError sqref="EN1:EN34" numberStoredAsText="true"/>
-    <ignoredError sqref="EO1:EO34" numberStoredAsText="true"/>
-    <ignoredError sqref="EP1:EP34" numberStoredAsText="true"/>
-    <ignoredError sqref="EQ1:EQ34" numberStoredAsText="true"/>
-    <ignoredError sqref="ER1:ER34" numberStoredAsText="true"/>
-    <ignoredError sqref="ES1:ES34" numberStoredAsText="true"/>
-    <ignoredError sqref="ET1:ET34" numberStoredAsText="true"/>
-    <ignoredError sqref="EU1:EU34" numberStoredAsText="true"/>
-    <ignoredError sqref="EV1:EV34" numberStoredAsText="true"/>
-    <ignoredError sqref="EW1:EW34" numberStoredAsText="true"/>
-    <ignoredError sqref="EX1:EX34" numberStoredAsText="true"/>
-    <ignoredError sqref="EY1:EY34" numberStoredAsText="true"/>
-    <ignoredError sqref="EZ1:EZ34" numberStoredAsText="true"/>
-    <ignoredError sqref="FA1:FA34" numberStoredAsText="true"/>
-    <ignoredError sqref="FB1:FB34" numberStoredAsText="true"/>
-    <ignoredError sqref="FC1:FC34" numberStoredAsText="true"/>
-    <ignoredError sqref="FD1:FD34" numberStoredAsText="true"/>
-    <ignoredError sqref="FE1:FE34" numberStoredAsText="true"/>
-    <ignoredError sqref="FF1:FF34" numberStoredAsText="true"/>
-    <ignoredError sqref="FG1:FG34" numberStoredAsText="true"/>
-    <ignoredError sqref="FH1:FH34" numberStoredAsText="true"/>
-    <ignoredError sqref="FI1:FI34" numberStoredAsText="true"/>
-    <ignoredError sqref="FJ1:FJ34" numberStoredAsText="true"/>
-    <ignoredError sqref="FK1:FK34" numberStoredAsText="true"/>
-    <ignoredError sqref="FL1:FL34" numberStoredAsText="true"/>
-    <ignoredError sqref="FM1:FM34" numberStoredAsText="true"/>
-    <ignoredError sqref="FN1:FN34" numberStoredAsText="true"/>
-    <ignoredError sqref="FO1:FO34" numberStoredAsText="true"/>
-    <ignoredError sqref="FP1:FP34" numberStoredAsText="true"/>
-    <ignoredError sqref="FQ1:FQ34" numberStoredAsText="true"/>
-    <ignoredError sqref="FR1:FR34" numberStoredAsText="true"/>
-    <ignoredError sqref="FS1:FS34" numberStoredAsText="true"/>
-    <ignoredError sqref="FT1:FT34" numberStoredAsText="true"/>
-    <ignoredError sqref="FU1:FU34" numberStoredAsText="true"/>
-    <ignoredError sqref="FV1:FV34" numberStoredAsText="true"/>
-    <ignoredError sqref="FW1:FW34" numberStoredAsText="true"/>
-    <ignoredError sqref="FX1:FX34" numberStoredAsText="true"/>
-    <ignoredError sqref="FY1:FY34" numberStoredAsText="true"/>
-    <ignoredError sqref="FZ1:FZ34" numberStoredAsText="true"/>
-    <ignoredError sqref="GA1:GA34" numberStoredAsText="true"/>
-    <ignoredError sqref="GB1:GB34" numberStoredAsText="true"/>
-    <ignoredError sqref="GC1:GC34" numberStoredAsText="true"/>
-    <ignoredError sqref="GD1:GD34" numberStoredAsText="true"/>
-    <ignoredError sqref="GE1:GE34" numberStoredAsText="true"/>
-    <ignoredError sqref="GF1:GF34" numberStoredAsText="true"/>
-    <ignoredError sqref="GG1:GG34" numberStoredAsText="true"/>
-    <ignoredError sqref="GH1:GH34" numberStoredAsText="true"/>
-    <ignoredError sqref="GI1:GI34" numberStoredAsText="true"/>
-    <ignoredError sqref="GJ1:GJ34" numberStoredAsText="true"/>
-    <ignoredError sqref="GK1:GK34" numberStoredAsText="true"/>
-    <ignoredError sqref="GL1:GL34" numberStoredAsText="true"/>
-    <ignoredError sqref="GM1:GM34" numberStoredAsText="true"/>
-    <ignoredError sqref="GN1:GN34" numberStoredAsText="true"/>
-    <ignoredError sqref="GO1:GO34" numberStoredAsText="true"/>
-    <ignoredError sqref="GP1:GP34" numberStoredAsText="true"/>
-    <ignoredError sqref="GQ1:GQ34" numberStoredAsText="true"/>
-    <ignoredError sqref="GR1:GR34" numberStoredAsText="true"/>
-    <ignoredError sqref="GS1:GS34" numberStoredAsText="true"/>
-    <ignoredError sqref="GT1:GT34" numberStoredAsText="true"/>
-    <ignoredError sqref="GU1:GU34" numberStoredAsText="true"/>
-    <ignoredError sqref="GV1:GV34" numberStoredAsText="true"/>
-    <ignoredError sqref="GW1:GW34" numberStoredAsText="true"/>
-    <ignoredError sqref="GX1:GX34" numberStoredAsText="true"/>
-    <ignoredError sqref="GY1:GY34" numberStoredAsText="true"/>
-    <ignoredError sqref="GZ1:GZ34" numberStoredAsText="true"/>
-    <ignoredError sqref="HA1:HA34" numberStoredAsText="true"/>
-    <ignoredError sqref="HB1:HB34" numberStoredAsText="true"/>
-    <ignoredError sqref="HC1:HC34" numberStoredAsText="true"/>
-    <ignoredError sqref="HD1:HD34" numberStoredAsText="true"/>
-    <ignoredError sqref="HE1:HE34" numberStoredAsText="true"/>
-    <ignoredError sqref="HF1:HF34" numberStoredAsText="true"/>
-    <ignoredError sqref="HG1:HG34" numberStoredAsText="true"/>
-    <ignoredError sqref="HH1:HH34" numberStoredAsText="true"/>
-    <ignoredError sqref="HI1:HI34" numberStoredAsText="true"/>
-    <ignoredError sqref="HJ1:HJ34" numberStoredAsText="true"/>
-    <ignoredError sqref="HK1:HK34" numberStoredAsText="true"/>
-    <ignoredError sqref="HL1:HL34" numberStoredAsText="true"/>
-    <ignoredError sqref="HM1:HM34" numberStoredAsText="true"/>
-    <ignoredError sqref="HN1:HN34" numberStoredAsText="true"/>
-    <ignoredError sqref="HO1:HO34" numberStoredAsText="true"/>
-    <ignoredError sqref="HP1:HP34" numberStoredAsText="true"/>
-    <ignoredError sqref="HQ1:HQ34" numberStoredAsText="true"/>
-    <ignoredError sqref="HR1:HR34" numberStoredAsText="true"/>
-    <ignoredError sqref="HS1:HS34" numberStoredAsText="true"/>
-    <ignoredError sqref="HT1:HT34" numberStoredAsText="true"/>
-    <ignoredError sqref="HU1:HU34" numberStoredAsText="true"/>
-    <ignoredError sqref="HV1:HV34" numberStoredAsText="true"/>
-    <ignoredError sqref="HW1:HW34" numberStoredAsText="true"/>
-    <ignoredError sqref="HX1:HX34" numberStoredAsText="true"/>
-    <ignoredError sqref="HY1:HY34" numberStoredAsText="true"/>
-    <ignoredError sqref="HZ1:HZ34" numberStoredAsText="true"/>
-    <ignoredError sqref="IA1:IA34" numberStoredAsText="true"/>
-    <ignoredError sqref="IB1:IB34" numberStoredAsText="true"/>
-    <ignoredError sqref="IC1:IC34" numberStoredAsText="true"/>
-    <ignoredError sqref="ID1:ID34" numberStoredAsText="true"/>
-    <ignoredError sqref="IE1:IE34" numberStoredAsText="true"/>
-    <ignoredError sqref="IF1:IF34" numberStoredAsText="true"/>
-    <ignoredError sqref="IG1:IG34" numberStoredAsText="true"/>
-    <ignoredError sqref="IH1:IH34" numberStoredAsText="true"/>
-    <ignoredError sqref="II1:II34" numberStoredAsText="true"/>
-    <ignoredError sqref="IJ1:IJ34" numberStoredAsText="true"/>
-    <ignoredError sqref="IK1:IK34" numberStoredAsText="true"/>
-    <ignoredError sqref="IL1:IL34" numberStoredAsText="true"/>
-    <ignoredError sqref="IM1:IM34" numberStoredAsText="true"/>
-    <ignoredError sqref="IN1:IN34" numberStoredAsText="true"/>
-    <ignoredError sqref="IO1:IO34" numberStoredAsText="true"/>
-    <ignoredError sqref="IP1:IP34" numberStoredAsText="true"/>
-    <ignoredError sqref="IQ1:IQ34" numberStoredAsText="true"/>
-    <ignoredError sqref="IR1:IR34" numberStoredAsText="true"/>
-    <ignoredError sqref="IS1:IS34" numberStoredAsText="true"/>
-    <ignoredError sqref="IT1:IT34" numberStoredAsText="true"/>
-    <ignoredError sqref="IU1:IU34" numberStoredAsText="true"/>
-    <ignoredError sqref="IV1:IV34" numberStoredAsText="true"/>
-    <ignoredError sqref="IW1:IW34" numberStoredAsText="true"/>
-    <ignoredError sqref="IX1:IX34" numberStoredAsText="true"/>
-    <ignoredError sqref="IY1:IY34" numberStoredAsText="true"/>
-    <ignoredError sqref="IZ1:IZ34" numberStoredAsText="true"/>
-    <ignoredError sqref="JA1:JA34" numberStoredAsText="true"/>
-    <ignoredError sqref="JB1:JB34" numberStoredAsText="true"/>
-    <ignoredError sqref="JC1:JC34" numberStoredAsText="true"/>
-    <ignoredError sqref="JD1:JD34" numberStoredAsText="true"/>
-    <ignoredError sqref="JE1:JE34" numberStoredAsText="true"/>
-    <ignoredError sqref="JF1:JF34" numberStoredAsText="true"/>
-    <ignoredError sqref="JG1:JG34" numberStoredAsText="true"/>
-    <ignoredError sqref="JH1:JH34" numberStoredAsText="true"/>
-    <ignoredError sqref="JI1:JI34" numberStoredAsText="true"/>
-    <ignoredError sqref="JJ1:JJ34" numberStoredAsText="true"/>
-    <ignoredError sqref="JK1:JK34" numberStoredAsText="true"/>
-    <ignoredError sqref="JL1:JL34" numberStoredAsText="true"/>
-    <ignoredError sqref="JM1:JM34" numberStoredAsText="true"/>
-    <ignoredError sqref="JN1:JN34" numberStoredAsText="true"/>
-    <ignoredError sqref="JO1:JO34" numberStoredAsText="true"/>
-    <ignoredError sqref="JP1:JP34" numberStoredAsText="true"/>
-    <ignoredError sqref="JQ1:JQ34" numberStoredAsText="true"/>
-    <ignoredError sqref="JR1:JR34" numberStoredAsText="true"/>
-    <ignoredError sqref="JS1:JS34" numberStoredAsText="true"/>
-    <ignoredError sqref="JT1:JT34" numberStoredAsText="true"/>
-    <ignoredError sqref="JU1:JU34" numberStoredAsText="true"/>
-    <ignoredError sqref="JV1:JV34" numberStoredAsText="true"/>
-    <ignoredError sqref="JW1:JW34" numberStoredAsText="true"/>
-    <ignoredError sqref="JX1:JX34" numberStoredAsText="true"/>
-    <ignoredError sqref="JY1:JY34" numberStoredAsText="true"/>
-    <ignoredError sqref="JZ1:JZ34" numberStoredAsText="true"/>
-    <ignoredError sqref="KA1:KA34" numberStoredAsText="true"/>
-    <ignoredError sqref="KB1:KB34" numberStoredAsText="true"/>
-    <ignoredError sqref="KC1:KC34" numberStoredAsText="true"/>
-    <ignoredError sqref="KD1:KD34" numberStoredAsText="true"/>
-    <ignoredError sqref="KE1:KE34" numberStoredAsText="true"/>
-    <ignoredError sqref="KF1:KF34" numberStoredAsText="true"/>
-    <ignoredError sqref="KG1:KG34" numberStoredAsText="true"/>
-    <ignoredError sqref="KH1:KH34" numberStoredAsText="true"/>
-    <ignoredError sqref="KI1:KI34" numberStoredAsText="true"/>
-    <ignoredError sqref="KJ1:KJ34" numberStoredAsText="true"/>
-    <ignoredError sqref="KK1:KK34" numberStoredAsText="true"/>
-    <ignoredError sqref="KL1:KL34" numberStoredAsText="true"/>
-    <ignoredError sqref="KM1:KM34" numberStoredAsText="true"/>
-    <ignoredError sqref="KN1:KN34" numberStoredAsText="true"/>
-    <ignoredError sqref="KO1:KO34" numberStoredAsText="true"/>
-    <ignoredError sqref="KP1:KP34" numberStoredAsText="true"/>
-    <ignoredError sqref="KQ1:KQ34" numberStoredAsText="true"/>
-    <ignoredError sqref="KR1:KR34" numberStoredAsText="true"/>
-    <ignoredError sqref="KS1:KS34" numberStoredAsText="true"/>
+    <ignoredError sqref="C1:C36" numberStoredAsText="true"/>
+    <ignoredError sqref="D1:D36" numberStoredAsText="true"/>
+    <ignoredError sqref="G1:G36" numberStoredAsText="true"/>
+    <ignoredError sqref="I1:I36" numberStoredAsText="true"/>
+    <ignoredError sqref="J1:J36" numberStoredAsText="true"/>
+    <ignoredError sqref="K1:K36" numberStoredAsText="true"/>
+    <ignoredError sqref="L1:L36" numberStoredAsText="true"/>
+    <ignoredError sqref="M1:M36" numberStoredAsText="true"/>
+    <ignoredError sqref="P1:P36" numberStoredAsText="true"/>
+    <ignoredError sqref="Q1:Q36" numberStoredAsText="true"/>
+    <ignoredError sqref="R1:R36" numberStoredAsText="true"/>
+    <ignoredError sqref="S1:S36" numberStoredAsText="true"/>
+    <ignoredError sqref="T1:T36" numberStoredAsText="true"/>
+    <ignoredError sqref="U1:U36" numberStoredAsText="true"/>
+    <ignoredError sqref="V1:V36" numberStoredAsText="true"/>
+    <ignoredError sqref="W1:W36" numberStoredAsText="true"/>
+    <ignoredError sqref="X1:X36" numberStoredAsText="true"/>
+    <ignoredError sqref="Y1:Y36" numberStoredAsText="true"/>
+    <ignoredError sqref="Z1:Z36" numberStoredAsText="true"/>
+    <ignoredError sqref="AA1:AA36" numberStoredAsText="true"/>
+    <ignoredError sqref="AB1:AB36" numberStoredAsText="true"/>
+    <ignoredError sqref="AC1:AC36" numberStoredAsText="true"/>
+    <ignoredError sqref="AE1:AE36" numberStoredAsText="true"/>
+    <ignoredError sqref="AF1:AF36" numberStoredAsText="true"/>
+    <ignoredError sqref="AG1:AG36" numberStoredAsText="true"/>
+    <ignoredError sqref="AH1:AH36" numberStoredAsText="true"/>
+    <ignoredError sqref="AI1:AI36" numberStoredAsText="true"/>
+    <ignoredError sqref="AJ1:AJ36" numberStoredAsText="true"/>
+    <ignoredError sqref="AK1:AK36" numberStoredAsText="true"/>
+    <ignoredError sqref="AL1:AL36" numberStoredAsText="true"/>
+    <ignoredError sqref="AM1:AM36" numberStoredAsText="true"/>
+    <ignoredError sqref="AN1:AN36" numberStoredAsText="true"/>
+    <ignoredError sqref="AO1:AO36" numberStoredAsText="true"/>
+    <ignoredError sqref="AP1:AP36" numberStoredAsText="true"/>
+    <ignoredError sqref="AQ1:AQ36" numberStoredAsText="true"/>
+    <ignoredError sqref="AR1:AR36" numberStoredAsText="true"/>
+    <ignoredError sqref="AS1:AS36" numberStoredAsText="true"/>
+    <ignoredError sqref="AT1:AT36" numberStoredAsText="true"/>
+    <ignoredError sqref="AU1:AU36" numberStoredAsText="true"/>
+    <ignoredError sqref="AV1:AV36" numberStoredAsText="true"/>
+    <ignoredError sqref="AW1:AW36" numberStoredAsText="true"/>
+    <ignoredError sqref="AX1:AX36" numberStoredAsText="true"/>
+    <ignoredError sqref="AY1:AY36" numberStoredAsText="true"/>
+    <ignoredError sqref="AZ1:AZ36" numberStoredAsText="true"/>
+    <ignoredError sqref="BA1:BA36" numberStoredAsText="true"/>
+    <ignoredError sqref="BB1:BB36" numberStoredAsText="true"/>
+    <ignoredError sqref="BC1:BC36" numberStoredAsText="true"/>
+    <ignoredError sqref="BD1:BD36" numberStoredAsText="true"/>
+    <ignoredError sqref="BE1:BE36" numberStoredAsText="true"/>
+    <ignoredError sqref="BF1:BF36" numberStoredAsText="true"/>
+    <ignoredError sqref="BG1:BG36" numberStoredAsText="true"/>
+    <ignoredError sqref="BH1:BH36" numberStoredAsText="true"/>
+    <ignoredError sqref="BI1:BI36" numberStoredAsText="true"/>
+    <ignoredError sqref="BJ1:BJ36" numberStoredAsText="true"/>
+    <ignoredError sqref="BK1:BK36" numberStoredAsText="true"/>
+    <ignoredError sqref="BL1:BL36" numberStoredAsText="true"/>
+    <ignoredError sqref="BM1:BM36" numberStoredAsText="true"/>
+    <ignoredError sqref="BN1:BN36" numberStoredAsText="true"/>
+    <ignoredError sqref="BO1:BO36" numberStoredAsText="true"/>
+    <ignoredError sqref="BP1:BP36" numberStoredAsText="true"/>
+    <ignoredError sqref="BQ1:BQ36" numberStoredAsText="true"/>
+    <ignoredError sqref="BR1:BR36" numberStoredAsText="true"/>
+    <ignoredError sqref="BS1:BS36" numberStoredAsText="true"/>
+    <ignoredError sqref="BT1:BT36" numberStoredAsText="true"/>
+    <ignoredError sqref="BU1:BU36" numberStoredAsText="true"/>
+    <ignoredError sqref="BV1:BV36" numberStoredAsText="true"/>
+    <ignoredError sqref="BW1:BW36" numberStoredAsText="true"/>
+    <ignoredError sqref="BX1:BX36" numberStoredAsText="true"/>
+    <ignoredError sqref="BY1:BY36" numberStoredAsText="true"/>
+    <ignoredError sqref="BZ1:BZ36" numberStoredAsText="true"/>
+    <ignoredError sqref="CA1:CA36" numberStoredAsText="true"/>
+    <ignoredError sqref="CB1:CB36" numberStoredAsText="true"/>
+    <ignoredError sqref="CC1:CC36" numberStoredAsText="true"/>
+    <ignoredError sqref="CD1:CD36" numberStoredAsText="true"/>
+    <ignoredError sqref="CE1:CE36" numberStoredAsText="true"/>
+    <ignoredError sqref="CF1:CF36" numberStoredAsText="true"/>
+    <ignoredError sqref="CG1:CG36" numberStoredAsText="true"/>
+    <ignoredError sqref="CH1:CH36" numberStoredAsText="true"/>
+    <ignoredError sqref="CI1:CI36" numberStoredAsText="true"/>
+    <ignoredError sqref="CJ1:CJ36" numberStoredAsText="true"/>
+    <ignoredError sqref="CK1:CK36" numberStoredAsText="true"/>
+    <ignoredError sqref="CL1:CL36" numberStoredAsText="true"/>
+    <ignoredError sqref="CM1:CM36" numberStoredAsText="true"/>
+    <ignoredError sqref="CN1:CN36" numberStoredAsText="true"/>
+    <ignoredError sqref="CO1:CO36" numberStoredAsText="true"/>
+    <ignoredError sqref="CP1:CP36" numberStoredAsText="true"/>
+    <ignoredError sqref="CQ1:CQ36" numberStoredAsText="true"/>
+    <ignoredError sqref="CR1:CR36" numberStoredAsText="true"/>
+    <ignoredError sqref="CS1:CS36" numberStoredAsText="true"/>
+    <ignoredError sqref="CT1:CT36" numberStoredAsText="true"/>
+    <ignoredError sqref="CU1:CU36" numberStoredAsText="true"/>
+    <ignoredError sqref="CV1:CV36" numberStoredAsText="true"/>
+    <ignoredError sqref="CW1:CW36" numberStoredAsText="true"/>
+    <ignoredError sqref="CX1:CX36" numberStoredAsText="true"/>
+    <ignoredError sqref="CY1:CY36" numberStoredAsText="true"/>
+    <ignoredError sqref="CZ1:CZ36" numberStoredAsText="true"/>
+    <ignoredError sqref="DA1:DA36" numberStoredAsText="true"/>
+    <ignoredError sqref="DB1:DB36" numberStoredAsText="true"/>
+    <ignoredError sqref="DC1:DC36" numberStoredAsText="true"/>
+    <ignoredError sqref="DD1:DD36" numberStoredAsText="true"/>
+    <ignoredError sqref="DE1:DE36" numberStoredAsText="true"/>
+    <ignoredError sqref="DF1:DF36" numberStoredAsText="true"/>
+    <ignoredError sqref="DG1:DG36" numberStoredAsText="true"/>
+    <ignoredError sqref="DH1:DH36" numberStoredAsText="true"/>
+    <ignoredError sqref="DI1:DI36" numberStoredAsText="true"/>
+    <ignoredError sqref="DJ1:DJ36" numberStoredAsText="true"/>
+    <ignoredError sqref="DK1:DK36" numberStoredAsText="true"/>
+    <ignoredError sqref="DL1:DL36" numberStoredAsText="true"/>
+    <ignoredError sqref="DM1:DM36" numberStoredAsText="true"/>
+    <ignoredError sqref="DN1:DN36" numberStoredAsText="true"/>
+    <ignoredError sqref="DO1:DO36" numberStoredAsText="true"/>
+    <ignoredError sqref="DP1:DP36" numberStoredAsText="true"/>
+    <ignoredError sqref="DQ1:DQ36" numberStoredAsText="true"/>
+    <ignoredError sqref="DR1:DR36" numberStoredAsText="true"/>
+    <ignoredError sqref="DS1:DS36" numberStoredAsText="true"/>
+    <ignoredError sqref="DT1:DT36" numberStoredAsText="true"/>
+    <ignoredError sqref="DU1:DU36" numberStoredAsText="true"/>
+    <ignoredError sqref="DV1:DV36" numberStoredAsText="true"/>
+    <ignoredError sqref="DW1:DW36" numberStoredAsText="true"/>
+    <ignoredError sqref="DX1:DX36" numberStoredAsText="true"/>
+    <ignoredError sqref="DY1:DY36" numberStoredAsText="true"/>
+    <ignoredError sqref="DZ1:DZ36" numberStoredAsText="true"/>
+    <ignoredError sqref="EA1:EA36" numberStoredAsText="true"/>
+    <ignoredError sqref="EB1:EB36" numberStoredAsText="true"/>
+    <ignoredError sqref="EC1:EC36" numberStoredAsText="true"/>
+    <ignoredError sqref="ED1:ED36" numberStoredAsText="true"/>
+    <ignoredError sqref="EE1:EE36" numberStoredAsText="true"/>
+    <ignoredError sqref="EF1:EF36" numberStoredAsText="true"/>
+    <ignoredError sqref="EG1:EG36" numberStoredAsText="true"/>
+    <ignoredError sqref="EH1:EH36" numberStoredAsText="true"/>
+    <ignoredError sqref="EI1:EI36" numberStoredAsText="true"/>
+    <ignoredError sqref="EJ1:EJ36" numberStoredAsText="true"/>
+    <ignoredError sqref="EK1:EK36" numberStoredAsText="true"/>
+    <ignoredError sqref="EL1:EL36" numberStoredAsText="true"/>
+    <ignoredError sqref="EM1:EM36" numberStoredAsText="true"/>
+    <ignoredError sqref="EN1:EN36" numberStoredAsText="true"/>
+    <ignoredError sqref="EO1:EO36" numberStoredAsText="true"/>
+    <ignoredError sqref="EP1:EP36" numberStoredAsText="true"/>
+    <ignoredError sqref="EQ1:EQ36" numberStoredAsText="true"/>
+    <ignoredError sqref="ER1:ER36" numberStoredAsText="true"/>
+    <ignoredError sqref="ES1:ES36" numberStoredAsText="true"/>
+    <ignoredError sqref="ET1:ET36" numberStoredAsText="true"/>
+    <ignoredError sqref="EU1:EU36" numberStoredAsText="true"/>
+    <ignoredError sqref="EV1:EV36" numberStoredAsText="true"/>
+    <ignoredError sqref="EW1:EW36" numberStoredAsText="true"/>
+    <ignoredError sqref="EX1:EX36" numberStoredAsText="true"/>
+    <ignoredError sqref="EY1:EY36" numberStoredAsText="true"/>
+    <ignoredError sqref="EZ1:EZ36" numberStoredAsText="true"/>
+    <ignoredError sqref="FA1:FA36" numberStoredAsText="true"/>
+    <ignoredError sqref="FB1:FB36" numberStoredAsText="true"/>
+    <ignoredError sqref="FC1:FC36" numberStoredAsText="true"/>
+    <ignoredError sqref="FD1:FD36" numberStoredAsText="true"/>
+    <ignoredError sqref="FE1:FE36" numberStoredAsText="true"/>
+    <ignoredError sqref="FF1:FF36" numberStoredAsText="true"/>
+    <ignoredError sqref="FG1:FG36" numberStoredAsText="true"/>
+    <ignoredError sqref="FH1:FH36" numberStoredAsText="true"/>
+    <ignoredError sqref="FI1:FI36" numberStoredAsText="true"/>
+    <ignoredError sqref="FJ1:FJ36" numberStoredAsText="true"/>
+    <ignoredError sqref="FK1:FK36" numberStoredAsText="true"/>
+    <ignoredError sqref="FL1:FL36" numberStoredAsText="true"/>
+    <ignoredError sqref="FM1:FM36" numberStoredAsText="true"/>
+    <ignoredError sqref="FN1:FN36" numberStoredAsText="true"/>
+    <ignoredError sqref="FO1:FO36" numberStoredAsText="true"/>
+    <ignoredError sqref="FP1:FP36" numberStoredAsText="true"/>
+    <ignoredError sqref="FQ1:FQ36" numberStoredAsText="true"/>
+    <ignoredError sqref="FR1:FR36" numberStoredAsText="true"/>
+    <ignoredError sqref="FS1:FS36" numberStoredAsText="true"/>
+    <ignoredError sqref="FT1:FT36" numberStoredAsText="true"/>
+    <ignoredError sqref="FU1:FU36" numberStoredAsText="true"/>
+    <ignoredError sqref="FV1:FV36" numberStoredAsText="true"/>
+    <ignoredError sqref="FW1:FW36" numberStoredAsText="true"/>
+    <ignoredError sqref="FX1:FX36" numberStoredAsText="true"/>
+    <ignoredError sqref="FY1:FY36" numberStoredAsText="true"/>
+    <ignoredError sqref="FZ1:FZ36" numberStoredAsText="true"/>
+    <ignoredError sqref="GA1:GA36" numberStoredAsText="true"/>
+    <ignoredError sqref="GB1:GB36" numberStoredAsText="true"/>
+    <ignoredError sqref="GC1:GC36" numberStoredAsText="true"/>
+    <ignoredError sqref="GD1:GD36" numberStoredAsText="true"/>
+    <ignoredError sqref="GE1:GE36" numberStoredAsText="true"/>
+    <ignoredError sqref="GF1:GF36" numberStoredAsText="true"/>
+    <ignoredError sqref="GG1:GG36" numberStoredAsText="true"/>
+    <ignoredError sqref="GH1:GH36" numberStoredAsText="true"/>
+    <ignoredError sqref="GI1:GI36" numberStoredAsText="true"/>
+    <ignoredError sqref="GJ1:GJ36" numberStoredAsText="true"/>
+    <ignoredError sqref="GK1:GK36" numberStoredAsText="true"/>
+    <ignoredError sqref="GL1:GL36" numberStoredAsText="true"/>
+    <ignoredError sqref="GM1:GM36" numberStoredAsText="true"/>
+    <ignoredError sqref="GN1:GN36" numberStoredAsText="true"/>
+    <ignoredError sqref="GO1:GO36" numberStoredAsText="true"/>
+    <ignoredError sqref="GP1:GP36" numberStoredAsText="true"/>
+    <ignoredError sqref="GQ1:GQ36" numberStoredAsText="true"/>
+    <ignoredError sqref="GR1:GR36" numberStoredAsText="true"/>
+    <ignoredError sqref="GS1:GS36" numberStoredAsText="true"/>
+    <ignoredError sqref="GT1:GT36" numberStoredAsText="true"/>
+    <ignoredError sqref="GU1:GU36" numberStoredAsText="true"/>
+    <ignoredError sqref="GV1:GV36" numberStoredAsText="true"/>
+    <ignoredError sqref="GW1:GW36" numberStoredAsText="true"/>
+    <ignoredError sqref="GX1:GX36" numberStoredAsText="true"/>
+    <ignoredError sqref="GY1:GY36" numberStoredAsText="true"/>
+    <ignoredError sqref="GZ1:GZ36" numberStoredAsText="true"/>
+    <ignoredError sqref="HA1:HA36" numberStoredAsText="true"/>
+    <ignoredError sqref="HB1:HB36" numberStoredAsText="true"/>
+    <ignoredError sqref="HC1:HC36" numberStoredAsText="true"/>
+    <ignoredError sqref="HD1:HD36" numberStoredAsText="true"/>
+    <ignoredError sqref="HE1:HE36" numberStoredAsText="true"/>
+    <ignoredError sqref="HF1:HF36" numberStoredAsText="true"/>
+    <ignoredError sqref="HG1:HG36" numberStoredAsText="true"/>
+    <ignoredError sqref="HH1:HH36" numberStoredAsText="true"/>
+    <ignoredError sqref="HI1:HI36" numberStoredAsText="true"/>
+    <ignoredError sqref="HJ1:HJ36" numberStoredAsText="true"/>
+    <ignoredError sqref="HK1:HK36" numberStoredAsText="true"/>
+    <ignoredError sqref="HL1:HL36" numberStoredAsText="true"/>
+    <ignoredError sqref="HM1:HM36" numberStoredAsText="true"/>
+    <ignoredError sqref="HN1:HN36" numberStoredAsText="true"/>
+    <ignoredError sqref="HO1:HO36" numberStoredAsText="true"/>
+    <ignoredError sqref="HP1:HP36" numberStoredAsText="true"/>
+    <ignoredError sqref="HQ1:HQ36" numberStoredAsText="true"/>
+    <ignoredError sqref="HR1:HR36" numberStoredAsText="true"/>
+    <ignoredError sqref="HS1:HS36" numberStoredAsText="true"/>
+    <ignoredError sqref="HT1:HT36" numberStoredAsText="true"/>
+    <ignoredError sqref="HU1:HU36" numberStoredAsText="true"/>
+    <ignoredError sqref="HV1:HV36" numberStoredAsText="true"/>
+    <ignoredError sqref="HW1:HW36" numberStoredAsText="true"/>
+    <ignoredError sqref="HX1:HX36" numberStoredAsText="true"/>
+    <ignoredError sqref="HY1:HY36" numberStoredAsText="true"/>
+    <ignoredError sqref="HZ1:HZ36" numberStoredAsText="true"/>
+    <ignoredError sqref="IA1:IA36" numberStoredAsText="true"/>
+    <ignoredError sqref="IB1:IB36" numberStoredAsText="true"/>
+    <ignoredError sqref="IC1:IC36" numberStoredAsText="true"/>
+    <ignoredError sqref="ID1:ID36" numberStoredAsText="true"/>
+    <ignoredError sqref="IE1:IE36" numberStoredAsText="true"/>
+    <ignoredError sqref="IF1:IF36" numberStoredAsText="true"/>
+    <ignoredError sqref="IG1:IG36" numberStoredAsText="true"/>
+    <ignoredError sqref="IH1:IH36" numberStoredAsText="true"/>
+    <ignoredError sqref="II1:II36" numberStoredAsText="true"/>
+    <ignoredError sqref="IJ1:IJ36" numberStoredAsText="true"/>
+    <ignoredError sqref="IK1:IK36" numberStoredAsText="true"/>
+    <ignoredError sqref="IL1:IL36" numberStoredAsText="true"/>
+    <ignoredError sqref="IM1:IM36" numberStoredAsText="true"/>
+    <ignoredError sqref="IN1:IN36" numberStoredAsText="true"/>
+    <ignoredError sqref="IO1:IO36" numberStoredAsText="true"/>
+    <ignoredError sqref="IP1:IP36" numberStoredAsText="true"/>
+    <ignoredError sqref="IQ1:IQ36" numberStoredAsText="true"/>
+    <ignoredError sqref="IR1:IR36" numberStoredAsText="true"/>
+    <ignoredError sqref="IS1:IS36" numberStoredAsText="true"/>
+    <ignoredError sqref="IT1:IT36" numberStoredAsText="true"/>
+    <ignoredError sqref="IU1:IU36" numberStoredAsText="true"/>
+    <ignoredError sqref="IV1:IV36" numberStoredAsText="true"/>
+    <ignoredError sqref="IW1:IW36" numberStoredAsText="true"/>
+    <ignoredError sqref="IX1:IX36" numberStoredAsText="true"/>
+    <ignoredError sqref="IY1:IY36" numberStoredAsText="true"/>
+    <ignoredError sqref="IZ1:IZ36" numberStoredAsText="true"/>
+    <ignoredError sqref="JA1:JA36" numberStoredAsText="true"/>
+    <ignoredError sqref="JB1:JB36" numberStoredAsText="true"/>
+    <ignoredError sqref="JC1:JC36" numberStoredAsText="true"/>
+    <ignoredError sqref="JD1:JD36" numberStoredAsText="true"/>
+    <ignoredError sqref="JE1:JE36" numberStoredAsText="true"/>
+    <ignoredError sqref="JF1:JF36" numberStoredAsText="true"/>
+    <ignoredError sqref="JG1:JG36" numberStoredAsText="true"/>
+    <ignoredError sqref="JH1:JH36" numberStoredAsText="true"/>
+    <ignoredError sqref="JI1:JI36" numberStoredAsText="true"/>
+    <ignoredError sqref="JJ1:JJ36" numberStoredAsText="true"/>
+    <ignoredError sqref="JK1:JK36" numberStoredAsText="true"/>
+    <ignoredError sqref="JL1:JL36" numberStoredAsText="true"/>
+    <ignoredError sqref="JM1:JM36" numberStoredAsText="true"/>
+    <ignoredError sqref="JN1:JN36" numberStoredAsText="true"/>
+    <ignoredError sqref="JO1:JO36" numberStoredAsText="true"/>
+    <ignoredError sqref="JP1:JP36" numberStoredAsText="true"/>
+    <ignoredError sqref="JQ1:JQ36" numberStoredAsText="true"/>
+    <ignoredError sqref="JR1:JR36" numberStoredAsText="true"/>
+    <ignoredError sqref="JS1:JS36" numberStoredAsText="true"/>
+    <ignoredError sqref="JT1:JT36" numberStoredAsText="true"/>
+    <ignoredError sqref="JU1:JU36" numberStoredAsText="true"/>
+    <ignoredError sqref="JV1:JV36" numberStoredAsText="true"/>
+    <ignoredError sqref="JW1:JW36" numberStoredAsText="true"/>
+    <ignoredError sqref="JX1:JX36" numberStoredAsText="true"/>
+    <ignoredError sqref="JY1:JY36" numberStoredAsText="true"/>
+    <ignoredError sqref="JZ1:JZ36" numberStoredAsText="true"/>
+    <ignoredError sqref="KA1:KA36" numberStoredAsText="true"/>
+    <ignoredError sqref="KB1:KB36" numberStoredAsText="true"/>
+    <ignoredError sqref="KC1:KC36" numberStoredAsText="true"/>
+    <ignoredError sqref="KD1:KD36" numberStoredAsText="true"/>
+    <ignoredError sqref="KE1:KE36" numberStoredAsText="true"/>
+    <ignoredError sqref="KF1:KF36" numberStoredAsText="true"/>
+    <ignoredError sqref="KG1:KG36" numberStoredAsText="true"/>
+    <ignoredError sqref="KH1:KH36" numberStoredAsText="true"/>
+    <ignoredError sqref="KI1:KI36" numberStoredAsText="true"/>
+    <ignoredError sqref="KJ1:KJ36" numberStoredAsText="true"/>
+    <ignoredError sqref="KK1:KK36" numberStoredAsText="true"/>
+    <ignoredError sqref="KL1:KL36" numberStoredAsText="true"/>
+    <ignoredError sqref="KM1:KM36" numberStoredAsText="true"/>
+    <ignoredError sqref="KN1:KN36" numberStoredAsText="true"/>
+    <ignoredError sqref="KO1:KO36" numberStoredAsText="true"/>
+    <ignoredError sqref="KP1:KP36" numberStoredAsText="true"/>
+    <ignoredError sqref="KQ1:KQ36" numberStoredAsText="true"/>
+    <ignoredError sqref="KR1:KR36" numberStoredAsText="true"/>
+    <ignoredError sqref="KS1:KS36" numberStoredAsText="true"/>
   </ignoredErrors>
   <drawing r:id="rId1"/>
 </worksheet>

--- a/data.xlsx
+++ b/data.xlsx
@@ -9,7 +9,7 @@
     <sheet name="Sheet0" r:id="rId3" sheetId="1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="true">Sheet0!$A$2:$KS$44</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="true">Sheet0!$A$2:$KS$47</definedName>
   </definedNames>
 </workbook>
 </file>
@@ -62304,307 +62304,4433 @@
         </is>
       </c>
     </row>
+    <row r="44">
+      <c r="A44" s="1" t="n">
+        <v>46204.759421296294</v>
+      </c>
+      <c r="B44" s="1" t="n">
+        <v>46204.767488425925</v>
+      </c>
+      <c r="C44" s="2" t="inlineStr">
+        <is>
+          <t>IP Address</t>
+        </is>
+      </c>
+      <c r="D44" s="2" t="inlineStr">
+        <is>
+          <t>91.42.83.10</t>
+        </is>
+      </c>
+      <c r="E44" t="n">
+        <v>100.0</v>
+      </c>
+      <c r="F44" t="n">
+        <v>696.0</v>
+      </c>
+      <c r="G44" s="2" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="H44" s="1" t="n">
+        <v>46204.76749625</v>
+      </c>
+      <c r="I44" s="2" t="inlineStr">
+        <is>
+          <t>R_8V4Mpp8VAL0NXjC</t>
+        </is>
+      </c>
+      <c r="J44" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="K44" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="L44" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="M44" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="N44" t="n">
+        <v>48.1815</v>
+      </c>
+      <c r="O44" t="n">
+        <v>11.2543</v>
+      </c>
+      <c r="P44" s="2" t="inlineStr">
+        <is>
+          <t>anonymous</t>
+        </is>
+      </c>
+      <c r="Q44" s="2" t="inlineStr">
+        <is>
+          <t>EN</t>
+        </is>
+      </c>
+      <c r="R44" s="2" t="inlineStr">
+        <is>
+          <t>I understand the explanation provided to me. I was able to save a copy of this form. I reached out to the listed researchers and have had all my questions answered to my satisfaction. Therefore, I voluntarily agree to participate in this online study.,I voluntarily consent to my data being recorded and subsequently processed in line with the GDPR. I have been informed about the consequences of withdrawing my consent.</t>
+        </is>
+      </c>
+      <c r="S44" t="n">
+        <v>0.87</v>
+      </c>
+      <c r="T44" t="n">
+        <v>3.655</v>
+      </c>
+      <c r="U44" t="n">
+        <v>4.11</v>
+      </c>
+      <c r="V44" t="n">
+        <v>5.0</v>
+      </c>
+      <c r="W44" s="2" t="inlineStr">
+        <is>
+          <t>Yes, I am using a desktop or laptop computer.</t>
+        </is>
+      </c>
+      <c r="X44" s="2" t="inlineStr">
+        <is>
+          <t>Yes, I am wearing headphones.</t>
+        </is>
+      </c>
+      <c r="Y44" s="2" t="inlineStr">
+        <is>
+          <t>Both Channels</t>
+        </is>
+      </c>
+      <c r="Z44" t="n">
+        <v>0.669</v>
+      </c>
+      <c r="AA44" t="n">
+        <v>7.967</v>
+      </c>
+      <c r="AB44" t="n">
+        <v>8.794</v>
+      </c>
+      <c r="AC44" t="n">
+        <v>8.0</v>
+      </c>
+      <c r="AD44" t="n">
+        <v>24.0</v>
+      </c>
+      <c r="AE44" s="2" t="inlineStr">
+        <is>
+          <t>Female</t>
+        </is>
+      </c>
+      <c r="AF44" s="2" t="inlineStr">
+        <is>
+          <t>German</t>
+        </is>
+      </c>
+      <c r="AG44" s="2" t="inlineStr">
+        <is>
+          <t>Understand very well</t>
+        </is>
+      </c>
+      <c r="AH44" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="AI44" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AJ44" s="2" t="inlineStr">
+        <is>
+          <t>Visual and Vibration (Screen lights up + phone vibrates)</t>
+        </is>
+      </c>
+      <c r="AK44" s="2" t="inlineStr">
+        <is>
+          <t>Personal Focus: To avoid distracting myself or breaking my concentration.</t>
+        </is>
+      </c>
+      <c r="AL44" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AM44" s="2" t="inlineStr">
+        <is>
+          <t>Used occasionally</t>
+        </is>
+      </c>
+      <c r="AN44" s="2" t="inlineStr">
+        <is>
+          <t>Emails,Calendar / Reminder Alerts</t>
+        </is>
+      </c>
+      <c r="AO44" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AP44" s="2" t="inlineStr">
+        <is>
+          <t>Somewhat disagree</t>
+        </is>
+      </c>
+      <c r="AQ44" s="2" t="inlineStr">
+        <is>
+          <t>Neither agree nor disagree</t>
+        </is>
+      </c>
+      <c r="AR44" t="n">
+        <v>0.953</v>
+      </c>
+      <c r="AS44" t="n">
+        <v>30.73</v>
+      </c>
+      <c r="AT44" t="n">
+        <v>31.319</v>
+      </c>
+      <c r="AU44" t="n">
+        <v>23.0</v>
+      </c>
+      <c r="AV44" s="2" t="inlineStr">
+        <is>
+          <t>🗣️Version 2,🗣️🗣️ Version 3</t>
+        </is>
+      </c>
+      <c r="AW44" s="2" t="inlineStr">
+        <is>
+          <t>🗣️🗣️ Version 3</t>
+        </is>
+      </c>
+      <c r="AX44" s="2" t="inlineStr">
+        <is>
+          <t>Quick</t>
+        </is>
+      </c>
+      <c r="AY44" s="2" t="inlineStr">
+        <is>
+          <t>Somewhat agree</t>
+        </is>
+      </c>
+      <c r="AZ44" s="2" t="inlineStr">
+        <is>
+          <t>Neither agree nor disagree</t>
+        </is>
+      </c>
+      <c r="BA44" s="2" t="inlineStr">
+        <is>
+          <t>Too intrusive</t>
+        </is>
+      </c>
+      <c r="BB44" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="BC44" s="2" t="inlineStr">
+        <is>
+          <t>Long (no strong limit)</t>
+        </is>
+      </c>
+      <c r="BD44" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="BE44" s="2" t="inlineStr">
+        <is>
+          <t>Neither agree nor disagree</t>
+        </is>
+      </c>
+      <c r="BF44" t="n">
+        <v>0.691</v>
+      </c>
+      <c r="BG44" t="n">
+        <v>4.421</v>
+      </c>
+      <c r="BH44" t="n">
+        <v>5.027</v>
+      </c>
+      <c r="BI44" t="n">
+        <v>7.0</v>
+      </c>
+      <c r="BJ44" t="n">
+        <v>0.039</v>
+      </c>
+      <c r="BK44" t="n">
+        <v>1.439</v>
+      </c>
+      <c r="BL44" t="n">
+        <v>2.225</v>
+      </c>
+      <c r="BM44" t="n">
+        <v>3.0</v>
+      </c>
+      <c r="BN44" s="2" t="inlineStr">
+        <is>
+          <t>Somewhat inappropriate</t>
+        </is>
+      </c>
+      <c r="BO44" s="2" t="inlineStr">
+        <is>
+          <t>Somewhat inappropriate</t>
+        </is>
+      </c>
+      <c r="BP44" s="2" t="inlineStr">
+        <is>
+          <t>Somewhat inappropriate</t>
+        </is>
+      </c>
+      <c r="BQ44" s="2" t="inlineStr">
+        <is>
+          <t>Difficult to detect</t>
+        </is>
+      </c>
+      <c r="BR44" s="2" t="inlineStr">
+        <is>
+          <t>Difficult to detect</t>
+        </is>
+      </c>
+      <c r="BS44" s="2" t="inlineStr">
+        <is>
+          <t>Difficult to detect</t>
+        </is>
+      </c>
+      <c r="BT44" s="2" t="inlineStr">
+        <is>
+          <t>Somewhat disruptive</t>
+        </is>
+      </c>
+      <c r="BU44" s="2" t="inlineStr">
+        <is>
+          <t>Somewhat disruptive</t>
+        </is>
+      </c>
+      <c r="BV44" s="2" t="inlineStr">
+        <is>
+          <t>Somewhat disruptive</t>
+        </is>
+      </c>
+      <c r="BW44" s="2" t="inlineStr">
+        <is>
+          <t>Neither acceptable nor unacceptable</t>
+        </is>
+      </c>
+      <c r="BX44" s="2" t="inlineStr">
+        <is>
+          <t>Neither acceptable nor unacceptable</t>
+        </is>
+      </c>
+      <c r="BY44" s="2" t="inlineStr">
+        <is>
+          <t>Neither acceptable nor unacceptable</t>
+        </is>
+      </c>
+      <c r="BZ44" s="2" t="inlineStr">
+        <is>
+          <t>🗣️ Version 2</t>
+        </is>
+      </c>
+      <c r="CA44" s="2" t="inlineStr">
+        <is>
+          <t>Störend</t>
+        </is>
+      </c>
+      <c r="CB44" s="2" t="inlineStr">
+        <is>
+          <t>Focus &amp; Mental Effort (e.g., needing to concentrate on my current task without being interrupted),Social Appropriateness (e.g., the presence of others, social etiquette, or not wanting to appear distracted)</t>
+        </is>
+      </c>
+      <c r="CC44" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="CD44" s="2" t="inlineStr">
+        <is>
+          <t>After I finish the current task (e.g., finish writing (part of the) code)</t>
+        </is>
+      </c>
+      <c r="CE44" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="CF44" s="2" t="inlineStr">
+        <is>
+          <t>🗣️ Version 2</t>
+        </is>
+      </c>
+      <c r="CG44" s="2" t="inlineStr">
+        <is>
+          <t>Störend</t>
+        </is>
+      </c>
+      <c r="CH44" t="n">
+        <v>2.974</v>
+      </c>
+      <c r="CI44" t="n">
+        <v>34.836</v>
+      </c>
+      <c r="CJ44" t="n">
+        <v>35.227</v>
+      </c>
+      <c r="CK44" t="n">
+        <v>38.0</v>
+      </c>
+      <c r="CL44" s="2" t="inlineStr">
+        <is>
+          <t>Somewhat inappropriate</t>
+        </is>
+      </c>
+      <c r="CM44" s="2" t="inlineStr">
+        <is>
+          <t>Completely inappropriate</t>
+        </is>
+      </c>
+      <c r="CN44" s="2" t="inlineStr">
+        <is>
+          <t>Completely inappropriate</t>
+        </is>
+      </c>
+      <c r="CO44" s="2" t="inlineStr">
+        <is>
+          <t>Neither easy nor difficult to detect</t>
+        </is>
+      </c>
+      <c r="CP44" s="2" t="inlineStr">
+        <is>
+          <t>Neither easy nor difficult to detect</t>
+        </is>
+      </c>
+      <c r="CQ44" s="2" t="inlineStr">
+        <is>
+          <t>Neither easy nor difficult to detect</t>
+        </is>
+      </c>
+      <c r="CR44" s="2" t="inlineStr">
+        <is>
+          <t>Disruptive</t>
+        </is>
+      </c>
+      <c r="CS44" s="2" t="inlineStr">
+        <is>
+          <t>Disruptive</t>
+        </is>
+      </c>
+      <c r="CT44" s="2" t="inlineStr">
+        <is>
+          <t>Disruptive</t>
+        </is>
+      </c>
+      <c r="CU44" s="2" t="inlineStr">
+        <is>
+          <t>Somewhat acceptable</t>
+        </is>
+      </c>
+      <c r="CV44" s="2" t="inlineStr">
+        <is>
+          <t>Somewhat acceptable</t>
+        </is>
+      </c>
+      <c r="CW44" s="2" t="inlineStr">
+        <is>
+          <t>Somewhat acceptable</t>
+        </is>
+      </c>
+      <c r="CX44" s="2" t="inlineStr">
+        <is>
+          <t>No audio notification at all</t>
+        </is>
+      </c>
+      <c r="CY44" s="2" t="inlineStr">
+        <is>
+          <t>Stört</t>
+        </is>
+      </c>
+      <c r="CZ44" s="2" t="inlineStr">
+        <is>
+          <t>Physical Safety &amp; Awareness (e.g., needing to pay visual or mental attention to my physical surroundings, like traffic)</t>
+        </is>
+      </c>
+      <c r="DA44" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="DB44" s="2" t="inlineStr">
+        <is>
+          <t>After the meeting segment I am currently involved in ends</t>
+        </is>
+      </c>
+      <c r="DC44" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="DD44" s="2" t="inlineStr">
+        <is>
+          <t>🗣️ Version 2</t>
+        </is>
+      </c>
+      <c r="DE44" s="2" t="inlineStr">
+        <is>
+          <t>Nicht störend</t>
+        </is>
+      </c>
+      <c r="DF44" t="n">
+        <v>6.578</v>
+      </c>
+      <c r="DG44" t="n">
+        <v>197.214</v>
+      </c>
+      <c r="DH44" t="n">
+        <v>198.17000000000002</v>
+      </c>
+      <c r="DI44" t="n">
+        <v>88.0</v>
+      </c>
+      <c r="DJ44" s="2" t="inlineStr">
+        <is>
+          <t>Appropriate</t>
+        </is>
+      </c>
+      <c r="DK44" s="2" t="inlineStr">
+        <is>
+          <t>Appropriate</t>
+        </is>
+      </c>
+      <c r="DL44" s="2" t="inlineStr">
+        <is>
+          <t>Appropriate</t>
+        </is>
+      </c>
+      <c r="DM44" s="2" t="inlineStr">
+        <is>
+          <t>Neither easy nor difficult to detect</t>
+        </is>
+      </c>
+      <c r="DN44" s="2" t="inlineStr">
+        <is>
+          <t>Neither easy nor difficult to detect</t>
+        </is>
+      </c>
+      <c r="DO44" s="2" t="inlineStr">
+        <is>
+          <t>Neither easy nor difficult to detect</t>
+        </is>
+      </c>
+      <c r="DP44" s="2" t="inlineStr">
+        <is>
+          <t>Somewhat disruptive</t>
+        </is>
+      </c>
+      <c r="DQ44" s="2" t="inlineStr">
+        <is>
+          <t>Somewhat disruptive</t>
+        </is>
+      </c>
+      <c r="DR44" s="2" t="inlineStr">
+        <is>
+          <t>Somewhat disruptive</t>
+        </is>
+      </c>
+      <c r="DS44" s="2" t="inlineStr">
+        <is>
+          <t>Acceptable</t>
+        </is>
+      </c>
+      <c r="DT44" s="2" t="inlineStr">
+        <is>
+          <t>Acceptable</t>
+        </is>
+      </c>
+      <c r="DU44" s="2" t="inlineStr">
+        <is>
+          <t>Acceptable</t>
+        </is>
+      </c>
+      <c r="DV44" s="2" t="inlineStr">
+        <is>
+          <t>🗣️ Version 2</t>
+        </is>
+      </c>
+      <c r="DW44" s="2" t="inlineStr">
+        <is>
+          <t>Störend</t>
+        </is>
+      </c>
+      <c r="DX44" s="2" t="inlineStr">
+        <is>
+          <t>Social Appropriateness (e.g., the presence of others, social etiquette, or not wanting to appear distracted),Physical Safety &amp; Awareness (e.g., needing to pay visual or mental attention to my physical surroundings, like traffic)</t>
+        </is>
+      </c>
+      <c r="DY44" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="DZ44" s="2" t="inlineStr">
+        <is>
+          <t>When I switch from relaxing to another task (e.g. tidying room). Music continues.</t>
+        </is>
+      </c>
+      <c r="EA44" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="EB44" s="2" t="inlineStr">
+        <is>
+          <t>🗣️ Version 2</t>
+        </is>
+      </c>
+      <c r="EC44" s="2" t="inlineStr">
+        <is>
+          <t>Störend</t>
+        </is>
+      </c>
+      <c r="ED44" t="n">
+        <v>0.942</v>
+      </c>
+      <c r="EE44" t="n">
+        <v>64.851</v>
+      </c>
+      <c r="EF44" t="n">
+        <v>69.02</v>
+      </c>
+      <c r="EG44" t="n">
+        <v>44.0</v>
+      </c>
+      <c r="EH44" s="2" t="inlineStr">
+        <is>
+          <t>Somewhat disagree</t>
+        </is>
+      </c>
+      <c r="EI44" t="n">
+        <v>5.023</v>
+      </c>
+      <c r="EJ44" t="n">
+        <v>10.856</v>
+      </c>
+      <c r="EK44" t="n">
+        <v>13.063</v>
+      </c>
+      <c r="EL44" t="n">
+        <v>4.0</v>
+      </c>
+      <c r="EM44" s="2" t="inlineStr">
+        <is>
+          <t>Neither appropriate nor inappropriate</t>
+        </is>
+      </c>
+      <c r="EN44" s="2" t="inlineStr">
+        <is>
+          <t>Neither appropriate nor inappropriate</t>
+        </is>
+      </c>
+      <c r="EO44" s="2" t="inlineStr">
+        <is>
+          <t>Neither appropriate nor inappropriate</t>
+        </is>
+      </c>
+      <c r="EP44" s="2" t="inlineStr">
+        <is>
+          <t>Somewhat difficult to detect</t>
+        </is>
+      </c>
+      <c r="EQ44" s="2" t="inlineStr">
+        <is>
+          <t>Somewhat difficult to detect</t>
+        </is>
+      </c>
+      <c r="ER44" s="2" t="inlineStr">
+        <is>
+          <t>Somewhat difficult to detect</t>
+        </is>
+      </c>
+      <c r="ES44" s="2" t="inlineStr">
+        <is>
+          <t>Somewhat disruptive</t>
+        </is>
+      </c>
+      <c r="ET44" s="2" t="inlineStr">
+        <is>
+          <t>Somewhat disruptive</t>
+        </is>
+      </c>
+      <c r="EU44" s="2" t="inlineStr">
+        <is>
+          <t>Somewhat disruptive</t>
+        </is>
+      </c>
+      <c r="EV44" s="2" t="inlineStr">
+        <is>
+          <t>Neither acceptable nor unacceptable</t>
+        </is>
+      </c>
+      <c r="EW44" s="2" t="inlineStr">
+        <is>
+          <t>Neither acceptable nor unacceptable</t>
+        </is>
+      </c>
+      <c r="EX44" s="2" t="inlineStr">
+        <is>
+          <t>Neither acceptable nor unacceptable</t>
+        </is>
+      </c>
+      <c r="EY44" s="2" t="inlineStr">
+        <is>
+          <t>🔔 Version 1</t>
+        </is>
+      </c>
+      <c r="EZ44" s="2" t="inlineStr">
+        <is>
+          <t>Störend</t>
+        </is>
+      </c>
+      <c r="FA44" s="2" t="inlineStr">
+        <is>
+          <t>Physical Safety &amp; Awareness (e.g., needing to pay visual or mental attention to my physical surroundings, like traffic)</t>
+        </is>
+      </c>
+      <c r="FB44" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="FC44" s="2" t="inlineStr">
+        <is>
+          <t>After I finish setting up the current part of the tent (e.g., finishing putting in a pole)</t>
+        </is>
+      </c>
+      <c r="FD44" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="FE44" s="2" t="inlineStr">
+        <is>
+          <t>🗣️ Version 2</t>
+        </is>
+      </c>
+      <c r="FF44" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Störend </t>
+        </is>
+      </c>
+      <c r="FG44" t="n">
+        <v>1.281</v>
+      </c>
+      <c r="FH44" t="n">
+        <v>45.239</v>
+      </c>
+      <c r="FI44" t="n">
+        <v>46.878</v>
+      </c>
+      <c r="FJ44" t="n">
+        <v>40.0</v>
+      </c>
+      <c r="FK44" s="2" t="inlineStr">
+        <is>
+          <t>Inappropriate</t>
+        </is>
+      </c>
+      <c r="FL44" s="2" t="inlineStr">
+        <is>
+          <t>Completely inappropriate</t>
+        </is>
+      </c>
+      <c r="FM44" s="2" t="inlineStr">
+        <is>
+          <t>Completely inappropriate</t>
+        </is>
+      </c>
+      <c r="FN44" s="2" t="inlineStr">
+        <is>
+          <t>Very difficult to detect</t>
+        </is>
+      </c>
+      <c r="FO44" s="2" t="inlineStr">
+        <is>
+          <t>Very difficult to detect</t>
+        </is>
+      </c>
+      <c r="FP44" s="2" t="inlineStr">
+        <is>
+          <t>Very difficult to detect</t>
+        </is>
+      </c>
+      <c r="FQ44" s="2" t="inlineStr">
+        <is>
+          <t>Not disruptive at all</t>
+        </is>
+      </c>
+      <c r="FR44" s="2" t="inlineStr">
+        <is>
+          <t>Not disruptive at all</t>
+        </is>
+      </c>
+      <c r="FS44" s="2" t="inlineStr">
+        <is>
+          <t>Not disruptive at all</t>
+        </is>
+      </c>
+      <c r="FT44" s="2" t="inlineStr">
+        <is>
+          <t>Unacceptable</t>
+        </is>
+      </c>
+      <c r="FU44" s="2" t="inlineStr">
+        <is>
+          <t>Unacceptable</t>
+        </is>
+      </c>
+      <c r="FV44" s="2" t="inlineStr">
+        <is>
+          <t>Unacceptable</t>
+        </is>
+      </c>
+      <c r="FW44" s="2" t="inlineStr">
+        <is>
+          <t>🔔 Version 1</t>
+        </is>
+      </c>
+      <c r="FX44" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Störend </t>
+        </is>
+      </c>
+      <c r="FY44" s="2" t="inlineStr">
+        <is>
+          <t>Social Appropriateness (e.g., the presence of others, social etiquette, or not wanting to appear distracted),Physical Safety &amp; Awareness (e.g., needing to pay visual or mental attention to my physical surroundings, like traffic)</t>
+        </is>
+      </c>
+      <c r="FZ44" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="GA44" s="2" t="inlineStr">
+        <is>
+          <t>After I reach a safe stopping point (e.g., at a traffic light)</t>
+        </is>
+      </c>
+      <c r="GB44" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="GC44" s="2" t="inlineStr">
+        <is>
+          <t>🗣️ Version 2</t>
+        </is>
+      </c>
+      <c r="GD44" s="2" t="inlineStr">
+        <is>
+          <t>Störend</t>
+        </is>
+      </c>
+      <c r="GE44" t="n">
+        <v>4.923</v>
+      </c>
+      <c r="GF44" t="n">
+        <v>34.111999999999995</v>
+      </c>
+      <c r="GG44" t="n">
+        <v>35.229</v>
+      </c>
+      <c r="GH44" t="n">
+        <v>37.0</v>
+      </c>
+      <c r="GI44" s="2" t="inlineStr">
+        <is>
+          <t>Neither appropriate nor inappropriate</t>
+        </is>
+      </c>
+      <c r="GJ44" s="2" t="inlineStr">
+        <is>
+          <t>Neither appropriate nor inappropriate</t>
+        </is>
+      </c>
+      <c r="GK44" s="2" t="inlineStr">
+        <is>
+          <t>Neither appropriate nor inappropriate</t>
+        </is>
+      </c>
+      <c r="GL44" s="2" t="inlineStr">
+        <is>
+          <t>Neither easy nor difficult to detect</t>
+        </is>
+      </c>
+      <c r="GM44" s="2" t="inlineStr">
+        <is>
+          <t>Neither easy nor difficult to detect</t>
+        </is>
+      </c>
+      <c r="GN44" s="2" t="inlineStr">
+        <is>
+          <t>Neither easy nor difficult to detect</t>
+        </is>
+      </c>
+      <c r="GO44" s="2" t="inlineStr">
+        <is>
+          <t>Moderately disruptive</t>
+        </is>
+      </c>
+      <c r="GP44" s="2" t="inlineStr">
+        <is>
+          <t>Moderately disruptive</t>
+        </is>
+      </c>
+      <c r="GQ44" s="2" t="inlineStr">
+        <is>
+          <t>Moderately disruptive</t>
+        </is>
+      </c>
+      <c r="GR44" s="2" t="inlineStr">
+        <is>
+          <t>Somewhat acceptable</t>
+        </is>
+      </c>
+      <c r="GS44" s="2" t="inlineStr">
+        <is>
+          <t>Somewhat acceptable</t>
+        </is>
+      </c>
+      <c r="GT44" s="2" t="inlineStr">
+        <is>
+          <t>Somewhat acceptable</t>
+        </is>
+      </c>
+      <c r="GU44" s="2" t="inlineStr">
+        <is>
+          <t>🗣️ Version 2</t>
+        </is>
+      </c>
+      <c r="GV44" s="2" t="inlineStr">
+        <is>
+          <t>Störend</t>
+        </is>
+      </c>
+      <c r="GW44" s="2" t="inlineStr">
+        <is>
+          <t>Acoustic Environment (e.g., the level of background noise, music, or other people talking),Focus &amp; Mental Effort (e.g., needing to concentrate on my current task without being interrupted)</t>
+        </is>
+      </c>
+      <c r="GX44" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="GY44" s="2" t="inlineStr">
+        <is>
+          <t>Once I have collected all items and start walking to the checkout</t>
+        </is>
+      </c>
+      <c r="GZ44" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="HA44" s="2" t="inlineStr">
+        <is>
+          <t>🗣️ Version 2</t>
+        </is>
+      </c>
+      <c r="HB44" s="2" t="inlineStr">
+        <is>
+          <t>Störend</t>
+        </is>
+      </c>
+      <c r="HC44" t="n">
+        <v>16.874</v>
+      </c>
+      <c r="HD44" t="n">
+        <v>51.02</v>
+      </c>
+      <c r="HE44" t="n">
+        <v>52.088</v>
+      </c>
+      <c r="HF44" t="n">
+        <v>45.0</v>
+      </c>
+      <c r="HG44" s="2" t="inlineStr">
+        <is>
+          <t>Agree</t>
+        </is>
+      </c>
+      <c r="HH44" t="n">
+        <v>1.681</v>
+      </c>
+      <c r="HI44" t="n">
+        <v>2.629</v>
+      </c>
+      <c r="HJ44" t="n">
+        <v>3.48</v>
+      </c>
+      <c r="HK44" t="n">
+        <v>2.0</v>
+      </c>
+      <c r="HL44" s="2" t="inlineStr">
+        <is>
+          <t>Somewhat inappropriate</t>
+        </is>
+      </c>
+      <c r="HM44" s="2" t="inlineStr">
+        <is>
+          <t>Somewhat inappropriate</t>
+        </is>
+      </c>
+      <c r="HN44" s="2" t="inlineStr">
+        <is>
+          <t>Somewhat inappropriate</t>
+        </is>
+      </c>
+      <c r="HO44" s="2" t="inlineStr">
+        <is>
+          <t>Somewhat difficult to detect</t>
+        </is>
+      </c>
+      <c r="HP44" s="2" t="inlineStr">
+        <is>
+          <t>Somewhat difficult to detect</t>
+        </is>
+      </c>
+      <c r="HQ44" s="2" t="inlineStr">
+        <is>
+          <t>Somewhat difficult to detect</t>
+        </is>
+      </c>
+      <c r="HR44" s="2" t="inlineStr">
+        <is>
+          <t>Somewhat disruptive</t>
+        </is>
+      </c>
+      <c r="HS44" s="2" t="inlineStr">
+        <is>
+          <t>Somewhat disruptive</t>
+        </is>
+      </c>
+      <c r="HT44" s="2" t="inlineStr">
+        <is>
+          <t>Somewhat disruptive</t>
+        </is>
+      </c>
+      <c r="HU44" s="2" t="inlineStr">
+        <is>
+          <t>Neither acceptable nor unacceptable</t>
+        </is>
+      </c>
+      <c r="HV44" s="2" t="inlineStr">
+        <is>
+          <t>Neither acceptable nor unacceptable</t>
+        </is>
+      </c>
+      <c r="HW44" s="2" t="inlineStr">
+        <is>
+          <t>Neither acceptable nor unacceptable</t>
+        </is>
+      </c>
+      <c r="HX44" s="2" t="inlineStr">
+        <is>
+          <t>🗣️🗣️ Version 3</t>
+        </is>
+      </c>
+      <c r="HY44" s="2" t="inlineStr">
+        <is>
+          <t>Egal</t>
+        </is>
+      </c>
+      <c r="HZ44" s="2" t="inlineStr">
+        <is>
+          <t>Focus &amp; Mental Effort (e.g., needing to concentrate on my current task without being interrupted)</t>
+        </is>
+      </c>
+      <c r="IA44" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="IB44" s="2" t="inlineStr">
+        <is>
+          <t>When there is a natural pause in the podcast or a brief break in cooking (e.g., waiting for water to boil)</t>
+        </is>
+      </c>
+      <c r="IC44" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="ID44" s="2" t="inlineStr">
+        <is>
+          <t>🗣️🗣️ Version 3</t>
+        </is>
+      </c>
+      <c r="IE44" s="2" t="inlineStr">
+        <is>
+          <t>Ist ok</t>
+        </is>
+      </c>
+      <c r="IF44" t="n">
+        <v>13.9</v>
+      </c>
+      <c r="IG44" t="n">
+        <v>39.263</v>
+      </c>
+      <c r="IH44" t="n">
+        <v>39.808</v>
+      </c>
+      <c r="II44" t="n">
+        <v>34.0</v>
+      </c>
+      <c r="IJ44" s="2" t="inlineStr">
+        <is>
+          <t>Somewhat inappropriate</t>
+        </is>
+      </c>
+      <c r="IK44" s="2" t="inlineStr">
+        <is>
+          <t>Inappropriate</t>
+        </is>
+      </c>
+      <c r="IL44" s="2" t="inlineStr">
+        <is>
+          <t>Inappropriate</t>
+        </is>
+      </c>
+      <c r="IM44" s="2" t="inlineStr">
+        <is>
+          <t>Difficult to detect</t>
+        </is>
+      </c>
+      <c r="IN44" s="2" t="inlineStr">
+        <is>
+          <t>Difficult to detect</t>
+        </is>
+      </c>
+      <c r="IO44" s="2" t="inlineStr">
+        <is>
+          <t>Difficult to detect</t>
+        </is>
+      </c>
+      <c r="IP44" s="2" t="inlineStr">
+        <is>
+          <t>Slightly disruptive</t>
+        </is>
+      </c>
+      <c r="IQ44" s="2" t="inlineStr">
+        <is>
+          <t>Slightly disruptive</t>
+        </is>
+      </c>
+      <c r="IR44" s="2" t="inlineStr">
+        <is>
+          <t>Slightly disruptive</t>
+        </is>
+      </c>
+      <c r="IS44" s="2" t="inlineStr">
+        <is>
+          <t>Somewhat acceptable</t>
+        </is>
+      </c>
+      <c r="IT44" s="2" t="inlineStr">
+        <is>
+          <t>Somewhat acceptable</t>
+        </is>
+      </c>
+      <c r="IU44" s="2" t="inlineStr">
+        <is>
+          <t>Somewhat acceptable</t>
+        </is>
+      </c>
+      <c r="IV44" s="2" t="inlineStr">
+        <is>
+          <t>🔔 Version 1</t>
+        </is>
+      </c>
+      <c r="IW44" s="2" t="inlineStr">
+        <is>
+          <t>Störend</t>
+        </is>
+      </c>
+      <c r="IX44" s="2" t="inlineStr">
+        <is>
+          <t>Focus &amp; Mental Effort (e.g., needing to concentrate on my current task without being interrupted)</t>
+        </is>
+      </c>
+      <c r="IY44" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="IZ44" s="2" t="inlineStr">
+        <is>
+          <t>When I briefly pause my studying/reading to take a sip of coffee or look up</t>
+        </is>
+      </c>
+      <c r="JA44" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="JB44" s="2" t="inlineStr">
+        <is>
+          <t>🗣️ Version 2</t>
+        </is>
+      </c>
+      <c r="JC44" s="2" t="inlineStr">
+        <is>
+          <t>Weniger störend</t>
+        </is>
+      </c>
+      <c r="JD44" t="n">
+        <v>1.098</v>
+      </c>
+      <c r="JE44" t="n">
+        <v>55.31</v>
+      </c>
+      <c r="JF44" t="n">
+        <v>56.039</v>
+      </c>
+      <c r="JG44" t="n">
+        <v>42.0</v>
+      </c>
+      <c r="JH44" s="2" t="inlineStr">
+        <is>
+          <t>Inappropriate</t>
+        </is>
+      </c>
+      <c r="JI44" s="2" t="inlineStr">
+        <is>
+          <t>Inappropriate</t>
+        </is>
+      </c>
+      <c r="JJ44" s="2" t="inlineStr">
+        <is>
+          <t>Inappropriate</t>
+        </is>
+      </c>
+      <c r="JK44" s="2" t="inlineStr">
+        <is>
+          <t>Very difficult to detect</t>
+        </is>
+      </c>
+      <c r="JL44" s="2" t="inlineStr">
+        <is>
+          <t>Very difficult to detect</t>
+        </is>
+      </c>
+      <c r="JM44" s="2" t="inlineStr">
+        <is>
+          <t>Very difficult to detect</t>
+        </is>
+      </c>
+      <c r="JN44" s="2" t="inlineStr">
+        <is>
+          <t>Not disruptive at all</t>
+        </is>
+      </c>
+      <c r="JO44" s="2" t="inlineStr">
+        <is>
+          <t>Not disruptive at all</t>
+        </is>
+      </c>
+      <c r="JP44" s="2" t="inlineStr">
+        <is>
+          <t>Not disruptive at all</t>
+        </is>
+      </c>
+      <c r="JQ44" s="2" t="inlineStr">
+        <is>
+          <t>Somewhat unacceptable</t>
+        </is>
+      </c>
+      <c r="JR44" s="2" t="inlineStr">
+        <is>
+          <t>Somewhat unacceptable</t>
+        </is>
+      </c>
+      <c r="JS44" s="2" t="inlineStr">
+        <is>
+          <t>Somewhat unacceptable</t>
+        </is>
+      </c>
+      <c r="JT44" s="2" t="inlineStr">
+        <is>
+          <t>🔔 Version 1</t>
+        </is>
+      </c>
+      <c r="JU44" s="2" t="inlineStr">
+        <is>
+          <t>Störend</t>
+        </is>
+      </c>
+      <c r="JV44" s="2" t="inlineStr">
+        <is>
+          <t>Social Appropriateness (e.g., the presence of others, social etiquette, or not wanting to appear distracted)</t>
+        </is>
+      </c>
+      <c r="JW44" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="JX44" s="2" t="inlineStr">
+        <is>
+          <t>After we completely conclude our current topic of conversation</t>
+        </is>
+      </c>
+      <c r="JY44" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="JZ44" s="2" t="inlineStr">
+        <is>
+          <t>🗣️ Version 2</t>
+        </is>
+      </c>
+      <c r="KA44" s="2" t="inlineStr">
+        <is>
+          <t>Störend</t>
+        </is>
+      </c>
+      <c r="KB44" t="n">
+        <v>3.053</v>
+      </c>
+      <c r="KC44" t="n">
+        <v>26.766</v>
+      </c>
+      <c r="KD44" t="n">
+        <v>27.764</v>
+      </c>
+      <c r="KE44" t="n">
+        <v>35.0</v>
+      </c>
+      <c r="KF44" s="2" t="inlineStr">
+        <is>
+          <t>Speech 'Version 2' (Sender) 🗣️</t>
+        </is>
+      </c>
+      <c r="KG44" s="2" t="inlineStr">
+        <is>
+          <t>Sound Only 'Version 1' 🔔</t>
+        </is>
+      </c>
+      <c r="KH44" s="2" t="inlineStr">
+        <is>
+          <t>Speech 'Version 2' (Sender) 🗣️</t>
+        </is>
+      </c>
+      <c r="KI44" s="2" t="inlineStr">
+        <is>
+          <t>Sound Only 'Version 1' 🔔</t>
+        </is>
+      </c>
+      <c r="KJ44" s="2" t="inlineStr">
+        <is>
+          <t>Moderate delay (Minutes): Can wait until I finish my current task (e.g., finishing an email or a conversation).</t>
+        </is>
+      </c>
+      <c r="KK44" s="2" t="inlineStr">
+        <is>
+          <t>Moderate delay (Minutes): Can wait until I finish my current task (e.g., finishing an email or a conversation).</t>
+        </is>
+      </c>
+      <c r="KL44" s="2" t="inlineStr">
+        <is>
+          <t>Moderate delay (Minutes): Can wait until I finish my current task (e.g., finishing an email or a conversation).</t>
+        </is>
+      </c>
+      <c r="KM44" s="2" t="inlineStr">
+        <is>
+          <t>Brief delay (Seconds): Can wait for a quick safe moment (e.g., until I finish crossing the street, silence).</t>
+        </is>
+      </c>
+      <c r="KN44" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="KO44" t="n">
+        <v>0.635</v>
+      </c>
+      <c r="KP44" t="n">
+        <v>14.25</v>
+      </c>
+      <c r="KQ44" t="n">
+        <v>17.403</v>
+      </c>
+      <c r="KR44" t="n">
+        <v>15.0</v>
+      </c>
+      <c r="KS44" s="2" t="inlineStr">
+        <is>
+          <t>696</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="1" t="n">
+        <v>46204.767962962964</v>
+      </c>
+      <c r="B45" s="1" t="n">
+        <v>46204.7758912037</v>
+      </c>
+      <c r="C45" s="2" t="inlineStr">
+        <is>
+          <t>IP Address</t>
+        </is>
+      </c>
+      <c r="D45" s="2" t="inlineStr">
+        <is>
+          <t>91.42.83.10</t>
+        </is>
+      </c>
+      <c r="E45" t="n">
+        <v>100.0</v>
+      </c>
+      <c r="F45" t="n">
+        <v>684.0</v>
+      </c>
+      <c r="G45" s="2" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="H45" s="1" t="n">
+        <v>46204.77590465278</v>
+      </c>
+      <c r="I45" s="2" t="inlineStr">
+        <is>
+          <t>R_27PsUrpQZ5QjNm1</t>
+        </is>
+      </c>
+      <c r="J45" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="K45" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="L45" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="M45" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="N45" t="n">
+        <v>48.1815</v>
+      </c>
+      <c r="O45" t="n">
+        <v>11.2543</v>
+      </c>
+      <c r="P45" s="2" t="inlineStr">
+        <is>
+          <t>anonymous</t>
+        </is>
+      </c>
+      <c r="Q45" s="2" t="inlineStr">
+        <is>
+          <t>EN</t>
+        </is>
+      </c>
+      <c r="R45" s="2" t="inlineStr">
+        <is>
+          <t>I understand the explanation provided to me. I was able to save a copy of this form. I reached out to the listed researchers and have had all my questions answered to my satisfaction. Therefore, I voluntarily agree to participate in this online study.,I voluntarily consent to my data being recorded and subsequently processed in line with the GDPR. I have been informed about the consequences of withdrawing my consent.</t>
+        </is>
+      </c>
+      <c r="S45" t="n">
+        <v>0.727</v>
+      </c>
+      <c r="T45" t="n">
+        <v>3.544</v>
+      </c>
+      <c r="U45" t="n">
+        <v>3.989</v>
+      </c>
+      <c r="V45" t="n">
+        <v>4.0</v>
+      </c>
+      <c r="W45" s="2" t="inlineStr">
+        <is>
+          <t>Yes, I am using a desktop or laptop computer.</t>
+        </is>
+      </c>
+      <c r="X45" s="2" t="inlineStr">
+        <is>
+          <t>Yes, I am wearing headphones.</t>
+        </is>
+      </c>
+      <c r="Y45" s="2" t="inlineStr">
+        <is>
+          <t>Both Channels</t>
+        </is>
+      </c>
+      <c r="Z45" t="n">
+        <v>0.569</v>
+      </c>
+      <c r="AA45" t="n">
+        <v>7.337</v>
+      </c>
+      <c r="AB45" t="n">
+        <v>8.063</v>
+      </c>
+      <c r="AC45" t="n">
+        <v>8.0</v>
+      </c>
+      <c r="AD45" t="n">
+        <v>20.0</v>
+      </c>
+      <c r="AE45" s="2" t="inlineStr">
+        <is>
+          <t>Female</t>
+        </is>
+      </c>
+      <c r="AF45" s="2" t="inlineStr">
+        <is>
+          <t>Deutsch</t>
+        </is>
+      </c>
+      <c r="AG45" s="2" t="inlineStr">
+        <is>
+          <t>Understand well</t>
+        </is>
+      </c>
+      <c r="AH45" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="AI45" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AJ45" s="2" t="inlineStr">
+        <is>
+          <t>Visual and Audio (Screen lights up + sound plays)</t>
+        </is>
+      </c>
+      <c r="AK45" s="2" t="inlineStr">
+        <is>
+          <t>Personal Focus: To avoid distracting myself or breaking my concentration.</t>
+        </is>
+      </c>
+      <c r="AL45" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AM45" s="2" t="inlineStr">
+        <is>
+          <t>Never</t>
+        </is>
+      </c>
+      <c r="AN45" s="2" t="inlineStr">
+        <is>
+          <t>Navigation / Directions</t>
+        </is>
+      </c>
+      <c r="AO45" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AP45" s="2" t="inlineStr">
+        <is>
+          <t>Neither agree nor disagree</t>
+        </is>
+      </c>
+      <c r="AQ45" s="2" t="inlineStr">
+        <is>
+          <t>Neither agree nor disagree</t>
+        </is>
+      </c>
+      <c r="AR45" t="n">
+        <v>1.382</v>
+      </c>
+      <c r="AS45" t="n">
+        <v>37.678</v>
+      </c>
+      <c r="AT45" t="n">
+        <v>38.898</v>
+      </c>
+      <c r="AU45" t="n">
+        <v>28.0</v>
+      </c>
+      <c r="AV45" s="2" t="inlineStr">
+        <is>
+          <t>🗣️Version 2,🗣️🗣️ Version 3</t>
+        </is>
+      </c>
+      <c r="AW45" s="2" t="inlineStr">
+        <is>
+          <t>🗣️Version 2</t>
+        </is>
+      </c>
+      <c r="AX45" s="2" t="inlineStr">
+        <is>
+          <t>Wichtige person</t>
+        </is>
+      </c>
+      <c r="AY45" s="2" t="inlineStr">
+        <is>
+          <t>Neither agree nor disagree</t>
+        </is>
+      </c>
+      <c r="AZ45" s="2" t="inlineStr">
+        <is>
+          <t>Neither agree nor disagree</t>
+        </is>
+      </c>
+      <c r="BA45" s="2" t="inlineStr">
+        <is>
+          <t>Depends on context</t>
+        </is>
+      </c>
+      <c r="BB45" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="BC45" s="2" t="inlineStr">
+        <is>
+          <t>Medium (up to ~1 minute spoken content)</t>
+        </is>
+      </c>
+      <c r="BD45" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="BE45" s="2" t="inlineStr">
+        <is>
+          <t>Neither agree nor disagree</t>
+        </is>
+      </c>
+      <c r="BF45" t="n">
+        <v>1.393</v>
+      </c>
+      <c r="BG45" t="n">
+        <v>8.675</v>
+      </c>
+      <c r="BH45" t="n">
+        <v>9.503</v>
+      </c>
+      <c r="BI45" t="n">
+        <v>7.0</v>
+      </c>
+      <c r="BJ45" t="n">
+        <v>1.285</v>
+      </c>
+      <c r="BK45" t="n">
+        <v>1.285</v>
+      </c>
+      <c r="BL45" t="n">
+        <v>2.099</v>
+      </c>
+      <c r="BM45" t="n">
+        <v>1.0</v>
+      </c>
+      <c r="BN45" s="2" t="inlineStr">
+        <is>
+          <t>Inappropriate</t>
+        </is>
+      </c>
+      <c r="BO45" s="2" t="inlineStr">
+        <is>
+          <t>Inappropriate</t>
+        </is>
+      </c>
+      <c r="BP45" s="2" t="inlineStr">
+        <is>
+          <t>Inappropriate</t>
+        </is>
+      </c>
+      <c r="BQ45" s="2" t="inlineStr">
+        <is>
+          <t>Difficult to detect</t>
+        </is>
+      </c>
+      <c r="BR45" s="2" t="inlineStr">
+        <is>
+          <t>Difficult to detect</t>
+        </is>
+      </c>
+      <c r="BS45" s="2" t="inlineStr">
+        <is>
+          <t>Difficult to detect</t>
+        </is>
+      </c>
+      <c r="BT45" s="2" t="inlineStr">
+        <is>
+          <t>Slightly disruptive</t>
+        </is>
+      </c>
+      <c r="BU45" s="2" t="inlineStr">
+        <is>
+          <t>Slightly disruptive</t>
+        </is>
+      </c>
+      <c r="BV45" s="2" t="inlineStr">
+        <is>
+          <t>Slightly disruptive</t>
+        </is>
+      </c>
+      <c r="BW45" s="2" t="inlineStr">
+        <is>
+          <t>Somewhat acceptable</t>
+        </is>
+      </c>
+      <c r="BX45" s="2" t="inlineStr">
+        <is>
+          <t>Somewhat acceptable</t>
+        </is>
+      </c>
+      <c r="BY45" s="2" t="inlineStr">
+        <is>
+          <t>Somewhat acceptable</t>
+        </is>
+      </c>
+      <c r="BZ45" s="2" t="inlineStr">
+        <is>
+          <t>No audio notification at all</t>
+        </is>
+      </c>
+      <c r="CA45" s="2" t="inlineStr">
+        <is>
+          <t>Stört</t>
+        </is>
+      </c>
+      <c r="CB45" s="2" t="inlineStr">
+        <is>
+          <t>Focus &amp; Mental Effort (e.g., needing to concentrate on my current task without being interrupted)</t>
+        </is>
+      </c>
+      <c r="CC45" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="CD45" s="2" t="inlineStr">
+        <is>
+          <t>Later, when I am done working</t>
+        </is>
+      </c>
+      <c r="CE45" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="CF45" s="2" t="inlineStr">
+        <is>
+          <t>🗣️🗣️ Version 3</t>
+        </is>
+      </c>
+      <c r="CG45" s="2" t="inlineStr">
+        <is>
+          <t>Ok</t>
+        </is>
+      </c>
+      <c r="CH45" t="n">
+        <v>2.457</v>
+      </c>
+      <c r="CI45" t="n">
+        <v>24.303</v>
+      </c>
+      <c r="CJ45" t="n">
+        <v>24.889</v>
+      </c>
+      <c r="CK45" t="n">
+        <v>30.0</v>
+      </c>
+      <c r="CL45" s="2" t="inlineStr">
+        <is>
+          <t>Completely inappropriate</t>
+        </is>
+      </c>
+      <c r="CM45" s="2" t="inlineStr">
+        <is>
+          <t>Completely inappropriate</t>
+        </is>
+      </c>
+      <c r="CN45" s="2" t="inlineStr">
+        <is>
+          <t>Completely inappropriate</t>
+        </is>
+      </c>
+      <c r="CO45" s="2" t="inlineStr">
+        <is>
+          <t>Very difficult to detect</t>
+        </is>
+      </c>
+      <c r="CP45" s="2" t="inlineStr">
+        <is>
+          <t>Very difficult to detect</t>
+        </is>
+      </c>
+      <c r="CQ45" s="2" t="inlineStr">
+        <is>
+          <t>Very difficult to detect</t>
+        </is>
+      </c>
+      <c r="CR45" s="2" t="inlineStr">
+        <is>
+          <t>Not disruptive at all</t>
+        </is>
+      </c>
+      <c r="CS45" s="2" t="inlineStr">
+        <is>
+          <t>Not disruptive at all</t>
+        </is>
+      </c>
+      <c r="CT45" s="2" t="inlineStr">
+        <is>
+          <t>Not disruptive at all</t>
+        </is>
+      </c>
+      <c r="CU45" s="2" t="inlineStr">
+        <is>
+          <t>Completely unacceptable</t>
+        </is>
+      </c>
+      <c r="CV45" s="2" t="inlineStr">
+        <is>
+          <t>Completely unacceptable</t>
+        </is>
+      </c>
+      <c r="CW45" s="2" t="inlineStr">
+        <is>
+          <t>Completely unacceptable</t>
+        </is>
+      </c>
+      <c r="CX45" s="2" t="inlineStr">
+        <is>
+          <t>No audio notification at all</t>
+        </is>
+      </c>
+      <c r="CY45" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Unhöflich </t>
+        </is>
+      </c>
+      <c r="CZ45" s="2" t="inlineStr">
+        <is>
+          <t>Acoustic Environment (e.g., the level of background noise, music, or other people talking),Focus &amp; Mental Effort (e.g., needing to concentrate on my current task without being interrupted),Social Appropriateness (e.g., the presence of others, social etiquette, or not wanting to appear distracted),Desire for Information (e.g., wanting to know the exact sender or content immediately without having to use my hands/phone)</t>
+        </is>
+      </c>
+      <c r="DA45" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="DB45" s="2" t="inlineStr">
+        <is>
+          <t>Later, when the meeting is over</t>
+        </is>
+      </c>
+      <c r="DC45" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="DD45" s="2" t="inlineStr">
+        <is>
+          <t>🗣️🗣️ Version 3</t>
+        </is>
+      </c>
+      <c r="DE45" s="2" t="inlineStr">
+        <is>
+          <t>Ok</t>
+        </is>
+      </c>
+      <c r="DF45" t="n">
+        <v>0.073</v>
+      </c>
+      <c r="DG45" t="n">
+        <v>51.836</v>
+      </c>
+      <c r="DH45" t="n">
+        <v>52.897</v>
+      </c>
+      <c r="DI45" t="n">
+        <v>56.0</v>
+      </c>
+      <c r="DJ45" s="2" t="inlineStr">
+        <is>
+          <t>Somewhat appropriate</t>
+        </is>
+      </c>
+      <c r="DK45" s="2" t="inlineStr">
+        <is>
+          <t>Somewhat appropriate</t>
+        </is>
+      </c>
+      <c r="DL45" s="2" t="inlineStr">
+        <is>
+          <t>Somewhat appropriate</t>
+        </is>
+      </c>
+      <c r="DM45" s="2" t="inlineStr">
+        <is>
+          <t>Neither easy nor difficult to detect</t>
+        </is>
+      </c>
+      <c r="DN45" s="2" t="inlineStr">
+        <is>
+          <t>Neither easy nor difficult to detect</t>
+        </is>
+      </c>
+      <c r="DO45" s="2" t="inlineStr">
+        <is>
+          <t>Neither easy nor difficult to detect</t>
+        </is>
+      </c>
+      <c r="DP45" s="2" t="inlineStr">
+        <is>
+          <t>Disruptive</t>
+        </is>
+      </c>
+      <c r="DQ45" s="2" t="inlineStr">
+        <is>
+          <t>Disruptive</t>
+        </is>
+      </c>
+      <c r="DR45" s="2" t="inlineStr">
+        <is>
+          <t>Disruptive</t>
+        </is>
+      </c>
+      <c r="DS45" s="2" t="inlineStr">
+        <is>
+          <t>Somewhat acceptable</t>
+        </is>
+      </c>
+      <c r="DT45" s="2" t="inlineStr">
+        <is>
+          <t>Somewhat acceptable</t>
+        </is>
+      </c>
+      <c r="DU45" s="2" t="inlineStr">
+        <is>
+          <t>Somewhat acceptable</t>
+        </is>
+      </c>
+      <c r="DV45" s="2" t="inlineStr">
+        <is>
+          <t>No audio notification at all</t>
+        </is>
+      </c>
+      <c r="DW45" s="2" t="inlineStr">
+        <is>
+          <t>Nervig</t>
+        </is>
+      </c>
+      <c r="DX45" s="2" t="inlineStr">
+        <is>
+          <t>Other (please specify):</t>
+        </is>
+      </c>
+      <c r="DY45" s="2" t="inlineStr">
+        <is>
+          <t>Selftime</t>
+        </is>
+      </c>
+      <c r="DZ45" s="2" t="inlineStr">
+        <is>
+          <t>When I switch from relaxing to another task (e.g. tidying room). Music continues.</t>
+        </is>
+      </c>
+      <c r="EA45" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="EB45" s="2" t="inlineStr">
+        <is>
+          <t>🗣️ Version 2</t>
+        </is>
+      </c>
+      <c r="EC45" s="2" t="inlineStr">
+        <is>
+          <t>Ok</t>
+        </is>
+      </c>
+      <c r="ED45" t="n">
+        <v>0.155</v>
+      </c>
+      <c r="EE45" t="n">
+        <v>147.611</v>
+      </c>
+      <c r="EF45" t="n">
+        <v>148.647</v>
+      </c>
+      <c r="EG45" t="n">
+        <v>84.0</v>
+      </c>
+      <c r="EH45" s="2" t="inlineStr">
+        <is>
+          <t>Somewhat disagree</t>
+        </is>
+      </c>
+      <c r="EI45" t="n">
+        <v>1.729</v>
+      </c>
+      <c r="EJ45" t="n">
+        <v>3.464</v>
+      </c>
+      <c r="EK45" t="n">
+        <v>4.351</v>
+      </c>
+      <c r="EL45" t="n">
+        <v>2.0</v>
+      </c>
+      <c r="EM45" s="2" t="inlineStr">
+        <is>
+          <t>Appropriate</t>
+        </is>
+      </c>
+      <c r="EN45" s="2" t="inlineStr">
+        <is>
+          <t>Appropriate</t>
+        </is>
+      </c>
+      <c r="EO45" s="2" t="inlineStr">
+        <is>
+          <t>Appropriate</t>
+        </is>
+      </c>
+      <c r="EP45" s="2" t="inlineStr">
+        <is>
+          <t>Neither easy nor difficult to detect</t>
+        </is>
+      </c>
+      <c r="EQ45" s="2" t="inlineStr">
+        <is>
+          <t>Neither easy nor difficult to detect</t>
+        </is>
+      </c>
+      <c r="ER45" s="2" t="inlineStr">
+        <is>
+          <t>Neither easy nor difficult to detect</t>
+        </is>
+      </c>
+      <c r="ES45" s="2" t="inlineStr">
+        <is>
+          <t>Somewhat disruptive</t>
+        </is>
+      </c>
+      <c r="ET45" s="2" t="inlineStr">
+        <is>
+          <t>Somewhat disruptive</t>
+        </is>
+      </c>
+      <c r="EU45" s="2" t="inlineStr">
+        <is>
+          <t>Somewhat disruptive</t>
+        </is>
+      </c>
+      <c r="EV45" s="2" t="inlineStr">
+        <is>
+          <t>Neither acceptable nor unacceptable</t>
+        </is>
+      </c>
+      <c r="EW45" s="2" t="inlineStr">
+        <is>
+          <t>Neither acceptable nor unacceptable</t>
+        </is>
+      </c>
+      <c r="EX45" s="2" t="inlineStr">
+        <is>
+          <t>Neither acceptable nor unacceptable</t>
+        </is>
+      </c>
+      <c r="EY45" s="2" t="inlineStr">
+        <is>
+          <t>🗣️ Version 2</t>
+        </is>
+      </c>
+      <c r="EZ45" s="2" t="inlineStr">
+        <is>
+          <t>Wenn’s wichtig ist ok</t>
+        </is>
+      </c>
+      <c r="FA45" s="2" t="inlineStr">
+        <is>
+          <t>Acoustic Environment (e.g., the level of background noise, music, or other people talking),Focus &amp; Mental Effort (e.g., needing to concentrate on my current task without being interrupted)</t>
+        </is>
+      </c>
+      <c r="FB45" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="FC45" s="2" t="inlineStr">
+        <is>
+          <t>When there is a brief pause in the physical setup (e.g., stopping to look at instructions or taking a breath)</t>
+        </is>
+      </c>
+      <c r="FD45" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="FE45" s="2" t="inlineStr">
+        <is>
+          <t>🗣️🗣️ Version 3</t>
+        </is>
+      </c>
+      <c r="FF45" s="2" t="inlineStr">
+        <is>
+          <t>Ok</t>
+        </is>
+      </c>
+      <c r="FG45" t="n">
+        <v>0.06</v>
+      </c>
+      <c r="FH45" t="n">
+        <v>46.389</v>
+      </c>
+      <c r="FI45" t="n">
+        <v>46.977</v>
+      </c>
+      <c r="FJ45" t="n">
+        <v>37.0</v>
+      </c>
+      <c r="FK45" s="2" t="inlineStr">
+        <is>
+          <t>Inappropriate</t>
+        </is>
+      </c>
+      <c r="FL45" s="2" t="inlineStr">
+        <is>
+          <t>Inappropriate</t>
+        </is>
+      </c>
+      <c r="FM45" s="2" t="inlineStr">
+        <is>
+          <t>Inappropriate</t>
+        </is>
+      </c>
+      <c r="FN45" s="2" t="inlineStr">
+        <is>
+          <t>Difficult to detect</t>
+        </is>
+      </c>
+      <c r="FO45" s="2" t="inlineStr">
+        <is>
+          <t>Difficult to detect</t>
+        </is>
+      </c>
+      <c r="FP45" s="2" t="inlineStr">
+        <is>
+          <t>Difficult to detect</t>
+        </is>
+      </c>
+      <c r="FQ45" s="2" t="inlineStr">
+        <is>
+          <t>Not disruptive at all</t>
+        </is>
+      </c>
+      <c r="FR45" s="2" t="inlineStr">
+        <is>
+          <t>Not disruptive at all</t>
+        </is>
+      </c>
+      <c r="FS45" s="2" t="inlineStr">
+        <is>
+          <t>Not disruptive at all</t>
+        </is>
+      </c>
+      <c r="FT45" s="2" t="inlineStr">
+        <is>
+          <t>Unacceptable</t>
+        </is>
+      </c>
+      <c r="FU45" s="2" t="inlineStr">
+        <is>
+          <t>Completely unacceptable</t>
+        </is>
+      </c>
+      <c r="FV45" s="2" t="inlineStr">
+        <is>
+          <t>Completely unacceptable</t>
+        </is>
+      </c>
+      <c r="FW45" s="2" t="inlineStr">
+        <is>
+          <t>No audio notification at all</t>
+        </is>
+      </c>
+      <c r="FX45" s="2" t="inlineStr">
+        <is>
+          <t>Stört</t>
+        </is>
+      </c>
+      <c r="FY45" s="2" t="inlineStr">
+        <is>
+          <t>Focus &amp; Mental Effort (e.g., needing to concentrate on my current task without being interrupted),Physical Safety &amp; Awareness (e.g., needing to pay visual or mental attention to my physical surroundings, like traffic)</t>
+        </is>
+      </c>
+      <c r="FZ45" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="GA45" s="2" t="inlineStr">
+        <is>
+          <t>After I have finished cycling / reached my destination</t>
+        </is>
+      </c>
+      <c r="GB45" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="GC45" s="2" t="inlineStr">
+        <is>
+          <t>🗣️🗣️ Version 3</t>
+        </is>
+      </c>
+      <c r="GD45" s="2" t="inlineStr">
+        <is>
+          <t>Ok</t>
+        </is>
+      </c>
+      <c r="GE45" t="n">
+        <v>0.104</v>
+      </c>
+      <c r="GF45" t="n">
+        <v>40.152</v>
+      </c>
+      <c r="GG45" t="n">
+        <v>40.604</v>
+      </c>
+      <c r="GH45" t="n">
+        <v>41.0</v>
+      </c>
+      <c r="GI45" s="2" t="inlineStr">
+        <is>
+          <t>Neither appropriate nor inappropriate</t>
+        </is>
+      </c>
+      <c r="GJ45" s="2" t="inlineStr">
+        <is>
+          <t>Neither appropriate nor inappropriate</t>
+        </is>
+      </c>
+      <c r="GK45" s="2" t="inlineStr">
+        <is>
+          <t>Neither appropriate nor inappropriate</t>
+        </is>
+      </c>
+      <c r="GL45" s="2" t="inlineStr">
+        <is>
+          <t>Neither easy nor difficult to detect</t>
+        </is>
+      </c>
+      <c r="GM45" s="2" t="inlineStr">
+        <is>
+          <t>Neither easy nor difficult to detect</t>
+        </is>
+      </c>
+      <c r="GN45" s="2" t="inlineStr">
+        <is>
+          <t>Neither easy nor difficult to detect</t>
+        </is>
+      </c>
+      <c r="GO45" s="2" t="inlineStr">
+        <is>
+          <t>Moderately disruptive</t>
+        </is>
+      </c>
+      <c r="GP45" s="2" t="inlineStr">
+        <is>
+          <t>Moderately disruptive</t>
+        </is>
+      </c>
+      <c r="GQ45" s="2" t="inlineStr">
+        <is>
+          <t>Moderately disruptive</t>
+        </is>
+      </c>
+      <c r="GR45" s="2" t="inlineStr">
+        <is>
+          <t>Neither acceptable nor unacceptable</t>
+        </is>
+      </c>
+      <c r="GS45" s="2" t="inlineStr">
+        <is>
+          <t>Neither acceptable nor unacceptable</t>
+        </is>
+      </c>
+      <c r="GT45" s="2" t="inlineStr">
+        <is>
+          <t>Neither acceptable nor unacceptable</t>
+        </is>
+      </c>
+      <c r="GU45" s="2" t="inlineStr">
+        <is>
+          <t>🗣️ Version 2</t>
+        </is>
+      </c>
+      <c r="GV45" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Nervig </t>
+        </is>
+      </c>
+      <c r="GW45" s="2" t="inlineStr">
+        <is>
+          <t>Acoustic Environment (e.g., the level of background noise, music, or other people talking)</t>
+        </is>
+      </c>
+      <c r="GX45" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="GY45" s="2" t="inlineStr">
+        <is>
+          <t>Once I have collected all items and start walking to the checkout</t>
+        </is>
+      </c>
+      <c r="GZ45" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="HA45" s="2" t="inlineStr">
+        <is>
+          <t>🗣️🗣️ Version 3</t>
+        </is>
+      </c>
+      <c r="HB45" s="2" t="inlineStr">
+        <is>
+          <t>Ok</t>
+        </is>
+      </c>
+      <c r="HC45" t="n">
+        <v>2.103</v>
+      </c>
+      <c r="HD45" t="n">
+        <v>24.917</v>
+      </c>
+      <c r="HE45" t="n">
+        <v>25.646</v>
+      </c>
+      <c r="HF45" t="n">
+        <v>31.0</v>
+      </c>
+      <c r="HG45" s="2" t="inlineStr">
+        <is>
+          <t>Agree</t>
+        </is>
+      </c>
+      <c r="HH45" t="n">
+        <v>1.365</v>
+      </c>
+      <c r="HI45" t="n">
+        <v>2.299</v>
+      </c>
+      <c r="HJ45" t="n">
+        <v>2.815</v>
+      </c>
+      <c r="HK45" t="n">
+        <v>2.0</v>
+      </c>
+      <c r="HL45" s="2" t="inlineStr">
+        <is>
+          <t>Somewhat appropriate</t>
+        </is>
+      </c>
+      <c r="HM45" s="2" t="inlineStr">
+        <is>
+          <t>Somewhat appropriate</t>
+        </is>
+      </c>
+      <c r="HN45" s="2" t="inlineStr">
+        <is>
+          <t>Somewhat appropriate</t>
+        </is>
+      </c>
+      <c r="HO45" s="2" t="inlineStr">
+        <is>
+          <t>Neither easy nor difficult to detect</t>
+        </is>
+      </c>
+      <c r="HP45" s="2" t="inlineStr">
+        <is>
+          <t>Neither easy nor difficult to detect</t>
+        </is>
+      </c>
+      <c r="HQ45" s="2" t="inlineStr">
+        <is>
+          <t>Neither easy nor difficult to detect</t>
+        </is>
+      </c>
+      <c r="HR45" s="2" t="inlineStr">
+        <is>
+          <t>Moderately disruptive</t>
+        </is>
+      </c>
+      <c r="HS45" s="2" t="inlineStr">
+        <is>
+          <t>Moderately disruptive</t>
+        </is>
+      </c>
+      <c r="HT45" s="2" t="inlineStr">
+        <is>
+          <t>Moderately disruptive</t>
+        </is>
+      </c>
+      <c r="HU45" s="2" t="inlineStr">
+        <is>
+          <t>Somewhat acceptable</t>
+        </is>
+      </c>
+      <c r="HV45" s="2" t="inlineStr">
+        <is>
+          <t>Somewhat acceptable</t>
+        </is>
+      </c>
+      <c r="HW45" s="2" t="inlineStr">
+        <is>
+          <t>Somewhat acceptable</t>
+        </is>
+      </c>
+      <c r="HX45" s="2" t="inlineStr">
+        <is>
+          <t>🗣️🗣️ Version 3</t>
+        </is>
+      </c>
+      <c r="HY45" s="2" t="inlineStr">
+        <is>
+          <t>Ok</t>
+        </is>
+      </c>
+      <c r="HZ45" s="2" t="inlineStr">
+        <is>
+          <t>Focus &amp; Mental Effort (e.g., needing to concentrate on my current task without being interrupted)</t>
+        </is>
+      </c>
+      <c r="IA45" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="IB45" s="2" t="inlineStr">
+        <is>
+          <t>After I finish an active cooking step (e.g., finishing chopping the vegetables)</t>
+        </is>
+      </c>
+      <c r="IC45" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="ID45" s="2" t="inlineStr">
+        <is>
+          <t>🗣️🗣️ Version 3</t>
+        </is>
+      </c>
+      <c r="IE45" s="2" t="inlineStr">
+        <is>
+          <t>Ok</t>
+        </is>
+      </c>
+      <c r="IF45" t="n">
+        <v>0.064</v>
+      </c>
+      <c r="IG45" t="n">
+        <v>45.55</v>
+      </c>
+      <c r="IH45" t="n">
+        <v>46.644999999999996</v>
+      </c>
+      <c r="II45" t="n">
+        <v>43.0</v>
+      </c>
+      <c r="IJ45" s="2" t="inlineStr">
+        <is>
+          <t>Somewhat inappropriate</t>
+        </is>
+      </c>
+      <c r="IK45" s="2" t="inlineStr">
+        <is>
+          <t>Somewhat inappropriate</t>
+        </is>
+      </c>
+      <c r="IL45" s="2" t="inlineStr">
+        <is>
+          <t>Somewhat inappropriate</t>
+        </is>
+      </c>
+      <c r="IM45" s="2" t="inlineStr">
+        <is>
+          <t>Difficult to detect</t>
+        </is>
+      </c>
+      <c r="IN45" s="2" t="inlineStr">
+        <is>
+          <t>Difficult to detect</t>
+        </is>
+      </c>
+      <c r="IO45" s="2" t="inlineStr">
+        <is>
+          <t>Difficult to detect</t>
+        </is>
+      </c>
+      <c r="IP45" s="2" t="inlineStr">
+        <is>
+          <t>Slightly disruptive</t>
+        </is>
+      </c>
+      <c r="IQ45" s="2" t="inlineStr">
+        <is>
+          <t>Slightly disruptive</t>
+        </is>
+      </c>
+      <c r="IR45" s="2" t="inlineStr">
+        <is>
+          <t>Slightly disruptive</t>
+        </is>
+      </c>
+      <c r="IS45" s="2" t="inlineStr">
+        <is>
+          <t>Unacceptable</t>
+        </is>
+      </c>
+      <c r="IT45" s="2" t="inlineStr">
+        <is>
+          <t>Unacceptable</t>
+        </is>
+      </c>
+      <c r="IU45" s="2" t="inlineStr">
+        <is>
+          <t>Unacceptable</t>
+        </is>
+      </c>
+      <c r="IV45" s="2" t="inlineStr">
+        <is>
+          <t>No audio notification at all</t>
+        </is>
+      </c>
+      <c r="IW45" s="2" t="inlineStr">
+        <is>
+          <t>Stört mich</t>
+        </is>
+      </c>
+      <c r="IX45" s="2" t="inlineStr">
+        <is>
+          <t>Focus &amp; Mental Effort (e.g., needing to concentrate on my current task without being interrupted)</t>
+        </is>
+      </c>
+      <c r="IY45" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="IZ45" s="2" t="inlineStr">
+        <is>
+          <t>After I finish completing the current study task</t>
+        </is>
+      </c>
+      <c r="JA45" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="JB45" s="2" t="inlineStr">
+        <is>
+          <t>🗣️ Version 2</t>
+        </is>
+      </c>
+      <c r="JC45" s="2" t="inlineStr">
+        <is>
+          <t>Ok</t>
+        </is>
+      </c>
+      <c r="JD45" t="n">
+        <v>0.041</v>
+      </c>
+      <c r="JE45" t="n">
+        <v>40.237</v>
+      </c>
+      <c r="JF45" t="n">
+        <v>41.673</v>
+      </c>
+      <c r="JG45" t="n">
+        <v>34.0</v>
+      </c>
+      <c r="JH45" s="2" t="inlineStr">
+        <is>
+          <t>Inappropriate</t>
+        </is>
+      </c>
+      <c r="JI45" s="2" t="inlineStr">
+        <is>
+          <t>Inappropriate</t>
+        </is>
+      </c>
+      <c r="JJ45" s="2" t="inlineStr">
+        <is>
+          <t>Inappropriate</t>
+        </is>
+      </c>
+      <c r="JK45" s="2" t="inlineStr">
+        <is>
+          <t>Difficult to detect</t>
+        </is>
+      </c>
+      <c r="JL45" s="2" t="inlineStr">
+        <is>
+          <t>Difficult to detect</t>
+        </is>
+      </c>
+      <c r="JM45" s="2" t="inlineStr">
+        <is>
+          <t>Difficult to detect</t>
+        </is>
+      </c>
+      <c r="JN45" s="2" t="inlineStr">
+        <is>
+          <t>Not disruptive at all</t>
+        </is>
+      </c>
+      <c r="JO45" s="2" t="inlineStr">
+        <is>
+          <t>Not disruptive at all</t>
+        </is>
+      </c>
+      <c r="JP45" s="2" t="inlineStr">
+        <is>
+          <t>Not disruptive at all</t>
+        </is>
+      </c>
+      <c r="JQ45" s="2" t="inlineStr">
+        <is>
+          <t>Completely unacceptable</t>
+        </is>
+      </c>
+      <c r="JR45" s="2" t="inlineStr">
+        <is>
+          <t>Completely unacceptable</t>
+        </is>
+      </c>
+      <c r="JS45" s="2" t="inlineStr">
+        <is>
+          <t>Completely unacceptable</t>
+        </is>
+      </c>
+      <c r="JT45" s="2" t="inlineStr">
+        <is>
+          <t>🗣️🗣️ Version 3</t>
+        </is>
+      </c>
+      <c r="JU45" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Unhöflich </t>
+        </is>
+      </c>
+      <c r="JV45" s="2" t="inlineStr">
+        <is>
+          <t>Social Appropriateness (e.g., the presence of others, social etiquette, or not wanting to appear distracted)</t>
+        </is>
+      </c>
+      <c r="JW45" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="JX45" s="2" t="inlineStr">
+        <is>
+          <t>After we completely conclude our current topic of conversation</t>
+        </is>
+      </c>
+      <c r="JY45" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="JZ45" s="2" t="inlineStr">
+        <is>
+          <t>🗣️ Version 2</t>
+        </is>
+      </c>
+      <c r="KA45" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Ok
+</t>
+        </is>
+      </c>
+      <c r="KB45" t="n">
+        <v>4.766</v>
+      </c>
+      <c r="KC45" t="n">
+        <v>65.158</v>
+      </c>
+      <c r="KD45" t="n">
+        <v>65.591</v>
+      </c>
+      <c r="KE45" t="n">
+        <v>44.0</v>
+      </c>
+      <c r="KF45" s="2" t="inlineStr">
+        <is>
+          <t>Mute (Do not notify me auditorily at all) 🔕</t>
+        </is>
+      </c>
+      <c r="KG45" s="2" t="inlineStr">
+        <is>
+          <t>Sound Only 'Version 1' 🔔</t>
+        </is>
+      </c>
+      <c r="KH45" s="2" t="inlineStr">
+        <is>
+          <t>Sound Only 'Version 1' 🔔</t>
+        </is>
+      </c>
+      <c r="KI45" s="2" t="inlineStr">
+        <is>
+          <t>Speech 'Version 2' (Sender) 🗣️</t>
+        </is>
+      </c>
+      <c r="KJ45" s="2" t="inlineStr">
+        <is>
+          <t>No delay: Must interrupt me immediately, regardless of my situation.</t>
+        </is>
+      </c>
+      <c r="KK45" s="2" t="inlineStr">
+        <is>
+          <t>No delay: Must interrupt me immediately, regardless of my situation.</t>
+        </is>
+      </c>
+      <c r="KL45" s="2" t="inlineStr">
+        <is>
+          <t>No delay: Must interrupt me immediately, regardless of my situation.</t>
+        </is>
+      </c>
+      <c r="KM45" s="2" t="inlineStr">
+        <is>
+          <t>Brief delay (Seconds): Can wait for a quick safe moment (e.g., until I finish crossing the street, silence).</t>
+        </is>
+      </c>
+      <c r="KN45" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="KO45" t="n">
+        <v>0.733</v>
+      </c>
+      <c r="KP45" t="n">
+        <v>40.294</v>
+      </c>
+      <c r="KQ45" t="n">
+        <v>41.471</v>
+      </c>
+      <c r="KR45" t="n">
+        <v>23.0</v>
+      </c>
+      <c r="KS45" s="2" t="inlineStr">
+        <is>
+          <t>684</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="1" t="n">
+        <v>46204.592453703706</v>
+      </c>
+      <c r="B46" s="1" t="n">
+        <v>46204.78240740741</v>
+      </c>
+      <c r="C46" s="2" t="inlineStr">
+        <is>
+          <t>IP Address</t>
+        </is>
+      </c>
+      <c r="D46" s="2" t="inlineStr">
+        <is>
+          <t>91.42.83.10</t>
+        </is>
+      </c>
+      <c r="E46" t="n">
+        <v>100.0</v>
+      </c>
+      <c r="F46" t="n">
+        <v>16412.0</v>
+      </c>
+      <c r="G46" s="2" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="H46" s="1" t="n">
+        <v>46204.782422847224</v>
+      </c>
+      <c r="I46" s="2" t="inlineStr">
+        <is>
+          <t>R_2g14nw1lpXOTjcz</t>
+        </is>
+      </c>
+      <c r="J46" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="K46" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="L46" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="M46" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="N46" t="n">
+        <v>48.1815</v>
+      </c>
+      <c r="O46" t="n">
+        <v>11.2543</v>
+      </c>
+      <c r="P46" s="2" t="inlineStr">
+        <is>
+          <t>anonymous</t>
+        </is>
+      </c>
+      <c r="Q46" s="2" t="inlineStr">
+        <is>
+          <t>EN</t>
+        </is>
+      </c>
+      <c r="R46" s="2" t="inlineStr">
+        <is>
+          <t>I understand the explanation provided to me. I was able to save a copy of this form. I reached out to the listed researchers and have had all my questions answered to my satisfaction. Therefore, I voluntarily agree to participate in this online study.,I voluntarily consent to my data being recorded and subsequently processed in line with the GDPR. I have been informed about the consequences of withdrawing my consent.</t>
+        </is>
+      </c>
+      <c r="S46" t="n">
+        <v>0.827</v>
+      </c>
+      <c r="T46" t="n">
+        <v>6.745</v>
+      </c>
+      <c r="U46" t="n">
+        <v>8.163</v>
+      </c>
+      <c r="V46" t="n">
+        <v>5.0</v>
+      </c>
+      <c r="W46" s="2" t="inlineStr">
+        <is>
+          <t>Yes, I am using a desktop or laptop computer.</t>
+        </is>
+      </c>
+      <c r="X46" s="2" t="inlineStr">
+        <is>
+          <t>Yes, I am wearing headphones.</t>
+        </is>
+      </c>
+      <c r="Y46" s="2" t="inlineStr">
+        <is>
+          <t>Both Channels</t>
+        </is>
+      </c>
+      <c r="Z46" t="n">
+        <v>0.773</v>
+      </c>
+      <c r="AA46" t="n">
+        <v>69.503</v>
+      </c>
+      <c r="AB46" t="n">
+        <v>70.155</v>
+      </c>
+      <c r="AC46" t="n">
+        <v>20.0</v>
+      </c>
+      <c r="AD46" t="n">
+        <v>24.0</v>
+      </c>
+      <c r="AE46" s="2" t="inlineStr">
+        <is>
+          <t>Female</t>
+        </is>
+      </c>
+      <c r="AF46" s="2" t="inlineStr">
+        <is>
+          <t>Deutsch</t>
+        </is>
+      </c>
+      <c r="AG46" s="2" t="inlineStr">
+        <is>
+          <t>Understand well</t>
+        </is>
+      </c>
+      <c r="AH46" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="AI46" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AJ46" s="2" t="inlineStr">
+        <is>
+          <t>No notification at all (Muted / Do Not Disturb)</t>
+        </is>
+      </c>
+      <c r="AK46" s="2" t="inlineStr">
+        <is>
+          <t>Personal Focus: To avoid distracting myself or breaking my concentration.</t>
+        </is>
+      </c>
+      <c r="AL46" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AM46" s="2" t="inlineStr">
+        <is>
+          <t>Tried once or twice</t>
+        </is>
+      </c>
+      <c r="AN46" s="2" t="inlineStr">
+        <is>
+          <t>Group Messages,Navigation / Directions</t>
+        </is>
+      </c>
+      <c r="AO46" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AP46" s="2" t="inlineStr">
+        <is>
+          <t>Somewhat disagree</t>
+        </is>
+      </c>
+      <c r="AQ46" s="2" t="inlineStr">
+        <is>
+          <t>Somewhat disagree</t>
+        </is>
+      </c>
+      <c r="AR46" t="n">
+        <v>2.241</v>
+      </c>
+      <c r="AS46" t="n">
+        <v>42.61</v>
+      </c>
+      <c r="AT46" t="n">
+        <v>43.764</v>
+      </c>
+      <c r="AU46" t="n">
+        <v>37.0</v>
+      </c>
+      <c r="AV46" s="2" t="inlineStr">
+        <is>
+          <t>🗣️Version 2,🗣️🗣️ Version 3</t>
+        </is>
+      </c>
+      <c r="AW46" s="2" t="inlineStr">
+        <is>
+          <t>🗣️🗣️ Version 3</t>
+        </is>
+      </c>
+      <c r="AX46" s="2" t="inlineStr">
+        <is>
+          <t>Kurz und knapp</t>
+        </is>
+      </c>
+      <c r="AY46" s="2" t="inlineStr">
+        <is>
+          <t>Somewhat disagree</t>
+        </is>
+      </c>
+      <c r="AZ46" s="2" t="inlineStr">
+        <is>
+          <t>Neither agree nor disagree</t>
+        </is>
+      </c>
+      <c r="BA46" s="2" t="inlineStr">
+        <is>
+          <t>Reduces need to look at a device</t>
+        </is>
+      </c>
+      <c r="BB46" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="BC46" s="2" t="inlineStr">
+        <is>
+          <t>Medium (up to ~1 minute spoken content)</t>
+        </is>
+      </c>
+      <c r="BD46" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="BE46" s="2" t="inlineStr">
+        <is>
+          <t>Disagree</t>
+        </is>
+      </c>
+      <c r="BF46" t="n">
+        <v>2.193</v>
+      </c>
+      <c r="BG46" t="n">
+        <v>30.371</v>
+      </c>
+      <c r="BH46" t="n">
+        <v>31.522</v>
+      </c>
+      <c r="BI46" t="n">
+        <v>16.0</v>
+      </c>
+      <c r="BJ46" t="n">
+        <v>1.934</v>
+      </c>
+      <c r="BK46" t="n">
+        <v>1.934</v>
+      </c>
+      <c r="BL46" t="n">
+        <v>3.106</v>
+      </c>
+      <c r="BM46" t="n">
+        <v>1.0</v>
+      </c>
+      <c r="BN46" s="2" t="inlineStr">
+        <is>
+          <t>Inappropriate</t>
+        </is>
+      </c>
+      <c r="BO46" s="2" t="inlineStr">
+        <is>
+          <t>Completely inappropriate</t>
+        </is>
+      </c>
+      <c r="BP46" s="2" t="inlineStr">
+        <is>
+          <t>Completely inappropriate</t>
+        </is>
+      </c>
+      <c r="BQ46" s="2" t="inlineStr">
+        <is>
+          <t>Difficult to detect</t>
+        </is>
+      </c>
+      <c r="BR46" s="2" t="inlineStr">
+        <is>
+          <t>Very difficult to detect</t>
+        </is>
+      </c>
+      <c r="BS46" s="2" t="inlineStr">
+        <is>
+          <t>Very difficult to detect</t>
+        </is>
+      </c>
+      <c r="BT46" s="2" t="inlineStr">
+        <is>
+          <t>Not disruptive at all</t>
+        </is>
+      </c>
+      <c r="BU46" s="2" t="inlineStr">
+        <is>
+          <t>Somewhat disruptive</t>
+        </is>
+      </c>
+      <c r="BV46" s="2" t="inlineStr">
+        <is>
+          <t>Slightly disruptive</t>
+        </is>
+      </c>
+      <c r="BW46" s="2" t="inlineStr">
+        <is>
+          <t>Completely unacceptable</t>
+        </is>
+      </c>
+      <c r="BX46" s="2" t="inlineStr">
+        <is>
+          <t>Completely unacceptable</t>
+        </is>
+      </c>
+      <c r="BY46" s="2" t="inlineStr">
+        <is>
+          <t>Completely unacceptable</t>
+        </is>
+      </c>
+      <c r="BZ46" s="2" t="inlineStr">
+        <is>
+          <t>🗣️ Version 2</t>
+        </is>
+      </c>
+      <c r="CA46" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="CB46" s="2" t="inlineStr">
+        <is>
+          <t>Focus &amp; Mental Effort (e.g., needing to concentrate on my current task without being interrupted)</t>
+        </is>
+      </c>
+      <c r="CC46" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="CD46" s="2" t="inlineStr">
+        <is>
+          <t>After I finish the current task (e.g., finish writing (part of the) code)</t>
+        </is>
+      </c>
+      <c r="CE46" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="CF46" s="2" t="inlineStr">
+        <is>
+          <t>🗣️ Version 2</t>
+        </is>
+      </c>
+      <c r="CG46" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="CH46" t="n">
+        <v>5.137</v>
+      </c>
+      <c r="CI46" t="n">
+        <v>50.601</v>
+      </c>
+      <c r="CJ46" t="n">
+        <v>51.532</v>
+      </c>
+      <c r="CK46" t="n">
+        <v>48.0</v>
+      </c>
+      <c r="CL46" s="2" t="inlineStr">
+        <is>
+          <t>Completely inappropriate</t>
+        </is>
+      </c>
+      <c r="CM46" s="2" t="inlineStr">
+        <is>
+          <t>Completely inappropriate</t>
+        </is>
+      </c>
+      <c r="CN46" s="2" t="inlineStr">
+        <is>
+          <t>Completely inappropriate</t>
+        </is>
+      </c>
+      <c r="CO46" s="2" t="inlineStr">
+        <is>
+          <t>Very difficult to detect</t>
+        </is>
+      </c>
+      <c r="CP46" s="2" t="inlineStr">
+        <is>
+          <t>Very difficult to detect</t>
+        </is>
+      </c>
+      <c r="CQ46" s="2" t="inlineStr">
+        <is>
+          <t>Very difficult to detect</t>
+        </is>
+      </c>
+      <c r="CR46" s="2" t="inlineStr">
+        <is>
+          <t>Extremely disruptive</t>
+        </is>
+      </c>
+      <c r="CS46" s="2" t="inlineStr">
+        <is>
+          <t>Extremely disruptive</t>
+        </is>
+      </c>
+      <c r="CT46" s="2" t="inlineStr">
+        <is>
+          <t>Extremely disruptive</t>
+        </is>
+      </c>
+      <c r="CU46" s="2" t="inlineStr">
+        <is>
+          <t>Neither acceptable nor unacceptable</t>
+        </is>
+      </c>
+      <c r="CV46" s="2" t="inlineStr">
+        <is>
+          <t>Somewhat unacceptable</t>
+        </is>
+      </c>
+      <c r="CW46" s="2" t="inlineStr">
+        <is>
+          <t>Unacceptable</t>
+        </is>
+      </c>
+      <c r="CX46" s="2" t="inlineStr">
+        <is>
+          <t>No audio notification at all</t>
+        </is>
+      </c>
+      <c r="CY46" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="CZ46" s="2" t="inlineStr">
+        <is>
+          <t>Focus &amp; Mental Effort (e.g., needing to concentrate on my current task without being interrupted)</t>
+        </is>
+      </c>
+      <c r="DA46" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="DB46" s="2" t="inlineStr">
+        <is>
+          <t>Later, when the meeting is over</t>
+        </is>
+      </c>
+      <c r="DC46" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="DD46" s="2" t="inlineStr">
+        <is>
+          <t>🔔 Version 1</t>
+        </is>
+      </c>
+      <c r="DE46" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="DF46" t="n">
+        <v>4.858</v>
+      </c>
+      <c r="DG46" t="n">
+        <v>39.61</v>
+      </c>
+      <c r="DH46" t="n">
+        <v>40.676</v>
+      </c>
+      <c r="DI46" t="n">
+        <v>38.0</v>
+      </c>
+      <c r="DJ46" s="2" t="inlineStr">
+        <is>
+          <t>Neither appropriate nor inappropriate</t>
+        </is>
+      </c>
+      <c r="DK46" s="2" t="inlineStr">
+        <is>
+          <t>Somewhat inappropriate</t>
+        </is>
+      </c>
+      <c r="DL46" s="2" t="inlineStr">
+        <is>
+          <t>Completely inappropriate</t>
+        </is>
+      </c>
+      <c r="DM46" s="2" t="inlineStr">
+        <is>
+          <t>Very difficult to detect</t>
+        </is>
+      </c>
+      <c r="DN46" s="2" t="inlineStr">
+        <is>
+          <t>Neither easy nor difficult to detect</t>
+        </is>
+      </c>
+      <c r="DO46" s="2" t="inlineStr">
+        <is>
+          <t>Somewhat difficult to detect</t>
+        </is>
+      </c>
+      <c r="DP46" s="2" t="inlineStr">
+        <is>
+          <t>Disruptive</t>
+        </is>
+      </c>
+      <c r="DQ46" s="2" t="inlineStr">
+        <is>
+          <t>Moderately disruptive</t>
+        </is>
+      </c>
+      <c r="DR46" s="2" t="inlineStr">
+        <is>
+          <t>Slightly disruptive</t>
+        </is>
+      </c>
+      <c r="DS46" s="2" t="inlineStr">
+        <is>
+          <t>Neither acceptable nor unacceptable</t>
+        </is>
+      </c>
+      <c r="DT46" s="2" t="inlineStr">
+        <is>
+          <t>Neither acceptable nor unacceptable</t>
+        </is>
+      </c>
+      <c r="DU46" s="2" t="inlineStr">
+        <is>
+          <t>Somewhat unacceptable</t>
+        </is>
+      </c>
+      <c r="DV46" s="2" t="inlineStr">
+        <is>
+          <t>🗣️ Version 2</t>
+        </is>
+      </c>
+      <c r="DW46" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="DX46" s="2" t="inlineStr">
+        <is>
+          <t>Focus &amp; Mental Effort (e.g., needing to concentrate on my current task without being interrupted)</t>
+        </is>
+      </c>
+      <c r="DY46" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="DZ46" s="2" t="inlineStr">
+        <is>
+          <t>When I am between songs / during a natural pause in music</t>
+        </is>
+      </c>
+      <c r="EA46" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="EB46" s="2" t="inlineStr">
+        <is>
+          <t>🗣️🗣️ Version 3</t>
+        </is>
+      </c>
+      <c r="EC46" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="ED46" t="n">
+        <v>2.083</v>
+      </c>
+      <c r="EE46" t="n">
+        <v>29.705</v>
+      </c>
+      <c r="EF46" t="n">
+        <v>30.71</v>
+      </c>
+      <c r="EG46" t="n">
+        <v>40.0</v>
+      </c>
+      <c r="EH46" s="2" t="inlineStr">
+        <is>
+          <t>Somewhat disagree</t>
+        </is>
+      </c>
+      <c r="EI46" t="n">
+        <v>0.822</v>
+      </c>
+      <c r="EJ46" t="n">
+        <v>6.602</v>
+      </c>
+      <c r="EK46" t="n">
+        <v>7.506</v>
+      </c>
+      <c r="EL46" t="n">
+        <v>6.0</v>
+      </c>
+      <c r="EM46" s="2" t="inlineStr">
+        <is>
+          <t>Inappropriate</t>
+        </is>
+      </c>
+      <c r="EN46" s="2" t="inlineStr">
+        <is>
+          <t>Inappropriate</t>
+        </is>
+      </c>
+      <c r="EO46" s="2" t="inlineStr">
+        <is>
+          <t>Inappropriate</t>
+        </is>
+      </c>
+      <c r="EP46" s="2" t="inlineStr">
+        <is>
+          <t>Easy to detect</t>
+        </is>
+      </c>
+      <c r="EQ46" s="2" t="inlineStr">
+        <is>
+          <t>Easy to detect</t>
+        </is>
+      </c>
+      <c r="ER46" s="2" t="inlineStr">
+        <is>
+          <t>Somewhat easy to detect</t>
+        </is>
+      </c>
+      <c r="ES46" s="2" t="inlineStr">
+        <is>
+          <t>Disruptive</t>
+        </is>
+      </c>
+      <c r="ET46" s="2" t="inlineStr">
+        <is>
+          <t>Disruptive</t>
+        </is>
+      </c>
+      <c r="EU46" s="2" t="inlineStr">
+        <is>
+          <t>Disruptive</t>
+        </is>
+      </c>
+      <c r="EV46" s="2" t="inlineStr">
+        <is>
+          <t>Acceptable</t>
+        </is>
+      </c>
+      <c r="EW46" s="2" t="inlineStr">
+        <is>
+          <t>Acceptable</t>
+        </is>
+      </c>
+      <c r="EX46" s="2" t="inlineStr">
+        <is>
+          <t>Acceptable</t>
+        </is>
+      </c>
+      <c r="EY46" s="2" t="inlineStr">
+        <is>
+          <t>🔔 Version 1</t>
+        </is>
+      </c>
+      <c r="EZ46" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="FA46" s="2" t="inlineStr">
+        <is>
+          <t>Focus &amp; Mental Effort (e.g., needing to concentrate on my current task without being interrupted)</t>
+        </is>
+      </c>
+      <c r="FB46" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="FC46" s="2" t="inlineStr">
+        <is>
+          <t>Later, when the whole tent is set up and we are done working</t>
+        </is>
+      </c>
+      <c r="FD46" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="FE46" s="2" t="inlineStr">
+        <is>
+          <t>🗣️🗣️ Version 3</t>
+        </is>
+      </c>
+      <c r="FF46" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="FG46" t="n">
+        <v>0.411</v>
+      </c>
+      <c r="FH46" t="n">
+        <v>52.151</v>
+      </c>
+      <c r="FI46" t="n">
+        <v>53.237</v>
+      </c>
+      <c r="FJ46" t="n">
+        <v>55.0</v>
+      </c>
+      <c r="FK46" s="2" t="inlineStr">
+        <is>
+          <t>Neither appropriate nor inappropriate</t>
+        </is>
+      </c>
+      <c r="FL46" s="2" t="inlineStr">
+        <is>
+          <t>Somewhat inappropriate</t>
+        </is>
+      </c>
+      <c r="FM46" s="2" t="inlineStr">
+        <is>
+          <t>Inappropriate</t>
+        </is>
+      </c>
+      <c r="FN46" s="2" t="inlineStr">
+        <is>
+          <t>Difficult to detect</t>
+        </is>
+      </c>
+      <c r="FO46" s="2" t="inlineStr">
+        <is>
+          <t>Very difficult to detect</t>
+        </is>
+      </c>
+      <c r="FP46" s="2" t="inlineStr">
+        <is>
+          <t>Somewhat difficult to detect</t>
+        </is>
+      </c>
+      <c r="FQ46" s="2" t="inlineStr">
+        <is>
+          <t>Slightly disruptive</t>
+        </is>
+      </c>
+      <c r="FR46" s="2" t="inlineStr">
+        <is>
+          <t>Not disruptive at all</t>
+        </is>
+      </c>
+      <c r="FS46" s="2" t="inlineStr">
+        <is>
+          <t>Very disruptive</t>
+        </is>
+      </c>
+      <c r="FT46" s="2" t="inlineStr">
+        <is>
+          <t>Somewhat unacceptable</t>
+        </is>
+      </c>
+      <c r="FU46" s="2" t="inlineStr">
+        <is>
+          <t>Somewhat unacceptable</t>
+        </is>
+      </c>
+      <c r="FV46" s="2" t="inlineStr">
+        <is>
+          <t>Completely unacceptable</t>
+        </is>
+      </c>
+      <c r="FW46" s="2" t="inlineStr">
+        <is>
+          <t>No audio notification at all</t>
+        </is>
+      </c>
+      <c r="FX46" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="FY46" s="2" t="inlineStr">
+        <is>
+          <t>Focus &amp; Mental Effort (e.g., needing to concentrate on my current task without being interrupted)</t>
+        </is>
+      </c>
+      <c r="FZ46" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="GA46" s="2" t="inlineStr">
+        <is>
+          <t>After I have finished cycling / reached my destination</t>
+        </is>
+      </c>
+      <c r="GB46" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="GC46" s="2" t="inlineStr">
+        <is>
+          <t>🗣️🗣️ Version 3</t>
+        </is>
+      </c>
+      <c r="GD46" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="GE46" t="n">
+        <v>0.93</v>
+      </c>
+      <c r="GF46" t="n">
+        <v>41.292</v>
+      </c>
+      <c r="GG46" t="n">
+        <v>42.576</v>
+      </c>
+      <c r="GH46" t="n">
+        <v>61.0</v>
+      </c>
+      <c r="GI46" s="2" t="inlineStr">
+        <is>
+          <t>Inappropriate</t>
+        </is>
+      </c>
+      <c r="GJ46" s="2" t="inlineStr">
+        <is>
+          <t>Inappropriate</t>
+        </is>
+      </c>
+      <c r="GK46" s="2" t="inlineStr">
+        <is>
+          <t>Completely inappropriate</t>
+        </is>
+      </c>
+      <c r="GL46" s="2" t="inlineStr">
+        <is>
+          <t>Difficult to detect</t>
+        </is>
+      </c>
+      <c r="GM46" s="2" t="inlineStr">
+        <is>
+          <t>Somewhat difficult to detect</t>
+        </is>
+      </c>
+      <c r="GN46" s="2" t="inlineStr">
+        <is>
+          <t>Somewhat difficult to detect</t>
+        </is>
+      </c>
+      <c r="GO46" s="2" t="inlineStr">
+        <is>
+          <t>Slightly disruptive</t>
+        </is>
+      </c>
+      <c r="GP46" s="2" t="inlineStr">
+        <is>
+          <t>Somewhat disruptive</t>
+        </is>
+      </c>
+      <c r="GQ46" s="2" t="inlineStr">
+        <is>
+          <t>Moderately disruptive</t>
+        </is>
+      </c>
+      <c r="GR46" s="2" t="inlineStr">
+        <is>
+          <t>Unacceptable</t>
+        </is>
+      </c>
+      <c r="GS46" s="2" t="inlineStr">
+        <is>
+          <t>Acceptable</t>
+        </is>
+      </c>
+      <c r="GT46" s="2" t="inlineStr">
+        <is>
+          <t>Acceptable</t>
+        </is>
+      </c>
+      <c r="GU46" s="2" t="inlineStr">
+        <is>
+          <t>No audio notification at all</t>
+        </is>
+      </c>
+      <c r="GV46" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="GW46" s="2" t="inlineStr">
+        <is>
+          <t>Acoustic Environment (e.g., the level of background noise, music, or other people talking),Focus &amp; Mental Effort (e.g., needing to concentrate on my current task without being interrupted),Social Appropriateness (e.g., the presence of others, social etiquette, or not wanting to appear distracted)</t>
+        </is>
+      </c>
+      <c r="GX46" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="GY46" s="2" t="inlineStr">
+        <is>
+          <t>After I am done shopping</t>
+        </is>
+      </c>
+      <c r="GZ46" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="HA46" s="2" t="inlineStr">
+        <is>
+          <t>🗣️🗣️ Version 3</t>
+        </is>
+      </c>
+      <c r="HB46" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="HC46" t="n">
+        <v>1.161</v>
+      </c>
+      <c r="HD46" t="n">
+        <v>42.36</v>
+      </c>
+      <c r="HE46" t="n">
+        <v>44.2</v>
+      </c>
+      <c r="HF46" t="n">
+        <v>58.0</v>
+      </c>
+      <c r="HG46" s="2" t="inlineStr">
+        <is>
+          <t>Agree</t>
+        </is>
+      </c>
+      <c r="HH46" t="n">
+        <v>1.788</v>
+      </c>
+      <c r="HI46" t="n">
+        <v>3.372</v>
+      </c>
+      <c r="HJ46" t="n">
+        <v>4.205</v>
+      </c>
+      <c r="HK46" t="n">
+        <v>4.0</v>
+      </c>
+      <c r="HL46" s="2" t="inlineStr">
+        <is>
+          <t>Neither appropriate nor inappropriate</t>
+        </is>
+      </c>
+      <c r="HM46" s="2" t="inlineStr">
+        <is>
+          <t>Somewhat inappropriate</t>
+        </is>
+      </c>
+      <c r="HN46" s="2" t="inlineStr">
+        <is>
+          <t>Somewhat inappropriate</t>
+        </is>
+      </c>
+      <c r="HO46" s="2" t="inlineStr">
+        <is>
+          <t>Somewhat difficult to detect</t>
+        </is>
+      </c>
+      <c r="HP46" s="2" t="inlineStr">
+        <is>
+          <t>Somewhat easy to detect</t>
+        </is>
+      </c>
+      <c r="HQ46" s="2" t="inlineStr">
+        <is>
+          <t>Easy to detect</t>
+        </is>
+      </c>
+      <c r="HR46" s="2" t="inlineStr">
+        <is>
+          <t>Disruptive</t>
+        </is>
+      </c>
+      <c r="HS46" s="2" t="inlineStr">
+        <is>
+          <t>Disruptive</t>
+        </is>
+      </c>
+      <c r="HT46" s="2" t="inlineStr">
+        <is>
+          <t>Disruptive</t>
+        </is>
+      </c>
+      <c r="HU46" s="2" t="inlineStr">
+        <is>
+          <t>Acceptable</t>
+        </is>
+      </c>
+      <c r="HV46" s="2" t="inlineStr">
+        <is>
+          <t>Acceptable</t>
+        </is>
+      </c>
+      <c r="HW46" s="2" t="inlineStr">
+        <is>
+          <t>Acceptable</t>
+        </is>
+      </c>
+      <c r="HX46" s="2" t="inlineStr">
+        <is>
+          <t>🗣️🗣️ Version 3</t>
+        </is>
+      </c>
+      <c r="HY46" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="HZ46" s="2" t="inlineStr">
+        <is>
+          <t>Focus &amp; Mental Effort (e.g., needing to concentrate on my current task without being interrupted)</t>
+        </is>
+      </c>
+      <c r="IA46" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="IB46" s="2" t="inlineStr">
+        <is>
+          <t>Later, when dinner is completely cooked and I am done in the kitchen</t>
+        </is>
+      </c>
+      <c r="IC46" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="ID46" s="2" t="inlineStr">
+        <is>
+          <t>🗣️ Version 2</t>
+        </is>
+      </c>
+      <c r="IE46" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="IF46" t="n">
+        <v>1.374</v>
+      </c>
+      <c r="IG46" t="n">
+        <v>37.827</v>
+      </c>
+      <c r="IH46" t="n">
+        <v>38.825</v>
+      </c>
+      <c r="II46" t="n">
+        <v>44.0</v>
+      </c>
+      <c r="IJ46" s="2" t="inlineStr">
+        <is>
+          <t>Neither appropriate nor inappropriate</t>
+        </is>
+      </c>
+      <c r="IK46" s="2" t="inlineStr">
+        <is>
+          <t>Inappropriate</t>
+        </is>
+      </c>
+      <c r="IL46" s="2" t="inlineStr">
+        <is>
+          <t>Inappropriate</t>
+        </is>
+      </c>
+      <c r="IM46" s="2" t="inlineStr">
+        <is>
+          <t>Difficult to detect</t>
+        </is>
+      </c>
+      <c r="IN46" s="2" t="inlineStr">
+        <is>
+          <t>Difficult to detect</t>
+        </is>
+      </c>
+      <c r="IO46" s="2" t="inlineStr">
+        <is>
+          <t>Very difficult to detect</t>
+        </is>
+      </c>
+      <c r="IP46" s="2" t="inlineStr">
+        <is>
+          <t>Not disruptive at all</t>
+        </is>
+      </c>
+      <c r="IQ46" s="2" t="inlineStr">
+        <is>
+          <t>Not disruptive at all</t>
+        </is>
+      </c>
+      <c r="IR46" s="2" t="inlineStr">
+        <is>
+          <t>Not disruptive at all</t>
+        </is>
+      </c>
+      <c r="IS46" s="2" t="inlineStr">
+        <is>
+          <t>Somewhat acceptable</t>
+        </is>
+      </c>
+      <c r="IT46" s="2" t="inlineStr">
+        <is>
+          <t>Neither acceptable nor unacceptable</t>
+        </is>
+      </c>
+      <c r="IU46" s="2" t="inlineStr">
+        <is>
+          <t>Somewhat unacceptable</t>
+        </is>
+      </c>
+      <c r="IV46" s="2" t="inlineStr">
+        <is>
+          <t>🗣️🗣️ Version 3</t>
+        </is>
+      </c>
+      <c r="IW46" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="IX46" s="2" t="inlineStr">
+        <is>
+          <t>Focus &amp; Mental Effort (e.g., needing to concentrate on my current task without being interrupted)</t>
+        </is>
+      </c>
+      <c r="IY46" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="IZ46" s="2" t="inlineStr">
+        <is>
+          <t>Later, when I am completely done studying</t>
+        </is>
+      </c>
+      <c r="JA46" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="JB46" s="2" t="inlineStr">
+        <is>
+          <t>🗣️🗣️ Version 3</t>
+        </is>
+      </c>
+      <c r="JC46" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="JD46" t="n">
+        <v>0.947</v>
+      </c>
+      <c r="JE46" t="n">
+        <v>38.239</v>
+      </c>
+      <c r="JF46" t="n">
+        <v>39.55</v>
+      </c>
+      <c r="JG46" t="n">
+        <v>51.0</v>
+      </c>
+      <c r="JH46" s="2" t="inlineStr">
+        <is>
+          <t>Completely inappropriate</t>
+        </is>
+      </c>
+      <c r="JI46" s="2" t="inlineStr">
+        <is>
+          <t>Completely inappropriate</t>
+        </is>
+      </c>
+      <c r="JJ46" s="2" t="inlineStr">
+        <is>
+          <t>Completely inappropriate</t>
+        </is>
+      </c>
+      <c r="JK46" s="2" t="inlineStr">
+        <is>
+          <t>Somewhat difficult to detect</t>
+        </is>
+      </c>
+      <c r="JL46" s="2" t="inlineStr">
+        <is>
+          <t>Difficult to detect</t>
+        </is>
+      </c>
+      <c r="JM46" s="2" t="inlineStr">
+        <is>
+          <t>Difficult to detect</t>
+        </is>
+      </c>
+      <c r="JN46" s="2" t="inlineStr">
+        <is>
+          <t>Slightly disruptive</t>
+        </is>
+      </c>
+      <c r="JO46" s="2" t="inlineStr">
+        <is>
+          <t>Disruptive</t>
+        </is>
+      </c>
+      <c r="JP46" s="2" t="inlineStr">
+        <is>
+          <t>Disruptive</t>
+        </is>
+      </c>
+      <c r="JQ46" s="2" t="inlineStr">
+        <is>
+          <t>Completely unacceptable</t>
+        </is>
+      </c>
+      <c r="JR46" s="2" t="inlineStr">
+        <is>
+          <t>Completely unacceptable</t>
+        </is>
+      </c>
+      <c r="JS46" s="2" t="inlineStr">
+        <is>
+          <t>Completely unacceptable</t>
+        </is>
+      </c>
+      <c r="JT46" s="2" t="inlineStr">
+        <is>
+          <t>No audio notification at all</t>
+        </is>
+      </c>
+      <c r="JU46" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="JV46" s="2" t="inlineStr">
+        <is>
+          <t>Acoustic Environment (e.g., the level of background noise, music, or other people talking),Social Appropriateness (e.g., the presence of others, social etiquette, or not wanting to appear distracted)</t>
+        </is>
+      </c>
+      <c r="JW46" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="JX46" s="2" t="inlineStr">
+        <is>
+          <t>After we completely conclude our current topic of conversation</t>
+        </is>
+      </c>
+      <c r="JY46" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="JZ46" s="2" t="inlineStr">
+        <is>
+          <t>🗣️ Version 2</t>
+        </is>
+      </c>
+      <c r="KA46" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="KB46" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="KC46" t="n">
+        <v>232.844</v>
+      </c>
+      <c r="KD46" t="n">
+        <v>233.828</v>
+      </c>
+      <c r="KE46" t="n">
+        <v>111.0</v>
+      </c>
+      <c r="KF46" s="2" t="inlineStr">
+        <is>
+          <t>Speech 'Version 2' (Sender) 🗣️</t>
+        </is>
+      </c>
+      <c r="KG46" s="2" t="inlineStr">
+        <is>
+          <t>Sound Only 'Version 1' 🔔</t>
+        </is>
+      </c>
+      <c r="KH46" s="2" t="inlineStr">
+        <is>
+          <t>Sound Only 'Version 1' 🔔</t>
+        </is>
+      </c>
+      <c r="KI46" s="2" t="inlineStr">
+        <is>
+          <t>Sound Only 'Version 1' 🔔</t>
+        </is>
+      </c>
+      <c r="KJ46" s="2" t="inlineStr">
+        <is>
+          <t>No delay: Must interrupt me immediately, regardless of my situation.</t>
+        </is>
+      </c>
+      <c r="KK46" s="2" t="inlineStr">
+        <is>
+          <t>No delay: Must interrupt me immediately, regardless of my situation.</t>
+        </is>
+      </c>
+      <c r="KL46" s="2" t="inlineStr">
+        <is>
+          <t>No delay: Must interrupt me immediately, regardless of my situation.</t>
+        </is>
+      </c>
+      <c r="KM46" s="2" t="inlineStr">
+        <is>
+          <t>No delay: Must interrupt me immediately, regardless of my situation.</t>
+        </is>
+      </c>
+      <c r="KN46" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="KO46" t="n">
+        <v>0.693</v>
+      </c>
+      <c r="KP46" t="n">
+        <v>17.509</v>
+      </c>
+      <c r="KQ46" t="n">
+        <v>19.474</v>
+      </c>
+      <c r="KR46" t="n">
+        <v>21.0</v>
+      </c>
+      <c r="KS46" s="2" t="inlineStr">
+        <is>
+          <t>16412</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A2:KS44"/>
+  <autoFilter ref="A2:KS47"/>
   <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
   <ignoredErrors>
-    <ignoredError sqref="C1:C43" numberStoredAsText="true"/>
-    <ignoredError sqref="D1:D43" numberStoredAsText="true"/>
-    <ignoredError sqref="G1:G43" numberStoredAsText="true"/>
-    <ignoredError sqref="I1:I43" numberStoredAsText="true"/>
-    <ignoredError sqref="J1:J43" numberStoredAsText="true"/>
-    <ignoredError sqref="K1:K43" numberStoredAsText="true"/>
-    <ignoredError sqref="L1:L43" numberStoredAsText="true"/>
-    <ignoredError sqref="M1:M43" numberStoredAsText="true"/>
-    <ignoredError sqref="P1:P43" numberStoredAsText="true"/>
-    <ignoredError sqref="Q1:Q43" numberStoredAsText="true"/>
-    <ignoredError sqref="R1:R43" numberStoredAsText="true"/>
-    <ignoredError sqref="S1:S43" numberStoredAsText="true"/>
-    <ignoredError sqref="T1:T43" numberStoredAsText="true"/>
-    <ignoredError sqref="U1:U43" numberStoredAsText="true"/>
-    <ignoredError sqref="V1:V43" numberStoredAsText="true"/>
-    <ignoredError sqref="W1:W43" numberStoredAsText="true"/>
-    <ignoredError sqref="X1:X43" numberStoredAsText="true"/>
-    <ignoredError sqref="Y1:Y43" numberStoredAsText="true"/>
-    <ignoredError sqref="Z1:Z43" numberStoredAsText="true"/>
-    <ignoredError sqref="AA1:AA43" numberStoredAsText="true"/>
-    <ignoredError sqref="AB1:AB43" numberStoredAsText="true"/>
-    <ignoredError sqref="AC1:AC43" numberStoredAsText="true"/>
-    <ignoredError sqref="AE1:AE43" numberStoredAsText="true"/>
-    <ignoredError sqref="AF1:AF43" numberStoredAsText="true"/>
-    <ignoredError sqref="AG1:AG43" numberStoredAsText="true"/>
-    <ignoredError sqref="AH1:AH43" numberStoredAsText="true"/>
-    <ignoredError sqref="AI1:AI43" numberStoredAsText="true"/>
-    <ignoredError sqref="AJ1:AJ43" numberStoredAsText="true"/>
-    <ignoredError sqref="AK1:AK43" numberStoredAsText="true"/>
-    <ignoredError sqref="AL1:AL43" numberStoredAsText="true"/>
-    <ignoredError sqref="AM1:AM43" numberStoredAsText="true"/>
-    <ignoredError sqref="AN1:AN43" numberStoredAsText="true"/>
-    <ignoredError sqref="AO1:AO43" numberStoredAsText="true"/>
-    <ignoredError sqref="AP1:AP43" numberStoredAsText="true"/>
-    <ignoredError sqref="AQ1:AQ43" numberStoredAsText="true"/>
-    <ignoredError sqref="AR1:AR43" numberStoredAsText="true"/>
-    <ignoredError sqref="AS1:AS43" numberStoredAsText="true"/>
-    <ignoredError sqref="AT1:AT43" numberStoredAsText="true"/>
-    <ignoredError sqref="AU1:AU43" numberStoredAsText="true"/>
-    <ignoredError sqref="AV1:AV43" numberStoredAsText="true"/>
-    <ignoredError sqref="AW1:AW43" numberStoredAsText="true"/>
-    <ignoredError sqref="AX1:AX43" numberStoredAsText="true"/>
-    <ignoredError sqref="AY1:AY43" numberStoredAsText="true"/>
-    <ignoredError sqref="AZ1:AZ43" numberStoredAsText="true"/>
-    <ignoredError sqref="BA1:BA43" numberStoredAsText="true"/>
-    <ignoredError sqref="BB1:BB43" numberStoredAsText="true"/>
-    <ignoredError sqref="BC1:BC43" numberStoredAsText="true"/>
-    <ignoredError sqref="BD1:BD43" numberStoredAsText="true"/>
-    <ignoredError sqref="BE1:BE43" numberStoredAsText="true"/>
-    <ignoredError sqref="BF1:BF43" numberStoredAsText="true"/>
-    <ignoredError sqref="BG1:BG43" numberStoredAsText="true"/>
-    <ignoredError sqref="BH1:BH43" numberStoredAsText="true"/>
-    <ignoredError sqref="BI1:BI43" numberStoredAsText="true"/>
-    <ignoredError sqref="BJ1:BJ43" numberStoredAsText="true"/>
-    <ignoredError sqref="BK1:BK43" numberStoredAsText="true"/>
-    <ignoredError sqref="BL1:BL43" numberStoredAsText="true"/>
-    <ignoredError sqref="BM1:BM43" numberStoredAsText="true"/>
-    <ignoredError sqref="BN1:BN43" numberStoredAsText="true"/>
-    <ignoredError sqref="BO1:BO43" numberStoredAsText="true"/>
-    <ignoredError sqref="BP1:BP43" numberStoredAsText="true"/>
-    <ignoredError sqref="BQ1:BQ43" numberStoredAsText="true"/>
-    <ignoredError sqref="BR1:BR43" numberStoredAsText="true"/>
-    <ignoredError sqref="BS1:BS43" numberStoredAsText="true"/>
-    <ignoredError sqref="BT1:BT43" numberStoredAsText="true"/>
-    <ignoredError sqref="BU1:BU43" numberStoredAsText="true"/>
-    <ignoredError sqref="BV1:BV43" numberStoredAsText="true"/>
-    <ignoredError sqref="BW1:BW43" numberStoredAsText="true"/>
-    <ignoredError sqref="BX1:BX43" numberStoredAsText="true"/>
-    <ignoredError sqref="BY1:BY43" numberStoredAsText="true"/>
-    <ignoredError sqref="BZ1:BZ43" numberStoredAsText="true"/>
-    <ignoredError sqref="CA1:CA43" numberStoredAsText="true"/>
-    <ignoredError sqref="CB1:CB43" numberStoredAsText="true"/>
-    <ignoredError sqref="CC1:CC43" numberStoredAsText="true"/>
-    <ignoredError sqref="CD1:CD43" numberStoredAsText="true"/>
-    <ignoredError sqref="CE1:CE43" numberStoredAsText="true"/>
-    <ignoredError sqref="CF1:CF43" numberStoredAsText="true"/>
-    <ignoredError sqref="CG1:CG43" numberStoredAsText="true"/>
-    <ignoredError sqref="CH1:CH43" numberStoredAsText="true"/>
-    <ignoredError sqref="CI1:CI43" numberStoredAsText="true"/>
-    <ignoredError sqref="CJ1:CJ43" numberStoredAsText="true"/>
-    <ignoredError sqref="CK1:CK43" numberStoredAsText="true"/>
-    <ignoredError sqref="CL1:CL43" numberStoredAsText="true"/>
-    <ignoredError sqref="CM1:CM43" numberStoredAsText="true"/>
-    <ignoredError sqref="CN1:CN43" numberStoredAsText="true"/>
-    <ignoredError sqref="CO1:CO43" numberStoredAsText="true"/>
-    <ignoredError sqref="CP1:CP43" numberStoredAsText="true"/>
-    <ignoredError sqref="CQ1:CQ43" numberStoredAsText="true"/>
-    <ignoredError sqref="CR1:CR43" numberStoredAsText="true"/>
-    <ignoredError sqref="CS1:CS43" numberStoredAsText="true"/>
-    <ignoredError sqref="CT1:CT43" numberStoredAsText="true"/>
-    <ignoredError sqref="CU1:CU43" numberStoredAsText="true"/>
-    <ignoredError sqref="CV1:CV43" numberStoredAsText="true"/>
-    <ignoredError sqref="CW1:CW43" numberStoredAsText="true"/>
-    <ignoredError sqref="CX1:CX43" numberStoredAsText="true"/>
-    <ignoredError sqref="CY1:CY43" numberStoredAsText="true"/>
-    <ignoredError sqref="CZ1:CZ43" numberStoredAsText="true"/>
-    <ignoredError sqref="DA1:DA43" numberStoredAsText="true"/>
-    <ignoredError sqref="DB1:DB43" numberStoredAsText="true"/>
-    <ignoredError sqref="DC1:DC43" numberStoredAsText="true"/>
-    <ignoredError sqref="DD1:DD43" numberStoredAsText="true"/>
-    <ignoredError sqref="DE1:DE43" numberStoredAsText="true"/>
-    <ignoredError sqref="DF1:DF43" numberStoredAsText="true"/>
-    <ignoredError sqref="DG1:DG43" numberStoredAsText="true"/>
-    <ignoredError sqref="DH1:DH43" numberStoredAsText="true"/>
-    <ignoredError sqref="DI1:DI43" numberStoredAsText="true"/>
-    <ignoredError sqref="DJ1:DJ43" numberStoredAsText="true"/>
-    <ignoredError sqref="DK1:DK43" numberStoredAsText="true"/>
-    <ignoredError sqref="DL1:DL43" numberStoredAsText="true"/>
-    <ignoredError sqref="DM1:DM43" numberStoredAsText="true"/>
-    <ignoredError sqref="DN1:DN43" numberStoredAsText="true"/>
-    <ignoredError sqref="DO1:DO43" numberStoredAsText="true"/>
-    <ignoredError sqref="DP1:DP43" numberStoredAsText="true"/>
-    <ignoredError sqref="DQ1:DQ43" numberStoredAsText="true"/>
-    <ignoredError sqref="DR1:DR43" numberStoredAsText="true"/>
-    <ignoredError sqref="DS1:DS43" numberStoredAsText="true"/>
-    <ignoredError sqref="DT1:DT43" numberStoredAsText="true"/>
-    <ignoredError sqref="DU1:DU43" numberStoredAsText="true"/>
-    <ignoredError sqref="DV1:DV43" numberStoredAsText="true"/>
-    <ignoredError sqref="DW1:DW43" numberStoredAsText="true"/>
-    <ignoredError sqref="DX1:DX43" numberStoredAsText="true"/>
-    <ignoredError sqref="DY1:DY43" numberStoredAsText="true"/>
-    <ignoredError sqref="DZ1:DZ43" numberStoredAsText="true"/>
-    <ignoredError sqref="EA1:EA43" numberStoredAsText="true"/>
-    <ignoredError sqref="EB1:EB43" numberStoredAsText="true"/>
-    <ignoredError sqref="EC1:EC43" numberStoredAsText="true"/>
-    <ignoredError sqref="ED1:ED43" numberStoredAsText="true"/>
-    <ignoredError sqref="EE1:EE43" numberStoredAsText="true"/>
-    <ignoredError sqref="EF1:EF43" numberStoredAsText="true"/>
-    <ignoredError sqref="EG1:EG43" numberStoredAsText="true"/>
-    <ignoredError sqref="EH1:EH43" numberStoredAsText="true"/>
-    <ignoredError sqref="EI1:EI43" numberStoredAsText="true"/>
-    <ignoredError sqref="EJ1:EJ43" numberStoredAsText="true"/>
-    <ignoredError sqref="EK1:EK43" numberStoredAsText="true"/>
-    <ignoredError sqref="EL1:EL43" numberStoredAsText="true"/>
-    <ignoredError sqref="EM1:EM43" numberStoredAsText="true"/>
-    <ignoredError sqref="EN1:EN43" numberStoredAsText="true"/>
-    <ignoredError sqref="EO1:EO43" numberStoredAsText="true"/>
-    <ignoredError sqref="EP1:EP43" numberStoredAsText="true"/>
-    <ignoredError sqref="EQ1:EQ43" numberStoredAsText="true"/>
-    <ignoredError sqref="ER1:ER43" numberStoredAsText="true"/>
-    <ignoredError sqref="ES1:ES43" numberStoredAsText="true"/>
-    <ignoredError sqref="ET1:ET43" numberStoredAsText="true"/>
-    <ignoredError sqref="EU1:EU43" numberStoredAsText="true"/>
-    <ignoredError sqref="EV1:EV43" numberStoredAsText="true"/>
-    <ignoredError sqref="EW1:EW43" numberStoredAsText="true"/>
-    <ignoredError sqref="EX1:EX43" numberStoredAsText="true"/>
-    <ignoredError sqref="EY1:EY43" numberStoredAsText="true"/>
-    <ignoredError sqref="EZ1:EZ43" numberStoredAsText="true"/>
-    <ignoredError sqref="FA1:FA43" numberStoredAsText="true"/>
-    <ignoredError sqref="FB1:FB43" numberStoredAsText="true"/>
-    <ignoredError sqref="FC1:FC43" numberStoredAsText="true"/>
-    <ignoredError sqref="FD1:FD43" numberStoredAsText="true"/>
-    <ignoredError sqref="FE1:FE43" numberStoredAsText="true"/>
-    <ignoredError sqref="FF1:FF43" numberStoredAsText="true"/>
-    <ignoredError sqref="FG1:FG43" numberStoredAsText="true"/>
-    <ignoredError sqref="FH1:FH43" numberStoredAsText="true"/>
-    <ignoredError sqref="FI1:FI43" numberStoredAsText="true"/>
-    <ignoredError sqref="FJ1:FJ43" numberStoredAsText="true"/>
-    <ignoredError sqref="FK1:FK43" numberStoredAsText="true"/>
-    <ignoredError sqref="FL1:FL43" numberStoredAsText="true"/>
-    <ignoredError sqref="FM1:FM43" numberStoredAsText="true"/>
-    <ignoredError sqref="FN1:FN43" numberStoredAsText="true"/>
-    <ignoredError sqref="FO1:FO43" numberStoredAsText="true"/>
-    <ignoredError sqref="FP1:FP43" numberStoredAsText="true"/>
-    <ignoredError sqref="FQ1:FQ43" numberStoredAsText="true"/>
-    <ignoredError sqref="FR1:FR43" numberStoredAsText="true"/>
-    <ignoredError sqref="FS1:FS43" numberStoredAsText="true"/>
-    <ignoredError sqref="FT1:FT43" numberStoredAsText="true"/>
-    <ignoredError sqref="FU1:FU43" numberStoredAsText="true"/>
-    <ignoredError sqref="FV1:FV43" numberStoredAsText="true"/>
-    <ignoredError sqref="FW1:FW43" numberStoredAsText="true"/>
-    <ignoredError sqref="FX1:FX43" numberStoredAsText="true"/>
-    <ignoredError sqref="FY1:FY43" numberStoredAsText="true"/>
-    <ignoredError sqref="FZ1:FZ43" numberStoredAsText="true"/>
-    <ignoredError sqref="GA1:GA43" numberStoredAsText="true"/>
-    <ignoredError sqref="GB1:GB43" numberStoredAsText="true"/>
-    <ignoredError sqref="GC1:GC43" numberStoredAsText="true"/>
-    <ignoredError sqref="GD1:GD43" numberStoredAsText="true"/>
-    <ignoredError sqref="GE1:GE43" numberStoredAsText="true"/>
-    <ignoredError sqref="GF1:GF43" numberStoredAsText="true"/>
-    <ignoredError sqref="GG1:GG43" numberStoredAsText="true"/>
-    <ignoredError sqref="GH1:GH43" numberStoredAsText="true"/>
-    <ignoredError sqref="GI1:GI43" numberStoredAsText="true"/>
-    <ignoredError sqref="GJ1:GJ43" numberStoredAsText="true"/>
-    <ignoredError sqref="GK1:GK43" numberStoredAsText="true"/>
-    <ignoredError sqref="GL1:GL43" numberStoredAsText="true"/>
-    <ignoredError sqref="GM1:GM43" numberStoredAsText="true"/>
-    <ignoredError sqref="GN1:GN43" numberStoredAsText="true"/>
-    <ignoredError sqref="GO1:GO43" numberStoredAsText="true"/>
-    <ignoredError sqref="GP1:GP43" numberStoredAsText="true"/>
-    <ignoredError sqref="GQ1:GQ43" numberStoredAsText="true"/>
-    <ignoredError sqref="GR1:GR43" numberStoredAsText="true"/>
-    <ignoredError sqref="GS1:GS43" numberStoredAsText="true"/>
-    <ignoredError sqref="GT1:GT43" numberStoredAsText="true"/>
-    <ignoredError sqref="GU1:GU43" numberStoredAsText="true"/>
-    <ignoredError sqref="GV1:GV43" numberStoredAsText="true"/>
-    <ignoredError sqref="GW1:GW43" numberStoredAsText="true"/>
-    <ignoredError sqref="GX1:GX43" numberStoredAsText="true"/>
-    <ignoredError sqref="GY1:GY43" numberStoredAsText="true"/>
-    <ignoredError sqref="GZ1:GZ43" numberStoredAsText="true"/>
-    <ignoredError sqref="HA1:HA43" numberStoredAsText="true"/>
-    <ignoredError sqref="HB1:HB43" numberStoredAsText="true"/>
-    <ignoredError sqref="HC1:HC43" numberStoredAsText="true"/>
-    <ignoredError sqref="HD1:HD43" numberStoredAsText="true"/>
-    <ignoredError sqref="HE1:HE43" numberStoredAsText="true"/>
-    <ignoredError sqref="HF1:HF43" numberStoredAsText="true"/>
-    <ignoredError sqref="HG1:HG43" numberStoredAsText="true"/>
-    <ignoredError sqref="HH1:HH43" numberStoredAsText="true"/>
-    <ignoredError sqref="HI1:HI43" numberStoredAsText="true"/>
-    <ignoredError sqref="HJ1:HJ43" numberStoredAsText="true"/>
-    <ignoredError sqref="HK1:HK43" numberStoredAsText="true"/>
-    <ignoredError sqref="HL1:HL43" numberStoredAsText="true"/>
-    <ignoredError sqref="HM1:HM43" numberStoredAsText="true"/>
-    <ignoredError sqref="HN1:HN43" numberStoredAsText="true"/>
-    <ignoredError sqref="HO1:HO43" numberStoredAsText="true"/>
-    <ignoredError sqref="HP1:HP43" numberStoredAsText="true"/>
-    <ignoredError sqref="HQ1:HQ43" numberStoredAsText="true"/>
-    <ignoredError sqref="HR1:HR43" numberStoredAsText="true"/>
-    <ignoredError sqref="HS1:HS43" numberStoredAsText="true"/>
-    <ignoredError sqref="HT1:HT43" numberStoredAsText="true"/>
-    <ignoredError sqref="HU1:HU43" numberStoredAsText="true"/>
-    <ignoredError sqref="HV1:HV43" numberStoredAsText="true"/>
-    <ignoredError sqref="HW1:HW43" numberStoredAsText="true"/>
-    <ignoredError sqref="HX1:HX43" numberStoredAsText="true"/>
-    <ignoredError sqref="HY1:HY43" numberStoredAsText="true"/>
-    <ignoredError sqref="HZ1:HZ43" numberStoredAsText="true"/>
-    <ignoredError sqref="IA1:IA43" numberStoredAsText="true"/>
-    <ignoredError sqref="IB1:IB43" numberStoredAsText="true"/>
-    <ignoredError sqref="IC1:IC43" numberStoredAsText="true"/>
-    <ignoredError sqref="ID1:ID43" numberStoredAsText="true"/>
-    <ignoredError sqref="IE1:IE43" numberStoredAsText="true"/>
-    <ignoredError sqref="IF1:IF43" numberStoredAsText="true"/>
-    <ignoredError sqref="IG1:IG43" numberStoredAsText="true"/>
-    <ignoredError sqref="IH1:IH43" numberStoredAsText="true"/>
-    <ignoredError sqref="II1:II43" numberStoredAsText="true"/>
-    <ignoredError sqref="IJ1:IJ43" numberStoredAsText="true"/>
-    <ignoredError sqref="IK1:IK43" numberStoredAsText="true"/>
-    <ignoredError sqref="IL1:IL43" numberStoredAsText="true"/>
-    <ignoredError sqref="IM1:IM43" numberStoredAsText="true"/>
-    <ignoredError sqref="IN1:IN43" numberStoredAsText="true"/>
-    <ignoredError sqref="IO1:IO43" numberStoredAsText="true"/>
-    <ignoredError sqref="IP1:IP43" numberStoredAsText="true"/>
-    <ignoredError sqref="IQ1:IQ43" numberStoredAsText="true"/>
-    <ignoredError sqref="IR1:IR43" numberStoredAsText="true"/>
-    <ignoredError sqref="IS1:IS43" numberStoredAsText="true"/>
-    <ignoredError sqref="IT1:IT43" numberStoredAsText="true"/>
-    <ignoredError sqref="IU1:IU43" numberStoredAsText="true"/>
-    <ignoredError sqref="IV1:IV43" numberStoredAsText="true"/>
-    <ignoredError sqref="IW1:IW43" numberStoredAsText="true"/>
-    <ignoredError sqref="IX1:IX43" numberStoredAsText="true"/>
-    <ignoredError sqref="IY1:IY43" numberStoredAsText="true"/>
-    <ignoredError sqref="IZ1:IZ43" numberStoredAsText="true"/>
-    <ignoredError sqref="JA1:JA43" numberStoredAsText="true"/>
-    <ignoredError sqref="JB1:JB43" numberStoredAsText="true"/>
-    <ignoredError sqref="JC1:JC43" numberStoredAsText="true"/>
-    <ignoredError sqref="JD1:JD43" numberStoredAsText="true"/>
-    <ignoredError sqref="JE1:JE43" numberStoredAsText="true"/>
-    <ignoredError sqref="JF1:JF43" numberStoredAsText="true"/>
-    <ignoredError sqref="JG1:JG43" numberStoredAsText="true"/>
-    <ignoredError sqref="JH1:JH43" numberStoredAsText="true"/>
-    <ignoredError sqref="JI1:JI43" numberStoredAsText="true"/>
-    <ignoredError sqref="JJ1:JJ43" numberStoredAsText="true"/>
-    <ignoredError sqref="JK1:JK43" numberStoredAsText="true"/>
-    <ignoredError sqref="JL1:JL43" numberStoredAsText="true"/>
-    <ignoredError sqref="JM1:JM43" numberStoredAsText="true"/>
-    <ignoredError sqref="JN1:JN43" numberStoredAsText="true"/>
-    <ignoredError sqref="JO1:JO43" numberStoredAsText="true"/>
-    <ignoredError sqref="JP1:JP43" numberStoredAsText="true"/>
-    <ignoredError sqref="JQ1:JQ43" numberStoredAsText="true"/>
-    <ignoredError sqref="JR1:JR43" numberStoredAsText="true"/>
-    <ignoredError sqref="JS1:JS43" numberStoredAsText="true"/>
-    <ignoredError sqref="JT1:JT43" numberStoredAsText="true"/>
-    <ignoredError sqref="JU1:JU43" numberStoredAsText="true"/>
-    <ignoredError sqref="JV1:JV43" numberStoredAsText="true"/>
-    <ignoredError sqref="JW1:JW43" numberStoredAsText="true"/>
-    <ignoredError sqref="JX1:JX43" numberStoredAsText="true"/>
-    <ignoredError sqref="JY1:JY43" numberStoredAsText="true"/>
-    <ignoredError sqref="JZ1:JZ43" numberStoredAsText="true"/>
-    <ignoredError sqref="KA1:KA43" numberStoredAsText="true"/>
-    <ignoredError sqref="KB1:KB43" numberStoredAsText="true"/>
-    <ignoredError sqref="KC1:KC43" numberStoredAsText="true"/>
-    <ignoredError sqref="KD1:KD43" numberStoredAsText="true"/>
-    <ignoredError sqref="KE1:KE43" numberStoredAsText="true"/>
-    <ignoredError sqref="KF1:KF43" numberStoredAsText="true"/>
-    <ignoredError sqref="KG1:KG43" numberStoredAsText="true"/>
-    <ignoredError sqref="KH1:KH43" numberStoredAsText="true"/>
-    <ignoredError sqref="KI1:KI43" numberStoredAsText="true"/>
-    <ignoredError sqref="KJ1:KJ43" numberStoredAsText="true"/>
-    <ignoredError sqref="KK1:KK43" numberStoredAsText="true"/>
-    <ignoredError sqref="KL1:KL43" numberStoredAsText="true"/>
-    <ignoredError sqref="KM1:KM43" numberStoredAsText="true"/>
-    <ignoredError sqref="KN1:KN43" numberStoredAsText="true"/>
-    <ignoredError sqref="KO1:KO43" numberStoredAsText="true"/>
-    <ignoredError sqref="KP1:KP43" numberStoredAsText="true"/>
-    <ignoredError sqref="KQ1:KQ43" numberStoredAsText="true"/>
-    <ignoredError sqref="KR1:KR43" numberStoredAsText="true"/>
-    <ignoredError sqref="KS1:KS43" numberStoredAsText="true"/>
+    <ignoredError sqref="C1:C46" numberStoredAsText="true"/>
+    <ignoredError sqref="D1:D46" numberStoredAsText="true"/>
+    <ignoredError sqref="G1:G46" numberStoredAsText="true"/>
+    <ignoredError sqref="I1:I46" numberStoredAsText="true"/>
+    <ignoredError sqref="J1:J46" numberStoredAsText="true"/>
+    <ignoredError sqref="K1:K46" numberStoredAsText="true"/>
+    <ignoredError sqref="L1:L46" numberStoredAsText="true"/>
+    <ignoredError sqref="M1:M46" numberStoredAsText="true"/>
+    <ignoredError sqref="P1:P46" numberStoredAsText="true"/>
+    <ignoredError sqref="Q1:Q46" numberStoredAsText="true"/>
+    <ignoredError sqref="R1:R46" numberStoredAsText="true"/>
+    <ignoredError sqref="S1:S46" numberStoredAsText="true"/>
+    <ignoredError sqref="T1:T46" numberStoredAsText="true"/>
+    <ignoredError sqref="U1:U46" numberStoredAsText="true"/>
+    <ignoredError sqref="V1:V46" numberStoredAsText="true"/>
+    <ignoredError sqref="W1:W46" numberStoredAsText="true"/>
+    <ignoredError sqref="X1:X46" numberStoredAsText="true"/>
+    <ignoredError sqref="Y1:Y46" numberStoredAsText="true"/>
+    <ignoredError sqref="Z1:Z46" numberStoredAsText="true"/>
+    <ignoredError sqref="AA1:AA46" numberStoredAsText="true"/>
+    <ignoredError sqref="AB1:AB46" numberStoredAsText="true"/>
+    <ignoredError sqref="AC1:AC46" numberStoredAsText="true"/>
+    <ignoredError sqref="AE1:AE46" numberStoredAsText="true"/>
+    <ignoredError sqref="AF1:AF46" numberStoredAsText="true"/>
+    <ignoredError sqref="AG1:AG46" numberStoredAsText="true"/>
+    <ignoredError sqref="AH1:AH46" numberStoredAsText="true"/>
+    <ignoredError sqref="AI1:AI46" numberStoredAsText="true"/>
+    <ignoredError sqref="AJ1:AJ46" numberStoredAsText="true"/>
+    <ignoredError sqref="AK1:AK46" numberStoredAsText="true"/>
+    <ignoredError sqref="AL1:AL46" numberStoredAsText="true"/>
+    <ignoredError sqref="AM1:AM46" numberStoredAsText="true"/>
+    <ignoredError sqref="AN1:AN46" numberStoredAsText="true"/>
+    <ignoredError sqref="AO1:AO46" numberStoredAsText="true"/>
+    <ignoredError sqref="AP1:AP46" numberStoredAsText="true"/>
+    <ignoredError sqref="AQ1:AQ46" numberStoredAsText="true"/>
+    <ignoredError sqref="AR1:AR46" numberStoredAsText="true"/>
+    <ignoredError sqref="AS1:AS46" numberStoredAsText="true"/>
+    <ignoredError sqref="AT1:AT46" numberStoredAsText="true"/>
+    <ignoredError sqref="AU1:AU46" numberStoredAsText="true"/>
+    <ignoredError sqref="AV1:AV46" numberStoredAsText="true"/>
+    <ignoredError sqref="AW1:AW46" numberStoredAsText="true"/>
+    <ignoredError sqref="AX1:AX46" numberStoredAsText="true"/>
+    <ignoredError sqref="AY1:AY46" numberStoredAsText="true"/>
+    <ignoredError sqref="AZ1:AZ46" numberStoredAsText="true"/>
+    <ignoredError sqref="BA1:BA46" numberStoredAsText="true"/>
+    <ignoredError sqref="BB1:BB46" numberStoredAsText="true"/>
+    <ignoredError sqref="BC1:BC46" numberStoredAsText="true"/>
+    <ignoredError sqref="BD1:BD46" numberStoredAsText="true"/>
+    <ignoredError sqref="BE1:BE46" numberStoredAsText="true"/>
+    <ignoredError sqref="BF1:BF46" numberStoredAsText="true"/>
+    <ignoredError sqref="BG1:BG46" numberStoredAsText="true"/>
+    <ignoredError sqref="BH1:BH46" numberStoredAsText="true"/>
+    <ignoredError sqref="BI1:BI46" numberStoredAsText="true"/>
+    <ignoredError sqref="BJ1:BJ46" numberStoredAsText="true"/>
+    <ignoredError sqref="BK1:BK46" numberStoredAsText="true"/>
+    <ignoredError sqref="BL1:BL46" numberStoredAsText="true"/>
+    <ignoredError sqref="BM1:BM46" numberStoredAsText="true"/>
+    <ignoredError sqref="BN1:BN46" numberStoredAsText="true"/>
+    <ignoredError sqref="BO1:BO46" numberStoredAsText="true"/>
+    <ignoredError sqref="BP1:BP46" numberStoredAsText="true"/>
+    <ignoredError sqref="BQ1:BQ46" numberStoredAsText="true"/>
+    <ignoredError sqref="BR1:BR46" numberStoredAsText="true"/>
+    <ignoredError sqref="BS1:BS46" numberStoredAsText="true"/>
+    <ignoredError sqref="BT1:BT46" numberStoredAsText="true"/>
+    <ignoredError sqref="BU1:BU46" numberStoredAsText="true"/>
+    <ignoredError sqref="BV1:BV46" numberStoredAsText="true"/>
+    <ignoredError sqref="BW1:BW46" numberStoredAsText="true"/>
+    <ignoredError sqref="BX1:BX46" numberStoredAsText="true"/>
+    <ignoredError sqref="BY1:BY46" numberStoredAsText="true"/>
+    <ignoredError sqref="BZ1:BZ46" numberStoredAsText="true"/>
+    <ignoredError sqref="CA1:CA46" numberStoredAsText="true"/>
+    <ignoredError sqref="CB1:CB46" numberStoredAsText="true"/>
+    <ignoredError sqref="CC1:CC46" numberStoredAsText="true"/>
+    <ignoredError sqref="CD1:CD46" numberStoredAsText="true"/>
+    <ignoredError sqref="CE1:CE46" numberStoredAsText="true"/>
+    <ignoredError sqref="CF1:CF46" numberStoredAsText="true"/>
+    <ignoredError sqref="CG1:CG46" numberStoredAsText="true"/>
+    <ignoredError sqref="CH1:CH46" numberStoredAsText="true"/>
+    <ignoredError sqref="CI1:CI46" numberStoredAsText="true"/>
+    <ignoredError sqref="CJ1:CJ46" numberStoredAsText="true"/>
+    <ignoredError sqref="CK1:CK46" numberStoredAsText="true"/>
+    <ignoredError sqref="CL1:CL46" numberStoredAsText="true"/>
+    <ignoredError sqref="CM1:CM46" numberStoredAsText="true"/>
+    <ignoredError sqref="CN1:CN46" numberStoredAsText="true"/>
+    <ignoredError sqref="CO1:CO46" numberStoredAsText="true"/>
+    <ignoredError sqref="CP1:CP46" numberStoredAsText="true"/>
+    <ignoredError sqref="CQ1:CQ46" numberStoredAsText="true"/>
+    <ignoredError sqref="CR1:CR46" numberStoredAsText="true"/>
+    <ignoredError sqref="CS1:CS46" numberStoredAsText="true"/>
+    <ignoredError sqref="CT1:CT46" numberStoredAsText="true"/>
+    <ignoredError sqref="CU1:CU46" numberStoredAsText="true"/>
+    <ignoredError sqref="CV1:CV46" numberStoredAsText="true"/>
+    <ignoredError sqref="CW1:CW46" numberStoredAsText="true"/>
+    <ignoredError sqref="CX1:CX46" numberStoredAsText="true"/>
+    <ignoredError sqref="CY1:CY46" numberStoredAsText="true"/>
+    <ignoredError sqref="CZ1:CZ46" numberStoredAsText="true"/>
+    <ignoredError sqref="DA1:DA46" numberStoredAsText="true"/>
+    <ignoredError sqref="DB1:DB46" numberStoredAsText="true"/>
+    <ignoredError sqref="DC1:DC46" numberStoredAsText="true"/>
+    <ignoredError sqref="DD1:DD46" numberStoredAsText="true"/>
+    <ignoredError sqref="DE1:DE46" numberStoredAsText="true"/>
+    <ignoredError sqref="DF1:DF46" numberStoredAsText="true"/>
+    <ignoredError sqref="DG1:DG46" numberStoredAsText="true"/>
+    <ignoredError sqref="DH1:DH46" numberStoredAsText="true"/>
+    <ignoredError sqref="DI1:DI46" numberStoredAsText="true"/>
+    <ignoredError sqref="DJ1:DJ46" numberStoredAsText="true"/>
+    <ignoredError sqref="DK1:DK46" numberStoredAsText="true"/>
+    <ignoredError sqref="DL1:DL46" numberStoredAsText="true"/>
+    <ignoredError sqref="DM1:DM46" numberStoredAsText="true"/>
+    <ignoredError sqref="DN1:DN46" numberStoredAsText="true"/>
+    <ignoredError sqref="DO1:DO46" numberStoredAsText="true"/>
+    <ignoredError sqref="DP1:DP46" numberStoredAsText="true"/>
+    <ignoredError sqref="DQ1:DQ46" numberStoredAsText="true"/>
+    <ignoredError sqref="DR1:DR46" numberStoredAsText="true"/>
+    <ignoredError sqref="DS1:DS46" numberStoredAsText="true"/>
+    <ignoredError sqref="DT1:DT46" numberStoredAsText="true"/>
+    <ignoredError sqref="DU1:DU46" numberStoredAsText="true"/>
+    <ignoredError sqref="DV1:DV46" numberStoredAsText="true"/>
+    <ignoredError sqref="DW1:DW46" numberStoredAsText="true"/>
+    <ignoredError sqref="DX1:DX46" numberStoredAsText="true"/>
+    <ignoredError sqref="DY1:DY46" numberStoredAsText="true"/>
+    <ignoredError sqref="DZ1:DZ46" numberStoredAsText="true"/>
+    <ignoredError sqref="EA1:EA46" numberStoredAsText="true"/>
+    <ignoredError sqref="EB1:EB46" numberStoredAsText="true"/>
+    <ignoredError sqref="EC1:EC46" numberStoredAsText="true"/>
+    <ignoredError sqref="ED1:ED46" numberStoredAsText="true"/>
+    <ignoredError sqref="EE1:EE46" numberStoredAsText="true"/>
+    <ignoredError sqref="EF1:EF46" numberStoredAsText="true"/>
+    <ignoredError sqref="EG1:EG46" numberStoredAsText="true"/>
+    <ignoredError sqref="EH1:EH46" numberStoredAsText="true"/>
+    <ignoredError sqref="EI1:EI46" numberStoredAsText="true"/>
+    <ignoredError sqref="EJ1:EJ46" numberStoredAsText="true"/>
+    <ignoredError sqref="EK1:EK46" numberStoredAsText="true"/>
+    <ignoredError sqref="EL1:EL46" numberStoredAsText="true"/>
+    <ignoredError sqref="EM1:EM46" numberStoredAsText="true"/>
+    <ignoredError sqref="EN1:EN46" numberStoredAsText="true"/>
+    <ignoredError sqref="EO1:EO46" numberStoredAsText="true"/>
+    <ignoredError sqref="EP1:EP46" numberStoredAsText="true"/>
+    <ignoredError sqref="EQ1:EQ46" numberStoredAsText="true"/>
+    <ignoredError sqref="ER1:ER46" numberStoredAsText="true"/>
+    <ignoredError sqref="ES1:ES46" numberStoredAsText="true"/>
+    <ignoredError sqref="ET1:ET46" numberStoredAsText="true"/>
+    <ignoredError sqref="EU1:EU46" numberStoredAsText="true"/>
+    <ignoredError sqref="EV1:EV46" numberStoredAsText="true"/>
+    <ignoredError sqref="EW1:EW46" numberStoredAsText="true"/>
+    <ignoredError sqref="EX1:EX46" numberStoredAsText="true"/>
+    <ignoredError sqref="EY1:EY46" numberStoredAsText="true"/>
+    <ignoredError sqref="EZ1:EZ46" numberStoredAsText="true"/>
+    <ignoredError sqref="FA1:FA46" numberStoredAsText="true"/>
+    <ignoredError sqref="FB1:FB46" numberStoredAsText="true"/>
+    <ignoredError sqref="FC1:FC46" numberStoredAsText="true"/>
+    <ignoredError sqref="FD1:FD46" numberStoredAsText="true"/>
+    <ignoredError sqref="FE1:FE46" numberStoredAsText="true"/>
+    <ignoredError sqref="FF1:FF46" numberStoredAsText="true"/>
+    <ignoredError sqref="FG1:FG46" numberStoredAsText="true"/>
+    <ignoredError sqref="FH1:FH46" numberStoredAsText="true"/>
+    <ignoredError sqref="FI1:FI46" numberStoredAsText="true"/>
+    <ignoredError sqref="FJ1:FJ46" numberStoredAsText="true"/>
+    <ignoredError sqref="FK1:FK46" numberStoredAsText="true"/>
+    <ignoredError sqref="FL1:FL46" numberStoredAsText="true"/>
+    <ignoredError sqref="FM1:FM46" numberStoredAsText="true"/>
+    <ignoredError sqref="FN1:FN46" numberStoredAsText="true"/>
+    <ignoredError sqref="FO1:FO46" numberStoredAsText="true"/>
+    <ignoredError sqref="FP1:FP46" numberStoredAsText="true"/>
+    <ignoredError sqref="FQ1:FQ46" numberStoredAsText="true"/>
+    <ignoredError sqref="FR1:FR46" numberStoredAsText="true"/>
+    <ignoredError sqref="FS1:FS46" numberStoredAsText="true"/>
+    <ignoredError sqref="FT1:FT46" numberStoredAsText="true"/>
+    <ignoredError sqref="FU1:FU46" numberStoredAsText="true"/>
+    <ignoredError sqref="FV1:FV46" numberStoredAsText="true"/>
+    <ignoredError sqref="FW1:FW46" numberStoredAsText="true"/>
+    <ignoredError sqref="FX1:FX46" numberStoredAsText="true"/>
+    <ignoredError sqref="FY1:FY46" numberStoredAsText="true"/>
+    <ignoredError sqref="FZ1:FZ46" numberStoredAsText="true"/>
+    <ignoredError sqref="GA1:GA46" numberStoredAsText="true"/>
+    <ignoredError sqref="GB1:GB46" numberStoredAsText="true"/>
+    <ignoredError sqref="GC1:GC46" numberStoredAsText="true"/>
+    <ignoredError sqref="GD1:GD46" numberStoredAsText="true"/>
+    <ignoredError sqref="GE1:GE46" numberStoredAsText="true"/>
+    <ignoredError sqref="GF1:GF46" numberStoredAsText="true"/>
+    <ignoredError sqref="GG1:GG46" numberStoredAsText="true"/>
+    <ignoredError sqref="GH1:GH46" numberStoredAsText="true"/>
+    <ignoredError sqref="GI1:GI46" numberStoredAsText="true"/>
+    <ignoredError sqref="GJ1:GJ46" numberStoredAsText="true"/>
+    <ignoredError sqref="GK1:GK46" numberStoredAsText="true"/>
+    <ignoredError sqref="GL1:GL46" numberStoredAsText="true"/>
+    <ignoredError sqref="GM1:GM46" numberStoredAsText="true"/>
+    <ignoredError sqref="GN1:GN46" numberStoredAsText="true"/>
+    <ignoredError sqref="GO1:GO46" numberStoredAsText="true"/>
+    <ignoredError sqref="GP1:GP46" numberStoredAsText="true"/>
+    <ignoredError sqref="GQ1:GQ46" numberStoredAsText="true"/>
+    <ignoredError sqref="GR1:GR46" numberStoredAsText="true"/>
+    <ignoredError sqref="GS1:GS46" numberStoredAsText="true"/>
+    <ignoredError sqref="GT1:GT46" numberStoredAsText="true"/>
+    <ignoredError sqref="GU1:GU46" numberStoredAsText="true"/>
+    <ignoredError sqref="GV1:GV46" numberStoredAsText="true"/>
+    <ignoredError sqref="GW1:GW46" numberStoredAsText="true"/>
+    <ignoredError sqref="GX1:GX46" numberStoredAsText="true"/>
+    <ignoredError sqref="GY1:GY46" numberStoredAsText="true"/>
+    <ignoredError sqref="GZ1:GZ46" numberStoredAsText="true"/>
+    <ignoredError sqref="HA1:HA46" numberStoredAsText="true"/>
+    <ignoredError sqref="HB1:HB46" numberStoredAsText="true"/>
+    <ignoredError sqref="HC1:HC46" numberStoredAsText="true"/>
+    <ignoredError sqref="HD1:HD46" numberStoredAsText="true"/>
+    <ignoredError sqref="HE1:HE46" numberStoredAsText="true"/>
+    <ignoredError sqref="HF1:HF46" numberStoredAsText="true"/>
+    <ignoredError sqref="HG1:HG46" numberStoredAsText="true"/>
+    <ignoredError sqref="HH1:HH46" numberStoredAsText="true"/>
+    <ignoredError sqref="HI1:HI46" numberStoredAsText="true"/>
+    <ignoredError sqref="HJ1:HJ46" numberStoredAsText="true"/>
+    <ignoredError sqref="HK1:HK46" numberStoredAsText="true"/>
+    <ignoredError sqref="HL1:HL46" numberStoredAsText="true"/>
+    <ignoredError sqref="HM1:HM46" numberStoredAsText="true"/>
+    <ignoredError sqref="HN1:HN46" numberStoredAsText="true"/>
+    <ignoredError sqref="HO1:HO46" numberStoredAsText="true"/>
+    <ignoredError sqref="HP1:HP46" numberStoredAsText="true"/>
+    <ignoredError sqref="HQ1:HQ46" numberStoredAsText="true"/>
+    <ignoredError sqref="HR1:HR46" numberStoredAsText="true"/>
+    <ignoredError sqref="HS1:HS46" numberStoredAsText="true"/>
+    <ignoredError sqref="HT1:HT46" numberStoredAsText="true"/>
+    <ignoredError sqref="HU1:HU46" numberStoredAsText="true"/>
+    <ignoredError sqref="HV1:HV46" numberStoredAsText="true"/>
+    <ignoredError sqref="HW1:HW46" numberStoredAsText="true"/>
+    <ignoredError sqref="HX1:HX46" numberStoredAsText="true"/>
+    <ignoredError sqref="HY1:HY46" numberStoredAsText="true"/>
+    <ignoredError sqref="HZ1:HZ46" numberStoredAsText="true"/>
+    <ignoredError sqref="IA1:IA46" numberStoredAsText="true"/>
+    <ignoredError sqref="IB1:IB46" numberStoredAsText="true"/>
+    <ignoredError sqref="IC1:IC46" numberStoredAsText="true"/>
+    <ignoredError sqref="ID1:ID46" numberStoredAsText="true"/>
+    <ignoredError sqref="IE1:IE46" numberStoredAsText="true"/>
+    <ignoredError sqref="IF1:IF46" numberStoredAsText="true"/>
+    <ignoredError sqref="IG1:IG46" numberStoredAsText="true"/>
+    <ignoredError sqref="IH1:IH46" numberStoredAsText="true"/>
+    <ignoredError sqref="II1:II46" numberStoredAsText="true"/>
+    <ignoredError sqref="IJ1:IJ46" numberStoredAsText="true"/>
+    <ignoredError sqref="IK1:IK46" numberStoredAsText="true"/>
+    <ignoredError sqref="IL1:IL46" numberStoredAsText="true"/>
+    <ignoredError sqref="IM1:IM46" numberStoredAsText="true"/>
+    <ignoredError sqref="IN1:IN46" numberStoredAsText="true"/>
+    <ignoredError sqref="IO1:IO46" numberStoredAsText="true"/>
+    <ignoredError sqref="IP1:IP46" numberStoredAsText="true"/>
+    <ignoredError sqref="IQ1:IQ46" numberStoredAsText="true"/>
+    <ignoredError sqref="IR1:IR46" numberStoredAsText="true"/>
+    <ignoredError sqref="IS1:IS46" numberStoredAsText="true"/>
+    <ignoredError sqref="IT1:IT46" numberStoredAsText="true"/>
+    <ignoredError sqref="IU1:IU46" numberStoredAsText="true"/>
+    <ignoredError sqref="IV1:IV46" numberStoredAsText="true"/>
+    <ignoredError sqref="IW1:IW46" numberStoredAsText="true"/>
+    <ignoredError sqref="IX1:IX46" numberStoredAsText="true"/>
+    <ignoredError sqref="IY1:IY46" numberStoredAsText="true"/>
+    <ignoredError sqref="IZ1:IZ46" numberStoredAsText="true"/>
+    <ignoredError sqref="JA1:JA46" numberStoredAsText="true"/>
+    <ignoredError sqref="JB1:JB46" numberStoredAsText="true"/>
+    <ignoredError sqref="JC1:JC46" numberStoredAsText="true"/>
+    <ignoredError sqref="JD1:JD46" numberStoredAsText="true"/>
+    <ignoredError sqref="JE1:JE46" numberStoredAsText="true"/>
+    <ignoredError sqref="JF1:JF46" numberStoredAsText="true"/>
+    <ignoredError sqref="JG1:JG46" numberStoredAsText="true"/>
+    <ignoredError sqref="JH1:JH46" numberStoredAsText="true"/>
+    <ignoredError sqref="JI1:JI46" numberStoredAsText="true"/>
+    <ignoredError sqref="JJ1:JJ46" numberStoredAsText="true"/>
+    <ignoredError sqref="JK1:JK46" numberStoredAsText="true"/>
+    <ignoredError sqref="JL1:JL46" numberStoredAsText="true"/>
+    <ignoredError sqref="JM1:JM46" numberStoredAsText="true"/>
+    <ignoredError sqref="JN1:JN46" numberStoredAsText="true"/>
+    <ignoredError sqref="JO1:JO46" numberStoredAsText="true"/>
+    <ignoredError sqref="JP1:JP46" numberStoredAsText="true"/>
+    <ignoredError sqref="JQ1:JQ46" numberStoredAsText="true"/>
+    <ignoredError sqref="JR1:JR46" numberStoredAsText="true"/>
+    <ignoredError sqref="JS1:JS46" numberStoredAsText="true"/>
+    <ignoredError sqref="JT1:JT46" numberStoredAsText="true"/>
+    <ignoredError sqref="JU1:JU46" numberStoredAsText="true"/>
+    <ignoredError sqref="JV1:JV46" numberStoredAsText="true"/>
+    <ignoredError sqref="JW1:JW46" numberStoredAsText="true"/>
+    <ignoredError sqref="JX1:JX46" numberStoredAsText="true"/>
+    <ignoredError sqref="JY1:JY46" numberStoredAsText="true"/>
+    <ignoredError sqref="JZ1:JZ46" numberStoredAsText="true"/>
+    <ignoredError sqref="KA1:KA46" numberStoredAsText="true"/>
+    <ignoredError sqref="KB1:KB46" numberStoredAsText="true"/>
+    <ignoredError sqref="KC1:KC46" numberStoredAsText="true"/>
+    <ignoredError sqref="KD1:KD46" numberStoredAsText="true"/>
+    <ignoredError sqref="KE1:KE46" numberStoredAsText="true"/>
+    <ignoredError sqref="KF1:KF46" numberStoredAsText="true"/>
+    <ignoredError sqref="KG1:KG46" numberStoredAsText="true"/>
+    <ignoredError sqref="KH1:KH46" numberStoredAsText="true"/>
+    <ignoredError sqref="KI1:KI46" numberStoredAsText="true"/>
+    <ignoredError sqref="KJ1:KJ46" numberStoredAsText="true"/>
+    <ignoredError sqref="KK1:KK46" numberStoredAsText="true"/>
+    <ignoredError sqref="KL1:KL46" numberStoredAsText="true"/>
+    <ignoredError sqref="KM1:KM46" numberStoredAsText="true"/>
+    <ignoredError sqref="KN1:KN46" numberStoredAsText="true"/>
+    <ignoredError sqref="KO1:KO46" numberStoredAsText="true"/>
+    <ignoredError sqref="KP1:KP46" numberStoredAsText="true"/>
+    <ignoredError sqref="KQ1:KQ46" numberStoredAsText="true"/>
+    <ignoredError sqref="KR1:KR46" numberStoredAsText="true"/>
+    <ignoredError sqref="KS1:KS46" numberStoredAsText="true"/>
   </ignoredErrors>
   <drawing r:id="rId1"/>
 </worksheet>

--- a/data.xlsx
+++ b/data.xlsx
@@ -9,7 +9,7 @@
     <sheet name="Sheet0" r:id="rId3" sheetId="1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="true">Sheet0!$A$2:$KS$47</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="true">Sheet0!$A$2:$KS$49</definedName>
   </definedNames>
 </workbook>
 </file>
@@ -66430,307 +66430,3057 @@
         </is>
       </c>
     </row>
+    <row r="47">
+      <c r="A47" s="1" t="n">
+        <v>46205.164247685185</v>
+      </c>
+      <c r="B47" s="1" t="n">
+        <v>46205.18255787037</v>
+      </c>
+      <c r="C47" s="2" t="inlineStr">
+        <is>
+          <t>IP Address</t>
+        </is>
+      </c>
+      <c r="D47" s="2" t="inlineStr">
+        <is>
+          <t>80.135.113.149</t>
+        </is>
+      </c>
+      <c r="E47" t="n">
+        <v>100.0</v>
+      </c>
+      <c r="F47" t="n">
+        <v>1582.0</v>
+      </c>
+      <c r="G47" s="2" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="H47" s="1" t="n">
+        <v>46205.18257430555</v>
+      </c>
+      <c r="I47" s="2" t="inlineStr">
+        <is>
+          <t>R_2dssgsqa4HHmfgN</t>
+        </is>
+      </c>
+      <c r="J47" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="K47" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="L47" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="M47" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="N47" t="n">
+        <v>48.1942</v>
+      </c>
+      <c r="O47" t="n">
+        <v>11.5159</v>
+      </c>
+      <c r="P47" s="2" t="inlineStr">
+        <is>
+          <t>anonymous</t>
+        </is>
+      </c>
+      <c r="Q47" s="2" t="inlineStr">
+        <is>
+          <t>EN</t>
+        </is>
+      </c>
+      <c r="R47" s="2" t="inlineStr">
+        <is>
+          <t>I understand the explanation provided to me. I was able to save a copy of this form. I reached out to the listed researchers and have had all my questions answered to my satisfaction. Therefore, I voluntarily agree to participate in this online study.,I voluntarily consent to my data being recorded and subsequently processed in line with the GDPR. I have been informed about the consequences of withdrawing my consent.</t>
+        </is>
+      </c>
+      <c r="S47" t="n">
+        <v>3.633</v>
+      </c>
+      <c r="T47" t="n">
+        <v>4.58</v>
+      </c>
+      <c r="U47" t="n">
+        <v>5.575</v>
+      </c>
+      <c r="V47" t="n">
+        <v>2.0</v>
+      </c>
+      <c r="W47" s="2" t="inlineStr">
+        <is>
+          <t>Yes, I am using a desktop or laptop computer.</t>
+        </is>
+      </c>
+      <c r="X47" s="2" t="inlineStr">
+        <is>
+          <t>Yes, I am wearing headphones.</t>
+        </is>
+      </c>
+      <c r="Y47" s="2" t="inlineStr">
+        <is>
+          <t>Right Channel</t>
+        </is>
+      </c>
+      <c r="Z47" t="n">
+        <v>1.397</v>
+      </c>
+      <c r="AA47" t="n">
+        <v>26.717</v>
+      </c>
+      <c r="AB47" t="n">
+        <v>29.723</v>
+      </c>
+      <c r="AC47" t="n">
+        <v>7.0</v>
+      </c>
+      <c r="AD47" t="n">
+        <v>35.0</v>
+      </c>
+      <c r="AE47" s="2" t="inlineStr">
+        <is>
+          <t>Female</t>
+        </is>
+      </c>
+      <c r="AF47" s="2" t="inlineStr">
+        <is>
+          <t>Korean</t>
+        </is>
+      </c>
+      <c r="AG47" s="2" t="inlineStr">
+        <is>
+          <t>Understand well</t>
+        </is>
+      </c>
+      <c r="AH47" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="AI47" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AJ47" s="2" t="inlineStr">
+        <is>
+          <t>No notification at all (Muted / Do Not Disturb)</t>
+        </is>
+      </c>
+      <c r="AK47" s="2" t="inlineStr">
+        <is>
+          <t>Social Etiquette: To avoid disturbing or annoying people around me.,Personal Focus: To avoid distracting myself or breaking my concentration.</t>
+        </is>
+      </c>
+      <c r="AL47" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AM47" s="2" t="inlineStr">
+        <is>
+          <t>Never</t>
+        </is>
+      </c>
+      <c r="AN47" s="2" t="inlineStr">
+        <is>
+          <t>Phone Calls</t>
+        </is>
+      </c>
+      <c r="AO47" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AP47" s="2" t="inlineStr">
+        <is>
+          <t>Neither agree nor disagree</t>
+        </is>
+      </c>
+      <c r="AQ47" s="2" t="inlineStr">
+        <is>
+          <t>Agree</t>
+        </is>
+      </c>
+      <c r="AR47" t="n">
+        <v>1.013</v>
+      </c>
+      <c r="AS47" t="n">
+        <v>57.961</v>
+      </c>
+      <c r="AT47" t="n">
+        <v>62.848</v>
+      </c>
+      <c r="AU47" t="n">
+        <v>27.0</v>
+      </c>
+      <c r="AV47" s="2" t="inlineStr">
+        <is>
+          <t>🗣️Version 2,🗣️🗣️ Version 3</t>
+        </is>
+      </c>
+      <c r="AW47" s="2" t="inlineStr">
+        <is>
+          <t>🗣️🗣️ Version 3</t>
+        </is>
+      </c>
+      <c r="AX47" s="2" t="inlineStr">
+        <is>
+          <t>To handle urgent matters quickly, I prefer to hear the notification, sender info, and the full message all at once</t>
+        </is>
+      </c>
+      <c r="AY47" s="2" t="inlineStr">
+        <is>
+          <t>Strongly agree</t>
+        </is>
+      </c>
+      <c r="AZ47" s="2" t="inlineStr">
+        <is>
+          <t>Strongly disagree</t>
+        </is>
+      </c>
+      <c r="BA47" s="2" t="inlineStr">
+        <is>
+          <t>I prefer control over when notifications speak</t>
+        </is>
+      </c>
+      <c r="BB47" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="BC47" s="2" t="inlineStr">
+        <is>
+          <t>Very short (1 sentence / headline only)</t>
+        </is>
+      </c>
+      <c r="BD47" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="BE47" s="2" t="inlineStr">
+        <is>
+          <t>Strongly agree</t>
+        </is>
+      </c>
+      <c r="BF47" t="n">
+        <v>13.87</v>
+      </c>
+      <c r="BG47" t="n">
+        <v>29.348</v>
+      </c>
+      <c r="BH47" t="n">
+        <v>30.199</v>
+      </c>
+      <c r="BI47" t="n">
+        <v>5.0</v>
+      </c>
+      <c r="BJ47" t="n">
+        <v>17.634</v>
+      </c>
+      <c r="BK47" t="n">
+        <v>19.288</v>
+      </c>
+      <c r="BL47" t="n">
+        <v>21.44</v>
+      </c>
+      <c r="BM47" t="n">
+        <v>2.0</v>
+      </c>
+      <c r="BN47" s="2" t="inlineStr">
+        <is>
+          <t>Completely appropriate</t>
+        </is>
+      </c>
+      <c r="BO47" s="2" t="inlineStr">
+        <is>
+          <t>Completely appropriate</t>
+        </is>
+      </c>
+      <c r="BP47" s="2" t="inlineStr">
+        <is>
+          <t>Completely appropriate</t>
+        </is>
+      </c>
+      <c r="BQ47" s="2" t="inlineStr">
+        <is>
+          <t>Very easy to detect</t>
+        </is>
+      </c>
+      <c r="BR47" s="2" t="inlineStr">
+        <is>
+          <t>Very easy to detect</t>
+        </is>
+      </c>
+      <c r="BS47" s="2" t="inlineStr">
+        <is>
+          <t>Very easy to detect</t>
+        </is>
+      </c>
+      <c r="BT47" s="2" t="inlineStr">
+        <is>
+          <t>Moderately disruptive</t>
+        </is>
+      </c>
+      <c r="BU47" s="2" t="inlineStr">
+        <is>
+          <t>Moderately disruptive</t>
+        </is>
+      </c>
+      <c r="BV47" s="2" t="inlineStr">
+        <is>
+          <t>Moderately disruptive</t>
+        </is>
+      </c>
+      <c r="BW47" s="2" t="inlineStr">
+        <is>
+          <t>Completely Acceptable</t>
+        </is>
+      </c>
+      <c r="BX47" s="2" t="inlineStr">
+        <is>
+          <t>Completely Acceptable</t>
+        </is>
+      </c>
+      <c r="BY47" s="2" t="inlineStr">
+        <is>
+          <t>Completely Acceptable</t>
+        </is>
+      </c>
+      <c r="BZ47" s="2" t="inlineStr">
+        <is>
+          <t>🗣️🗣️ Version 3</t>
+        </is>
+      </c>
+      <c r="CA47" s="2" t="inlineStr">
+        <is>
+          <t>Because I am alone at my desk, privacy is not an issue. Receiving the full text through my glasses gives me the exact context I need while letting me keep my full concentration on the complex code</t>
+        </is>
+      </c>
+      <c r="CB47" s="2" t="inlineStr">
+        <is>
+          <t>Acoustic Environment (e.g., the level of background noise, music, or other people talking),Focus &amp; Mental Effort (e.g., needing to concentrate on my current task without being interrupted),Social Appropriateness (e.g., the presence of others, social etiquette, or not wanting to appear distracted)</t>
+        </is>
+      </c>
+      <c r="CC47" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="CD47" s="2" t="inlineStr">
+        <is>
+          <t>Immediately</t>
+        </is>
+      </c>
+      <c r="CE47" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="CF47" s="2" t="inlineStr">
+        <is>
+          <t>Not applicable (I chose "Immediately" in the previous question).</t>
+        </is>
+      </c>
+      <c r="CG47" s="2" t="inlineStr">
+        <is>
+          <t>I chose to hear the notification instantly because delaying it would only make me curious and distract me from my work. Getting the full context immediately kept my mind clear</t>
+        </is>
+      </c>
+      <c r="CH47" t="n">
+        <v>7.975</v>
+      </c>
+      <c r="CI47" t="n">
+        <v>63.469</v>
+      </c>
+      <c r="CJ47" t="n">
+        <v>81.425</v>
+      </c>
+      <c r="CK47" t="n">
+        <v>32.0</v>
+      </c>
+      <c r="CL47" s="2" t="inlineStr">
+        <is>
+          <t>Inappropriate</t>
+        </is>
+      </c>
+      <c r="CM47" s="2" t="inlineStr">
+        <is>
+          <t>Completely inappropriate</t>
+        </is>
+      </c>
+      <c r="CN47" s="2" t="inlineStr">
+        <is>
+          <t>Completely inappropriate</t>
+        </is>
+      </c>
+      <c r="CO47" s="2" t="inlineStr">
+        <is>
+          <t>Neither easy nor difficult to detect</t>
+        </is>
+      </c>
+      <c r="CP47" s="2" t="inlineStr">
+        <is>
+          <t>Somewhat difficult to detect</t>
+        </is>
+      </c>
+      <c r="CQ47" s="2" t="inlineStr">
+        <is>
+          <t>Somewhat difficult to detect</t>
+        </is>
+      </c>
+      <c r="CR47" s="2" t="inlineStr">
+        <is>
+          <t>Extremely disruptive</t>
+        </is>
+      </c>
+      <c r="CS47" s="2" t="inlineStr">
+        <is>
+          <t>Extremely disruptive</t>
+        </is>
+      </c>
+      <c r="CT47" s="2" t="inlineStr">
+        <is>
+          <t>Extremely disruptive</t>
+        </is>
+      </c>
+      <c r="CU47" s="2" t="inlineStr">
+        <is>
+          <t>Completely unacceptable</t>
+        </is>
+      </c>
+      <c r="CV47" s="2" t="inlineStr">
+        <is>
+          <t>Completely unacceptable</t>
+        </is>
+      </c>
+      <c r="CW47" s="2" t="inlineStr">
+        <is>
+          <t>Completely unacceptable</t>
+        </is>
+      </c>
+      <c r="CX47" s="2" t="inlineStr">
+        <is>
+          <t>🔔 Version 1</t>
+        </is>
+      </c>
+      <c r="CY47" s="2" t="inlineStr">
+        <is>
+          <t>To maintain respect for my colleagues and keep up with the continuous flow of the meeting, I choose to wait until the session ends before checking any messages</t>
+        </is>
+      </c>
+      <c r="CZ47" s="2" t="inlineStr">
+        <is>
+          <t>Focus &amp; Mental Effort (e.g., needing to concentrate on my current task without being interrupted),Social Appropriateness (e.g., the presence of others, social etiquette, or not wanting to appear distracted)</t>
+        </is>
+      </c>
+      <c r="DA47" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="DB47" s="2" t="inlineStr">
+        <is>
+          <t>Later, when the meeting is over</t>
+        </is>
+      </c>
+      <c r="DC47" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="DD47" s="2" t="inlineStr">
+        <is>
+          <t>🗣️ Version 2</t>
+        </is>
+      </c>
+      <c r="DE47" s="2" t="inlineStr">
+        <is>
+          <t>I prefer delaying all notifications until the meeting is completely over, as even private alerts can break my concentration when I need to be fully engaged in the room</t>
+        </is>
+      </c>
+      <c r="DF47" t="n">
+        <v>9.104</v>
+      </c>
+      <c r="DG47" t="n">
+        <v>118.899</v>
+      </c>
+      <c r="DH47" t="n">
+        <v>120.013</v>
+      </c>
+      <c r="DI47" t="n">
+        <v>39.0</v>
+      </c>
+      <c r="DJ47" s="2" t="inlineStr">
+        <is>
+          <t>Completely appropriate</t>
+        </is>
+      </c>
+      <c r="DK47" s="2" t="inlineStr">
+        <is>
+          <t>Completely appropriate</t>
+        </is>
+      </c>
+      <c r="DL47" s="2" t="inlineStr">
+        <is>
+          <t>Completely appropriate</t>
+        </is>
+      </c>
+      <c r="DM47" s="2" t="inlineStr">
+        <is>
+          <t>Somewhat easy to detect</t>
+        </is>
+      </c>
+      <c r="DN47" s="2" t="inlineStr">
+        <is>
+          <t>Very easy to detect</t>
+        </is>
+      </c>
+      <c r="DO47" s="2" t="inlineStr">
+        <is>
+          <t>Very easy to detect</t>
+        </is>
+      </c>
+      <c r="DP47" s="2" t="inlineStr">
+        <is>
+          <t>Slightly disruptive</t>
+        </is>
+      </c>
+      <c r="DQ47" s="2" t="inlineStr">
+        <is>
+          <t>Moderately disruptive</t>
+        </is>
+      </c>
+      <c r="DR47" s="2" t="inlineStr">
+        <is>
+          <t>Moderately disruptive</t>
+        </is>
+      </c>
+      <c r="DS47" s="2" t="inlineStr">
+        <is>
+          <t>Completely Acceptable</t>
+        </is>
+      </c>
+      <c r="DT47" s="2" t="inlineStr">
+        <is>
+          <t>Completely Acceptable</t>
+        </is>
+      </c>
+      <c r="DU47" s="2" t="inlineStr">
+        <is>
+          <t>Completely Acceptable</t>
+        </is>
+      </c>
+      <c r="DV47" s="2" t="inlineStr">
+        <is>
+          <t>🗣️🗣️ Version 3</t>
+        </is>
+      </c>
+      <c r="DW47" s="2" t="inlineStr">
+        <is>
+          <t>When I'm listening to music at home alone, I prefer option 3 because I'm in a private space and want the convenience of knowing exactly who texted me and what they said without having to look at my phone</t>
+        </is>
+      </c>
+      <c r="DX47" s="2" t="inlineStr">
+        <is>
+          <t>Social Appropriateness (e.g., the presence of others, social etiquette, or not wanting to appear distracted)</t>
+        </is>
+      </c>
+      <c r="DY47" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="DZ47" s="2" t="inlineStr">
+        <is>
+          <t>Immediately</t>
+        </is>
+      </c>
+      <c r="EA47" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="EB47" s="2" t="inlineStr">
+        <is>
+          <t>🗣️🗣️ Version 3</t>
+        </is>
+      </c>
+      <c r="EC47" s="2" t="inlineStr">
+        <is>
+          <t>Because I was just chilling and listening to music by myself, I had the time to listen to the whole message, so I preferred option 3 for immediate and complete information</t>
+        </is>
+      </c>
+      <c r="ED47" t="n">
+        <v>0.381</v>
+      </c>
+      <c r="EE47" t="n">
+        <v>136.127</v>
+      </c>
+      <c r="EF47" t="n">
+        <v>137.218</v>
+      </c>
+      <c r="EG47" t="n">
+        <v>37.0</v>
+      </c>
+      <c r="EH47" s="2" t="inlineStr">
+        <is>
+          <t>Somewhat disagree</t>
+        </is>
+      </c>
+      <c r="EI47" t="n">
+        <v>1.525</v>
+      </c>
+      <c r="EJ47" t="n">
+        <v>3.428</v>
+      </c>
+      <c r="EK47" t="n">
+        <v>4.339</v>
+      </c>
+      <c r="EL47" t="n">
+        <v>2.0</v>
+      </c>
+      <c r="EM47" s="2" t="inlineStr">
+        <is>
+          <t>Neither appropriate nor inappropriate</t>
+        </is>
+      </c>
+      <c r="EN47" s="2" t="inlineStr">
+        <is>
+          <t>Neither appropriate nor inappropriate</t>
+        </is>
+      </c>
+      <c r="EO47" s="2" t="inlineStr">
+        <is>
+          <t>Neither appropriate nor inappropriate</t>
+        </is>
+      </c>
+      <c r="EP47" s="2" t="inlineStr">
+        <is>
+          <t>Easy to detect</t>
+        </is>
+      </c>
+      <c r="EQ47" s="2" t="inlineStr">
+        <is>
+          <t>Very easy to detect</t>
+        </is>
+      </c>
+      <c r="ER47" s="2" t="inlineStr">
+        <is>
+          <t>Very easy to detect</t>
+        </is>
+      </c>
+      <c r="ES47" s="2" t="inlineStr">
+        <is>
+          <t>Disruptive</t>
+        </is>
+      </c>
+      <c r="ET47" s="2" t="inlineStr">
+        <is>
+          <t>Disruptive</t>
+        </is>
+      </c>
+      <c r="EU47" s="2" t="inlineStr">
+        <is>
+          <t>Disruptive</t>
+        </is>
+      </c>
+      <c r="EV47" s="2" t="inlineStr">
+        <is>
+          <t>Neither acceptable nor unacceptable</t>
+        </is>
+      </c>
+      <c r="EW47" s="2" t="inlineStr">
+        <is>
+          <t>Neither acceptable nor unacceptable</t>
+        </is>
+      </c>
+      <c r="EX47" s="2" t="inlineStr">
+        <is>
+          <t>Neither acceptable nor unacceptable</t>
+        </is>
+      </c>
+      <c r="EY47" s="2" t="inlineStr">
+        <is>
+          <t>🗣️ Version 2</t>
+        </is>
+      </c>
+      <c r="EZ47" s="2" t="inlineStr">
+        <is>
+          <t>Since I was working with a group in a noisy outdoor setting, I preferred option 2 to quickly check who was calling or texting without losing track of the teamwork and safety around me</t>
+        </is>
+      </c>
+      <c r="FA47" s="2" t="inlineStr">
+        <is>
+          <t>Focus &amp; Mental Effort (e.g., needing to concentrate on my current task without being interrupted),Physical Safety &amp; Awareness (e.g., needing to pay visual or mental attention to my physical surroundings, like traffic)</t>
+        </is>
+      </c>
+      <c r="FB47" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="FC47" s="2" t="inlineStr">
+        <is>
+          <t>Later, when the whole tent is set up and we are done working</t>
+        </is>
+      </c>
+      <c r="FD47" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="FE47" s="2" t="inlineStr">
+        <is>
+          <t>🗣️🗣️ Version 3</t>
+        </is>
+      </c>
+      <c r="FF47" s="2" t="inlineStr">
+        <is>
+          <t>Once the tent was completely set up and I could finally relax, I preferred option 3 because I had the time to listen to the full message content without messing up the teamwork</t>
+        </is>
+      </c>
+      <c r="FG47" t="n">
+        <v>20.946</v>
+      </c>
+      <c r="FH47" t="n">
+        <v>129.672</v>
+      </c>
+      <c r="FI47" t="n">
+        <v>140.963</v>
+      </c>
+      <c r="FJ47" t="n">
+        <v>48.0</v>
+      </c>
+      <c r="FK47" s="2" t="inlineStr">
+        <is>
+          <t>Completely inappropriate</t>
+        </is>
+      </c>
+      <c r="FL47" s="2" t="inlineStr">
+        <is>
+          <t>Completely inappropriate</t>
+        </is>
+      </c>
+      <c r="FM47" s="2" t="inlineStr">
+        <is>
+          <t>Completely inappropriate</t>
+        </is>
+      </c>
+      <c r="FN47" s="2" t="inlineStr">
+        <is>
+          <t>Neither easy nor difficult to detect</t>
+        </is>
+      </c>
+      <c r="FO47" s="2" t="inlineStr">
+        <is>
+          <t>Very easy to detect</t>
+        </is>
+      </c>
+      <c r="FP47" s="2" t="inlineStr">
+        <is>
+          <t>Very easy to detect</t>
+        </is>
+      </c>
+      <c r="FQ47" s="2" t="inlineStr">
+        <is>
+          <t>Extremely disruptive</t>
+        </is>
+      </c>
+      <c r="FR47" s="2" t="inlineStr">
+        <is>
+          <t>Extremely disruptive</t>
+        </is>
+      </c>
+      <c r="FS47" s="2" t="inlineStr">
+        <is>
+          <t>Extremely disruptive</t>
+        </is>
+      </c>
+      <c r="FT47" s="2" t="inlineStr">
+        <is>
+          <t>Unacceptable</t>
+        </is>
+      </c>
+      <c r="FU47" s="2" t="inlineStr">
+        <is>
+          <t>Unacceptable</t>
+        </is>
+      </c>
+      <c r="FV47" s="2" t="inlineStr">
+        <is>
+          <t>Unacceptable</t>
+        </is>
+      </c>
+      <c r="FW47" s="2" t="inlineStr">
+        <is>
+          <t>🔔 Version 1</t>
+        </is>
+      </c>
+      <c r="FX47" s="2" t="inlineStr">
+        <is>
+          <t>I choose option 1 while cycling because I need to stay aware of my surroundings, like car horns or traffic sounds, without being distracted by a voice reading out a full message</t>
+        </is>
+      </c>
+      <c r="FY47" s="2" t="inlineStr">
+        <is>
+          <t>Physical Safety &amp; Awareness (e.g., needing to pay visual or mental attention to my physical surroundings, like traffic)</t>
+        </is>
+      </c>
+      <c r="FZ47" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="GA47" s="2" t="inlineStr">
+        <is>
+          <t>After I have finished cycling / reached my destination</t>
+        </is>
+      </c>
+      <c r="GB47" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="GC47" s="2" t="inlineStr">
+        <is>
+          <t>🗣️🗣️ Version 3</t>
+        </is>
+      </c>
+      <c r="GD47" s="2" t="inlineStr">
+        <is>
+          <t>Finally in a safe, stationary position where I could comfortably listen to the full message without any safety risks</t>
+        </is>
+      </c>
+      <c r="GE47" t="n">
+        <v>14.712</v>
+      </c>
+      <c r="GF47" t="n">
+        <v>130.681</v>
+      </c>
+      <c r="GG47" t="n">
+        <v>133.789</v>
+      </c>
+      <c r="GH47" t="n">
+        <v>42.0</v>
+      </c>
+      <c r="GI47" s="2" t="inlineStr">
+        <is>
+          <t>Appropriate</t>
+        </is>
+      </c>
+      <c r="GJ47" s="2" t="inlineStr">
+        <is>
+          <t>Appropriate</t>
+        </is>
+      </c>
+      <c r="GK47" s="2" t="inlineStr">
+        <is>
+          <t>Appropriate</t>
+        </is>
+      </c>
+      <c r="GL47" s="2" t="inlineStr">
+        <is>
+          <t>Easy to detect</t>
+        </is>
+      </c>
+      <c r="GM47" s="2" t="inlineStr">
+        <is>
+          <t>Easy to detect</t>
+        </is>
+      </c>
+      <c r="GN47" s="2" t="inlineStr">
+        <is>
+          <t>Easy to detect</t>
+        </is>
+      </c>
+      <c r="GO47" s="2" t="inlineStr">
+        <is>
+          <t>Moderately disruptive</t>
+        </is>
+      </c>
+      <c r="GP47" s="2" t="inlineStr">
+        <is>
+          <t>Moderately disruptive</t>
+        </is>
+      </c>
+      <c r="GQ47" s="2" t="inlineStr">
+        <is>
+          <t>Moderately disruptive</t>
+        </is>
+      </c>
+      <c r="GR47" s="2" t="inlineStr">
+        <is>
+          <t>Acceptable</t>
+        </is>
+      </c>
+      <c r="GS47" s="2" t="inlineStr">
+        <is>
+          <t>Acceptable</t>
+        </is>
+      </c>
+      <c r="GT47" s="2" t="inlineStr">
+        <is>
+          <t>Acceptable</t>
+        </is>
+      </c>
+      <c r="GU47" s="2" t="inlineStr">
+        <is>
+          <t>🔔 Version 1</t>
+        </is>
+      </c>
+      <c r="GV47" s="2" t="inlineStr">
+        <is>
+          <t>While shopping at the supermarket, I prefer option 1 for privacy reasons, as I don't want people in the crowded aisles to overhear my personal messages</t>
+        </is>
+      </c>
+      <c r="GW47" s="2" t="inlineStr">
+        <is>
+          <t>Social Appropriateness (e.g., the presence of others, social etiquette, or not wanting to appear distracted)</t>
+        </is>
+      </c>
+      <c r="GX47" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="GY47" s="2" t="inlineStr">
+        <is>
+          <t>Immediately</t>
+        </is>
+      </c>
+      <c r="GZ47" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="HA47" s="2" t="inlineStr">
+        <is>
+          <t>Not applicable (I chose "Immediately" in the previous question).</t>
+        </is>
+      </c>
+      <c r="HB47" s="2" t="inlineStr">
+        <is>
+          <t>Because I wasn't with anyone, I preferred option 3 for immediate notifications. I could catch up on all the details freely since I wasn't engaged in any social interaction at that moment</t>
+        </is>
+      </c>
+      <c r="HC47" t="n">
+        <v>17.62</v>
+      </c>
+      <c r="HD47" t="n">
+        <v>110.043</v>
+      </c>
+      <c r="HE47" t="n">
+        <v>111.017</v>
+      </c>
+      <c r="HF47" t="n">
+        <v>35.0</v>
+      </c>
+      <c r="HG47" s="2" t="inlineStr">
+        <is>
+          <t>Agree</t>
+        </is>
+      </c>
+      <c r="HH47" t="n">
+        <v>2.216</v>
+      </c>
+      <c r="HI47" t="n">
+        <v>5.808</v>
+      </c>
+      <c r="HJ47" t="n">
+        <v>6.145</v>
+      </c>
+      <c r="HK47" t="n">
+        <v>2.0</v>
+      </c>
+      <c r="HL47" s="2" t="inlineStr">
+        <is>
+          <t>Appropriate</t>
+        </is>
+      </c>
+      <c r="HM47" s="2" t="inlineStr">
+        <is>
+          <t>Appropriate</t>
+        </is>
+      </c>
+      <c r="HN47" s="2" t="inlineStr">
+        <is>
+          <t>Appropriate</t>
+        </is>
+      </c>
+      <c r="HO47" s="2" t="inlineStr">
+        <is>
+          <t>Easy to detect</t>
+        </is>
+      </c>
+      <c r="HP47" s="2" t="inlineStr">
+        <is>
+          <t>Very difficult to detect</t>
+        </is>
+      </c>
+      <c r="HQ47" s="2" t="inlineStr">
+        <is>
+          <t>Very difficult to detect</t>
+        </is>
+      </c>
+      <c r="HR47" s="2" t="inlineStr">
+        <is>
+          <t>Not disruptive at all</t>
+        </is>
+      </c>
+      <c r="HS47" s="2" t="inlineStr">
+        <is>
+          <t>Not disruptive at all</t>
+        </is>
+      </c>
+      <c r="HT47" s="2" t="inlineStr">
+        <is>
+          <t>Not disruptive at all</t>
+        </is>
+      </c>
+      <c r="HU47" s="2" t="inlineStr">
+        <is>
+          <t>Completely Acceptable</t>
+        </is>
+      </c>
+      <c r="HV47" s="2" t="inlineStr">
+        <is>
+          <t>Completely Acceptable</t>
+        </is>
+      </c>
+      <c r="HW47" s="2" t="inlineStr">
+        <is>
+          <t>Completely Acceptable</t>
+        </is>
+      </c>
+      <c r="HX47" s="2" t="inlineStr">
+        <is>
+          <t>🔔 Version 1</t>
+        </is>
+      </c>
+      <c r="HY47" s="2" t="inlineStr">
+        <is>
+          <t>I chose option 1 while playing a podcast because a simple alert tone stands out better against the spoken words, whereas a read-out message just gets buried in the audio</t>
+        </is>
+      </c>
+      <c r="HZ47" s="2" t="inlineStr">
+        <is>
+          <t>Acoustic Environment (e.g., the level of background noise, music, or other people talking)</t>
+        </is>
+      </c>
+      <c r="IA47" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="IB47" s="2" t="inlineStr">
+        <is>
+          <t>Immediately</t>
+        </is>
+      </c>
+      <c r="IC47" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="ID47" s="2" t="inlineStr">
+        <is>
+          <t>🔔 Version 1</t>
+        </is>
+      </c>
+      <c r="IE47" s="2" t="inlineStr">
+        <is>
+          <t>While listening to a podcast, I preferred option 1 because hearing the full message would overlap with the host's voice, making it confusing and hard to understand either one.</t>
+        </is>
+      </c>
+      <c r="IF47" t="n">
+        <v>15.69</v>
+      </c>
+      <c r="IG47" t="n">
+        <v>125.622</v>
+      </c>
+      <c r="IH47" t="n">
+        <v>126.478</v>
+      </c>
+      <c r="II47" t="n">
+        <v>32.0</v>
+      </c>
+      <c r="IJ47" s="2" t="inlineStr">
+        <is>
+          <t>Completely appropriate</t>
+        </is>
+      </c>
+      <c r="IK47" s="2" t="inlineStr">
+        <is>
+          <t>Neither appropriate nor inappropriate</t>
+        </is>
+      </c>
+      <c r="IL47" s="2" t="inlineStr">
+        <is>
+          <t>Somewhat inappropriate</t>
+        </is>
+      </c>
+      <c r="IM47" s="2" t="inlineStr">
+        <is>
+          <t>Somewhat easy to detect</t>
+        </is>
+      </c>
+      <c r="IN47" s="2" t="inlineStr">
+        <is>
+          <t>Very easy to detect</t>
+        </is>
+      </c>
+      <c r="IO47" s="2" t="inlineStr">
+        <is>
+          <t>Very easy to detect</t>
+        </is>
+      </c>
+      <c r="IP47" s="2" t="inlineStr">
+        <is>
+          <t>Slightly disruptive</t>
+        </is>
+      </c>
+      <c r="IQ47" s="2" t="inlineStr">
+        <is>
+          <t>Very disruptive</t>
+        </is>
+      </c>
+      <c r="IR47" s="2" t="inlineStr">
+        <is>
+          <t>Very disruptive</t>
+        </is>
+      </c>
+      <c r="IS47" s="2" t="inlineStr">
+        <is>
+          <t>Somewhat acceptable</t>
+        </is>
+      </c>
+      <c r="IT47" s="2" t="inlineStr">
+        <is>
+          <t>Somewhat unacceptable</t>
+        </is>
+      </c>
+      <c r="IU47" s="2" t="inlineStr">
+        <is>
+          <t>Somewhat unacceptable</t>
+        </is>
+      </c>
+      <c r="IV47" s="2" t="inlineStr">
+        <is>
+          <t>🔔 Version 1</t>
+        </is>
+      </c>
+      <c r="IW47" s="2" t="inlineStr">
+        <is>
+          <t>To avoid disturbing people around me in a quiet cafe, I prefer just a simple notification sound without reading out the details</t>
+        </is>
+      </c>
+      <c r="IX47" s="2" t="inlineStr">
+        <is>
+          <t>Social Appropriateness (e.g., the presence of others, social etiquette, or not wanting to appear distracted)</t>
+        </is>
+      </c>
+      <c r="IY47" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="IZ47" s="2" t="inlineStr">
+        <is>
+          <t>Later, when I am completely done studying</t>
+        </is>
+      </c>
+      <c r="JA47" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="JB47" s="2" t="inlineStr">
+        <is>
+          <t>🗣️🗣️ Version 3</t>
+        </is>
+      </c>
+      <c r="JC47" s="2" t="inlineStr">
+        <is>
+          <t>I prefer delaying version 3 until I’m completely done studying because I want to fully focus on my work first, and then catch up on all the missed details once I'm finally free</t>
+        </is>
+      </c>
+      <c r="JD47" t="n">
+        <v>3.431</v>
+      </c>
+      <c r="JE47" t="n">
+        <v>178.393</v>
+      </c>
+      <c r="JF47" t="n">
+        <v>180.152</v>
+      </c>
+      <c r="JG47" t="n">
+        <v>44.0</v>
+      </c>
+      <c r="JH47" s="2" t="inlineStr">
+        <is>
+          <t>Neither appropriate nor inappropriate</t>
+        </is>
+      </c>
+      <c r="JI47" s="2" t="inlineStr">
+        <is>
+          <t>Neither appropriate nor inappropriate</t>
+        </is>
+      </c>
+      <c r="JJ47" s="2" t="inlineStr">
+        <is>
+          <t>Neither appropriate nor inappropriate</t>
+        </is>
+      </c>
+      <c r="JK47" s="2" t="inlineStr">
+        <is>
+          <t>Very easy to detect</t>
+        </is>
+      </c>
+      <c r="JL47" s="2" t="inlineStr">
+        <is>
+          <t>Very easy to detect</t>
+        </is>
+      </c>
+      <c r="JM47" s="2" t="inlineStr">
+        <is>
+          <t>Very easy to detect</t>
+        </is>
+      </c>
+      <c r="JN47" s="2" t="inlineStr">
+        <is>
+          <t>Not disruptive at all</t>
+        </is>
+      </c>
+      <c r="JO47" s="2" t="inlineStr">
+        <is>
+          <t>Not disruptive at all</t>
+        </is>
+      </c>
+      <c r="JP47" s="2" t="inlineStr">
+        <is>
+          <t>Not disruptive at all</t>
+        </is>
+      </c>
+      <c r="JQ47" s="2" t="inlineStr">
+        <is>
+          <t>Somewhat acceptable</t>
+        </is>
+      </c>
+      <c r="JR47" s="2" t="inlineStr">
+        <is>
+          <t>Somewhat acceptable</t>
+        </is>
+      </c>
+      <c r="JS47" s="2" t="inlineStr">
+        <is>
+          <t>Somewhat acceptable</t>
+        </is>
+      </c>
+      <c r="JT47" s="2" t="inlineStr">
+        <is>
+          <t>🗣️ Version 2</t>
+        </is>
+      </c>
+      <c r="JU47" s="2" t="inlineStr">
+        <is>
+          <t>I preferred option 2 because knowing the sender was enough to tell me if it was urgent, allowing me to be polite and not get distracted by the full text</t>
+        </is>
+      </c>
+      <c r="JV47" s="2" t="inlineStr">
+        <is>
+          <t>Social Appropriateness (e.g., the presence of others, social etiquette, or not wanting to appear distracted)</t>
+        </is>
+      </c>
+      <c r="JW47" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="JX47" s="2" t="inlineStr">
+        <is>
+          <t>Later, after Jessica has left / our hangout is over</t>
+        </is>
+      </c>
+      <c r="JY47" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="JZ47" s="2" t="inlineStr">
+        <is>
+          <t>🗣️🗣️ Version 3</t>
+        </is>
+      </c>
+      <c r="KA47" s="2" t="inlineStr">
+        <is>
+          <t>After we finished talking, I preferred option 3 since I no longer had to worry about social etiquette or interrupting someone, allowing me to get the full information right away.</t>
+        </is>
+      </c>
+      <c r="KB47" t="n">
+        <v>1.289</v>
+      </c>
+      <c r="KC47" t="n">
+        <v>113.626</v>
+      </c>
+      <c r="KD47" t="n">
+        <v>133.367</v>
+      </c>
+      <c r="KE47" t="n">
+        <v>30.0</v>
+      </c>
+      <c r="KF47" s="2" t="inlineStr">
+        <is>
+          <t>Speech 'Version 2' (Sender) 🗣️</t>
+        </is>
+      </c>
+      <c r="KG47" s="2" t="inlineStr">
+        <is>
+          <t>Mute (Do not notify me auditorily at all) 🔕</t>
+        </is>
+      </c>
+      <c r="KH47" s="2" t="inlineStr">
+        <is>
+          <t>Mute (Do not notify me auditorily at all) 🔕</t>
+        </is>
+      </c>
+      <c r="KI47" s="2" t="inlineStr">
+        <is>
+          <t>Speech 'Version 2' (Sender) 🗣️</t>
+        </is>
+      </c>
+      <c r="KJ47" s="2" t="inlineStr">
+        <is>
+          <t>Moderate delay (Minutes): Can wait until I finish my current task (e.g., finishing an email or a conversation).</t>
+        </is>
+      </c>
+      <c r="KK47" s="2" t="inlineStr">
+        <is>
+          <t>Indefinite delay (Hours): Can be withheld entirely until I manually check my phone or ask the device.</t>
+        </is>
+      </c>
+      <c r="KL47" s="2" t="inlineStr">
+        <is>
+          <t>Indefinite delay (Hours): Can be withheld entirely until I manually check my phone or ask the device.</t>
+        </is>
+      </c>
+      <c r="KM47" s="2" t="inlineStr">
+        <is>
+          <t>Brief delay (Seconds): Can wait for a quick safe moment (e.g., until I finish crossing the street, silence).</t>
+        </is>
+      </c>
+      <c r="KN47" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="KO47" t="n">
+        <v>0.695</v>
+      </c>
+      <c r="KP47" t="n">
+        <v>54.646</v>
+      </c>
+      <c r="KQ47" t="n">
+        <v>55.821</v>
+      </c>
+      <c r="KR47" t="n">
+        <v>11.0</v>
+      </c>
+      <c r="KS47" s="2" t="inlineStr">
+        <is>
+          <t>1582</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="1" t="n">
+        <v>46205.46065972222</v>
+      </c>
+      <c r="B48" s="1" t="n">
+        <v>46205.53240740741</v>
+      </c>
+      <c r="C48" s="2" t="inlineStr">
+        <is>
+          <t>IP Address</t>
+        </is>
+      </c>
+      <c r="D48" s="2" t="inlineStr">
+        <is>
+          <t>138.246.3.121</t>
+        </is>
+      </c>
+      <c r="E48" t="n">
+        <v>100.0</v>
+      </c>
+      <c r="F48" t="n">
+        <v>6198.0</v>
+      </c>
+      <c r="G48" s="2" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="H48" s="1" t="n">
+        <v>46205.532423854165</v>
+      </c>
+      <c r="I48" s="2" t="inlineStr">
+        <is>
+          <t>R_40YDrxd2bce8vm3</t>
+        </is>
+      </c>
+      <c r="J48" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="K48" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="L48" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="M48" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="N48" t="n">
+        <v>48.1477</v>
+      </c>
+      <c r="O48" t="n">
+        <v>11.5695</v>
+      </c>
+      <c r="P48" s="2" t="inlineStr">
+        <is>
+          <t>anonymous</t>
+        </is>
+      </c>
+      <c r="Q48" s="2" t="inlineStr">
+        <is>
+          <t>EN</t>
+        </is>
+      </c>
+      <c r="R48" s="2" t="inlineStr">
+        <is>
+          <t>I understand the explanation provided to me. I was able to save a copy of this form. I reached out to the listed researchers and have had all my questions answered to my satisfaction. Therefore, I voluntarily agree to participate in this online study.,I voluntarily consent to my data being recorded and subsequently processed in line with the GDPR. I have been informed about the consequences of withdrawing my consent.</t>
+        </is>
+      </c>
+      <c r="S48" t="n">
+        <v>476.193</v>
+      </c>
+      <c r="T48" t="n">
+        <v>476.876</v>
+      </c>
+      <c r="U48" t="n">
+        <v>478.829</v>
+      </c>
+      <c r="V48" t="n">
+        <v>2.0</v>
+      </c>
+      <c r="W48" s="2" t="inlineStr">
+        <is>
+          <t>Yes, I am using a desktop or laptop computer.</t>
+        </is>
+      </c>
+      <c r="X48" s="2" t="inlineStr">
+        <is>
+          <t>Yes, I am wearing headphones.</t>
+        </is>
+      </c>
+      <c r="Y48" s="2" t="inlineStr">
+        <is>
+          <t>Right Channel</t>
+        </is>
+      </c>
+      <c r="Z48" t="n">
+        <v>28.635</v>
+      </c>
+      <c r="AA48" t="n">
+        <v>2841.979</v>
+      </c>
+      <c r="AB48" t="n">
+        <v>2845.354</v>
+      </c>
+      <c r="AC48" t="n">
+        <v>5.0</v>
+      </c>
+      <c r="AD48" t="n">
+        <v>23.0</v>
+      </c>
+      <c r="AE48" s="2" t="inlineStr">
+        <is>
+          <t>Female</t>
+        </is>
+      </c>
+      <c r="AF48" s="2" t="inlineStr">
+        <is>
+          <t>Chinese</t>
+        </is>
+      </c>
+      <c r="AG48" s="2" t="inlineStr">
+        <is>
+          <t>Understand very well</t>
+        </is>
+      </c>
+      <c r="AH48" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="AI48" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AJ48" s="2" t="inlineStr">
+        <is>
+          <t>Visual and Vibration (Screen lights up + phone vibrates)</t>
+        </is>
+      </c>
+      <c r="AK48" s="2" t="inlineStr">
+        <is>
+          <t>Awareness: To ensure I don't miss any messages (e.g., needing sound/vibration to notice them).,Habit: It's just my default setting / I never bothered to change it.</t>
+        </is>
+      </c>
+      <c r="AL48" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AM48" s="2" t="inlineStr">
+        <is>
+          <t>Tried once or twice</t>
+        </is>
+      </c>
+      <c r="AN48" s="2" t="inlineStr">
+        <is>
+          <t>Direct Instant Messages (e.g., WhatsApp, iMessage),Group Messages,Emails</t>
+        </is>
+      </c>
+      <c r="AO48" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AP48" s="2" t="inlineStr">
+        <is>
+          <t>Somewhat agree</t>
+        </is>
+      </c>
+      <c r="AQ48" s="2" t="inlineStr">
+        <is>
+          <t>Strongly agree</t>
+        </is>
+      </c>
+      <c r="AR48" t="n">
+        <v>1.265</v>
+      </c>
+      <c r="AS48" t="n">
+        <v>61.976</v>
+      </c>
+      <c r="AT48" t="n">
+        <v>63.624</v>
+      </c>
+      <c r="AU48" t="n">
+        <v>16.0</v>
+      </c>
+      <c r="AV48" s="2" t="inlineStr">
+        <is>
+          <t>🗣️Version 2,🗣️🗣️ Version 3</t>
+        </is>
+      </c>
+      <c r="AW48" s="2" t="inlineStr">
+        <is>
+          <t>🗣️🗣️ Version 3</t>
+        </is>
+      </c>
+      <c r="AX48" s="2" t="inlineStr">
+        <is>
+          <t>I can know what Lily wants to do and get the information immediately.</t>
+        </is>
+      </c>
+      <c r="AY48" s="2" t="inlineStr">
+        <is>
+          <t>Strongly agree</t>
+        </is>
+      </c>
+      <c r="AZ48" s="2" t="inlineStr">
+        <is>
+          <t>Strongly agree</t>
+        </is>
+      </c>
+      <c r="BA48" s="2" t="inlineStr">
+        <is>
+          <t>Speech is easier to understand,Reduces need to look at a device</t>
+        </is>
+      </c>
+      <c r="BB48" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="BC48" s="2" t="inlineStr">
+        <is>
+          <t>Very short (1 sentence / headline only),Short (2–3 sentences),It depends on the situation</t>
+        </is>
+      </c>
+      <c r="BD48" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="BE48" s="2" t="inlineStr">
+        <is>
+          <t>Strongly agree</t>
+        </is>
+      </c>
+      <c r="BF48" t="n">
+        <v>7.834</v>
+      </c>
+      <c r="BG48" t="n">
+        <v>31.571</v>
+      </c>
+      <c r="BH48" t="n">
+        <v>32.808</v>
+      </c>
+      <c r="BI48" t="n">
+        <v>6.0</v>
+      </c>
+      <c r="BJ48" t="n">
+        <v>25.519</v>
+      </c>
+      <c r="BK48" t="n">
+        <v>28.669</v>
+      </c>
+      <c r="BL48" t="n">
+        <v>29.928</v>
+      </c>
+      <c r="BM48" t="n">
+        <v>6.0</v>
+      </c>
+      <c r="BN48" s="2" t="inlineStr">
+        <is>
+          <t>Completely inappropriate</t>
+        </is>
+      </c>
+      <c r="BO48" s="2" t="inlineStr">
+        <is>
+          <t>Somewhat appropriate</t>
+        </is>
+      </c>
+      <c r="BP48" s="2" t="inlineStr">
+        <is>
+          <t>Appropriate</t>
+        </is>
+      </c>
+      <c r="BQ48" s="2" t="inlineStr">
+        <is>
+          <t>Difficult to detect</t>
+        </is>
+      </c>
+      <c r="BR48" s="2" t="inlineStr">
+        <is>
+          <t>Easy to detect</t>
+        </is>
+      </c>
+      <c r="BS48" s="2" t="inlineStr">
+        <is>
+          <t>Very easy to detect</t>
+        </is>
+      </c>
+      <c r="BT48" s="2" t="inlineStr">
+        <is>
+          <t>Slightly disruptive</t>
+        </is>
+      </c>
+      <c r="BU48" s="2" t="inlineStr">
+        <is>
+          <t>Moderately disruptive</t>
+        </is>
+      </c>
+      <c r="BV48" s="2" t="inlineStr">
+        <is>
+          <t>Very disruptive</t>
+        </is>
+      </c>
+      <c r="BW48" s="2" t="inlineStr">
+        <is>
+          <t>Acceptable</t>
+        </is>
+      </c>
+      <c r="BX48" s="2" t="inlineStr">
+        <is>
+          <t>Somewhat acceptable</t>
+        </is>
+      </c>
+      <c r="BY48" s="2" t="inlineStr">
+        <is>
+          <t>Acceptable</t>
+        </is>
+      </c>
+      <c r="BZ48" s="2" t="inlineStr">
+        <is>
+          <t>🗣️ Version 2</t>
+        </is>
+      </c>
+      <c r="CA48" s="2" t="inlineStr">
+        <is>
+          <t>It reminds me of checking the smartphone.</t>
+        </is>
+      </c>
+      <c r="CB48" s="2" t="inlineStr">
+        <is>
+          <t>Acoustic Environment (e.g., the level of background noise, music, or other people talking),Focus &amp; Mental Effort (e.g., needing to concentrate on my current task without being interrupted),Social Appropriateness (e.g., the presence of others, social etiquette, or not wanting to appear distracted)</t>
+        </is>
+      </c>
+      <c r="CC48" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="CD48" s="2" t="inlineStr">
+        <is>
+          <t>Immediately</t>
+        </is>
+      </c>
+      <c r="CE48" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="CF48" s="2" t="inlineStr">
+        <is>
+          <t>🗣️🗣️ Version 3</t>
+        </is>
+      </c>
+      <c r="CG48" s="2" t="inlineStr">
+        <is>
+          <t>What if there is an emergency.</t>
+        </is>
+      </c>
+      <c r="CH48" t="n">
+        <v>33.377</v>
+      </c>
+      <c r="CI48" t="n">
+        <v>137.903</v>
+      </c>
+      <c r="CJ48" t="n">
+        <v>161.481</v>
+      </c>
+      <c r="CK48" t="n">
+        <v>26.0</v>
+      </c>
+      <c r="CL48" s="2" t="inlineStr">
+        <is>
+          <t>Completely appropriate</t>
+        </is>
+      </c>
+      <c r="CM48" s="2" t="inlineStr">
+        <is>
+          <t>Somewhat inappropriate</t>
+        </is>
+      </c>
+      <c r="CN48" s="2" t="inlineStr">
+        <is>
+          <t>Inappropriate</t>
+        </is>
+      </c>
+      <c r="CO48" s="2" t="inlineStr">
+        <is>
+          <t>Very easy to detect</t>
+        </is>
+      </c>
+      <c r="CP48" s="2" t="inlineStr">
+        <is>
+          <t>Very easy to detect</t>
+        </is>
+      </c>
+      <c r="CQ48" s="2" t="inlineStr">
+        <is>
+          <t>Very easy to detect</t>
+        </is>
+      </c>
+      <c r="CR48" s="2" t="inlineStr">
+        <is>
+          <t>Not disruptive at all</t>
+        </is>
+      </c>
+      <c r="CS48" s="2" t="inlineStr">
+        <is>
+          <t>Disruptive</t>
+        </is>
+      </c>
+      <c r="CT48" s="2" t="inlineStr">
+        <is>
+          <t>Extremely disruptive</t>
+        </is>
+      </c>
+      <c r="CU48" s="2" t="inlineStr">
+        <is>
+          <t>Completely Acceptable</t>
+        </is>
+      </c>
+      <c r="CV48" s="2" t="inlineStr">
+        <is>
+          <t>Somewhat unacceptable</t>
+        </is>
+      </c>
+      <c r="CW48" s="2" t="inlineStr">
+        <is>
+          <t>Unacceptable</t>
+        </is>
+      </c>
+      <c r="CX48" s="2" t="inlineStr">
+        <is>
+          <t>🔔 Version 1</t>
+        </is>
+      </c>
+      <c r="CY48" s="2" t="inlineStr">
+        <is>
+          <t>It can remind me of the new message while not disturbing the discussion.</t>
+        </is>
+      </c>
+      <c r="CZ48" s="2" t="inlineStr">
+        <is>
+          <t>Acoustic Environment (e.g., the level of background noise, music, or other people talking),Social Appropriateness (e.g., the presence of others, social etiquette, or not wanting to appear distracted)</t>
+        </is>
+      </c>
+      <c r="DA48" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="DB48" s="2" t="inlineStr">
+        <is>
+          <t>Immediately</t>
+        </is>
+      </c>
+      <c r="DC48" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="DD48" s="2" t="inlineStr">
+        <is>
+          <t>Not applicable (I chose "Immediately" in the previous question).</t>
+        </is>
+      </c>
+      <c r="DE48" s="2" t="inlineStr">
+        <is>
+          <t>I can decide whether listen to the speakers or check my phone.</t>
+        </is>
+      </c>
+      <c r="DF48" t="n">
+        <v>32.762</v>
+      </c>
+      <c r="DG48" t="n">
+        <v>125.837</v>
+      </c>
+      <c r="DH48" t="n">
+        <v>163.053</v>
+      </c>
+      <c r="DI48" t="n">
+        <v>22.0</v>
+      </c>
+      <c r="DJ48" s="2" t="inlineStr">
+        <is>
+          <t>Completely inappropriate</t>
+        </is>
+      </c>
+      <c r="DK48" s="2" t="inlineStr">
+        <is>
+          <t>Appropriate</t>
+        </is>
+      </c>
+      <c r="DL48" s="2" t="inlineStr">
+        <is>
+          <t>Completely appropriate</t>
+        </is>
+      </c>
+      <c r="DM48" s="2" t="inlineStr">
+        <is>
+          <t>Very difficult to detect</t>
+        </is>
+      </c>
+      <c r="DN48" s="2" t="inlineStr">
+        <is>
+          <t>Easy to detect</t>
+        </is>
+      </c>
+      <c r="DO48" s="2" t="inlineStr">
+        <is>
+          <t>Very easy to detect</t>
+        </is>
+      </c>
+      <c r="DP48" s="2" t="inlineStr">
+        <is>
+          <t>Not disruptive at all</t>
+        </is>
+      </c>
+      <c r="DQ48" s="2" t="inlineStr">
+        <is>
+          <t>Disruptive</t>
+        </is>
+      </c>
+      <c r="DR48" s="2" t="inlineStr">
+        <is>
+          <t>Very disruptive</t>
+        </is>
+      </c>
+      <c r="DS48" s="2" t="inlineStr">
+        <is>
+          <t>Unacceptable</t>
+        </is>
+      </c>
+      <c r="DT48" s="2" t="inlineStr">
+        <is>
+          <t>Acceptable</t>
+        </is>
+      </c>
+      <c r="DU48" s="2" t="inlineStr">
+        <is>
+          <t>Completely Acceptable</t>
+        </is>
+      </c>
+      <c r="DV48" s="2" t="inlineStr">
+        <is>
+          <t>🗣️🗣️ Version 3</t>
+        </is>
+      </c>
+      <c r="DW48" s="2" t="inlineStr">
+        <is>
+          <t>Because  the music is too loud I can hear the message only in this way.</t>
+        </is>
+      </c>
+      <c r="DX48" s="2" t="inlineStr">
+        <is>
+          <t>Acoustic Environment (e.g., the level of background noise, music, or other people talking),Focus &amp; Mental Effort (e.g., needing to concentrate on my current task without being interrupted)</t>
+        </is>
+      </c>
+      <c r="DY48" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="DZ48" s="2" t="inlineStr">
+        <is>
+          <t>Immediately</t>
+        </is>
+      </c>
+      <c r="EA48" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="EB48" s="2" t="inlineStr">
+        <is>
+          <t>Not applicable (I chose "Immediately" in the previous question).</t>
+        </is>
+      </c>
+      <c r="EC48" s="2" t="inlineStr">
+        <is>
+          <t>I am not working or doing something important so I can receive the message at first time.</t>
+        </is>
+      </c>
+      <c r="ED48" t="n">
+        <v>387.868</v>
+      </c>
+      <c r="EE48" t="n">
+        <v>532.521</v>
+      </c>
+      <c r="EF48" t="n">
+        <v>532.895</v>
+      </c>
+      <c r="EG48" t="n">
+        <v>25.0</v>
+      </c>
+      <c r="EH48" s="2" t="inlineStr">
+        <is>
+          <t>Somewhat disagree</t>
+        </is>
+      </c>
+      <c r="EI48" t="n">
+        <v>12.005</v>
+      </c>
+      <c r="EJ48" t="n">
+        <v>14.908</v>
+      </c>
+      <c r="EK48" t="n">
+        <v>16.799</v>
+      </c>
+      <c r="EL48" t="n">
+        <v>2.0</v>
+      </c>
+      <c r="EM48" s="2" t="inlineStr">
+        <is>
+          <t>Neither appropriate nor inappropriate</t>
+        </is>
+      </c>
+      <c r="EN48" s="2" t="inlineStr">
+        <is>
+          <t>Somewhat appropriate</t>
+        </is>
+      </c>
+      <c r="EO48" s="2" t="inlineStr">
+        <is>
+          <t>Neither appropriate nor inappropriate</t>
+        </is>
+      </c>
+      <c r="EP48" s="2" t="inlineStr">
+        <is>
+          <t>Somewhat easy to detect</t>
+        </is>
+      </c>
+      <c r="EQ48" s="2" t="inlineStr">
+        <is>
+          <t>Easy to detect</t>
+        </is>
+      </c>
+      <c r="ER48" s="2" t="inlineStr">
+        <is>
+          <t>Very easy to detect</t>
+        </is>
+      </c>
+      <c r="ES48" s="2" t="inlineStr">
+        <is>
+          <t>Somewhat disruptive</t>
+        </is>
+      </c>
+      <c r="ET48" s="2" t="inlineStr">
+        <is>
+          <t>Moderately disruptive</t>
+        </is>
+      </c>
+      <c r="EU48" s="2" t="inlineStr">
+        <is>
+          <t>Very disruptive</t>
+        </is>
+      </c>
+      <c r="EV48" s="2" t="inlineStr">
+        <is>
+          <t>Somewhat acceptable</t>
+        </is>
+      </c>
+      <c r="EW48" s="2" t="inlineStr">
+        <is>
+          <t>Acceptable</t>
+        </is>
+      </c>
+      <c r="EX48" s="2" t="inlineStr">
+        <is>
+          <t>Somewhat acceptable</t>
+        </is>
+      </c>
+      <c r="EY48" s="2" t="inlineStr">
+        <is>
+          <t>🗣️ Version 2</t>
+        </is>
+      </c>
+      <c r="EZ48" s="2" t="inlineStr">
+        <is>
+          <t>I can hear the new message.</t>
+        </is>
+      </c>
+      <c r="FA48" s="2" t="inlineStr">
+        <is>
+          <t>Acoustic Environment (e.g., the level of background noise, music, or other people talking),Focus &amp; Mental Effort (e.g., needing to concentrate on my current task without being interrupted),Social Appropriateness (e.g., the presence of others, social etiquette, or not wanting to appear distracted)</t>
+        </is>
+      </c>
+      <c r="FB48" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="FC48" s="2" t="inlineStr">
+        <is>
+          <t>When there is a brief pause in the physical setup (e.g., stopping to look at instructions or taking a breath)</t>
+        </is>
+      </c>
+      <c r="FD48" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="FE48" s="2" t="inlineStr">
+        <is>
+          <t>🗣️ Version 2</t>
+        </is>
+      </c>
+      <c r="FF48" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">I can check it during the short break. </t>
+        </is>
+      </c>
+      <c r="FG48" t="n">
+        <v>71.188</v>
+      </c>
+      <c r="FH48" t="n">
+        <v>122.237</v>
+      </c>
+      <c r="FI48" t="n">
+        <v>144.178</v>
+      </c>
+      <c r="FJ48" t="n">
+        <v>23.0</v>
+      </c>
+      <c r="FK48" s="2" t="inlineStr">
+        <is>
+          <t>Somewhat inappropriate</t>
+        </is>
+      </c>
+      <c r="FL48" s="2" t="inlineStr">
+        <is>
+          <t>Somewhat appropriate</t>
+        </is>
+      </c>
+      <c r="FM48" s="2" t="inlineStr">
+        <is>
+          <t>Completely appropriate</t>
+        </is>
+      </c>
+      <c r="FN48" s="2" t="inlineStr">
+        <is>
+          <t>Somewhat difficult to detect</t>
+        </is>
+      </c>
+      <c r="FO48" s="2" t="inlineStr">
+        <is>
+          <t>Somewhat easy to detect</t>
+        </is>
+      </c>
+      <c r="FP48" s="2" t="inlineStr">
+        <is>
+          <t>Very easy to detect</t>
+        </is>
+      </c>
+      <c r="FQ48" s="2" t="inlineStr">
+        <is>
+          <t>Not disruptive at all</t>
+        </is>
+      </c>
+      <c r="FR48" s="2" t="inlineStr">
+        <is>
+          <t>Slightly disruptive</t>
+        </is>
+      </c>
+      <c r="FS48" s="2" t="inlineStr">
+        <is>
+          <t>Moderately disruptive</t>
+        </is>
+      </c>
+      <c r="FT48" s="2" t="inlineStr">
+        <is>
+          <t>Neither acceptable nor unacceptable</t>
+        </is>
+      </c>
+      <c r="FU48" s="2" t="inlineStr">
+        <is>
+          <t>Somewhat acceptable</t>
+        </is>
+      </c>
+      <c r="FV48" s="2" t="inlineStr">
+        <is>
+          <t>Completely Acceptable</t>
+        </is>
+      </c>
+      <c r="FW48" s="2" t="inlineStr">
+        <is>
+          <t>🗣️🗣️ Version 3</t>
+        </is>
+      </c>
+      <c r="FX48" s="2" t="inlineStr">
+        <is>
+          <t>While I am riding, directly message can help me get  the information.</t>
+        </is>
+      </c>
+      <c r="FY48" s="2" t="inlineStr">
+        <is>
+          <t>Acoustic Environment (e.g., the level of background noise, music, or other people talking),Social Appropriateness (e.g., the presence of others, social etiquette, or not wanting to appear distracted),Physical Safety &amp; Awareness (e.g., needing to pay visual or mental attention to my physical surroundings, like traffic)</t>
+        </is>
+      </c>
+      <c r="FZ48" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="GA48" s="2" t="inlineStr">
+        <is>
+          <t>After I reach a safe stopping point (e.g., at a traffic light)</t>
+        </is>
+      </c>
+      <c r="GB48" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="GC48" s="2" t="inlineStr">
+        <is>
+          <t>🗣️🗣️ Version 3</t>
+        </is>
+      </c>
+      <c r="GD48" s="2" t="inlineStr">
+        <is>
+          <t>It is beneficial for my safety.</t>
+        </is>
+      </c>
+      <c r="GE48" t="n">
+        <v>86.827</v>
+      </c>
+      <c r="GF48" t="n">
+        <v>224.566</v>
+      </c>
+      <c r="GG48" t="n">
+        <v>262.059</v>
+      </c>
+      <c r="GH48" t="n">
+        <v>24.0</v>
+      </c>
+      <c r="GI48" s="2" t="inlineStr">
+        <is>
+          <t>Somewhat inappropriate</t>
+        </is>
+      </c>
+      <c r="GJ48" s="2" t="inlineStr">
+        <is>
+          <t>Somewhat appropriate</t>
+        </is>
+      </c>
+      <c r="GK48" s="2" t="inlineStr">
+        <is>
+          <t>Completely appropriate</t>
+        </is>
+      </c>
+      <c r="GL48" s="2" t="inlineStr">
+        <is>
+          <t>Somewhat difficult to detect</t>
+        </is>
+      </c>
+      <c r="GM48" s="2" t="inlineStr">
+        <is>
+          <t>Easy to detect</t>
+        </is>
+      </c>
+      <c r="GN48" s="2" t="inlineStr">
+        <is>
+          <t>Very easy to detect</t>
+        </is>
+      </c>
+      <c r="GO48" s="2" t="inlineStr">
+        <is>
+          <t>Not disruptive at all</t>
+        </is>
+      </c>
+      <c r="GP48" s="2" t="inlineStr">
+        <is>
+          <t>Moderately disruptive</t>
+        </is>
+      </c>
+      <c r="GQ48" s="2" t="inlineStr">
+        <is>
+          <t>Moderately disruptive</t>
+        </is>
+      </c>
+      <c r="GR48" s="2" t="inlineStr">
+        <is>
+          <t>Somewhat acceptable</t>
+        </is>
+      </c>
+      <c r="GS48" s="2" t="inlineStr">
+        <is>
+          <t>Acceptable</t>
+        </is>
+      </c>
+      <c r="GT48" s="2" t="inlineStr">
+        <is>
+          <t>Neither acceptable nor unacceptable</t>
+        </is>
+      </c>
+      <c r="GU48" s="2" t="inlineStr">
+        <is>
+          <t>🗣️ Version 2</t>
+        </is>
+      </c>
+      <c r="GV48" s="2" t="inlineStr">
+        <is>
+          <t>Make sure I receive the new message.</t>
+        </is>
+      </c>
+      <c r="GW48" s="2" t="inlineStr">
+        <is>
+          <t>Acoustic Environment (e.g., the level of background noise, music, or other people talking),Social Appropriateness (e.g., the presence of others, social etiquette, or not wanting to appear distracted),Physical Safety &amp; Awareness (e.g., needing to pay visual or mental attention to my physical surroundings, like traffic),Desire for Information (e.g., wanting to know the exact sender or content immediately without having to use my hands/phone)</t>
+        </is>
+      </c>
+      <c r="GX48" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="GY48" s="2" t="inlineStr">
+        <is>
+          <t>Immediately</t>
+        </is>
+      </c>
+      <c r="GZ48" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="HA48" s="2" t="inlineStr">
+        <is>
+          <t>🗣️ Version 2</t>
+        </is>
+      </c>
+      <c r="HB48" s="2" t="inlineStr">
+        <is>
+          <t>Make sure i do receive the new message.</t>
+        </is>
+      </c>
+      <c r="HC48" t="n">
+        <v>46.54</v>
+      </c>
+      <c r="HD48" t="n">
+        <v>194.909</v>
+      </c>
+      <c r="HE48" t="n">
+        <v>227.693</v>
+      </c>
+      <c r="HF48" t="n">
+        <v>23.0</v>
+      </c>
+      <c r="HG48" s="2" t="inlineStr">
+        <is>
+          <t>Agree</t>
+        </is>
+      </c>
+      <c r="HH48" t="n">
+        <v>2.769</v>
+      </c>
+      <c r="HI48" t="n">
+        <v>2.769</v>
+      </c>
+      <c r="HJ48" t="n">
+        <v>3.486</v>
+      </c>
+      <c r="HK48" t="n">
+        <v>1.0</v>
+      </c>
+      <c r="HL48" s="2" t="inlineStr">
+        <is>
+          <t>Somewhat appropriate</t>
+        </is>
+      </c>
+      <c r="HM48" s="2" t="inlineStr">
+        <is>
+          <t>Appropriate</t>
+        </is>
+      </c>
+      <c r="HN48" s="2" t="inlineStr">
+        <is>
+          <t>Completely appropriate</t>
+        </is>
+      </c>
+      <c r="HO48" s="2" t="inlineStr">
+        <is>
+          <t>Neither easy nor difficult to detect</t>
+        </is>
+      </c>
+      <c r="HP48" s="2" t="inlineStr">
+        <is>
+          <t>Somewhat easy to detect</t>
+        </is>
+      </c>
+      <c r="HQ48" s="2" t="inlineStr">
+        <is>
+          <t>Very easy to detect</t>
+        </is>
+      </c>
+      <c r="HR48" s="2" t="inlineStr">
+        <is>
+          <t>Not disruptive at all</t>
+        </is>
+      </c>
+      <c r="HS48" s="2" t="inlineStr">
+        <is>
+          <t>Somewhat disruptive</t>
+        </is>
+      </c>
+      <c r="HT48" s="2" t="inlineStr">
+        <is>
+          <t>Moderately disruptive</t>
+        </is>
+      </c>
+      <c r="HU48" s="2" t="inlineStr">
+        <is>
+          <t>Acceptable</t>
+        </is>
+      </c>
+      <c r="HV48" s="2" t="inlineStr">
+        <is>
+          <t>Acceptable</t>
+        </is>
+      </c>
+      <c r="HW48" s="2" t="inlineStr">
+        <is>
+          <t>Completely Acceptable</t>
+        </is>
+      </c>
+      <c r="HX48" s="2" t="inlineStr">
+        <is>
+          <t>🗣️🗣️ Version 3</t>
+        </is>
+      </c>
+      <c r="HY48" s="2" t="inlineStr">
+        <is>
+          <t>I do not need to check the phone.</t>
+        </is>
+      </c>
+      <c r="HZ48" s="2" t="inlineStr">
+        <is>
+          <t>Acoustic Environment (e.g., the level of background noise, music, or other people talking),Social Appropriateness (e.g., the presence of others, social etiquette, or not wanting to appear distracted),Physical Safety &amp; Awareness (e.g., needing to pay visual or mental attention to my physical surroundings, like traffic)</t>
+        </is>
+      </c>
+      <c r="IA48" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="IB48" s="2" t="inlineStr">
+        <is>
+          <t>Immediately</t>
+        </is>
+      </c>
+      <c r="IC48" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="ID48" s="2" t="inlineStr">
+        <is>
+          <t>🗣️🗣️ Version 3</t>
+        </is>
+      </c>
+      <c r="IE48" s="2" t="inlineStr">
+        <is>
+          <t>i am cooking so i do not have time to check the phone.</t>
+        </is>
+      </c>
+      <c r="IF48" t="n">
+        <v>49.274</v>
+      </c>
+      <c r="IG48" t="n">
+        <v>106.323</v>
+      </c>
+      <c r="IH48" t="n">
+        <v>125.416</v>
+      </c>
+      <c r="II48" t="n">
+        <v>22.0</v>
+      </c>
+      <c r="IJ48" s="2" t="inlineStr">
+        <is>
+          <t>Somewhat appropriate</t>
+        </is>
+      </c>
+      <c r="IK48" s="2" t="inlineStr">
+        <is>
+          <t>Appropriate</t>
+        </is>
+      </c>
+      <c r="IL48" s="2" t="inlineStr">
+        <is>
+          <t>Somewhat inappropriate</t>
+        </is>
+      </c>
+      <c r="IM48" s="2" t="inlineStr">
+        <is>
+          <t>Neither easy nor difficult to detect</t>
+        </is>
+      </c>
+      <c r="IN48" s="2" t="inlineStr">
+        <is>
+          <t>Somewhat easy to detect</t>
+        </is>
+      </c>
+      <c r="IO48" s="2" t="inlineStr">
+        <is>
+          <t>Easy to detect</t>
+        </is>
+      </c>
+      <c r="IP48" s="2" t="inlineStr">
+        <is>
+          <t>Slightly disruptive</t>
+        </is>
+      </c>
+      <c r="IQ48" s="2" t="inlineStr">
+        <is>
+          <t>Somewhat disruptive</t>
+        </is>
+      </c>
+      <c r="IR48" s="2" t="inlineStr">
+        <is>
+          <t>Disruptive</t>
+        </is>
+      </c>
+      <c r="IS48" s="2" t="inlineStr">
+        <is>
+          <t>Acceptable</t>
+        </is>
+      </c>
+      <c r="IT48" s="2" t="inlineStr">
+        <is>
+          <t>Acceptable</t>
+        </is>
+      </c>
+      <c r="IU48" s="2" t="inlineStr">
+        <is>
+          <t>Somewhat acceptable</t>
+        </is>
+      </c>
+      <c r="IV48" s="2" t="inlineStr">
+        <is>
+          <t>🗣️ Version 2</t>
+        </is>
+      </c>
+      <c r="IW48" s="2" t="inlineStr">
+        <is>
+          <t>I can know who send the message and decide whether check it or not.</t>
+        </is>
+      </c>
+      <c r="IX48" s="2" t="inlineStr">
+        <is>
+          <t>Acoustic Environment (e.g., the level of background noise, music, or other people talking),Focus &amp; Mental Effort (e.g., needing to concentrate on my current task without being interrupted),Social Appropriateness (e.g., the presence of others, social etiquette, or not wanting to appear distracted)</t>
+        </is>
+      </c>
+      <c r="IY48" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="IZ48" s="2" t="inlineStr">
+        <is>
+          <t>When I briefly pause my studying/reading to take a sip of coffee or look up</t>
+        </is>
+      </c>
+      <c r="JA48" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="JB48" s="2" t="inlineStr">
+        <is>
+          <t>🗣️ Version 2</t>
+        </is>
+      </c>
+      <c r="JC48" s="2" t="inlineStr">
+        <is>
+          <t>I finished my task so I can check the exact message through the phone.</t>
+        </is>
+      </c>
+      <c r="JD48" t="n">
+        <v>27.167</v>
+      </c>
+      <c r="JE48" t="n">
+        <v>133.817</v>
+      </c>
+      <c r="JF48" t="n">
+        <v>173.228</v>
+      </c>
+      <c r="JG48" t="n">
+        <v>25.0</v>
+      </c>
+      <c r="JH48" s="2" t="inlineStr">
+        <is>
+          <t>Completely appropriate</t>
+        </is>
+      </c>
+      <c r="JI48" s="2" t="inlineStr">
+        <is>
+          <t>Somewhat inappropriate</t>
+        </is>
+      </c>
+      <c r="JJ48" s="2" t="inlineStr">
+        <is>
+          <t>Completely inappropriate</t>
+        </is>
+      </c>
+      <c r="JK48" s="2" t="inlineStr">
+        <is>
+          <t>Very easy to detect</t>
+        </is>
+      </c>
+      <c r="JL48" s="2" t="inlineStr">
+        <is>
+          <t>Very easy to detect</t>
+        </is>
+      </c>
+      <c r="JM48" s="2" t="inlineStr">
+        <is>
+          <t>Very easy to detect</t>
+        </is>
+      </c>
+      <c r="JN48" s="2" t="inlineStr">
+        <is>
+          <t>Moderately disruptive</t>
+        </is>
+      </c>
+      <c r="JO48" s="2" t="inlineStr">
+        <is>
+          <t>Very disruptive</t>
+        </is>
+      </c>
+      <c r="JP48" s="2" t="inlineStr">
+        <is>
+          <t>Extremely disruptive</t>
+        </is>
+      </c>
+      <c r="JQ48" s="2" t="inlineStr">
+        <is>
+          <t>Completely Acceptable</t>
+        </is>
+      </c>
+      <c r="JR48" s="2" t="inlineStr">
+        <is>
+          <t>Somewhat unacceptable</t>
+        </is>
+      </c>
+      <c r="JS48" s="2" t="inlineStr">
+        <is>
+          <t>Unacceptable</t>
+        </is>
+      </c>
+      <c r="JT48" s="2" t="inlineStr">
+        <is>
+          <t>🔔 Version 1</t>
+        </is>
+      </c>
+      <c r="JU48" s="2" t="inlineStr">
+        <is>
+          <t>I can hear the voice clearly.</t>
+        </is>
+      </c>
+      <c r="JV48" s="2" t="inlineStr">
+        <is>
+          <t>Acoustic Environment (e.g., the level of background noise, music, or other people talking),Focus &amp; Mental Effort (e.g., needing to concentrate on my current task without being interrupted),Social Appropriateness (e.g., the presence of others, social etiquette, or not wanting to appear distracted),Desire for Information (e.g., wanting to know the exact sender or content immediately without having to use my hands/phone)</t>
+        </is>
+      </c>
+      <c r="JW48" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="JX48" s="2" t="inlineStr">
+        <is>
+          <t>Immediately</t>
+        </is>
+      </c>
+      <c r="JY48" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="JZ48" s="2" t="inlineStr">
+        <is>
+          <t>Not applicable (I chose "Immediately" in the previous question).</t>
+        </is>
+      </c>
+      <c r="KA48" s="2" t="inlineStr">
+        <is>
+          <t>I can hear the remind voice of the message and decide whether to check it.</t>
+        </is>
+      </c>
+      <c r="KB48" t="n">
+        <v>16.409</v>
+      </c>
+      <c r="KC48" t="n">
+        <v>92.175</v>
+      </c>
+      <c r="KD48" t="n">
+        <v>127.172</v>
+      </c>
+      <c r="KE48" t="n">
+        <v>23.0</v>
+      </c>
+      <c r="KF48" s="2" t="inlineStr">
+        <is>
+          <t>Mute (Do not notify me auditorily at all) 🔕</t>
+        </is>
+      </c>
+      <c r="KG48" s="2" t="inlineStr">
+        <is>
+          <t>Mute (Do not notify me auditorily at all) 🔕</t>
+        </is>
+      </c>
+      <c r="KH48" s="2" t="inlineStr">
+        <is>
+          <t>Sound Only 'Version 1' 🔔</t>
+        </is>
+      </c>
+      <c r="KI48" s="2" t="inlineStr">
+        <is>
+          <t>Speech 'Version 2' (Sender) 🗣️</t>
+        </is>
+      </c>
+      <c r="KJ48" s="2" t="inlineStr">
+        <is>
+          <t>Indefinite delay (Hours): Can be withheld entirely until I manually check my phone or ask the device.</t>
+        </is>
+      </c>
+      <c r="KK48" s="2" t="inlineStr">
+        <is>
+          <t>Indefinite delay (Hours): Can be withheld entirely until I manually check my phone or ask the device.</t>
+        </is>
+      </c>
+      <c r="KL48" s="2" t="inlineStr">
+        <is>
+          <t>Moderate delay (Minutes): Can wait until I finish my current task (e.g., finishing an email or a conversation).</t>
+        </is>
+      </c>
+      <c r="KM48" s="2" t="inlineStr">
+        <is>
+          <t>No delay: Must interrupt me immediately, regardless of my situation.</t>
+        </is>
+      </c>
+      <c r="KN48" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="KO48" t="n">
+        <v>18.648</v>
+      </c>
+      <c r="KP48" t="n">
+        <v>200.674</v>
+      </c>
+      <c r="KQ48" t="n">
+        <v>203.901</v>
+      </c>
+      <c r="KR48" t="n">
+        <v>8.0</v>
+      </c>
+      <c r="KS48" s="2" t="inlineStr">
+        <is>
+          <t>6198</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A2:KS47"/>
+  <autoFilter ref="A2:KS49"/>
   <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
   <ignoredErrors>
-    <ignoredError sqref="C1:C46" numberStoredAsText="true"/>
-    <ignoredError sqref="D1:D46" numberStoredAsText="true"/>
-    <ignoredError sqref="G1:G46" numberStoredAsText="true"/>
-    <ignoredError sqref="I1:I46" numberStoredAsText="true"/>
-    <ignoredError sqref="J1:J46" numberStoredAsText="true"/>
-    <ignoredError sqref="K1:K46" numberStoredAsText="true"/>
-    <ignoredError sqref="L1:L46" numberStoredAsText="true"/>
-    <ignoredError sqref="M1:M46" numberStoredAsText="true"/>
-    <ignoredError sqref="P1:P46" numberStoredAsText="true"/>
-    <ignoredError sqref="Q1:Q46" numberStoredAsText="true"/>
-    <ignoredError sqref="R1:R46" numberStoredAsText="true"/>
-    <ignoredError sqref="S1:S46" numberStoredAsText="true"/>
-    <ignoredError sqref="T1:T46" numberStoredAsText="true"/>
-    <ignoredError sqref="U1:U46" numberStoredAsText="true"/>
-    <ignoredError sqref="V1:V46" numberStoredAsText="true"/>
-    <ignoredError sqref="W1:W46" numberStoredAsText="true"/>
-    <ignoredError sqref="X1:X46" numberStoredAsText="true"/>
-    <ignoredError sqref="Y1:Y46" numberStoredAsText="true"/>
-    <ignoredError sqref="Z1:Z46" numberStoredAsText="true"/>
-    <ignoredError sqref="AA1:AA46" numberStoredAsText="true"/>
-    <ignoredError sqref="AB1:AB46" numberStoredAsText="true"/>
-    <ignoredError sqref="AC1:AC46" numberStoredAsText="true"/>
-    <ignoredError sqref="AE1:AE46" numberStoredAsText="true"/>
-    <ignoredError sqref="AF1:AF46" numberStoredAsText="true"/>
-    <ignoredError sqref="AG1:AG46" numberStoredAsText="true"/>
-    <ignoredError sqref="AH1:AH46" numberStoredAsText="true"/>
-    <ignoredError sqref="AI1:AI46" numberStoredAsText="true"/>
-    <ignoredError sqref="AJ1:AJ46" numberStoredAsText="true"/>
-    <ignoredError sqref="AK1:AK46" numberStoredAsText="true"/>
-    <ignoredError sqref="AL1:AL46" numberStoredAsText="true"/>
-    <ignoredError sqref="AM1:AM46" numberStoredAsText="true"/>
-    <ignoredError sqref="AN1:AN46" numberStoredAsText="true"/>
-    <ignoredError sqref="AO1:AO46" numberStoredAsText="true"/>
-    <ignoredError sqref="AP1:AP46" numberStoredAsText="true"/>
-    <ignoredError sqref="AQ1:AQ46" numberStoredAsText="true"/>
-    <ignoredError sqref="AR1:AR46" numberStoredAsText="true"/>
-    <ignoredError sqref="AS1:AS46" numberStoredAsText="true"/>
-    <ignoredError sqref="AT1:AT46" numberStoredAsText="true"/>
-    <ignoredError sqref="AU1:AU46" numberStoredAsText="true"/>
-    <ignoredError sqref="AV1:AV46" numberStoredAsText="true"/>
-    <ignoredError sqref="AW1:AW46" numberStoredAsText="true"/>
-    <ignoredError sqref="AX1:AX46" numberStoredAsText="true"/>
-    <ignoredError sqref="AY1:AY46" numberStoredAsText="true"/>
-    <ignoredError sqref="AZ1:AZ46" numberStoredAsText="true"/>
-    <ignoredError sqref="BA1:BA46" numberStoredAsText="true"/>
-    <ignoredError sqref="BB1:BB46" numberStoredAsText="true"/>
-    <ignoredError sqref="BC1:BC46" numberStoredAsText="true"/>
-    <ignoredError sqref="BD1:BD46" numberStoredAsText="true"/>
-    <ignoredError sqref="BE1:BE46" numberStoredAsText="true"/>
-    <ignoredError sqref="BF1:BF46" numberStoredAsText="true"/>
-    <ignoredError sqref="BG1:BG46" numberStoredAsText="true"/>
-    <ignoredError sqref="BH1:BH46" numberStoredAsText="true"/>
-    <ignoredError sqref="BI1:BI46" numberStoredAsText="true"/>
-    <ignoredError sqref="BJ1:BJ46" numberStoredAsText="true"/>
-    <ignoredError sqref="BK1:BK46" numberStoredAsText="true"/>
-    <ignoredError sqref="BL1:BL46" numberStoredAsText="true"/>
-    <ignoredError sqref="BM1:BM46" numberStoredAsText="true"/>
-    <ignoredError sqref="BN1:BN46" numberStoredAsText="true"/>
-    <ignoredError sqref="BO1:BO46" numberStoredAsText="true"/>
-    <ignoredError sqref="BP1:BP46" numberStoredAsText="true"/>
-    <ignoredError sqref="BQ1:BQ46" numberStoredAsText="true"/>
-    <ignoredError sqref="BR1:BR46" numberStoredAsText="true"/>
-    <ignoredError sqref="BS1:BS46" numberStoredAsText="true"/>
-    <ignoredError sqref="BT1:BT46" numberStoredAsText="true"/>
-    <ignoredError sqref="BU1:BU46" numberStoredAsText="true"/>
-    <ignoredError sqref="BV1:BV46" numberStoredAsText="true"/>
-    <ignoredError sqref="BW1:BW46" numberStoredAsText="true"/>
-    <ignoredError sqref="BX1:BX46" numberStoredAsText="true"/>
-    <ignoredError sqref="BY1:BY46" numberStoredAsText="true"/>
-    <ignoredError sqref="BZ1:BZ46" numberStoredAsText="true"/>
-    <ignoredError sqref="CA1:CA46" numberStoredAsText="true"/>
-    <ignoredError sqref="CB1:CB46" numberStoredAsText="true"/>
-    <ignoredError sqref="CC1:CC46" numberStoredAsText="true"/>
-    <ignoredError sqref="CD1:CD46" numberStoredAsText="true"/>
-    <ignoredError sqref="CE1:CE46" numberStoredAsText="true"/>
-    <ignoredError sqref="CF1:CF46" numberStoredAsText="true"/>
-    <ignoredError sqref="CG1:CG46" numberStoredAsText="true"/>
-    <ignoredError sqref="CH1:CH46" numberStoredAsText="true"/>
-    <ignoredError sqref="CI1:CI46" numberStoredAsText="true"/>
-    <ignoredError sqref="CJ1:CJ46" numberStoredAsText="true"/>
-    <ignoredError sqref="CK1:CK46" numberStoredAsText="true"/>
-    <ignoredError sqref="CL1:CL46" numberStoredAsText="true"/>
-    <ignoredError sqref="CM1:CM46" numberStoredAsText="true"/>
-    <ignoredError sqref="CN1:CN46" numberStoredAsText="true"/>
-    <ignoredError sqref="CO1:CO46" numberStoredAsText="true"/>
-    <ignoredError sqref="CP1:CP46" numberStoredAsText="true"/>
-    <ignoredError sqref="CQ1:CQ46" numberStoredAsText="true"/>
-    <ignoredError sqref="CR1:CR46" numberStoredAsText="true"/>
-    <ignoredError sqref="CS1:CS46" numberStoredAsText="true"/>
-    <ignoredError sqref="CT1:CT46" numberStoredAsText="true"/>
-    <ignoredError sqref="CU1:CU46" numberStoredAsText="true"/>
-    <ignoredError sqref="CV1:CV46" numberStoredAsText="true"/>
-    <ignoredError sqref="CW1:CW46" numberStoredAsText="true"/>
-    <ignoredError sqref="CX1:CX46" numberStoredAsText="true"/>
-    <ignoredError sqref="CY1:CY46" numberStoredAsText="true"/>
-    <ignoredError sqref="CZ1:CZ46" numberStoredAsText="true"/>
-    <ignoredError sqref="DA1:DA46" numberStoredAsText="true"/>
-    <ignoredError sqref="DB1:DB46" numberStoredAsText="true"/>
-    <ignoredError sqref="DC1:DC46" numberStoredAsText="true"/>
-    <ignoredError sqref="DD1:DD46" numberStoredAsText="true"/>
-    <ignoredError sqref="DE1:DE46" numberStoredAsText="true"/>
-    <ignoredError sqref="DF1:DF46" numberStoredAsText="true"/>
-    <ignoredError sqref="DG1:DG46" numberStoredAsText="true"/>
-    <ignoredError sqref="DH1:DH46" numberStoredAsText="true"/>
-    <ignoredError sqref="DI1:DI46" numberStoredAsText="true"/>
-    <ignoredError sqref="DJ1:DJ46" numberStoredAsText="true"/>
-    <ignoredError sqref="DK1:DK46" numberStoredAsText="true"/>
-    <ignoredError sqref="DL1:DL46" numberStoredAsText="true"/>
-    <ignoredError sqref="DM1:DM46" numberStoredAsText="true"/>
-    <ignoredError sqref="DN1:DN46" numberStoredAsText="true"/>
-    <ignoredError sqref="DO1:DO46" numberStoredAsText="true"/>
-    <ignoredError sqref="DP1:DP46" numberStoredAsText="true"/>
-    <ignoredError sqref="DQ1:DQ46" numberStoredAsText="true"/>
-    <ignoredError sqref="DR1:DR46" numberStoredAsText="true"/>
-    <ignoredError sqref="DS1:DS46" numberStoredAsText="true"/>
-    <ignoredError sqref="DT1:DT46" numberStoredAsText="true"/>
-    <ignoredError sqref="DU1:DU46" numberStoredAsText="true"/>
-    <ignoredError sqref="DV1:DV46" numberStoredAsText="true"/>
-    <ignoredError sqref="DW1:DW46" numberStoredAsText="true"/>
-    <ignoredError sqref="DX1:DX46" numberStoredAsText="true"/>
-    <ignoredError sqref="DY1:DY46" numberStoredAsText="true"/>
-    <ignoredError sqref="DZ1:DZ46" numberStoredAsText="true"/>
-    <ignoredError sqref="EA1:EA46" numberStoredAsText="true"/>
-    <ignoredError sqref="EB1:EB46" numberStoredAsText="true"/>
-    <ignoredError sqref="EC1:EC46" numberStoredAsText="true"/>
-    <ignoredError sqref="ED1:ED46" numberStoredAsText="true"/>
-    <ignoredError sqref="EE1:EE46" numberStoredAsText="true"/>
-    <ignoredError sqref="EF1:EF46" numberStoredAsText="true"/>
-    <ignoredError sqref="EG1:EG46" numberStoredAsText="true"/>
-    <ignoredError sqref="EH1:EH46" numberStoredAsText="true"/>
-    <ignoredError sqref="EI1:EI46" numberStoredAsText="true"/>
-    <ignoredError sqref="EJ1:EJ46" numberStoredAsText="true"/>
-    <ignoredError sqref="EK1:EK46" numberStoredAsText="true"/>
-    <ignoredError sqref="EL1:EL46" numberStoredAsText="true"/>
-    <ignoredError sqref="EM1:EM46" numberStoredAsText="true"/>
-    <ignoredError sqref="EN1:EN46" numberStoredAsText="true"/>
-    <ignoredError sqref="EO1:EO46" numberStoredAsText="true"/>
-    <ignoredError sqref="EP1:EP46" numberStoredAsText="true"/>
-    <ignoredError sqref="EQ1:EQ46" numberStoredAsText="true"/>
-    <ignoredError sqref="ER1:ER46" numberStoredAsText="true"/>
-    <ignoredError sqref="ES1:ES46" numberStoredAsText="true"/>
-    <ignoredError sqref="ET1:ET46" numberStoredAsText="true"/>
-    <ignoredError sqref="EU1:EU46" numberStoredAsText="true"/>
-    <ignoredError sqref="EV1:EV46" numberStoredAsText="true"/>
-    <ignoredError sqref="EW1:EW46" numberStoredAsText="true"/>
-    <ignoredError sqref="EX1:EX46" numberStoredAsText="true"/>
-    <ignoredError sqref="EY1:EY46" numberStoredAsText="true"/>
-    <ignoredError sqref="EZ1:EZ46" numberStoredAsText="true"/>
-    <ignoredError sqref="FA1:FA46" numberStoredAsText="true"/>
-    <ignoredError sqref="FB1:FB46" numberStoredAsText="true"/>
-    <ignoredError sqref="FC1:FC46" numberStoredAsText="true"/>
-    <ignoredError sqref="FD1:FD46" numberStoredAsText="true"/>
-    <ignoredError sqref="FE1:FE46" numberStoredAsText="true"/>
-    <ignoredError sqref="FF1:FF46" numberStoredAsText="true"/>
-    <ignoredError sqref="FG1:FG46" numberStoredAsText="true"/>
-    <ignoredError sqref="FH1:FH46" numberStoredAsText="true"/>
-    <ignoredError sqref="FI1:FI46" numberStoredAsText="true"/>
-    <ignoredError sqref="FJ1:FJ46" numberStoredAsText="true"/>
-    <ignoredError sqref="FK1:FK46" numberStoredAsText="true"/>
-    <ignoredError sqref="FL1:FL46" numberStoredAsText="true"/>
-    <ignoredError sqref="FM1:FM46" numberStoredAsText="true"/>
-    <ignoredError sqref="FN1:FN46" numberStoredAsText="true"/>
-    <ignoredError sqref="FO1:FO46" numberStoredAsText="true"/>
-    <ignoredError sqref="FP1:FP46" numberStoredAsText="true"/>
-    <ignoredError sqref="FQ1:FQ46" numberStoredAsText="true"/>
-    <ignoredError sqref="FR1:FR46" numberStoredAsText="true"/>
-    <ignoredError sqref="FS1:FS46" numberStoredAsText="true"/>
-    <ignoredError sqref="FT1:FT46" numberStoredAsText="true"/>
-    <ignoredError sqref="FU1:FU46" numberStoredAsText="true"/>
-    <ignoredError sqref="FV1:FV46" numberStoredAsText="true"/>
-    <ignoredError sqref="FW1:FW46" numberStoredAsText="true"/>
-    <ignoredError sqref="FX1:FX46" numberStoredAsText="true"/>
-    <ignoredError sqref="FY1:FY46" numberStoredAsText="true"/>
-    <ignoredError sqref="FZ1:FZ46" numberStoredAsText="true"/>
-    <ignoredError sqref="GA1:GA46" numberStoredAsText="true"/>
-    <ignoredError sqref="GB1:GB46" numberStoredAsText="true"/>
-    <ignoredError sqref="GC1:GC46" numberStoredAsText="true"/>
-    <ignoredError sqref="GD1:GD46" numberStoredAsText="true"/>
-    <ignoredError sqref="GE1:GE46" numberStoredAsText="true"/>
-    <ignoredError sqref="GF1:GF46" numberStoredAsText="true"/>
-    <ignoredError sqref="GG1:GG46" numberStoredAsText="true"/>
-    <ignoredError sqref="GH1:GH46" numberStoredAsText="true"/>
-    <ignoredError sqref="GI1:GI46" numberStoredAsText="true"/>
-    <ignoredError sqref="GJ1:GJ46" numberStoredAsText="true"/>
-    <ignoredError sqref="GK1:GK46" numberStoredAsText="true"/>
-    <ignoredError sqref="GL1:GL46" numberStoredAsText="true"/>
-    <ignoredError sqref="GM1:GM46" numberStoredAsText="true"/>
-    <ignoredError sqref="GN1:GN46" numberStoredAsText="true"/>
-    <ignoredError sqref="GO1:GO46" numberStoredAsText="true"/>
-    <ignoredError sqref="GP1:GP46" numberStoredAsText="true"/>
-    <ignoredError sqref="GQ1:GQ46" numberStoredAsText="true"/>
-    <ignoredError sqref="GR1:GR46" numberStoredAsText="true"/>
-    <ignoredError sqref="GS1:GS46" numberStoredAsText="true"/>
-    <ignoredError sqref="GT1:GT46" numberStoredAsText="true"/>
-    <ignoredError sqref="GU1:GU46" numberStoredAsText="true"/>
-    <ignoredError sqref="GV1:GV46" numberStoredAsText="true"/>
-    <ignoredError sqref="GW1:GW46" numberStoredAsText="true"/>
-    <ignoredError sqref="GX1:GX46" numberStoredAsText="true"/>
-    <ignoredError sqref="GY1:GY46" numberStoredAsText="true"/>
-    <ignoredError sqref="GZ1:GZ46" numberStoredAsText="true"/>
-    <ignoredError sqref="HA1:HA46" numberStoredAsText="true"/>
-    <ignoredError sqref="HB1:HB46" numberStoredAsText="true"/>
-    <ignoredError sqref="HC1:HC46" numberStoredAsText="true"/>
-    <ignoredError sqref="HD1:HD46" numberStoredAsText="true"/>
-    <ignoredError sqref="HE1:HE46" numberStoredAsText="true"/>
-    <ignoredError sqref="HF1:HF46" numberStoredAsText="true"/>
-    <ignoredError sqref="HG1:HG46" numberStoredAsText="true"/>
-    <ignoredError sqref="HH1:HH46" numberStoredAsText="true"/>
-    <ignoredError sqref="HI1:HI46" numberStoredAsText="true"/>
-    <ignoredError sqref="HJ1:HJ46" numberStoredAsText="true"/>
-    <ignoredError sqref="HK1:HK46" numberStoredAsText="true"/>
-    <ignoredError sqref="HL1:HL46" numberStoredAsText="true"/>
-    <ignoredError sqref="HM1:HM46" numberStoredAsText="true"/>
-    <ignoredError sqref="HN1:HN46" numberStoredAsText="true"/>
-    <ignoredError sqref="HO1:HO46" numberStoredAsText="true"/>
-    <ignoredError sqref="HP1:HP46" numberStoredAsText="true"/>
-    <ignoredError sqref="HQ1:HQ46" numberStoredAsText="true"/>
-    <ignoredError sqref="HR1:HR46" numberStoredAsText="true"/>
-    <ignoredError sqref="HS1:HS46" numberStoredAsText="true"/>
-    <ignoredError sqref="HT1:HT46" numberStoredAsText="true"/>
-    <ignoredError sqref="HU1:HU46" numberStoredAsText="true"/>
-    <ignoredError sqref="HV1:HV46" numberStoredAsText="true"/>
-    <ignoredError sqref="HW1:HW46" numberStoredAsText="true"/>
-    <ignoredError sqref="HX1:HX46" numberStoredAsText="true"/>
-    <ignoredError sqref="HY1:HY46" numberStoredAsText="true"/>
-    <ignoredError sqref="HZ1:HZ46" numberStoredAsText="true"/>
-    <ignoredError sqref="IA1:IA46" numberStoredAsText="true"/>
-    <ignoredError sqref="IB1:IB46" numberStoredAsText="true"/>
-    <ignoredError sqref="IC1:IC46" numberStoredAsText="true"/>
-    <ignoredError sqref="ID1:ID46" numberStoredAsText="true"/>
-    <ignoredError sqref="IE1:IE46" numberStoredAsText="true"/>
-    <ignoredError sqref="IF1:IF46" numberStoredAsText="true"/>
-    <ignoredError sqref="IG1:IG46" numberStoredAsText="true"/>
-    <ignoredError sqref="IH1:IH46" numberStoredAsText="true"/>
-    <ignoredError sqref="II1:II46" numberStoredAsText="true"/>
-    <ignoredError sqref="IJ1:IJ46" numberStoredAsText="true"/>
-    <ignoredError sqref="IK1:IK46" numberStoredAsText="true"/>
-    <ignoredError sqref="IL1:IL46" numberStoredAsText="true"/>
-    <ignoredError sqref="IM1:IM46" numberStoredAsText="true"/>
-    <ignoredError sqref="IN1:IN46" numberStoredAsText="true"/>
-    <ignoredError sqref="IO1:IO46" numberStoredAsText="true"/>
-    <ignoredError sqref="IP1:IP46" numberStoredAsText="true"/>
-    <ignoredError sqref="IQ1:IQ46" numberStoredAsText="true"/>
-    <ignoredError sqref="IR1:IR46" numberStoredAsText="true"/>
-    <ignoredError sqref="IS1:IS46" numberStoredAsText="true"/>
-    <ignoredError sqref="IT1:IT46" numberStoredAsText="true"/>
-    <ignoredError sqref="IU1:IU46" numberStoredAsText="true"/>
-    <ignoredError sqref="IV1:IV46" numberStoredAsText="true"/>
-    <ignoredError sqref="IW1:IW46" numberStoredAsText="true"/>
-    <ignoredError sqref="IX1:IX46" numberStoredAsText="true"/>
-    <ignoredError sqref="IY1:IY46" numberStoredAsText="true"/>
-    <ignoredError sqref="IZ1:IZ46" numberStoredAsText="true"/>
-    <ignoredError sqref="JA1:JA46" numberStoredAsText="true"/>
-    <ignoredError sqref="JB1:JB46" numberStoredAsText="true"/>
-    <ignoredError sqref="JC1:JC46" numberStoredAsText="true"/>
-    <ignoredError sqref="JD1:JD46" numberStoredAsText="true"/>
-    <ignoredError sqref="JE1:JE46" numberStoredAsText="true"/>
-    <ignoredError sqref="JF1:JF46" numberStoredAsText="true"/>
-    <ignoredError sqref="JG1:JG46" numberStoredAsText="true"/>
-    <ignoredError sqref="JH1:JH46" numberStoredAsText="true"/>
-    <ignoredError sqref="JI1:JI46" numberStoredAsText="true"/>
-    <ignoredError sqref="JJ1:JJ46" numberStoredAsText="true"/>
-    <ignoredError sqref="JK1:JK46" numberStoredAsText="true"/>
-    <ignoredError sqref="JL1:JL46" numberStoredAsText="true"/>
-    <ignoredError sqref="JM1:JM46" numberStoredAsText="true"/>
-    <ignoredError sqref="JN1:JN46" numberStoredAsText="true"/>
-    <ignoredError sqref="JO1:JO46" numberStoredAsText="true"/>
-    <ignoredError sqref="JP1:JP46" numberStoredAsText="true"/>
-    <ignoredError sqref="JQ1:JQ46" numberStoredAsText="true"/>
-    <ignoredError sqref="JR1:JR46" numberStoredAsText="true"/>
-    <ignoredError sqref="JS1:JS46" numberStoredAsText="true"/>
-    <ignoredError sqref="JT1:JT46" numberStoredAsText="true"/>
-    <ignoredError sqref="JU1:JU46" numberStoredAsText="true"/>
-    <ignoredError sqref="JV1:JV46" numberStoredAsText="true"/>
-    <ignoredError sqref="JW1:JW46" numberStoredAsText="true"/>
-    <ignoredError sqref="JX1:JX46" numberStoredAsText="true"/>
-    <ignoredError sqref="JY1:JY46" numberStoredAsText="true"/>
-    <ignoredError sqref="JZ1:JZ46" numberStoredAsText="true"/>
-    <ignoredError sqref="KA1:KA46" numberStoredAsText="true"/>
-    <ignoredError sqref="KB1:KB46" numberStoredAsText="true"/>
-    <ignoredError sqref="KC1:KC46" numberStoredAsText="true"/>
-    <ignoredError sqref="KD1:KD46" numberStoredAsText="true"/>
-    <ignoredError sqref="KE1:KE46" numberStoredAsText="true"/>
-    <ignoredError sqref="KF1:KF46" numberStoredAsText="true"/>
-    <ignoredError sqref="KG1:KG46" numberStoredAsText="true"/>
-    <ignoredError sqref="KH1:KH46" numberStoredAsText="true"/>
-    <ignoredError sqref="KI1:KI46" numberStoredAsText="true"/>
-    <ignoredError sqref="KJ1:KJ46" numberStoredAsText="true"/>
-    <ignoredError sqref="KK1:KK46" numberStoredAsText="true"/>
-    <ignoredError sqref="KL1:KL46" numberStoredAsText="true"/>
-    <ignoredError sqref="KM1:KM46" numberStoredAsText="true"/>
-    <ignoredError sqref="KN1:KN46" numberStoredAsText="true"/>
-    <ignoredError sqref="KO1:KO46" numberStoredAsText="true"/>
-    <ignoredError sqref="KP1:KP46" numberStoredAsText="true"/>
-    <ignoredError sqref="KQ1:KQ46" numberStoredAsText="true"/>
-    <ignoredError sqref="KR1:KR46" numberStoredAsText="true"/>
-    <ignoredError sqref="KS1:KS46" numberStoredAsText="true"/>
+    <ignoredError sqref="C1:C48" numberStoredAsText="true"/>
+    <ignoredError sqref="D1:D48" numberStoredAsText="true"/>
+    <ignoredError sqref="G1:G48" numberStoredAsText="true"/>
+    <ignoredError sqref="I1:I48" numberStoredAsText="true"/>
+    <ignoredError sqref="J1:J48" numberStoredAsText="true"/>
+    <ignoredError sqref="K1:K48" numberStoredAsText="true"/>
+    <ignoredError sqref="L1:L48" numberStoredAsText="true"/>
+    <ignoredError sqref="M1:M48" numberStoredAsText="true"/>
+    <ignoredError sqref="P1:P48" numberStoredAsText="true"/>
+    <ignoredError sqref="Q1:Q48" numberStoredAsText="true"/>
+    <ignoredError sqref="R1:R48" numberStoredAsText="true"/>
+    <ignoredError sqref="S1:S48" numberStoredAsText="true"/>
+    <ignoredError sqref="T1:T48" numberStoredAsText="true"/>
+    <ignoredError sqref="U1:U48" numberStoredAsText="true"/>
+    <ignoredError sqref="V1:V48" numberStoredAsText="true"/>
+    <ignoredError sqref="W1:W48" numberStoredAsText="true"/>
+    <ignoredError sqref="X1:X48" numberStoredAsText="true"/>
+    <ignoredError sqref="Y1:Y48" numberStoredAsText="true"/>
+    <ignoredError sqref="Z1:Z48" numberStoredAsText="true"/>
+    <ignoredError sqref="AA1:AA48" numberStoredAsText="true"/>
+    <ignoredError sqref="AB1:AB48" numberStoredAsText="true"/>
+    <ignoredError sqref="AC1:AC48" numberStoredAsText="true"/>
+    <ignoredError sqref="AE1:AE48" numberStoredAsText="true"/>
+    <ignoredError sqref="AF1:AF48" numberStoredAsText="true"/>
+    <ignoredError sqref="AG1:AG48" numberStoredAsText="true"/>
+    <ignoredError sqref="AH1:AH48" numberStoredAsText="true"/>
+    <ignoredError sqref="AI1:AI48" numberStoredAsText="true"/>
+    <ignoredError sqref="AJ1:AJ48" numberStoredAsText="true"/>
+    <ignoredError sqref="AK1:AK48" numberStoredAsText="true"/>
+    <ignoredError sqref="AL1:AL48" numberStoredAsText="true"/>
+    <ignoredError sqref="AM1:AM48" numberStoredAsText="true"/>
+    <ignoredError sqref="AN1:AN48" numberStoredAsText="true"/>
+    <ignoredError sqref="AO1:AO48" numberStoredAsText="true"/>
+    <ignoredError sqref="AP1:AP48" numberStoredAsText="true"/>
+    <ignoredError sqref="AQ1:AQ48" numberStoredAsText="true"/>
+    <ignoredError sqref="AR1:AR48" numberStoredAsText="true"/>
+    <ignoredError sqref="AS1:AS48" numberStoredAsText="true"/>
+    <ignoredError sqref="AT1:AT48" numberStoredAsText="true"/>
+    <ignoredError sqref="AU1:AU48" numberStoredAsText="true"/>
+    <ignoredError sqref="AV1:AV48" numberStoredAsText="true"/>
+    <ignoredError sqref="AW1:AW48" numberStoredAsText="true"/>
+    <ignoredError sqref="AX1:AX48" numberStoredAsText="true"/>
+    <ignoredError sqref="AY1:AY48" numberStoredAsText="true"/>
+    <ignoredError sqref="AZ1:AZ48" numberStoredAsText="true"/>
+    <ignoredError sqref="BA1:BA48" numberStoredAsText="true"/>
+    <ignoredError sqref="BB1:BB48" numberStoredAsText="true"/>
+    <ignoredError sqref="BC1:BC48" numberStoredAsText="true"/>
+    <ignoredError sqref="BD1:BD48" numberStoredAsText="true"/>
+    <ignoredError sqref="BE1:BE48" numberStoredAsText="true"/>
+    <ignoredError sqref="BF1:BF48" numberStoredAsText="true"/>
+    <ignoredError sqref="BG1:BG48" numberStoredAsText="true"/>
+    <ignoredError sqref="BH1:BH48" numberStoredAsText="true"/>
+    <ignoredError sqref="BI1:BI48" numberStoredAsText="true"/>
+    <ignoredError sqref="BJ1:BJ48" numberStoredAsText="true"/>
+    <ignoredError sqref="BK1:BK48" numberStoredAsText="true"/>
+    <ignoredError sqref="BL1:BL48" numberStoredAsText="true"/>
+    <ignoredError sqref="BM1:BM48" numberStoredAsText="true"/>
+    <ignoredError sqref="BN1:BN48" numberStoredAsText="true"/>
+    <ignoredError sqref="BO1:BO48" numberStoredAsText="true"/>
+    <ignoredError sqref="BP1:BP48" numberStoredAsText="true"/>
+    <ignoredError sqref="BQ1:BQ48" numberStoredAsText="true"/>
+    <ignoredError sqref="BR1:BR48" numberStoredAsText="true"/>
+    <ignoredError sqref="BS1:BS48" numberStoredAsText="true"/>
+    <ignoredError sqref="BT1:BT48" numberStoredAsText="true"/>
+    <ignoredError sqref="BU1:BU48" numberStoredAsText="true"/>
+    <ignoredError sqref="BV1:BV48" numberStoredAsText="true"/>
+    <ignoredError sqref="BW1:BW48" numberStoredAsText="true"/>
+    <ignoredError sqref="BX1:BX48" numberStoredAsText="true"/>
+    <ignoredError sqref="BY1:BY48" numberStoredAsText="true"/>
+    <ignoredError sqref="BZ1:BZ48" numberStoredAsText="true"/>
+    <ignoredError sqref="CA1:CA48" numberStoredAsText="true"/>
+    <ignoredError sqref="CB1:CB48" numberStoredAsText="true"/>
+    <ignoredError sqref="CC1:CC48" numberStoredAsText="true"/>
+    <ignoredError sqref="CD1:CD48" numberStoredAsText="true"/>
+    <ignoredError sqref="CE1:CE48" numberStoredAsText="true"/>
+    <ignoredError sqref="CF1:CF48" numberStoredAsText="true"/>
+    <ignoredError sqref="CG1:CG48" numberStoredAsText="true"/>
+    <ignoredError sqref="CH1:CH48" numberStoredAsText="true"/>
+    <ignoredError sqref="CI1:CI48" numberStoredAsText="true"/>
+    <ignoredError sqref="CJ1:CJ48" numberStoredAsText="true"/>
+    <ignoredError sqref="CK1:CK48" numberStoredAsText="true"/>
+    <ignoredError sqref="CL1:CL48" numberStoredAsText="true"/>
+    <ignoredError sqref="CM1:CM48" numberStoredAsText="true"/>
+    <ignoredError sqref="CN1:CN48" numberStoredAsText="true"/>
+    <ignoredError sqref="CO1:CO48" numberStoredAsText="true"/>
+    <ignoredError sqref="CP1:CP48" numberStoredAsText="true"/>
+    <ignoredError sqref="CQ1:CQ48" numberStoredAsText="true"/>
+    <ignoredError sqref="CR1:CR48" numberStoredAsText="true"/>
+    <ignoredError sqref="CS1:CS48" numberStoredAsText="true"/>
+    <ignoredError sqref="CT1:CT48" numberStoredAsText="true"/>
+    <ignoredError sqref="CU1:CU48" numberStoredAsText="true"/>
+    <ignoredError sqref="CV1:CV48" numberStoredAsText="true"/>
+    <ignoredError sqref="CW1:CW48" numberStoredAsText="true"/>
+    <ignoredError sqref="CX1:CX48" numberStoredAsText="true"/>
+    <ignoredError sqref="CY1:CY48" numberStoredAsText="true"/>
+    <ignoredError sqref="CZ1:CZ48" numberStoredAsText="true"/>
+    <ignoredError sqref="DA1:DA48" numberStoredAsText="true"/>
+    <ignoredError sqref="DB1:DB48" numberStoredAsText="true"/>
+    <ignoredError sqref="DC1:DC48" numberStoredAsText="true"/>
+    <ignoredError sqref="DD1:DD48" numberStoredAsText="true"/>
+    <ignoredError sqref="DE1:DE48" numberStoredAsText="true"/>
+    <ignoredError sqref="DF1:DF48" numberStoredAsText="true"/>
+    <ignoredError sqref="DG1:DG48" numberStoredAsText="true"/>
+    <ignoredError sqref="DH1:DH48" numberStoredAsText="true"/>
+    <ignoredError sqref="DI1:DI48" numberStoredAsText="true"/>
+    <ignoredError sqref="DJ1:DJ48" numberStoredAsText="true"/>
+    <ignoredError sqref="DK1:DK48" numberStoredAsText="true"/>
+    <ignoredError sqref="DL1:DL48" numberStoredAsText="true"/>
+    <ignoredError sqref="DM1:DM48" numberStoredAsText="true"/>
+    <ignoredError sqref="DN1:DN48" numberStoredAsText="true"/>
+    <ignoredError sqref="DO1:DO48" numberStoredAsText="true"/>
+    <ignoredError sqref="DP1:DP48" numberStoredAsText="true"/>
+    <ignoredError sqref="DQ1:DQ48" numberStoredAsText="true"/>
+    <ignoredError sqref="DR1:DR48" numberStoredAsText="true"/>
+    <ignoredError sqref="DS1:DS48" numberStoredAsText="true"/>
+    <ignoredError sqref="DT1:DT48" numberStoredAsText="true"/>
+    <ignoredError sqref="DU1:DU48" numberStoredAsText="true"/>
+    <ignoredError sqref="DV1:DV48" numberStoredAsText="true"/>
+    <ignoredError sqref="DW1:DW48" numberStoredAsText="true"/>
+    <ignoredError sqref="DX1:DX48" numberStoredAsText="true"/>
+    <ignoredError sqref="DY1:DY48" numberStoredAsText="true"/>
+    <ignoredError sqref="DZ1:DZ48" numberStoredAsText="true"/>
+    <ignoredError sqref="EA1:EA48" numberStoredAsText="true"/>
+    <ignoredError sqref="EB1:EB48" numberStoredAsText="true"/>
+    <ignoredError sqref="EC1:EC48" numberStoredAsText="true"/>
+    <ignoredError sqref="ED1:ED48" numberStoredAsText="true"/>
+    <ignoredError sqref="EE1:EE48" numberStoredAsText="true"/>
+    <ignoredError sqref="EF1:EF48" numberStoredAsText="true"/>
+    <ignoredError sqref="EG1:EG48" numberStoredAsText="true"/>
+    <ignoredError sqref="EH1:EH48" numberStoredAsText="true"/>
+    <ignoredError sqref="EI1:EI48" numberStoredAsText="true"/>
+    <ignoredError sqref="EJ1:EJ48" numberStoredAsText="true"/>
+    <ignoredError sqref="EK1:EK48" numberStoredAsText="true"/>
+    <ignoredError sqref="EL1:EL48" numberStoredAsText="true"/>
+    <ignoredError sqref="EM1:EM48" numberStoredAsText="true"/>
+    <ignoredError sqref="EN1:EN48" numberStoredAsText="true"/>
+    <ignoredError sqref="EO1:EO48" numberStoredAsText="true"/>
+    <ignoredError sqref="EP1:EP48" numberStoredAsText="true"/>
+    <ignoredError sqref="EQ1:EQ48" numberStoredAsText="true"/>
+    <ignoredError sqref="ER1:ER48" numberStoredAsText="true"/>
+    <ignoredError sqref="ES1:ES48" numberStoredAsText="true"/>
+    <ignoredError sqref="ET1:ET48" numberStoredAsText="true"/>
+    <ignoredError sqref="EU1:EU48" numberStoredAsText="true"/>
+    <ignoredError sqref="EV1:EV48" numberStoredAsText="true"/>
+    <ignoredError sqref="EW1:EW48" numberStoredAsText="true"/>
+    <ignoredError sqref="EX1:EX48" numberStoredAsText="true"/>
+    <ignoredError sqref="EY1:EY48" numberStoredAsText="true"/>
+    <ignoredError sqref="EZ1:EZ48" numberStoredAsText="true"/>
+    <ignoredError sqref="FA1:FA48" numberStoredAsText="true"/>
+    <ignoredError sqref="FB1:FB48" numberStoredAsText="true"/>
+    <ignoredError sqref="FC1:FC48" numberStoredAsText="true"/>
+    <ignoredError sqref="FD1:FD48" numberStoredAsText="true"/>
+    <ignoredError sqref="FE1:FE48" numberStoredAsText="true"/>
+    <ignoredError sqref="FF1:FF48" numberStoredAsText="true"/>
+    <ignoredError sqref="FG1:FG48" numberStoredAsText="true"/>
+    <ignoredError sqref="FH1:FH48" numberStoredAsText="true"/>
+    <ignoredError sqref="FI1:FI48" numberStoredAsText="true"/>
+    <ignoredError sqref="FJ1:FJ48" numberStoredAsText="true"/>
+    <ignoredError sqref="FK1:FK48" numberStoredAsText="true"/>
+    <ignoredError sqref="FL1:FL48" numberStoredAsText="true"/>
+    <ignoredError sqref="FM1:FM48" numberStoredAsText="true"/>
+    <ignoredError sqref="FN1:FN48" numberStoredAsText="true"/>
+    <ignoredError sqref="FO1:FO48" numberStoredAsText="true"/>
+    <ignoredError sqref="FP1:FP48" numberStoredAsText="true"/>
+    <ignoredError sqref="FQ1:FQ48" numberStoredAsText="true"/>
+    <ignoredError sqref="FR1:FR48" numberStoredAsText="true"/>
+    <ignoredError sqref="FS1:FS48" numberStoredAsText="true"/>
+    <ignoredError sqref="FT1:FT48" numberStoredAsText="true"/>
+    <ignoredError sqref="FU1:FU48" numberStoredAsText="true"/>
+    <ignoredError sqref="FV1:FV48" numberStoredAsText="true"/>
+    <ignoredError sqref="FW1:FW48" numberStoredAsText="true"/>
+    <ignoredError sqref="FX1:FX48" numberStoredAsText="true"/>
+    <ignoredError sqref="FY1:FY48" numberStoredAsText="true"/>
+    <ignoredError sqref="FZ1:FZ48" numberStoredAsText="true"/>
+    <ignoredError sqref="GA1:GA48" numberStoredAsText="true"/>
+    <ignoredError sqref="GB1:GB48" numberStoredAsText="true"/>
+    <ignoredError sqref="GC1:GC48" numberStoredAsText="true"/>
+    <ignoredError sqref="GD1:GD48" numberStoredAsText="true"/>
+    <ignoredError sqref="GE1:GE48" numberStoredAsText="true"/>
+    <ignoredError sqref="GF1:GF48" numberStoredAsText="true"/>
+    <ignoredError sqref="GG1:GG48" numberStoredAsText="true"/>
+    <ignoredError sqref="GH1:GH48" numberStoredAsText="true"/>
+    <ignoredError sqref="GI1:GI48" numberStoredAsText="true"/>
+    <ignoredError sqref="GJ1:GJ48" numberStoredAsText="true"/>
+    <ignoredError sqref="GK1:GK48" numberStoredAsText="true"/>
+    <ignoredError sqref="GL1:GL48" numberStoredAsText="true"/>
+    <ignoredError sqref="GM1:GM48" numberStoredAsText="true"/>
+    <ignoredError sqref="GN1:GN48" numberStoredAsText="true"/>
+    <ignoredError sqref="GO1:GO48" numberStoredAsText="true"/>
+    <ignoredError sqref="GP1:GP48" numberStoredAsText="true"/>
+    <ignoredError sqref="GQ1:GQ48" numberStoredAsText="true"/>
+    <ignoredError sqref="GR1:GR48" numberStoredAsText="true"/>
+    <ignoredError sqref="GS1:GS48" numberStoredAsText="true"/>
+    <ignoredError sqref="GT1:GT48" numberStoredAsText="true"/>
+    <ignoredError sqref="GU1:GU48" numberStoredAsText="true"/>
+    <ignoredError sqref="GV1:GV48" numberStoredAsText="true"/>
+    <ignoredError sqref="GW1:GW48" numberStoredAsText="true"/>
+    <ignoredError sqref="GX1:GX48" numberStoredAsText="true"/>
+    <ignoredError sqref="GY1:GY48" numberStoredAsText="true"/>
+    <ignoredError sqref="GZ1:GZ48" numberStoredAsText="true"/>
+    <ignoredError sqref="HA1:HA48" numberStoredAsText="true"/>
+    <ignoredError sqref="HB1:HB48" numberStoredAsText="true"/>
+    <ignoredError sqref="HC1:HC48" numberStoredAsText="true"/>
+    <ignoredError sqref="HD1:HD48" numberStoredAsText="true"/>
+    <ignoredError sqref="HE1:HE48" numberStoredAsText="true"/>
+    <ignoredError sqref="HF1:HF48" numberStoredAsText="true"/>
+    <ignoredError sqref="HG1:HG48" numberStoredAsText="true"/>
+    <ignoredError sqref="HH1:HH48" numberStoredAsText="true"/>
+    <ignoredError sqref="HI1:HI48" numberStoredAsText="true"/>
+    <ignoredError sqref="HJ1:HJ48" numberStoredAsText="true"/>
+    <ignoredError sqref="HK1:HK48" numberStoredAsText="true"/>
+    <ignoredError sqref="HL1:HL48" numberStoredAsText="true"/>
+    <ignoredError sqref="HM1:HM48" numberStoredAsText="true"/>
+    <ignoredError sqref="HN1:HN48" numberStoredAsText="true"/>
+    <ignoredError sqref="HO1:HO48" numberStoredAsText="true"/>
+    <ignoredError sqref="HP1:HP48" numberStoredAsText="true"/>
+    <ignoredError sqref="HQ1:HQ48" numberStoredAsText="true"/>
+    <ignoredError sqref="HR1:HR48" numberStoredAsText="true"/>
+    <ignoredError sqref="HS1:HS48" numberStoredAsText="true"/>
+    <ignoredError sqref="HT1:HT48" numberStoredAsText="true"/>
+    <ignoredError sqref="HU1:HU48" numberStoredAsText="true"/>
+    <ignoredError sqref="HV1:HV48" numberStoredAsText="true"/>
+    <ignoredError sqref="HW1:HW48" numberStoredAsText="true"/>
+    <ignoredError sqref="HX1:HX48" numberStoredAsText="true"/>
+    <ignoredError sqref="HY1:HY48" numberStoredAsText="true"/>
+    <ignoredError sqref="HZ1:HZ48" numberStoredAsText="true"/>
+    <ignoredError sqref="IA1:IA48" numberStoredAsText="true"/>
+    <ignoredError sqref="IB1:IB48" numberStoredAsText="true"/>
+    <ignoredError sqref="IC1:IC48" numberStoredAsText="true"/>
+    <ignoredError sqref="ID1:ID48" numberStoredAsText="true"/>
+    <ignoredError sqref="IE1:IE48" numberStoredAsText="true"/>
+    <ignoredError sqref="IF1:IF48" numberStoredAsText="true"/>
+    <ignoredError sqref="IG1:IG48" numberStoredAsText="true"/>
+    <ignoredError sqref="IH1:IH48" numberStoredAsText="true"/>
+    <ignoredError sqref="II1:II48" numberStoredAsText="true"/>
+    <ignoredError sqref="IJ1:IJ48" numberStoredAsText="true"/>
+    <ignoredError sqref="IK1:IK48" numberStoredAsText="true"/>
+    <ignoredError sqref="IL1:IL48" numberStoredAsText="true"/>
+    <ignoredError sqref="IM1:IM48" numberStoredAsText="true"/>
+    <ignoredError sqref="IN1:IN48" numberStoredAsText="true"/>
+    <ignoredError sqref="IO1:IO48" numberStoredAsText="true"/>
+    <ignoredError sqref="IP1:IP48" numberStoredAsText="true"/>
+    <ignoredError sqref="IQ1:IQ48" numberStoredAsText="true"/>
+    <ignoredError sqref="IR1:IR48" numberStoredAsText="true"/>
+    <ignoredError sqref="IS1:IS48" numberStoredAsText="true"/>
+    <ignoredError sqref="IT1:IT48" numberStoredAsText="true"/>
+    <ignoredError sqref="IU1:IU48" numberStoredAsText="true"/>
+    <ignoredError sqref="IV1:IV48" numberStoredAsText="true"/>
+    <ignoredError sqref="IW1:IW48" numberStoredAsText="true"/>
+    <ignoredError sqref="IX1:IX48" numberStoredAsText="true"/>
+    <ignoredError sqref="IY1:IY48" numberStoredAsText="true"/>
+    <ignoredError sqref="IZ1:IZ48" numberStoredAsText="true"/>
+    <ignoredError sqref="JA1:JA48" numberStoredAsText="true"/>
+    <ignoredError sqref="JB1:JB48" numberStoredAsText="true"/>
+    <ignoredError sqref="JC1:JC48" numberStoredAsText="true"/>
+    <ignoredError sqref="JD1:JD48" numberStoredAsText="true"/>
+    <ignoredError sqref="JE1:JE48" numberStoredAsText="true"/>
+    <ignoredError sqref="JF1:JF48" numberStoredAsText="true"/>
+    <ignoredError sqref="JG1:JG48" numberStoredAsText="true"/>
+    <ignoredError sqref="JH1:JH48" numberStoredAsText="true"/>
+    <ignoredError sqref="JI1:JI48" numberStoredAsText="true"/>
+    <ignoredError sqref="JJ1:JJ48" numberStoredAsText="true"/>
+    <ignoredError sqref="JK1:JK48" numberStoredAsText="true"/>
+    <ignoredError sqref="JL1:JL48" numberStoredAsText="true"/>
+    <ignoredError sqref="JM1:JM48" numberStoredAsText="true"/>
+    <ignoredError sqref="JN1:JN48" numberStoredAsText="true"/>
+    <ignoredError sqref="JO1:JO48" numberStoredAsText="true"/>
+    <ignoredError sqref="JP1:JP48" numberStoredAsText="true"/>
+    <ignoredError sqref="JQ1:JQ48" numberStoredAsText="true"/>
+    <ignoredError sqref="JR1:JR48" numberStoredAsText="true"/>
+    <ignoredError sqref="JS1:JS48" numberStoredAsText="true"/>
+    <ignoredError sqref="JT1:JT48" numberStoredAsText="true"/>
+    <ignoredError sqref="JU1:JU48" numberStoredAsText="true"/>
+    <ignoredError sqref="JV1:JV48" numberStoredAsText="true"/>
+    <ignoredError sqref="JW1:JW48" numberStoredAsText="true"/>
+    <ignoredError sqref="JX1:JX48" numberStoredAsText="true"/>
+    <ignoredError sqref="JY1:JY48" numberStoredAsText="true"/>
+    <ignoredError sqref="JZ1:JZ48" numberStoredAsText="true"/>
+    <ignoredError sqref="KA1:KA48" numberStoredAsText="true"/>
+    <ignoredError sqref="KB1:KB48" numberStoredAsText="true"/>
+    <ignoredError sqref="KC1:KC48" numberStoredAsText="true"/>
+    <ignoredError sqref="KD1:KD48" numberStoredAsText="true"/>
+    <ignoredError sqref="KE1:KE48" numberStoredAsText="true"/>
+    <ignoredError sqref="KF1:KF48" numberStoredAsText="true"/>
+    <ignoredError sqref="KG1:KG48" numberStoredAsText="true"/>
+    <ignoredError sqref="KH1:KH48" numberStoredAsText="true"/>
+    <ignoredError sqref="KI1:KI48" numberStoredAsText="true"/>
+    <ignoredError sqref="KJ1:KJ48" numberStoredAsText="true"/>
+    <ignoredError sqref="KK1:KK48" numberStoredAsText="true"/>
+    <ignoredError sqref="KL1:KL48" numberStoredAsText="true"/>
+    <ignoredError sqref="KM1:KM48" numberStoredAsText="true"/>
+    <ignoredError sqref="KN1:KN48" numberStoredAsText="true"/>
+    <ignoredError sqref="KO1:KO48" numberStoredAsText="true"/>
+    <ignoredError sqref="KP1:KP48" numberStoredAsText="true"/>
+    <ignoredError sqref="KQ1:KQ48" numberStoredAsText="true"/>
+    <ignoredError sqref="KR1:KR48" numberStoredAsText="true"/>
+    <ignoredError sqref="KS1:KS48" numberStoredAsText="true"/>
   </ignoredErrors>
   <drawing r:id="rId1"/>
 </worksheet>
